--- a/ADSK.xlsx
+++ b/ADSK.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10821"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10927"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26AF0111-2164-CF49-998A-4895BF6EE8A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CA66BC9-D0B0-0B42-97A4-FF6D27B9CC4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" activeTab="2" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>
@@ -2416,14 +2416,14 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -15145,10 +15145,10 @@
     <v>326.2</v>
     <v>185.5</v>
     <v>1.3087</v>
-    <v>0.69</v>
-    <v>3.2650000000000001E-3</v>
-    <v>0.99</v>
-    <v>4.6700000000000005E-3</v>
+    <v>9.56</v>
+    <v>4.5094000000000002E-2</v>
+    <v>0.24</v>
+    <v>1.083E-3</v>
     <v>USD</v>
     <v>Autodesk, Inc. is engaged in three-dimensional (3D) design, engineering and entertainment technology solutions, spanning architecture, engineering, construction, product design, manufacturing, media and entertainment. Its architecture, engineering, construction and operations products improve the way building, infrastructure, and industrial projects are designed, built, and operated. Its product development and manufacturing software provides manufacturers in the automotive, transportation, industrial machinery, consumer products, and building product industries with comprehensive digital design, engineering, manufacturing, and production solutions. Its product offerings include AutoCAD Civil 3D, Autodesk Build, BIM Collaborate Pro, Building Connected, Revit, Tandem, AutoCAD, AutoCAD LT, Inventor, Vault, Maya, 3ds Max, Flow Production Tracking, among others. AutoCAD Civil 3D solution offers surveying, design, analysis, and documentation solution.</v>
     <v>14300</v>
@@ -15156,25 +15156,25 @@
     <v>XNAS</v>
     <v>XNAS</v>
     <v>One Market, Ste. 400., SAN FRANCISCO, CA, 94105 US</v>
-    <v>214.33</v>
+    <v>226.93</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46297.995213043752</v>
+    <v>46300.890108888285</v>
     <v>0</v>
-    <v>210.67</v>
-    <v>44308000000</v>
+    <v>218.21</v>
+    <v>46306040000</v>
     <v>AUTODESK, INC.</v>
     <v>AUTODESK, INC.</v>
-    <v>213</v>
-    <v>27.396899999999999</v>
-    <v>211.31</v>
+    <v>219.23</v>
+    <v>27.4864</v>
     <v>212</v>
-    <v>212.99</v>
+    <v>221.56</v>
+    <v>221.8</v>
     <v>209000000</v>
     <v>ADSK</v>
     <v>AUTODESK, INC. (XNAS:ADSK)</v>
-    <v>1672967</v>
-    <v>2378049</v>
+    <v>3212083</v>
+    <v>2286438</v>
     <v>1994</v>
   </rv>
   <rv s="2">
@@ -15430,9 +15430,9 @@
       <v>at close</v>
       <v>from previous close</v>
       <v>from previous close</v>
-      <v>Source: Nasdaq</v>
+      <v>Source: Nasdaq Last Sale</v>
       <v>GMT</v>
-      <v>Delayed 15 minutes</v>
+      <v>Real-Time Nasdaq Last Sale</v>
       <v>from close</v>
       <v>from close</v>
     </spb>
@@ -16029,7 +16029,7 @@
       </c>
       <c r="F3" s="185">
         <f ca="1">Statement!AC154</f>
-        <v>44520</v>
+        <v>46527.6</v>
       </c>
       <c r="H3" s="183" t="str">
         <f>'AVG target price'!B5</f>
@@ -16037,7 +16037,7 @@
       </c>
       <c r="I3" s="209">
         <f ca="1">'AVG target price'!C5</f>
-        <v>118.20421260632114</v>
+        <v>117.94549730051374</v>
       </c>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.2">
@@ -16053,7 +16053,7 @@
       </c>
       <c r="F4" s="186">
         <f ca="1">Statement!AC155</f>
-        <v>43641</v>
+        <v>45648.6</v>
       </c>
       <c r="H4" s="183" t="str">
         <f>'AVG target price'!B6</f>
@@ -16061,7 +16061,7 @@
       </c>
       <c r="I4" s="209">
         <f ca="1">'AVG target price'!C6</f>
-        <v>347.32689793653873</v>
+        <v>347.05184206395262</v>
       </c>
     </row>
     <row r="5" spans="2:9" x14ac:dyDescent="0.2">
@@ -16070,7 +16070,7 @@
       </c>
       <c r="C5" s="206" cm="1">
         <f t="array" aca="1" ref="C5" ca="1">_FV(C3,"Price",TRUE)</f>
-        <v>212</v>
+        <v>221.56</v>
       </c>
       <c r="E5" s="183" t="s">
         <v>242</v>
@@ -16094,14 +16094,14 @@
       </c>
       <c r="C6" s="206" cm="1">
         <f t="array" aca="1" ref="C6" ca="1">_FV(C3,"Price (Extended hours)",TRUE)</f>
-        <v>212.99</v>
+        <v>221.8</v>
       </c>
       <c r="E6" s="183" t="s">
         <v>236</v>
       </c>
       <c r="F6" s="188">
         <f ca="1">Statement!AC151</f>
-        <v>27.42561448900388</v>
+        <v>28.662354463130658</v>
       </c>
       <c r="H6" s="183" t="str">
         <f>'AVG target price'!B8</f>
@@ -16109,7 +16109,7 @@
       </c>
       <c r="I6" s="209">
         <f ca="1">'AVG target price'!C8</f>
-        <v>345.78539129097703</v>
+        <v>345.51162031984416</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -16118,14 +16118,14 @@
       </c>
       <c r="C7" s="6" cm="1">
         <f t="array" aca="1" ref="C7" ca="1">_FV(C3,"Change")</f>
-        <v>0.69</v>
+        <v>9.56</v>
       </c>
       <c r="E7" s="184" t="s">
         <v>200</v>
       </c>
       <c r="F7" s="189">
         <f ca="1">Statement!AC152</f>
-        <v>5.7966623876765091</v>
+        <v>6.0580590500641858</v>
       </c>
       <c r="H7" s="183" t="str">
         <f>'AVG target price'!B9</f>
@@ -16133,7 +16133,7 @@
       </c>
       <c r="I7" s="209">
         <f ca="1">'AVG target price'!C9</f>
-        <v>220.22162982511608</v>
+        <v>220.05252078330085</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
@@ -16142,14 +16142,14 @@
       </c>
       <c r="C8" s="6" cm="1">
         <f t="array" aca="1" ref="C8" ca="1">_FV(C3,"Change (extended hours)",TRUE)</f>
-        <v>0.99</v>
+        <v>0.24</v>
       </c>
       <c r="E8" s="183" t="s">
         <v>264</v>
       </c>
       <c r="F8" s="190">
         <f ca="1">Statement!AC162</f>
-        <v>4.7124887690925425E-2</v>
+        <v>4.5091515573552045E-2</v>
       </c>
       <c r="H8" s="182" t="str">
         <f>'AVG target price'!B10</f>
@@ -16157,7 +16157,7 @@
       </c>
       <c r="I8" s="210">
         <f ca="1">'AVG target price'!C10</f>
-        <v>243.98631657763909</v>
+        <v>243.79098633937073</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -16166,14 +16166,14 @@
       </c>
       <c r="C9" s="73" cm="1">
         <f t="array" aca="1" ref="C9" ca="1">_FV(C3,"Change (%)",TRUE)</f>
-        <v>3.2650000000000001E-3</v>
+        <v>4.5094000000000002E-2</v>
       </c>
       <c r="E9" s="183" t="s">
         <v>287</v>
       </c>
       <c r="F9" s="190">
         <f ca="1">Statement!AC163</f>
-        <v>3.6462264150943398E-2</v>
+        <v>3.4888969128001449E-2</v>
       </c>
       <c r="H9" s="182" t="str">
         <f>'AVG target price'!B12</f>
@@ -16181,7 +16181,7 @@
       </c>
       <c r="I9" s="211">
         <f ca="1">'AVG target price'!C12</f>
-        <v>0.15087885178131644</v>
+        <v>0.10033844709952487</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -16190,14 +16190,14 @@
       </c>
       <c r="C10" s="73" cm="1">
         <f t="array" aca="1" ref="C10" ca="1">_FV(C3,"Change % (extended hours)",TRUE)</f>
-        <v>4.6700000000000005E-3</v>
+        <v>1.083E-3</v>
       </c>
       <c r="E10" s="183" t="s">
         <v>292</v>
       </c>
       <c r="F10" s="190">
         <f ca="1">Statement!AC165</f>
-        <v>3.5736747529200356E-2</v>
+        <v>3.4194757520267544E-2</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -16268,7 +16268,7 @@
       </c>
       <c r="C14" s="208" cm="1">
         <f t="array" aca="1" ref="C14" ca="1">_FV(C3,"Volume average",TRUE)</f>
-        <v>2378049</v>
+        <v>2286438</v>
       </c>
       <c r="E14" s="184" t="s">
         <v>104</v>
@@ -16284,7 +16284,7 @@
       </c>
       <c r="F15" s="190">
         <f ca="1">Statement!AC177</f>
-        <v>1.9743935309973044E-2</v>
+        <v>1.8892012482913369E-2</v>
       </c>
     </row>
     <row r="16" spans="2:9" x14ac:dyDescent="0.2">
@@ -17848,35 +17848,35 @@
       </c>
       <c r="S18" s="47"/>
       <c r="T18" s="95">
-        <f>T6/S6-1</f>
+        <f t="shared" ref="T18:Z19" si="17">T6/S6-1</f>
         <v>4.5020463847203374E-2</v>
       </c>
       <c r="U18" s="95">
-        <f>U6/T6-1</f>
+        <f t="shared" si="17"/>
         <v>5.2219321148825326E-3</v>
       </c>
       <c r="V18" s="95">
-        <f>V6/U6-1</f>
+        <f t="shared" si="17"/>
         <v>8.2467532467532578E-2</v>
       </c>
       <c r="W18" s="95">
-        <f>W6/V6-1</f>
+        <f t="shared" si="17"/>
         <v>4.4991001799639996E-2</v>
       </c>
       <c r="X18" s="95">
-        <f>X6/W6-1</f>
+        <f t="shared" si="17"/>
         <v>4.8794489092996551E-2</v>
       </c>
       <c r="Y18" s="95">
-        <f>Y6/X6-1</f>
+        <f t="shared" si="17"/>
         <v>4.9261083743843415E-3</v>
       </c>
       <c r="Z18" s="96">
-        <f>Z6/Y6-1</f>
+        <f t="shared" si="17"/>
         <v>6.3180827886710311E-2</v>
       </c>
       <c r="AA18" s="95">
-        <f t="shared" ref="AA18:AA19" si="17">AA6/Z6-1</f>
+        <f t="shared" ref="AA18:AA19" si="18">AA6/Z6-1</f>
         <v>4.0245133196721294E-2</v>
       </c>
       <c r="AB18" s="95"/>
@@ -17889,19 +17889,19 @@
       </c>
       <c r="C19" s="47"/>
       <c r="D19" s="95">
-        <f t="shared" ref="D19:G19" si="18">D7/C7-1</f>
+        <f t="shared" ref="D19:G19" si="19">D7/C7-1</f>
         <v>0.15599999999999992</v>
       </c>
       <c r="E19" s="95">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0.13148788927335642</v>
       </c>
       <c r="F19" s="95">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0.14067278287461771</v>
       </c>
       <c r="G19" s="96">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0.15281501340482584</v>
       </c>
       <c r="H19" s="95">
@@ -17932,35 +17932,35 @@
       </c>
       <c r="S19" s="47"/>
       <c r="T19" s="95">
-        <f>T7/S7-1</f>
+        <f t="shared" si="17"/>
         <v>2.8846153846153744E-2</v>
       </c>
       <c r="U19" s="95">
-        <f>U7/T7-1</f>
+        <f t="shared" si="17"/>
         <v>-0.13084112149532712</v>
       </c>
       <c r="V19" s="95">
-        <f>V7/U7-1</f>
+        <f t="shared" si="17"/>
         <v>3.2258064516129004E-2</v>
       </c>
       <c r="W19" s="95">
-        <f>W7/V7-1</f>
+        <f t="shared" si="17"/>
         <v>0.15625</v>
       </c>
       <c r="X19" s="95">
-        <f>X7/W7-1</f>
+        <f t="shared" si="17"/>
         <v>0.1711711711711712</v>
       </c>
       <c r="Y19" s="95">
-        <f>Y7/X7-1</f>
+        <f t="shared" si="17"/>
         <v>-0.24615384615384617</v>
       </c>
       <c r="Z19" s="96">
-        <f>Z7/Y7-1</f>
+        <f t="shared" si="17"/>
         <v>-4.081632653061229E-2</v>
       </c>
       <c r="AA19" s="95">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0.13693085106382985</v>
       </c>
       <c r="AB19" s="95"/>
@@ -17998,19 +17998,19 @@
       </c>
       <c r="C21" s="47"/>
       <c r="D21" s="95">
-        <f t="shared" ref="D21:D25" si="19">D9/C9-1</f>
+        <f t="shared" ref="D21:D25" si="20">D9/C9-1</f>
         <v>0.15693245302183856</v>
       </c>
       <c r="E21" s="95">
-        <f t="shared" ref="E21:E25" si="20">E9/D9-1</f>
+        <f t="shared" ref="E21:E25" si="21">E9/D9-1</f>
         <v>0.13257243195785784</v>
       </c>
       <c r="F21" s="95">
-        <f t="shared" ref="F21:F25" si="21">F9/E9-1</f>
+        <f t="shared" ref="F21:F25" si="22">F9/E9-1</f>
         <v>0.1383720930232557</v>
       </c>
       <c r="G21" s="96">
-        <f t="shared" ref="G21:G25" si="22">G9/F9-1</f>
+        <f t="shared" ref="G21:G25" si="23">G9/F9-1</f>
         <v>0.21995233231188283</v>
       </c>
       <c r="H21" s="97">
@@ -18031,36 +18031,36 @@
       <c r="O21" s="5"/>
       <c r="Q21" s="91"/>
       <c r="R21" s="1" t="str">
-        <f t="shared" ref="R21:R25" si="23">R9</f>
+        <f t="shared" ref="R21:R25" si="24">R9</f>
         <v>AECO</v>
       </c>
       <c r="S21" s="47"/>
       <c r="T21" s="95">
-        <f t="shared" ref="T21:Z21" si="24">T9/S9-1</f>
+        <f t="shared" ref="T21:Z21" si="25">T9/S9-1</f>
         <v>6.391478029294273E-2</v>
       </c>
       <c r="U21" s="95">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>1.2515644555694649E-2</v>
       </c>
       <c r="V21" s="95">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>8.5290482076637808E-2</v>
       </c>
       <c r="W21" s="95">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>4.8974943052391806E-2</v>
       </c>
       <c r="X21" s="95">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>5.8631921824104261E-2</v>
       </c>
       <c r="Y21" s="95">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>-5.12820512820511E-3</v>
       </c>
       <c r="Z21" s="96">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>6.0824742268041243E-2</v>
       </c>
       <c r="AA21" s="97">
@@ -18071,24 +18071,24 @@
     </row>
     <row r="22" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B22" s="1" t="str">
-        <f t="shared" ref="B22:B25" si="25">B10</f>
+        <f t="shared" ref="B22:B25" si="26">B10</f>
         <v>AutoCAD and AutoCAD LT</v>
       </c>
       <c r="C22" s="47"/>
       <c r="D22" s="95">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0.114951768488746</v>
       </c>
       <c r="E22" s="95">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>5.4073540014419663E-2</v>
       </c>
       <c r="F22" s="95">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>7.523939808481539E-2</v>
       </c>
       <c r="G22" s="96">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0.13676844783715003</v>
       </c>
       <c r="H22" s="97">
@@ -18109,36 +18109,36 @@
       <c r="O22" s="5"/>
       <c r="Q22" s="91"/>
       <c r="R22" s="1" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>AutoCAD and AutoCAD LT</v>
       </c>
       <c r="S22" s="47"/>
       <c r="T22" s="95">
-        <f t="shared" ref="T22:Z22" si="26">T10/S10-1</f>
+        <f t="shared" ref="T22:Z22" si="27">T10/S10-1</f>
         <v>2.7638190954773822E-2</v>
       </c>
       <c r="U22" s="95">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>4.8899755501221609E-3</v>
       </c>
       <c r="V22" s="95">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>7.0559610705596132E-2</v>
       </c>
       <c r="W22" s="95">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>4.0909090909091006E-2</v>
       </c>
       <c r="X22" s="95">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>4.366812227074246E-2</v>
       </c>
       <c r="Y22" s="95">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>-8.3682008368201055E-3</v>
       </c>
       <c r="Z22" s="96">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>5.4852320675105481E-2</v>
       </c>
       <c r="AA22" s="97">
@@ -18149,24 +18149,24 @@
     </row>
     <row r="23" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B23" s="1" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>Manufacturing</v>
       </c>
       <c r="C23" s="47"/>
       <c r="D23" s="95">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0.11643835616438358</v>
       </c>
       <c r="E23" s="95">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>8.6912065439672892E-2</v>
       </c>
       <c r="F23" s="95">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0.11853245531514589</v>
       </c>
       <c r="G23" s="96">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0.15979814970563488</v>
       </c>
       <c r="H23" s="97">
@@ -18187,36 +18187,36 @@
       <c r="O23" s="5"/>
       <c r="Q23" s="91"/>
       <c r="R23" s="1" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>Manufacturing</v>
       </c>
       <c r="S23" s="47"/>
       <c r="T23" s="95">
-        <f t="shared" ref="T23:Z23" si="27">T11/S11-1</f>
+        <f t="shared" ref="T23:Z23" si="28">T11/S11-1</f>
         <v>3.5830618892508159E-2</v>
       </c>
       <c r="U23" s="95">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>-2.8301886792452824E-2</v>
       </c>
       <c r="V23" s="95">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>8.0906148867313954E-2</v>
       </c>
       <c r="W23" s="95">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>6.2874251497005984E-2</v>
       </c>
       <c r="X23" s="95">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>7.3239436619718212E-2</v>
       </c>
       <c r="Y23" s="95">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>-3.6745406824146953E-2</v>
       </c>
       <c r="Z23" s="96">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>4.9046321525885617E-2</v>
       </c>
       <c r="AA23" s="97">
@@ -18227,24 +18227,24 @@
     </row>
     <row r="24" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B24" s="1" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>Media and Entertainment</v>
       </c>
       <c r="C24" s="47"/>
       <c r="D24" s="95">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0.12355212355212353</v>
       </c>
       <c r="E24" s="95">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>1.3745704467353903E-2</v>
       </c>
       <c r="F24" s="95">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>6.7796610169491567E-2</v>
       </c>
       <c r="G24" s="96">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>5.3968253968253999E-2</v>
       </c>
       <c r="H24" s="97">
@@ -18265,36 +18265,36 @@
       <c r="O24" s="5"/>
       <c r="Q24" s="91"/>
       <c r="R24" s="1" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>Media and Entertainment</v>
       </c>
       <c r="S24" s="47"/>
       <c r="T24" s="95">
-        <f t="shared" ref="T24:Z24" si="28">T12/S12-1</f>
+        <f t="shared" ref="T24:Z24" si="29">T12/S12-1</f>
         <v>1.2048192771084265E-2</v>
       </c>
       <c r="U24" s="95">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>-9.5238095238095233E-2</v>
       </c>
       <c r="V24" s="95">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>5.2631578947368363E-2</v>
       </c>
       <c r="W24" s="95">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>7.4999999999999956E-2</v>
       </c>
       <c r="X24" s="95">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>4.6511627906976827E-2</v>
       </c>
       <c r="Y24" s="95">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>-4.4444444444444398E-2</v>
       </c>
       <c r="Z24" s="96">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>6.9767441860465018E-2</v>
       </c>
       <c r="AA24" s="97">
@@ -18305,24 +18305,24 @@
     </row>
     <row r="25" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B25" s="1" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>Other</v>
       </c>
       <c r="C25" s="47"/>
       <c r="D25" s="95">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0.86842105263157898</v>
       </c>
       <c r="E25" s="95">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0.36619718309859151</v>
       </c>
       <c r="F25" s="95">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0.21649484536082464</v>
       </c>
       <c r="G25" s="96">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>5.9322033898305149E-2</v>
       </c>
       <c r="H25" s="97">
@@ -18343,36 +18343,36 @@
       <c r="O25" s="5"/>
       <c r="Q25" s="91"/>
       <c r="R25" s="1" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>Other</v>
       </c>
       <c r="S25" s="47"/>
       <c r="T25" s="95">
-        <f t="shared" ref="T25:Z25" si="29">T13/S13-1</f>
+        <f t="shared" ref="T25:Z25" si="30">T13/S13-1</f>
         <v>-6.4516129032258118E-2</v>
       </c>
       <c r="U25" s="95">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>-3.4482758620689613E-2</v>
       </c>
       <c r="V25" s="95">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>0.10714285714285721</v>
       </c>
       <c r="W25" s="95">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>6.4516129032258007E-2</v>
       </c>
       <c r="X25" s="95">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="Y25" s="95">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>0.1212121212121211</v>
       </c>
       <c r="Z25" s="96">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>8.1081081081081141E-2</v>
       </c>
       <c r="AA25" s="97">
@@ -18388,39 +18388,39 @@
       </c>
       <c r="C26" s="47"/>
       <c r="D26" s="103">
-        <f t="shared" ref="D26:L26" si="30">D14/C14-1</f>
+        <f t="shared" ref="D26:L26" si="31">D14/C14-1</f>
         <v>0.14113087095303234</v>
       </c>
       <c r="E26" s="103">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>9.8301698301698215E-2</v>
       </c>
       <c r="F26" s="103">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>0.11533563762052035</v>
       </c>
       <c r="G26" s="104">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>0.1753384439732506</v>
       </c>
       <c r="H26" s="103">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>0.15692756036636135</v>
       </c>
       <c r="I26" s="103">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>0.16363064093983049</v>
       </c>
       <c r="J26" s="103">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>0.12542293101710844</v>
       </c>
       <c r="K26" s="103">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>0.12221822534874449</v>
       </c>
       <c r="L26" s="103">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>9.2496163043021884E-2</v>
       </c>
       <c r="O26" s="5"/>
@@ -18431,35 +18431,35 @@
       </c>
       <c r="S26" s="47"/>
       <c r="T26" s="103">
-        <f t="shared" ref="T26:AA26" si="31">T14/S14-1</f>
+        <f t="shared" ref="T26:AA26" si="32">T14/S14-1</f>
         <v>4.3949044585987362E-2</v>
       </c>
       <c r="U26" s="103">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>-3.6607687614399476E-3</v>
       </c>
       <c r="V26" s="103">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>7.9608083282302511E-2</v>
       </c>
       <c r="W26" s="103">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>5.1049347702779357E-2</v>
       </c>
       <c r="X26" s="103">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>5.6125202374527783E-2</v>
       </c>
       <c r="Y26" s="103">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>-1.1752682677567683E-2</v>
       </c>
       <c r="Z26" s="104">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>5.7911065149948371E-2</v>
       </c>
       <c r="AA26" s="103">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>4.4687194525904195E-2</v>
       </c>
       <c r="AB26" s="103"/>
@@ -18502,90 +18502,90 @@
     <row r="29" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B29" s="16"/>
       <c r="C29" s="12">
-        <f t="shared" ref="C29:L29" si="32">C17</f>
+        <f t="shared" ref="C29:L29" si="33">C17</f>
         <v>2022</v>
       </c>
       <c r="D29" s="12">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>2023</v>
       </c>
       <c r="E29" s="12">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>2024</v>
       </c>
       <c r="F29" s="12">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>2025</v>
       </c>
       <c r="G29" s="12">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>2026</v>
       </c>
       <c r="H29" s="12">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>2027</v>
       </c>
       <c r="I29" s="12">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>2028</v>
       </c>
       <c r="J29" s="12">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>2029</v>
       </c>
       <c r="K29" s="12">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>2030</v>
       </c>
       <c r="L29" s="12">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>2031</v>
       </c>
       <c r="O29" s="5"/>
       <c r="Q29" s="91"/>
       <c r="R29" s="16"/>
       <c r="S29" s="12" t="str">
-        <f t="shared" ref="S29:AC29" si="33">S17</f>
+        <f t="shared" ref="S29:AC29" si="34">S17</f>
         <v>Q3 2025</v>
       </c>
       <c r="T29" s="12" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>Q4 2025</v>
       </c>
       <c r="U29" s="12" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>Q1 2026</v>
       </c>
       <c r="V29" s="12" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>Q2 2026</v>
       </c>
       <c r="W29" s="12" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>Q3 2026</v>
       </c>
       <c r="X29" s="12" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>Q4 2026</v>
       </c>
       <c r="Y29" s="12" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>Q1 2027</v>
       </c>
       <c r="Z29" s="12" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>Q2 2027</v>
       </c>
       <c r="AA29" s="12" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>FQ1</v>
       </c>
       <c r="AB29" s="12" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>FQ2</v>
       </c>
       <c r="AC29" s="12" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>FQ3</v>
       </c>
       <c r="AE29" s="8" t="s">
@@ -18602,19 +18602,19 @@
         <v>5.699954400364797E-2</v>
       </c>
       <c r="D30" s="95">
-        <f t="shared" ref="D30:G30" si="34">D7/D14</f>
+        <f t="shared" ref="D30:G30" si="35">D7/D14</f>
         <v>5.774225774225774E-2</v>
       </c>
       <c r="E30" s="95">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>5.9486992905221033E-2</v>
       </c>
       <c r="F30" s="95">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>6.0838362420486056E-2</v>
       </c>
       <c r="G30" s="96">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>5.9672495142936439E-2</v>
       </c>
       <c r="H30" s="97">
@@ -18643,31 +18643,31 @@
         <v>6.6242038216560509E-2</v>
       </c>
       <c r="T30" s="95">
-        <f t="shared" ref="T30:Z30" si="35">T7/T14</f>
+        <f t="shared" ref="T30:Z30" si="36">T7/T14</f>
         <v>6.5283709579011598E-2</v>
       </c>
       <c r="U30" s="95">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>5.6950398040416413E-2</v>
       </c>
       <c r="V30" s="95">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>5.4452637549631311E-2</v>
       </c>
       <c r="W30" s="95">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>5.9902860226659471E-2</v>
       </c>
       <c r="X30" s="95">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>6.642820643842616E-2</v>
       </c>
       <c r="Y30" s="95">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>5.0672182006204755E-2</v>
       </c>
       <c r="Z30" s="96">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>4.5943304007820138E-2</v>
       </c>
       <c r="AA30" s="97">
@@ -18676,7 +18676,7 @@
       <c r="AB30" s="97"/>
       <c r="AC30" s="97"/>
       <c r="AE30" s="95">
-        <f t="shared" ref="AE30" si="36">AE7/AE14</f>
+        <f t="shared" ref="AE30" si="37">AE7/AE14</f>
         <v>5.3114770949776013E-2</v>
       </c>
     </row>
@@ -19895,116 +19895,116 @@
         <v>128</v>
       </c>
       <c r="C22" s="12">
-        <f>C5</f>
+        <f t="shared" ref="C22:L22" si="6">C5</f>
         <v>2022</v>
       </c>
       <c r="D22" s="12">
-        <f>D5</f>
+        <f t="shared" si="6"/>
         <v>2023</v>
       </c>
       <c r="E22" s="12">
-        <f>E5</f>
+        <f t="shared" si="6"/>
         <v>2024</v>
       </c>
       <c r="F22" s="12">
-        <f>F5</f>
+        <f t="shared" si="6"/>
         <v>2025</v>
       </c>
       <c r="G22" s="12">
-        <f>G5</f>
+        <f t="shared" si="6"/>
         <v>2026</v>
       </c>
       <c r="H22" s="12">
-        <f>H5</f>
+        <f t="shared" si="6"/>
         <v>2027</v>
       </c>
       <c r="I22" s="12">
-        <f>I5</f>
+        <f t="shared" si="6"/>
         <v>2028</v>
       </c>
       <c r="J22" s="12">
-        <f>J5</f>
+        <f t="shared" si="6"/>
         <v>2029</v>
       </c>
       <c r="K22" s="12">
-        <f>K5</f>
+        <f t="shared" si="6"/>
         <v>2030</v>
       </c>
       <c r="L22" s="12">
-        <f>L5</f>
+        <f t="shared" si="6"/>
         <v>2031</v>
       </c>
       <c r="O22" s="16" t="s">
         <v>128</v>
       </c>
       <c r="P22" s="12" t="str">
-        <f>P5</f>
+        <f t="shared" ref="P22:Z22" si="7">P5</f>
         <v>Q3 2025</v>
       </c>
       <c r="Q22" s="12" t="str">
-        <f>Q5</f>
+        <f t="shared" si="7"/>
         <v>Q4 2025</v>
       </c>
       <c r="R22" s="12" t="str">
-        <f>R5</f>
+        <f t="shared" si="7"/>
         <v>Q1 2026</v>
       </c>
       <c r="S22" s="12" t="str">
-        <f>S5</f>
+        <f t="shared" si="7"/>
         <v>Q2 2026</v>
       </c>
       <c r="T22" s="12" t="str">
-        <f>T5</f>
+        <f t="shared" si="7"/>
         <v>Q3 2026</v>
       </c>
       <c r="U22" s="12" t="str">
-        <f>U5</f>
+        <f t="shared" si="7"/>
         <v>Q4 2026</v>
       </c>
       <c r="V22" s="12" t="str">
-        <f>V5</f>
+        <f t="shared" si="7"/>
         <v>Q1 2027</v>
       </c>
       <c r="W22" s="12" t="str">
-        <f>W5</f>
+        <f t="shared" si="7"/>
         <v>Q2 2027</v>
       </c>
       <c r="X22" s="12" t="str">
-        <f>X5</f>
+        <f t="shared" si="7"/>
         <v>FQ1</v>
       </c>
       <c r="Y22" s="12" t="str">
-        <f>Y5</f>
+        <f t="shared" si="7"/>
         <v>FQ2</v>
       </c>
       <c r="Z22" s="12" t="str">
-        <f>Z5</f>
+        <f t="shared" si="7"/>
         <v>FQ3</v>
       </c>
     </row>
     <row r="23" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B23" s="1" t="str">
-        <f>B11</f>
+        <f t="shared" ref="B23:B29" si="8">B11</f>
         <v>Subscription COGS</v>
       </c>
       <c r="C23" s="95">
-        <f>C11/C$6</f>
+        <f t="shared" ref="C23:G29" si="9">C11/C$6</f>
         <v>6.8171454628362979E-2</v>
       </c>
       <c r="D23" s="95">
-        <f>D11/D$6</f>
+        <f t="shared" si="9"/>
         <v>6.8531468531468534E-2</v>
       </c>
       <c r="E23" s="95">
-        <f>E11/E$6</f>
+        <f t="shared" si="9"/>
         <v>6.9310533018009823E-2</v>
       </c>
       <c r="F23" s="95">
-        <f>F11/F$6</f>
+        <f t="shared" si="9"/>
         <v>6.7362583591583758E-2</v>
       </c>
       <c r="G23" s="96">
-        <f>G11/G$6</f>
+        <f t="shared" si="9"/>
         <v>6.4252012212045517E-2</v>
       </c>
       <c r="H23" s="97">
@@ -20023,39 +20023,39 @@
         <v>0.06</v>
       </c>
       <c r="O23" s="1" t="str">
-        <f>O11</f>
+        <f t="shared" ref="O23:O29" si="10">O11</f>
         <v>Subscription COGS</v>
       </c>
       <c r="P23" s="95">
-        <f>P11/P$6</f>
+        <f t="shared" ref="P23:W29" si="11">P11/P$6</f>
         <v>6.6878980891719744E-2</v>
       </c>
       <c r="Q23" s="95">
-        <f>Q11/Q$6</f>
+        <f t="shared" si="11"/>
         <v>6.5893837705918237E-2</v>
       </c>
       <c r="R23" s="95">
-        <f>R11/R$6</f>
+        <f t="shared" si="11"/>
         <v>6.7973055725658302E-2</v>
       </c>
       <c r="S23" s="95">
-        <f>S11/S$6</f>
+        <f t="shared" si="11"/>
         <v>6.4662507090187185E-2</v>
       </c>
       <c r="T23" s="95">
-        <f>T11/T$6</f>
+        <f t="shared" si="11"/>
         <v>6.3680518078791146E-2</v>
       </c>
       <c r="U23" s="95">
-        <f>U11/U$6</f>
+        <f t="shared" si="11"/>
         <v>6.1318344404701075E-2</v>
       </c>
       <c r="V23" s="95">
-        <f>V11/V$6</f>
+        <f t="shared" si="11"/>
         <v>6.6701137538779737E-2</v>
       </c>
       <c r="W23" s="96">
-        <f>W11/W$6</f>
+        <f t="shared" si="11"/>
         <v>6.3538611925708699E-2</v>
       </c>
       <c r="X23" s="97">
@@ -20066,27 +20066,27 @@
     </row>
     <row r="24" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B24" s="1" t="str">
-        <f>B12</f>
+        <f t="shared" si="8"/>
         <v>Other COGS</v>
       </c>
       <c r="C24" s="95">
-        <f>C12/C$6</f>
+        <f t="shared" si="9"/>
         <v>1.5275877792977656E-2</v>
       </c>
       <c r="D24" s="95">
-        <f>D12/D$6</f>
+        <f t="shared" si="9"/>
         <v>1.5784215784215783E-2</v>
       </c>
       <c r="E24" s="95">
-        <f>E12/E$6</f>
+        <f t="shared" si="9"/>
         <v>1.491722757867928E-2</v>
       </c>
       <c r="F24" s="95">
-        <f>F12/F$6</f>
+        <f t="shared" si="9"/>
         <v>1.3048442342195401E-2</v>
       </c>
       <c r="G24" s="96">
-        <f>G12/G$6</f>
+        <f t="shared" si="9"/>
         <v>1.2489592006661115E-2</v>
       </c>
       <c r="H24" s="97">
@@ -20105,39 +20105,39 @@
         <v>1.2E-2</v>
       </c>
       <c r="O24" s="1" t="str">
-        <f>O12</f>
+        <f t="shared" si="10"/>
         <v>Other COGS</v>
       </c>
       <c r="P24" s="95">
-        <f>P12/P$6</f>
+        <f t="shared" si="11"/>
         <v>1.2101910828025478E-2</v>
       </c>
       <c r="Q24" s="95">
-        <f>Q12/Q$6</f>
+        <f t="shared" si="11"/>
         <v>1.4032946918852958E-2</v>
       </c>
       <c r="R24" s="95">
-        <f>R12/R$6</f>
+        <f t="shared" si="11"/>
         <v>1.4696876913655848E-2</v>
       </c>
       <c r="S24" s="95">
-        <f>S12/S$6</f>
+        <f t="shared" si="11"/>
         <v>1.2478729438457176E-2</v>
       </c>
       <c r="T24" s="95">
-        <f>T12/T$6</f>
+        <f t="shared" si="11"/>
         <v>1.1872638963842417E-2</v>
       </c>
       <c r="U24" s="95">
-        <f>U12/U$6</f>
+        <f t="shared" si="11"/>
         <v>1.1241696474195196E-2</v>
       </c>
       <c r="V24" s="95">
-        <f>V12/V$6</f>
+        <f t="shared" si="11"/>
         <v>1.0858324715615306E-2</v>
       </c>
       <c r="W24" s="96">
-        <f>W12/W$6</f>
+        <f t="shared" si="11"/>
         <v>1.0752688172043012E-2</v>
       </c>
       <c r="X24" s="97">
@@ -20148,27 +20148,27 @@
     </row>
     <row r="25" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B25" s="1" t="str">
-        <f>B13</f>
+        <f t="shared" si="8"/>
         <v>Amortization of developed tech COGS</v>
       </c>
       <c r="C25" s="95">
-        <f>C13/C$6</f>
+        <f t="shared" si="9"/>
         <v>1.1855905152758778E-2</v>
       </c>
       <c r="D25" s="95">
-        <f>D13/D$6</f>
+        <f t="shared" si="9"/>
         <v>1.1588411588411588E-2</v>
       </c>
       <c r="E25" s="95">
-        <f>E13/E$6</f>
+        <f t="shared" si="9"/>
         <v>8.7320356558122612E-3</v>
       </c>
       <c r="F25" s="95">
-        <f>F13/F$6</f>
+        <f t="shared" si="9"/>
         <v>1.3863969988582614E-2</v>
       </c>
       <c r="G25" s="96">
-        <f>G13/G$6</f>
+        <f t="shared" si="9"/>
         <v>1.3461004718290313E-2</v>
       </c>
       <c r="H25" s="97">
@@ -20187,39 +20187,39 @@
         <v>1.0999999999999999E-2</v>
       </c>
       <c r="O25" s="1" t="str">
-        <f>O13</f>
+        <f t="shared" si="10"/>
         <v>Amortization of developed tech COGS</v>
       </c>
       <c r="P25" s="95">
-        <f>P13/P$6</f>
+        <f t="shared" si="11"/>
         <v>1.4649681528662421E-2</v>
       </c>
       <c r="Q25" s="95">
-        <f>Q13/Q$6</f>
+        <f t="shared" si="11"/>
         <v>1.4032946918852958E-2</v>
       </c>
       <c r="R25" s="95">
-        <f>R13/R$6</f>
+        <f t="shared" si="11"/>
         <v>1.5309246785058175E-2</v>
       </c>
       <c r="S25" s="95">
-        <f>S13/S$6</f>
+        <f t="shared" si="11"/>
         <v>1.3045944412932501E-2</v>
       </c>
       <c r="T25" s="95">
-        <f>T13/T$6</f>
+        <f t="shared" si="11"/>
         <v>1.3491635186184566E-2</v>
       </c>
       <c r="U25" s="95">
-        <f>U13/U$6</f>
+        <f t="shared" si="11"/>
         <v>1.2263668880940215E-2</v>
       </c>
       <c r="V25" s="95">
-        <f>V13/V$6</f>
+        <f t="shared" si="11"/>
         <v>1.2926577042399173E-2</v>
       </c>
       <c r="W25" s="96">
-        <f>W13/W$6</f>
+        <f t="shared" si="11"/>
         <v>1.1730205278592375E-2</v>
       </c>
       <c r="X25" s="97">
@@ -20230,27 +20230,27 @@
     </row>
     <row r="26" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B26" s="16" t="str">
-        <f>B14</f>
+        <f t="shared" si="8"/>
         <v>COGS</v>
       </c>
       <c r="C26" s="103">
-        <f>C14/C$6</f>
+        <f t="shared" si="9"/>
         <v>9.5303237574099406E-2</v>
       </c>
       <c r="D26" s="103">
-        <f>D14/D$6</f>
+        <f t="shared" si="9"/>
         <v>9.5904095904095904E-2</v>
       </c>
       <c r="E26" s="103">
-        <f>E14/E$6</f>
+        <f t="shared" si="9"/>
         <v>9.2959796252501364E-2</v>
       </c>
       <c r="F26" s="103">
-        <f>F14/F$6</f>
+        <f t="shared" si="9"/>
         <v>9.4274995922361771E-2</v>
       </c>
       <c r="G26" s="104">
-        <f>G14/G$6</f>
+        <f t="shared" si="9"/>
         <v>9.0202608936996942E-2</v>
       </c>
       <c r="H26" s="103">
@@ -20274,39 +20274,39 @@
         <v>8.299999999999999E-2</v>
       </c>
       <c r="O26" s="16" t="str">
-        <f>O14</f>
+        <f t="shared" si="10"/>
         <v>COGS</v>
       </c>
       <c r="P26" s="103">
-        <f>P14/P$6</f>
+        <f t="shared" si="11"/>
         <v>9.3630573248407636E-2</v>
       </c>
       <c r="Q26" s="103">
-        <f>Q14/Q$6</f>
+        <f t="shared" si="11"/>
         <v>9.3959731543624164E-2</v>
       </c>
       <c r="R26" s="103">
-        <f>R14/R$6</f>
+        <f t="shared" si="11"/>
         <v>9.7979179424372315E-2</v>
       </c>
       <c r="S26" s="103">
-        <f>S14/S$6</f>
+        <f t="shared" si="11"/>
         <v>9.0187180941576864E-2</v>
       </c>
       <c r="T26" s="103">
-        <f>T14/T$6</f>
+        <f t="shared" si="11"/>
         <v>8.9044792228818129E-2</v>
       </c>
       <c r="U26" s="103">
-        <f>U14/U$6</f>
+        <f t="shared" si="11"/>
         <v>8.4823709759836483E-2</v>
       </c>
       <c r="V26" s="103">
-        <f>V14/V$6</f>
+        <f t="shared" si="11"/>
         <v>9.0486039296794205E-2</v>
       </c>
       <c r="W26" s="104">
-        <f>W14/W$6</f>
+        <f t="shared" si="11"/>
         <v>8.6021505376344093E-2</v>
       </c>
       <c r="X26" s="103">
@@ -20318,27 +20318,27 @@
     </row>
     <row r="27" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B27" s="1" t="str">
-        <f>B15</f>
+        <f t="shared" si="8"/>
         <v>Sales and marketing</v>
       </c>
       <c r="C27" s="95">
-        <f>C15/C$6</f>
+        <f t="shared" si="9"/>
         <v>0.37004103967168261</v>
       </c>
       <c r="D27" s="95">
-        <f>D15/D$6</f>
+        <f t="shared" si="9"/>
         <v>0.34865134865134867</v>
       </c>
       <c r="E27" s="95">
-        <f>E15/E$6</f>
+        <f t="shared" si="9"/>
         <v>0.33163543751136981</v>
       </c>
       <c r="F27" s="95">
-        <f>F15/F$6</f>
+        <f t="shared" si="9"/>
         <v>0.32621105855488503</v>
       </c>
       <c r="G27" s="96">
-        <f>G15/G$6</f>
+        <f t="shared" si="9"/>
         <v>0.32930890924229811</v>
       </c>
       <c r="H27" s="97">
@@ -20357,39 +20357,39 @@
         <v>0.31</v>
       </c>
       <c r="O27" s="1" t="str">
-        <f>O15</f>
+        <f t="shared" si="10"/>
         <v>Sales and marketing</v>
       </c>
       <c r="P27" s="95">
-        <f>P15/P$6</f>
+        <f t="shared" si="11"/>
         <v>0.33439490445859871</v>
       </c>
       <c r="Q27" s="95">
-        <f>Q15/Q$6</f>
+        <f t="shared" si="11"/>
         <v>0.32092739475289811</v>
       </c>
       <c r="R27" s="95">
-        <f>R15/R$6</f>
+        <f t="shared" si="11"/>
         <v>0.3466013472137171</v>
       </c>
       <c r="S27" s="95">
-        <f>S15/S$6</f>
+        <f t="shared" si="11"/>
         <v>0.31707317073170732</v>
       </c>
       <c r="T27" s="95">
-        <f>T15/T$6</f>
+        <f t="shared" si="11"/>
         <v>0.33027522935779818</v>
       </c>
       <c r="U27" s="95">
-        <f>U15/U$6</f>
+        <f t="shared" si="11"/>
         <v>0.3249872253449157</v>
       </c>
       <c r="V27" s="95">
-        <f>V15/V$6</f>
+        <f t="shared" si="11"/>
         <v>0.3066184074457084</v>
       </c>
       <c r="W27" s="96">
-        <f>W15/W$6</f>
+        <f t="shared" si="11"/>
         <v>0.30107526881720431</v>
       </c>
       <c r="X27" s="97">
@@ -20400,27 +20400,27 @@
     </row>
     <row r="28" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B28" s="1" t="str">
-        <f>B16</f>
+        <f t="shared" si="8"/>
         <v>R&amp;D</v>
       </c>
       <c r="C28" s="95">
-        <f>C16/C$6</f>
+        <f t="shared" si="9"/>
         <v>0.25421796625626997</v>
       </c>
       <c r="D28" s="95">
-        <f>D16/D$6</f>
+        <f t="shared" si="9"/>
         <v>0.24355644355644357</v>
       </c>
       <c r="E28" s="95">
-        <f>E16/E$6</f>
+        <f t="shared" si="9"/>
         <v>0.24977260323812989</v>
       </c>
       <c r="F28" s="95">
-        <f>F16/F$6</f>
+        <f t="shared" si="9"/>
         <v>0.24221171097700211</v>
       </c>
       <c r="G28" s="96">
-        <f>G16/G$6</f>
+        <f t="shared" si="9"/>
         <v>0.22800444074382459</v>
       </c>
       <c r="H28" s="97">
@@ -20439,39 +20439,39 @@
         <v>0.21</v>
       </c>
       <c r="O28" s="1" t="str">
-        <f>O16</f>
+        <f t="shared" si="10"/>
         <v>R&amp;D</v>
       </c>
       <c r="P28" s="95">
-        <f>P16/P$6</f>
+        <f t="shared" si="11"/>
         <v>0.24076433121019108</v>
       </c>
       <c r="Q28" s="95">
-        <f>Q16/Q$6</f>
+        <f t="shared" si="11"/>
         <v>0.2397803538743136</v>
       </c>
       <c r="R28" s="95">
-        <f>R16/R$6</f>
+        <f t="shared" si="11"/>
         <v>0.24127372933251684</v>
       </c>
       <c r="S28" s="95">
-        <f>S16/S$6</f>
+        <f t="shared" si="11"/>
         <v>0.23425978445830969</v>
       </c>
       <c r="T28" s="95">
-        <f>T16/T$6</f>
+        <f t="shared" si="11"/>
         <v>0.22450080949811116</v>
       </c>
       <c r="U28" s="95">
-        <f>U16/U$6</f>
+        <f t="shared" si="11"/>
         <v>0.21461420541645376</v>
       </c>
       <c r="V28" s="95">
-        <f>V16/V$6</f>
+        <f t="shared" si="11"/>
         <v>0.21768355739400208</v>
       </c>
       <c r="W28" s="96">
-        <f>W16/W$6</f>
+        <f t="shared" si="11"/>
         <v>0.22678396871945258</v>
       </c>
       <c r="X28" s="97">
@@ -20482,27 +20482,27 @@
     </row>
     <row r="29" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B29" s="1" t="str">
-        <f>B17</f>
+        <f t="shared" si="8"/>
         <v>General and administrative</v>
       </c>
       <c r="C29" s="95">
-        <f>C17/C$6</f>
+        <f t="shared" si="9"/>
         <v>0.13041495668034656</v>
       </c>
       <c r="D29" s="95">
-        <f>D17/D$6</f>
+        <f t="shared" si="9"/>
         <v>0.1062937062937063</v>
       </c>
       <c r="E29" s="95">
-        <f>E17/E$6</f>
+        <f t="shared" si="9"/>
         <v>0.11278879388757504</v>
       </c>
       <c r="F29" s="95">
-        <f>F17/F$6</f>
+        <f t="shared" si="9"/>
         <v>0.10601859403033763</v>
       </c>
       <c r="G29" s="96">
-        <f>G17/G$6</f>
+        <f t="shared" si="9"/>
         <v>9.6169858451290585E-2</v>
       </c>
       <c r="H29" s="97">
@@ -20521,39 +20521,39 @@
         <v>0.1</v>
       </c>
       <c r="O29" s="1" t="str">
-        <f>O17</f>
+        <f t="shared" si="10"/>
         <v>General and administrative</v>
       </c>
       <c r="P29" s="95">
-        <f>P17/P$6</f>
+        <f t="shared" si="11"/>
         <v>0.10254777070063695</v>
       </c>
       <c r="Q29" s="95">
-        <f>Q17/Q$6</f>
+        <f t="shared" si="11"/>
         <v>0.10555216595485052</v>
       </c>
       <c r="R29" s="95">
-        <f>R17/R$6</f>
+        <f t="shared" si="11"/>
         <v>9.9203919167176968E-2</v>
       </c>
       <c r="S29" s="95">
-        <f>S17/S$6</f>
+        <f t="shared" si="11"/>
         <v>9.5292115711854794E-2</v>
       </c>
       <c r="T29" s="95">
-        <f>T17/T$6</f>
+        <f t="shared" si="11"/>
         <v>9.2822450080949817E-2</v>
       </c>
       <c r="U29" s="95">
-        <f>U17/U$6</f>
+        <f t="shared" si="11"/>
         <v>9.7598364844149202E-2</v>
       </c>
       <c r="V29" s="95">
-        <f>V17/V$6</f>
+        <f t="shared" si="11"/>
         <v>8.376421923474664E-2</v>
       </c>
       <c r="W29" s="96">
-        <f>W17/W$6</f>
+        <f t="shared" si="11"/>
         <v>8.7487781036168139E-2</v>
       </c>
       <c r="X29" s="97">
@@ -20564,7 +20564,7 @@
     </row>
     <row r="30" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B30" s="16" t="str">
-        <f t="shared" ref="B30" si="6">B18</f>
+        <f t="shared" ref="B30" si="12">B18</f>
         <v>OpEx</v>
       </c>
       <c r="C30" s="103">
@@ -20572,79 +20572,79 @@
         <v>0.76379388964888284</v>
       </c>
       <c r="D30" s="103">
-        <f t="shared" ref="D30:L30" si="7">D18/D$6</f>
+        <f t="shared" ref="D30:L30" si="13">D18/D$6</f>
         <v>0.70649350649350651</v>
       </c>
       <c r="E30" s="103">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v>0.7018373658359105</v>
       </c>
       <c r="F30" s="103">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v>0.6848801174359811</v>
       </c>
       <c r="G30" s="104">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v>0.6908132112128782</v>
       </c>
       <c r="H30" s="103">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v>0.65</v>
       </c>
       <c r="I30" s="103">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v>0.64999999999999991</v>
       </c>
       <c r="J30" s="103">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v>0.64</v>
       </c>
       <c r="K30" s="103">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v>0.62</v>
       </c>
       <c r="L30" s="103">
-        <f t="shared" si="7"/>
+        <f t="shared" si="13"/>
         <v>0.62</v>
       </c>
       <c r="O30" s="16" t="str">
-        <f t="shared" ref="O30" si="8">O18</f>
+        <f t="shared" ref="O30" si="14">O18</f>
         <v>OpEx</v>
       </c>
       <c r="P30" s="103">
-        <f t="shared" ref="P30:V30" si="9">P18/P$6</f>
+        <f t="shared" ref="P30:V30" si="15">P18/P$6</f>
         <v>0.68598726114649677</v>
       </c>
       <c r="Q30" s="103">
-        <f t="shared" si="9"/>
+        <f t="shared" si="15"/>
         <v>0.68273337400854184</v>
       </c>
       <c r="R30" s="103">
-        <f t="shared" si="9"/>
+        <f t="shared" si="15"/>
         <v>0.75933864053888545</v>
       </c>
       <c r="S30" s="103">
-        <f t="shared" si="9"/>
+        <f t="shared" si="15"/>
         <v>0.65796937039137837</v>
       </c>
       <c r="T30" s="103">
-        <f t="shared" si="9"/>
+        <f t="shared" si="15"/>
         <v>0.657312466270912</v>
       </c>
       <c r="U30" s="103">
-        <f t="shared" si="9"/>
+        <f t="shared" si="15"/>
         <v>0.69494123658661211</v>
       </c>
       <c r="V30" s="103">
-        <f t="shared" si="9"/>
+        <f t="shared" si="15"/>
         <v>0.62978283350568764</v>
       </c>
       <c r="W30" s="104">
-        <f t="shared" ref="W30:X30" si="10">W18/W$6</f>
+        <f t="shared" ref="W30:X30" si="16">W18/W$6</f>
         <v>0.62121212121212122</v>
       </c>
       <c r="X30" s="103">
-        <f t="shared" si="10"/>
+        <f t="shared" si="16"/>
         <v>0.52900000000000003</v>
       </c>
       <c r="Y30" s="16"/>
@@ -22109,12 +22109,6 @@
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="H3:L3"/>
-    <mergeCell ref="P3:W3"/>
-    <mergeCell ref="X3:Z3"/>
-    <mergeCell ref="C5:L5"/>
-    <mergeCell ref="P5:Z5"/>
     <mergeCell ref="C40:L40"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="P11:Z11"/>
@@ -22122,6 +22116,12 @@
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="C26:L26"/>
     <mergeCell ref="C33:L33"/>
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="H3:L3"/>
+    <mergeCell ref="P3:W3"/>
+    <mergeCell ref="X3:Z3"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="P5:Z5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -23181,16 +23181,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="C31:L31"/>
+    <mergeCell ref="C25:L25"/>
+    <mergeCell ref="C2:G2"/>
+    <mergeCell ref="H2:L2"/>
+    <mergeCell ref="S2:Z2"/>
     <mergeCell ref="AA2:AC2"/>
     <mergeCell ref="C4:L4"/>
     <mergeCell ref="S4:AC4"/>
     <mergeCell ref="C13:L13"/>
     <mergeCell ref="C18:L18"/>
-    <mergeCell ref="C31:L31"/>
-    <mergeCell ref="C25:L25"/>
-    <mergeCell ref="C2:G2"/>
-    <mergeCell ref="H2:L2"/>
-    <mergeCell ref="S2:Z2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -23273,7 +23273,7 @@
       </c>
       <c r="C6" s="135">
         <f ca="1">Overview!C5</f>
-        <v>212</v>
+        <v>221.56</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -23282,7 +23282,7 @@
       </c>
       <c r="C7" s="136">
         <f ca="1">C5*C6</f>
-        <v>44520</v>
+        <v>46527.6</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -23352,7 +23352,7 @@
       </c>
       <c r="C16" s="46">
         <f ca="1">C8/(C8+C7)</f>
-        <v>7.2461352556356509E-2</v>
+        <v>6.955221015246292E-2</v>
       </c>
     </row>
     <row r="17" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -23361,7 +23361,7 @@
       </c>
       <c r="C17" s="46">
         <f ca="1">C7/(C8+C7)</f>
-        <v>0.92753864744364345</v>
+        <v>0.93044778984753707</v>
       </c>
     </row>
     <row r="18" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -23388,7 +23388,7 @@
       </c>
       <c r="C20" s="46">
         <f ca="1">(C17*C19)+(C16*C18)</f>
-        <v>0.10706226926121921</v>
+        <v>0.10724691689330795</v>
       </c>
     </row>
   </sheetData>
@@ -23639,7 +23639,7 @@
       </c>
       <c r="L8" s="128">
         <f ca="1">L7*(1+C14)/(C15-C14)</f>
-        <v>28840.009925525919</v>
+        <v>28778.973504620913</v>
       </c>
       <c r="N8" s="91"/>
       <c r="O8" s="16"/>
@@ -23693,23 +23693,23 @@
       <c r="G10" s="140"/>
       <c r="H10" s="128">
         <f ca="1">H7/(1+$C$15)^H9</f>
-        <v>1861.6080604326387</v>
+        <v>1861.2976133995592</v>
       </c>
       <c r="I10" s="128">
         <f t="shared" ref="I10:L10" ca="1" si="0">I7/(1+$C$15)^I9</f>
-        <v>1269.8242065956549</v>
+        <v>1269.4007229464412</v>
       </c>
       <c r="J10" s="128">
         <f t="shared" ca="1" si="0"/>
-        <v>569.60056042298197</v>
+        <v>569.3156433333728</v>
       </c>
       <c r="K10" s="128">
         <f t="shared" ca="1" si="0"/>
-        <v>1419.0632606139084</v>
+        <v>1418.1169093360447</v>
       </c>
       <c r="L10" s="128">
         <f t="shared" ca="1" si="0"/>
-        <v>1480.3519129564443</v>
+        <v>1479.1179861811524</v>
       </c>
       <c r="N10" s="91"/>
     </row>
@@ -23728,7 +23728,7 @@
       <c r="K11" s="139"/>
       <c r="L11" s="128">
         <f ca="1">L8/(1+C15)^L9</f>
-        <v>17343.43664630581</v>
+        <v>17292.305557911313</v>
       </c>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.2">
@@ -23751,7 +23751,7 @@
       </c>
       <c r="C15" s="137">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.10706226926121921</v>
+        <v>0.10724691689330795</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.2">
@@ -23766,7 +23766,7 @@
       </c>
       <c r="C19" s="64">
         <f ca="1">SUM(H10:L10)</f>
-        <v>6600.4480010216284</v>
+        <v>6597.2488751965702</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.2">
@@ -23775,7 +23775,7 @@
       </c>
       <c r="C20" s="64">
         <f ca="1">L11</f>
-        <v>17343.43664630581</v>
+        <v>17292.305557911313</v>
       </c>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.2">
@@ -23784,7 +23784,7 @@
       </c>
       <c r="C21" s="94">
         <f ca="1">C19+C20</f>
-        <v>23943.884647327439</v>
+        <v>23889.554433107885</v>
       </c>
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.2">
@@ -23811,7 +23811,7 @@
       </c>
       <c r="C24" s="94">
         <f ca="1">C21+C22-C23</f>
-        <v>24822.884647327439</v>
+        <v>24768.554433107885</v>
       </c>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.2">
@@ -23829,7 +23829,7 @@
       </c>
       <c r="C26" s="234">
         <f ca="1">C24/C25</f>
-        <v>118.20421260632114</v>
+        <v>117.94549730051374</v>
       </c>
     </row>
   </sheetData>
@@ -24098,23 +24098,23 @@
       <c r="G9" s="140"/>
       <c r="H9" s="92">
         <f ca="1">DCF!H10</f>
-        <v>1861.6080604326387</v>
+        <v>1861.2976133995592</v>
       </c>
       <c r="I9" s="92">
         <f ca="1">DCF!I10</f>
-        <v>1269.8242065956549</v>
+        <v>1269.4007229464412</v>
       </c>
       <c r="J9" s="92">
         <f ca="1">DCF!J10</f>
-        <v>569.60056042298197</v>
+        <v>569.3156433333728</v>
       </c>
       <c r="K9" s="92">
         <f ca="1">DCF!K10</f>
-        <v>1419.0632606139084</v>
+        <v>1418.1169093360447</v>
       </c>
       <c r="L9" s="92">
         <f ca="1">DCF!L10</f>
-        <v>1480.3519129564443</v>
+        <v>1479.1179861811524</v>
       </c>
       <c r="N9" s="91"/>
     </row>
@@ -24900,7 +24900,7 @@
       </c>
       <c r="C41" s="137">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.10706226926121921</v>
+        <v>0.10724691689330795</v>
       </c>
     </row>
     <row r="42" spans="2:14" x14ac:dyDescent="0.2">
@@ -24926,7 +24926,7 @@
       </c>
       <c r="C44" s="24">
         <f ca="1">C43/(1+C41)^5</f>
-        <v>66939.552478607948</v>
+        <v>66883.755944414632</v>
       </c>
     </row>
     <row r="45" spans="2:14" x14ac:dyDescent="0.2">
@@ -24935,7 +24935,7 @@
       </c>
       <c r="C45" s="108">
         <f ca="1">SUM(H9:K9)+C44</f>
-        <v>72059.648566673131</v>
+        <v>72001.88683343005</v>
       </c>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.2">
@@ -24962,7 +24962,7 @@
       </c>
       <c r="C48" s="108">
         <f ca="1">C45+C46-C47</f>
-        <v>72938.648566673131</v>
+        <v>72880.88683343005</v>
       </c>
     </row>
     <row r="49" spans="2:3" x14ac:dyDescent="0.2">
@@ -24980,7 +24980,7 @@
       </c>
       <c r="C50" s="234">
         <f ca="1">C48/C49</f>
-        <v>347.32689793653873</v>
+        <v>347.05184206395262</v>
       </c>
     </row>
     <row r="52" spans="2:3" x14ac:dyDescent="0.2">
@@ -25063,7 +25063,7 @@
       </c>
       <c r="C62" s="137">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.10706226926121921</v>
+        <v>0.10724691689330795</v>
       </c>
     </row>
     <row r="63" spans="2:3" x14ac:dyDescent="0.2">
@@ -25089,7 +25089,7 @@
       </c>
       <c r="C65" s="24">
         <f ca="1">C64/(1+C62)^5</f>
-        <v>66615.836083039991</v>
+        <v>66560.309378151855</v>
       </c>
     </row>
     <row r="66" spans="2:3" x14ac:dyDescent="0.2">
@@ -25098,7 +25098,7 @@
       </c>
       <c r="C66" s="108">
         <f ca="1">SUM(H9:K9)+C65</f>
-        <v>71735.932171105174</v>
+        <v>71678.440267167272</v>
       </c>
     </row>
     <row r="67" spans="2:3" x14ac:dyDescent="0.2">
@@ -25125,7 +25125,7 @@
       </c>
       <c r="C69" s="108">
         <f ca="1">C66+C67-C68</f>
-        <v>72614.932171105174</v>
+        <v>72557.440267167272</v>
       </c>
     </row>
     <row r="70" spans="2:3" x14ac:dyDescent="0.2">
@@ -25143,7 +25143,7 @@
       </c>
       <c r="C71" s="234">
         <f ca="1">C69/C70</f>
-        <v>345.78539129097703</v>
+        <v>345.51162031984416</v>
       </c>
     </row>
     <row r="73" spans="2:3" x14ac:dyDescent="0.2">
@@ -25167,7 +25167,7 @@
       </c>
       <c r="C75" s="137">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.10706226926121921</v>
+        <v>0.10724691689330795</v>
       </c>
     </row>
     <row r="76" spans="2:3" x14ac:dyDescent="0.2">
@@ -25193,7 +25193,7 @@
       </c>
       <c r="C78" s="24">
         <f ca="1">C77/(1+C75)^5</f>
-        <v>40247.446175209196</v>
+        <v>40213.898475477763</v>
       </c>
     </row>
     <row r="79" spans="2:3" x14ac:dyDescent="0.2">
@@ -25202,7 +25202,7 @@
       </c>
       <c r="C79" s="108">
         <f ca="1">SUM(H9:K9)+C78</f>
-        <v>45367.542263274379</v>
+        <v>45332.029364493181</v>
       </c>
     </row>
     <row r="80" spans="2:3" x14ac:dyDescent="0.2">
@@ -25229,7 +25229,7 @@
       </c>
       <c r="C82" s="108">
         <f ca="1">C79+C80-C81</f>
-        <v>46246.542263274379</v>
+        <v>46211.029364493181</v>
       </c>
     </row>
     <row r="83" spans="2:3" x14ac:dyDescent="0.2">
@@ -25247,22 +25247,22 @@
       </c>
       <c r="C84" s="234">
         <f ca="1">C82/C83</f>
-        <v>220.22162982511608</v>
+        <v>220.05252078330085</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="B73:C73"/>
+    <mergeCell ref="C27:L27"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="B60:C60"/>
     <mergeCell ref="C22:L22"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="H2:L2"/>
     <mergeCell ref="C4:L4"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="C17:L17"/>
-    <mergeCell ref="B73:C73"/>
-    <mergeCell ref="C27:L27"/>
-    <mergeCell ref="B39:C39"/>
-    <mergeCell ref="B52:C52"/>
-    <mergeCell ref="B60:C60"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -25312,7 +25312,7 @@
       </c>
       <c r="C5" s="135">
         <f ca="1">DCF!C26</f>
-        <v>118.20421260632114</v>
+        <v>117.94549730051374</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.2">
@@ -25321,7 +25321,7 @@
       </c>
       <c r="C6" s="135">
         <f ca="1">Multiples!C50</f>
-        <v>347.32689793653873</v>
+        <v>347.05184206395262</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.2">
@@ -25339,7 +25339,7 @@
       </c>
       <c r="C8" s="135">
         <f ca="1">Multiples!C71</f>
-        <v>345.78539129097703</v>
+        <v>345.51162031984416</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
@@ -25348,7 +25348,7 @@
       </c>
       <c r="C9" s="135">
         <f ca="1">Multiples!C84</f>
-        <v>220.22162982511608</v>
+        <v>220.05252078330085</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
@@ -25357,7 +25357,7 @@
       </c>
       <c r="C10" s="234">
         <f ca="1">AVERAGE(C5:C9)</f>
-        <v>243.98631657763909</v>
+        <v>243.79098633937073</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -25366,7 +25366,7 @@
       </c>
       <c r="C11" s="135">
         <f ca="1">Overview!C5</f>
-        <v>212</v>
+        <v>221.56</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.2">
@@ -25375,7 +25375,7 @@
       </c>
       <c r="C12" s="154">
         <f ca="1">(C10-C11)/C11</f>
-        <v>0.15087885178131644</v>
+        <v>0.10033844709952487</v>
       </c>
     </row>
   </sheetData>
@@ -26099,7 +26099,7 @@
       <c r="K8" s="139"/>
       <c r="L8" s="128">
         <f ca="1">L7*(1+C20)/(C21-C20)</f>
-        <v>57276.825446755276</v>
+        <v>57155.605917528395</v>
       </c>
       <c r="N8" s="91"/>
       <c r="O8" s="16"/>
@@ -26153,23 +26153,23 @@
       <c r="G10" s="140"/>
       <c r="H10" s="128">
         <f ca="1">H7/(1+$C$21)^H9</f>
-        <v>958.70767045110335</v>
+        <v>958.54779364448223</v>
       </c>
       <c r="I10" s="128">
         <f t="shared" ref="I10:L10" ca="1" si="1">I7/(1+$C$21)^I9</f>
-        <v>1268.6790763342897</v>
+        <v>1268.255974583562</v>
       </c>
       <c r="J10" s="128">
         <f t="shared" ca="1" si="1"/>
-        <v>1678.8710973503341</v>
+        <v>1678.0313175114049</v>
       </c>
       <c r="K10" s="128">
         <f t="shared" ca="1" si="1"/>
-        <v>2221.6872762356711</v>
+        <v>2220.2056674510354</v>
       </c>
       <c r="L10" s="128">
         <f t="shared" ca="1" si="1"/>
-        <v>2940.0079381779306</v>
+        <v>2937.5573353971072</v>
       </c>
       <c r="N10" s="91"/>
     </row>
@@ -26188,15 +26188,15 @@
       <c r="K11" s="139"/>
       <c r="L11" s="128">
         <f ca="1">L8/(1+C21)^L9</f>
-        <v>34444.405393844594</v>
+        <v>34342.858049289687</v>
       </c>
     </row>
     <row r="13" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B14" s="251" t="s">
+      <c r="B14" s="250" t="s">
         <v>221</v>
       </c>
-      <c r="C14" s="252"/>
+      <c r="C14" s="251"/>
     </row>
     <row r="15" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B15" s="155" t="s">
@@ -26204,7 +26204,7 @@
       </c>
       <c r="C15" s="156">
         <f ca="1">Overview!C5</f>
-        <v>212</v>
+        <v>221.56</v>
       </c>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.2">
@@ -26213,7 +26213,7 @@
       </c>
       <c r="C16" s="156">
         <f ca="1">C36</f>
-        <v>212.39884426982738</v>
+        <v>211.88734994199655</v>
       </c>
     </row>
     <row r="17" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -26223,20 +26223,20 @@
       <c r="C17" s="158">
         <v>0.46500000000000002</v>
       </c>
-      <c r="E17" s="250" t="s">
+      <c r="E17" s="252" t="s">
         <v>224</v>
       </c>
-      <c r="F17" s="250"/>
-      <c r="G17" s="250"/>
-      <c r="H17" s="250"/>
-      <c r="I17" s="250"/>
+      <c r="F17" s="252"/>
+      <c r="G17" s="252"/>
+      <c r="H17" s="252"/>
+      <c r="I17" s="252"/>
     </row>
     <row r="18" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="19" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B19" s="251" t="s">
+      <c r="B19" s="250" t="s">
         <v>183</v>
       </c>
-      <c r="C19" s="252"/>
+      <c r="C19" s="251"/>
     </row>
     <row r="20" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B20" s="159" t="s">
@@ -26252,7 +26252,7 @@
       </c>
       <c r="C21" s="220">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.10706226926121921</v>
+        <v>0.10724691689330795</v>
       </c>
     </row>
     <row r="22" spans="2:9" x14ac:dyDescent="0.2">
@@ -26270,7 +26270,7 @@
       </c>
       <c r="C23" s="161">
         <f ca="1">C15*C22</f>
-        <v>44308</v>
+        <v>46306.04</v>
       </c>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.2">
@@ -26297,15 +26297,15 @@
       </c>
       <c r="C26" s="162">
         <f ca="1">C23+C25-C24</f>
-        <v>43429</v>
+        <v>45427.040000000001</v>
       </c>
     </row>
     <row r="27" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B28" s="251" t="s">
+      <c r="B28" s="250" t="s">
         <v>185</v>
       </c>
-      <c r="C28" s="252"/>
+      <c r="C28" s="251"/>
     </row>
     <row r="29" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B29" s="159" t="s">
@@ -26313,7 +26313,7 @@
       </c>
       <c r="C29" s="161">
         <f ca="1">SUM(H10:L10)</f>
-        <v>9067.9530585493285</v>
+        <v>9062.5980885875906</v>
       </c>
     </row>
     <row r="30" spans="2:9" x14ac:dyDescent="0.2">
@@ -26322,7 +26322,7 @@
       </c>
       <c r="C30" s="161">
         <f ca="1">L11</f>
-        <v>34444.405393844594</v>
+        <v>34342.858049289687</v>
       </c>
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.2">
@@ -26331,7 +26331,7 @@
       </c>
       <c r="C31" s="164">
         <f ca="1">C29+C30</f>
-        <v>43512.358452393921</v>
+        <v>43405.456137877278</v>
       </c>
     </row>
     <row r="32" spans="2:9" x14ac:dyDescent="0.2">
@@ -26358,7 +26358,7 @@
       </c>
       <c r="C34" s="164">
         <f ca="1">C31+C32-C33</f>
-        <v>44391.358452393921</v>
+        <v>44284.456137877278</v>
       </c>
     </row>
     <row r="35" spans="2:3" x14ac:dyDescent="0.2">
@@ -26376,21 +26376,21 @@
       </c>
       <c r="C36" s="167">
         <f ca="1">C34/C35</f>
-        <v>212.39884426982738</v>
+        <v>211.88734994199655</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="E17:I17"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="H3:L3"/>
     <mergeCell ref="P3:W3"/>
     <mergeCell ref="X3:Z3"/>
     <mergeCell ref="C5:L5"/>
     <mergeCell ref="P5:Z5"/>
     <mergeCell ref="B14:C14"/>
-    <mergeCell ref="E17:I17"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="H3:L3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -33046,7 +33046,7 @@
       </c>
       <c r="AC117" s="63">
         <f ca="1">Overview!C5</f>
-        <v>212</v>
+        <v>221.56</v>
       </c>
     </row>
     <row r="118" spans="1:31" x14ac:dyDescent="0.2">
@@ -33117,7 +33117,7 @@
       </c>
       <c r="AC118" s="65">
         <f ca="1">AC117/AC86</f>
-        <v>212</v>
+        <v>221.56</v>
       </c>
     </row>
     <row r="120" spans="1:31" x14ac:dyDescent="0.2">
@@ -34423,7 +34423,7 @@
       <c r="AA151" s="49"/>
       <c r="AC151" s="72">
         <f ca="1">AC118/Statement!AC27</f>
-        <v>27.42561448900388</v>
+        <v>28.662354463130658</v>
       </c>
     </row>
     <row r="152" spans="2:29" x14ac:dyDescent="0.2">
@@ -34460,7 +34460,7 @@
       <c r="AA152" s="49"/>
       <c r="AC152" s="72">
         <f ca="1">AC118/(Statement!AC5/Statement!AC23)</f>
-        <v>5.7966623876765091</v>
+        <v>6.0580590500641858</v>
       </c>
     </row>
     <row r="153" spans="2:29" x14ac:dyDescent="0.2">
@@ -34521,7 +34521,7 @@
       </c>
       <c r="AC153" s="72">
         <f ca="1">AC118/(Statement!AC50/Statement!AC76)</f>
-        <v>13.097250960685781</v>
+        <v>13.687862843629913</v>
       </c>
     </row>
     <row r="154" spans="2:29" x14ac:dyDescent="0.2">
@@ -34582,7 +34582,7 @@
       </c>
       <c r="AC154" s="143">
         <f ca="1">Statement!AC118*Statement!AC79</f>
-        <v>44520</v>
+        <v>46527.6</v>
       </c>
     </row>
     <row r="155" spans="2:29" x14ac:dyDescent="0.2">
@@ -34643,7 +34643,7 @@
       </c>
       <c r="AC155" s="143">
         <f ca="1">AC154+AC109-AC108+AC49+AC46</f>
-        <v>43641</v>
+        <v>45648.6</v>
       </c>
     </row>
     <row r="156" spans="2:29" x14ac:dyDescent="0.2">
@@ -34680,7 +34680,7 @@
       <c r="AA156" s="49"/>
       <c r="AC156" s="181">
         <f ca="1">AC155/AC5</f>
-        <v>5.6021822849807448</v>
+        <v>5.8598973042361999</v>
       </c>
     </row>
     <row r="157" spans="2:29" x14ac:dyDescent="0.2">
@@ -34717,7 +34717,7 @@
       <c r="AA157" s="49"/>
       <c r="AC157" s="181">
         <f ca="1">AC155/AC13</f>
-        <v>21.38216560509554</v>
+        <v>22.365801077902987</v>
       </c>
     </row>
     <row r="158" spans="2:29" x14ac:dyDescent="0.2">
@@ -34814,7 +34814,7 @@
       <c r="Z159" s="49"/>
       <c r="AA159" s="49"/>
       <c r="AC159" s="64">
-        <f>AC110+AC54+AC111+AC56+AC58+AC59</f>
+        <f>AC110+AC54+AC111+AC56+AC58+AC59+AC57</f>
         <v>1216.0769596199527</v>
       </c>
     </row>
@@ -34852,7 +34852,7 @@
       <c r="AA160" s="49"/>
       <c r="AC160" s="72">
         <f t="shared" ref="AC160:AC161" ca="1" si="155">AC154/AC158</f>
-        <v>21.220209723546233</v>
+        <v>22.177121067683508</v>
       </c>
     </row>
     <row r="161" spans="2:29" x14ac:dyDescent="0.2">
@@ -34889,7 +34889,7 @@
       <c r="AA161" s="49"/>
       <c r="AC161" s="72">
         <f t="shared" ca="1" si="155"/>
-        <v>35.886709023447537</v>
+        <v>37.537591382593135</v>
       </c>
     </row>
     <row r="162" spans="2:29" x14ac:dyDescent="0.2">
@@ -34926,7 +34926,7 @@
       <c r="AA162" s="49"/>
       <c r="AC162" s="74">
         <f t="shared" ref="AC162" ca="1" si="158">AC158/AC154</f>
-        <v>4.7124887690925425E-2</v>
+        <v>4.5091515573552045E-2</v>
       </c>
     </row>
     <row r="163" spans="2:29" x14ac:dyDescent="0.2">
@@ -34963,7 +34963,7 @@
       <c r="AA163" s="49"/>
       <c r="AC163" s="74">
         <f ca="1">AC27/AC118</f>
-        <v>3.6462264150943398E-2</v>
+        <v>3.4888969128001449E-2</v>
       </c>
     </row>
     <row r="164" spans="2:29" x14ac:dyDescent="0.2">
@@ -35037,7 +35037,7 @@
       <c r="AA165" s="49"/>
       <c r="AC165" s="154">
         <f ca="1">-AC64/AC154</f>
-        <v>3.5736747529200356E-2</v>
+        <v>3.4194757520267544E-2</v>
       </c>
     </row>
     <row r="166" spans="2:29" x14ac:dyDescent="0.2">
@@ -35074,7 +35074,7 @@
       <c r="AA166" s="49"/>
       <c r="AC166" s="154">
         <f ca="1">-(AC64+AC65)/AC154</f>
-        <v>3.5736747529200356E-2</v>
+        <v>3.4194757520267544E-2</v>
       </c>
     </row>
     <row r="167" spans="2:29" x14ac:dyDescent="0.2">
@@ -35577,7 +35577,7 @@
       <c r="AA177" s="49"/>
       <c r="AC177" s="154">
         <f ca="1">(AC108-AC109)/AC154</f>
-        <v>1.9743935309973044E-2</v>
+        <v>1.8892012482913369E-2</v>
       </c>
     </row>
     <row r="178" spans="1:31" x14ac:dyDescent="0.2">
@@ -36606,94 +36606,61 @@
       <c r="K203" s="81"/>
       <c r="L203" s="81"/>
       <c r="M203" s="81">
-        <f>IF(L188=0,
+        <f t="shared" ref="M203:Q204" si="182">IF(L188=0,
 IF(M188=0,0,IF(M188&gt;0,1,-1)),
 (M188-L188)/ABS(L188)
 )</f>
         <v>1</v>
       </c>
       <c r="N203" s="81">
-        <f>IF(M188=0,
-IF(N188=0,0,IF(N188&gt;0,1,-1)),
-(N188-M188)/ABS(M188)
-)</f>
+        <f t="shared" si="182"/>
         <v>0.14023210831721469</v>
       </c>
       <c r="O203" s="81">
-        <f>IF(N188=0,
-IF(O188=0,0,IF(O188&gt;0,1,-1)),
-(O188-N188)/ABS(N188)
-)</f>
+        <f t="shared" si="182"/>
         <v>9.6268023748939779E-2</v>
       </c>
       <c r="P203" s="81">
-        <f>IF(O188=0,
-IF(P188=0,0,IF(P188&gt;0,1,-1)),
-(P188-O188)/ABS(O188)
-)</f>
+        <f t="shared" si="182"/>
         <v>0.1137330754352031</v>
       </c>
       <c r="Q203" s="81">
-        <f>IF(P188=0,
-IF(Q188=0,0,IF(Q188&gt;0,1,-1)),
-(Q188-P188)/ABS(P188)
-)</f>
+        <f t="shared" si="182"/>
         <v>0.17679749913164294</v>
       </c>
       <c r="T203" s="81">
-        <f>IF(S188=0,
+        <f t="shared" ref="T203:AA204" si="183">IF(S188=0,
 IF(T188=0,0,IF(T188&gt;0,1,-1)),
 (T188-S188)/ABS(S188)
 )</f>
         <v>1</v>
       </c>
       <c r="U203" s="81">
-        <f>IF(T188=0,
-IF(U188=0,0,IF(U188&gt;0,1,-1)),
-(U188-T188)/ABS(T188)
-)</f>
+        <f t="shared" si="183"/>
         <v>4.5020463847203276E-2</v>
       </c>
       <c r="V203" s="81">
-        <f>IF(U188=0,
-IF(V188=0,0,IF(V188&gt;0,1,-1)),
-(V188-U188)/ABS(U188)
-)</f>
+        <f t="shared" si="183"/>
         <v>5.2219321148825066E-3</v>
       </c>
       <c r="W203" s="81">
-        <f>IF(V188=0,
-IF(W188=0,0,IF(W188&gt;0,1,-1)),
-(W188-V188)/ABS(V188)
-)</f>
+        <f t="shared" si="183"/>
         <v>8.2467532467532467E-2</v>
       </c>
       <c r="X203" s="81">
-        <f>IF(W188=0,
-IF(X188=0,0,IF(X188&gt;0,1,-1)),
-(X188-W188)/ABS(W188)
-)</f>
+        <f t="shared" si="183"/>
         <v>4.4991001799640072E-2</v>
       </c>
       <c r="Y203" s="81">
-        <f>IF(X188=0,
-IF(Y188=0,0,IF(Y188&gt;0,1,-1)),
-(Y188-X188)/ABS(X188)
-)</f>
+        <f t="shared" si="183"/>
         <v>4.8794489092996558E-2</v>
       </c>
       <c r="Z203" s="81">
-        <f>IF(Y188=0,
-IF(Z188=0,0,IF(Z188&gt;0,1,-1)),
-(Z188-Y188)/ABS(Y188)
-)</f>
+        <f t="shared" si="183"/>
         <v>4.9261083743842365E-3</v>
       </c>
       <c r="AA203" s="81">
-        <f>IF(Z188=0,
-IF(AA188=0,0,IF(AA188&gt;0,1,-1)),
-(AA188-Z188)/ABS(Z188)
-)</f>
+        <f t="shared" si="183"/>
         <v>6.3180827886710242E-2</v>
       </c>
       <c r="AC203" s="49"/>
@@ -36704,94 +36671,55 @@
         <v>Other</v>
       </c>
       <c r="M204" s="81">
-        <f>IF(L189=0,
-IF(M189=0,0,IF(M189&gt;0,1,-1)),
-(M189-L189)/ABS(L189)
-)</f>
+        <f t="shared" si="182"/>
         <v>1</v>
       </c>
       <c r="N204" s="81">
-        <f>IF(M189=0,
-IF(N189=0,0,IF(N189&gt;0,1,-1)),
-(N189-M189)/ABS(M189)
-)</f>
+        <f t="shared" si="182"/>
         <v>0.156</v>
       </c>
       <c r="O204" s="81">
-        <f>IF(N189=0,
-IF(O189=0,0,IF(O189&gt;0,1,-1)),
-(O189-N189)/ABS(N189)
-)</f>
+        <f t="shared" si="182"/>
         <v>0.13148788927335639</v>
       </c>
       <c r="P204" s="81">
-        <f>IF(O189=0,
-IF(P189=0,0,IF(P189&gt;0,1,-1)),
-(P189-O189)/ABS(O189)
-)</f>
+        <f t="shared" si="182"/>
         <v>0.14067278287461774</v>
       </c>
       <c r="Q204" s="81">
-        <f>IF(P189=0,
-IF(Q189=0,0,IF(Q189&gt;0,1,-1)),
-(Q189-P189)/ABS(P189)
-)</f>
+        <f t="shared" si="182"/>
         <v>0.15281501340482573</v>
       </c>
       <c r="T204" s="81">
-        <f>IF(S189=0,
-IF(T189=0,0,IF(T189&gt;0,1,-1)),
-(T189-S189)/ABS(S189)
-)</f>
+        <f t="shared" si="183"/>
         <v>1</v>
       </c>
       <c r="U204" s="81">
-        <f>IF(T189=0,
-IF(U189=0,0,IF(U189&gt;0,1,-1)),
-(U189-T189)/ABS(T189)
-)</f>
+        <f t="shared" si="183"/>
         <v>2.8846153846153848E-2</v>
       </c>
       <c r="V204" s="81">
-        <f>IF(U189=0,
-IF(V189=0,0,IF(V189&gt;0,1,-1)),
-(V189-U189)/ABS(U189)
-)</f>
+        <f t="shared" si="183"/>
         <v>-0.13084112149532709</v>
       </c>
       <c r="W204" s="81">
-        <f>IF(V189=0,
-IF(W189=0,0,IF(W189&gt;0,1,-1)),
-(W189-V189)/ABS(V189)
-)</f>
+        <f t="shared" si="183"/>
         <v>3.2258064516129031E-2</v>
       </c>
       <c r="X204" s="81">
-        <f>IF(W189=0,
-IF(X189=0,0,IF(X189&gt;0,1,-1)),
-(X189-W189)/ABS(W189)
-)</f>
+        <f t="shared" si="183"/>
         <v>0.15625</v>
       </c>
       <c r="Y204" s="81">
-        <f>IF(X189=0,
-IF(Y189=0,0,IF(Y189&gt;0,1,-1)),
-(Y189-X189)/ABS(X189)
-)</f>
+        <f t="shared" si="183"/>
         <v>0.17117117117117117</v>
       </c>
       <c r="Z204" s="81">
-        <f>IF(Y189=0,
-IF(Z189=0,0,IF(Z189&gt;0,1,-1)),
-(Z189-Y189)/ABS(Y189)
-)</f>
+        <f t="shared" si="183"/>
         <v>-0.24615384615384617</v>
       </c>
       <c r="AA204" s="81">
-        <f>IF(Z189=0,
-IF(AA189=0,0,IF(AA189&gt;0,1,-1)),
-(AA189-Z189)/ABS(Z189)
-)</f>
+        <f t="shared" si="183"/>
         <v>-4.0816326530612242E-2</v>
       </c>
       <c r="AC204" s="49"/>
@@ -36825,64 +36753,64 @@
         <v>1</v>
       </c>
       <c r="N206" s="81">
-        <f t="shared" ref="N206:Q206" si="182">IF(M195=0,
+        <f t="shared" ref="N206:Q206" si="184">IF(M195=0,
 IF(N195=0,0,IF(N195&gt;0,1,-1)),
 (N195-M195)/ABS(M195)
 )</f>
         <v>0.1569324530218385</v>
       </c>
       <c r="O206" s="81">
-        <f t="shared" si="182"/>
+        <f t="shared" si="184"/>
         <v>0.13257243195785778</v>
       </c>
       <c r="P206" s="81">
-        <f t="shared" si="182"/>
+        <f t="shared" si="184"/>
         <v>0.13837209302325582</v>
       </c>
       <c r="Q206" s="81">
-        <f t="shared" si="182"/>
+        <f t="shared" si="184"/>
         <v>0.21995233231188288</v>
       </c>
       <c r="T206" s="81">
-        <f t="shared" ref="T206:AA210" si="183">IF(S195=0,
+        <f t="shared" ref="T206:AA210" si="185">IF(S195=0,
 IF(T195=0,0,IF(T195&gt;0,1,-1)),
 (T195-S195)/ABS(S195)
 )</f>
         <v>1</v>
       </c>
       <c r="U206" s="81">
-        <f t="shared" si="183"/>
+        <f t="shared" si="185"/>
         <v>6.3914780292942744E-2</v>
       </c>
       <c r="V206" s="81">
-        <f t="shared" si="183"/>
+        <f t="shared" si="185"/>
         <v>1.2515644555694618E-2</v>
       </c>
       <c r="W206" s="81">
-        <f t="shared" si="183"/>
+        <f t="shared" si="185"/>
         <v>8.5290482076637822E-2</v>
       </c>
       <c r="X206" s="81">
-        <f t="shared" si="183"/>
+        <f t="shared" si="185"/>
         <v>4.8974943052391799E-2</v>
       </c>
       <c r="Y206" s="81">
-        <f t="shared" si="183"/>
+        <f t="shared" si="185"/>
         <v>5.8631921824104233E-2</v>
       </c>
       <c r="Z206" s="81">
-        <f t="shared" si="183"/>
+        <f t="shared" si="185"/>
         <v>-5.1282051282051282E-3</v>
       </c>
       <c r="AA206" s="81">
-        <f t="shared" si="183"/>
+        <f t="shared" si="185"/>
         <v>6.0824742268041236E-2</v>
       </c>
       <c r="AC206" s="49"/>
     </row>
     <row r="207" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B207" s="20" t="str">
-        <f t="shared" ref="B207:B210" si="184">B196</f>
+        <f t="shared" ref="B207:B210" si="186">B196</f>
         <v>AutoCAD and AutoCAD LT</v>
       </c>
       <c r="M207" s="81">
@@ -36900,230 +36828,230 @@
         <v>0.11495176848874598</v>
       </c>
       <c r="O207" s="81">
-        <f t="shared" ref="O207:Q207" si="185">IF(N196=0,
+        <f t="shared" ref="O207:Q207" si="187">IF(N196=0,
 IF(O196=0,0,IF(O196&gt;0,1,-1)),
 (O196-N196)/ABS(N196)
 )</f>
         <v>5.4073540014419608E-2</v>
       </c>
       <c r="P207" s="81">
+        <f t="shared" si="187"/>
+        <v>7.523939808481532E-2</v>
+      </c>
+      <c r="Q207" s="81">
+        <f t="shared" si="187"/>
+        <v>0.13676844783715011</v>
+      </c>
+      <c r="T207" s="81">
         <f t="shared" si="185"/>
-        <v>7.523939808481532E-2</v>
-      </c>
-      <c r="Q207" s="81">
+        <v>1</v>
+      </c>
+      <c r="U207" s="81">
         <f t="shared" si="185"/>
-        <v>0.13676844783715011</v>
-      </c>
-      <c r="T207" s="81">
-        <f t="shared" si="183"/>
-        <v>1</v>
-      </c>
-      <c r="U207" s="81">
-        <f t="shared" si="183"/>
         <v>2.7638190954773871E-2</v>
       </c>
       <c r="V207" s="81">
-        <f t="shared" si="183"/>
+        <f t="shared" si="185"/>
         <v>4.8899755501222494E-3</v>
       </c>
       <c r="W207" s="81">
-        <f t="shared" si="183"/>
+        <f t="shared" si="185"/>
         <v>7.0559610705596104E-2</v>
       </c>
       <c r="X207" s="81">
-        <f t="shared" si="183"/>
+        <f t="shared" si="185"/>
         <v>4.0909090909090909E-2</v>
       </c>
       <c r="Y207" s="81">
-        <f t="shared" si="183"/>
+        <f t="shared" si="185"/>
         <v>4.3668122270742356E-2</v>
       </c>
       <c r="Z207" s="81">
-        <f t="shared" si="183"/>
+        <f t="shared" si="185"/>
         <v>-8.368200836820083E-3</v>
       </c>
       <c r="AA207" s="81">
-        <f t="shared" si="183"/>
+        <f t="shared" si="185"/>
         <v>5.4852320675105488E-2</v>
       </c>
       <c r="AC207" s="49"/>
     </row>
     <row r="208" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B208" s="20" t="str">
-        <f t="shared" si="184"/>
+        <f t="shared" si="186"/>
         <v>Manufacturing</v>
       </c>
       <c r="M208" s="81">
-        <f t="shared" ref="M208:Q210" si="186">IF(L197=0,
+        <f t="shared" ref="M208:Q210" si="188">IF(L197=0,
 IF(M197=0,0,IF(M197&gt;0,1,-1)),
 (M197-L197)/ABS(L197)
 )</f>
         <v>1</v>
       </c>
       <c r="N208" s="81">
-        <f t="shared" si="186"/>
+        <f t="shared" si="188"/>
         <v>0.11643835616438356</v>
       </c>
       <c r="O208" s="81">
-        <f t="shared" si="186"/>
+        <f t="shared" si="188"/>
         <v>8.6912065439672795E-2</v>
       </c>
       <c r="P208" s="81">
-        <f t="shared" si="186"/>
+        <f t="shared" si="188"/>
         <v>0.11853245531514581</v>
       </c>
       <c r="Q208" s="81">
-        <f t="shared" si="186"/>
+        <f t="shared" si="188"/>
         <v>0.159798149705635</v>
       </c>
       <c r="T208" s="81">
-        <f t="shared" si="183"/>
+        <f t="shared" si="185"/>
         <v>1</v>
       </c>
       <c r="U208" s="81">
-        <f t="shared" si="183"/>
+        <f t="shared" si="185"/>
         <v>3.5830618892508145E-2</v>
       </c>
       <c r="V208" s="81">
-        <f t="shared" si="183"/>
+        <f t="shared" si="185"/>
         <v>-2.8301886792452831E-2</v>
       </c>
       <c r="W208" s="81">
-        <f t="shared" si="183"/>
+        <f t="shared" si="185"/>
         <v>8.0906148867313912E-2</v>
       </c>
       <c r="X208" s="81">
-        <f t="shared" si="183"/>
+        <f t="shared" si="185"/>
         <v>6.2874251497005984E-2</v>
       </c>
       <c r="Y208" s="81">
-        <f t="shared" si="183"/>
+        <f t="shared" si="185"/>
         <v>7.3239436619718309E-2</v>
       </c>
       <c r="Z208" s="81">
-        <f t="shared" si="183"/>
+        <f t="shared" si="185"/>
         <v>-3.6745406824146981E-2</v>
       </c>
       <c r="AA208" s="81">
-        <f t="shared" si="183"/>
+        <f t="shared" si="185"/>
         <v>4.9046321525885561E-2</v>
       </c>
       <c r="AC208" s="49"/>
     </row>
     <row r="209" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B209" s="20" t="str">
-        <f t="shared" si="184"/>
+        <f t="shared" si="186"/>
         <v>Media and Entertainment</v>
       </c>
       <c r="M209" s="81">
-        <f t="shared" si="186"/>
+        <f t="shared" si="188"/>
         <v>1</v>
       </c>
       <c r="N209" s="81">
-        <f t="shared" si="186"/>
+        <f t="shared" si="188"/>
         <v>0.12355212355212356</v>
       </c>
       <c r="O209" s="81">
-        <f t="shared" si="186"/>
+        <f t="shared" si="188"/>
         <v>1.3745704467353952E-2</v>
       </c>
       <c r="P209" s="81">
-        <f t="shared" si="186"/>
+        <f t="shared" si="188"/>
         <v>6.7796610169491525E-2</v>
       </c>
       <c r="Q209" s="81">
-        <f t="shared" si="186"/>
+        <f t="shared" si="188"/>
         <v>5.3968253968253971E-2</v>
       </c>
       <c r="T209" s="81">
-        <f t="shared" si="183"/>
+        <f t="shared" si="185"/>
         <v>1</v>
       </c>
       <c r="U209" s="81">
-        <f t="shared" si="183"/>
+        <f t="shared" si="185"/>
         <v>1.2048192771084338E-2</v>
       </c>
       <c r="V209" s="81">
-        <f t="shared" si="183"/>
+        <f t="shared" si="185"/>
         <v>-9.5238095238095233E-2</v>
       </c>
       <c r="W209" s="81">
-        <f t="shared" si="183"/>
+        <f t="shared" si="185"/>
         <v>5.2631578947368418E-2</v>
       </c>
       <c r="X209" s="81">
-        <f t="shared" si="183"/>
+        <f t="shared" si="185"/>
         <v>7.4999999999999997E-2</v>
       </c>
       <c r="Y209" s="81">
-        <f t="shared" si="183"/>
+        <f t="shared" si="185"/>
         <v>4.6511627906976744E-2</v>
       </c>
       <c r="Z209" s="81">
-        <f t="shared" si="183"/>
+        <f t="shared" si="185"/>
         <v>-4.4444444444444446E-2</v>
       </c>
       <c r="AA209" s="81">
-        <f t="shared" si="183"/>
+        <f t="shared" si="185"/>
         <v>6.9767441860465115E-2</v>
       </c>
       <c r="AC209" s="49"/>
     </row>
     <row r="210" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B210" s="20" t="str">
-        <f t="shared" si="184"/>
+        <f t="shared" si="186"/>
         <v>Other</v>
       </c>
       <c r="M210" s="81">
-        <f t="shared" si="186"/>
+        <f t="shared" si="188"/>
         <v>1</v>
       </c>
       <c r="N210" s="81">
-        <f t="shared" si="186"/>
+        <f t="shared" si="188"/>
         <v>0.86842105263157898</v>
       </c>
       <c r="O210" s="81">
-        <f t="shared" si="186"/>
+        <f t="shared" si="188"/>
         <v>0.36619718309859156</v>
       </c>
       <c r="P210" s="81">
-        <f t="shared" si="186"/>
+        <f t="shared" si="188"/>
         <v>0.21649484536082475</v>
       </c>
       <c r="Q210" s="81">
-        <f t="shared" si="186"/>
+        <f t="shared" si="188"/>
         <v>5.9322033898305086E-2</v>
       </c>
       <c r="T210" s="81">
-        <f t="shared" si="183"/>
+        <f t="shared" si="185"/>
         <v>1</v>
       </c>
       <c r="U210" s="81">
-        <f t="shared" si="183"/>
+        <f t="shared" si="185"/>
         <v>-6.4516129032258063E-2</v>
       </c>
       <c r="V210" s="81">
-        <f t="shared" si="183"/>
+        <f t="shared" si="185"/>
         <v>-3.4482758620689655E-2</v>
       </c>
       <c r="W210" s="81">
-        <f t="shared" si="183"/>
+        <f t="shared" si="185"/>
         <v>0.10714285714285714</v>
       </c>
       <c r="X210" s="81">
-        <f t="shared" si="183"/>
+        <f t="shared" si="185"/>
         <v>6.4516129032258063E-2</v>
       </c>
       <c r="Y210" s="81">
-        <f t="shared" si="183"/>
+        <f t="shared" si="185"/>
         <v>0</v>
       </c>
       <c r="Z210" s="81">
-        <f t="shared" si="183"/>
+        <f t="shared" si="185"/>
         <v>0.12121212121212122</v>
       </c>
       <c r="AA210" s="81">
-        <f t="shared" si="183"/>
+        <f t="shared" si="185"/>
         <v>8.1081081081081086E-2</v>
       </c>
       <c r="AC210" s="49"/>
@@ -37263,15 +37191,15 @@
         <v>86.136354537811769</v>
       </c>
       <c r="O218" s="143">
-        <f t="shared" ref="O218:Q218" si="187">100*(1+((O118-$M118)/ABS($M118)))</f>
+        <f t="shared" ref="O218:Q218" si="189">100*(1+((O118-$M118)/ABS($M118)))</f>
         <v>101.60935185555869</v>
       </c>
       <c r="P218" s="143">
-        <f t="shared" si="187"/>
+        <f t="shared" si="189"/>
         <v>124.58865446975457</v>
       </c>
       <c r="Q218" s="143">
-        <f t="shared" si="187"/>
+        <f t="shared" si="189"/>
         <v>101.23303575003003</v>
       </c>
       <c r="T218" s="49"/>
@@ -37296,15 +37224,15 @@
         <v>114.11308709530323</v>
       </c>
       <c r="O219" s="143">
-        <f t="shared" ref="O219:Q219" si="188">100*(1+((O5-$M5)/ABS($M5)))</f>
+        <f t="shared" ref="O219:Q219" si="190">100*(1+((O5-$M5)/ABS($M5)))</f>
         <v>125.33059735522116</v>
       </c>
       <c r="P219" s="143">
-        <f t="shared" si="188"/>
+        <f t="shared" si="190"/>
         <v>139.78568171454629</v>
       </c>
       <c r="Q219" s="143">
-        <f t="shared" si="188"/>
+        <f t="shared" si="190"/>
         <v>164.2954856361149</v>
       </c>
       <c r="T219" s="49"/>
@@ -37329,15 +37257,15 @@
         <v>168.74999999999997</v>
       </c>
       <c r="O220" s="143">
-        <f t="shared" ref="O220:Q220" si="189">100*(1+((O27-$M27)/ABS($M27)))</f>
+        <f t="shared" ref="O220:Q220" si="191">100*(1+((O27-$M27)/ABS($M27)))</f>
         <v>187.05357142857144</v>
       </c>
       <c r="P220" s="143">
-        <f t="shared" si="189"/>
+        <f t="shared" si="191"/>
         <v>228.57142857142856</v>
       </c>
       <c r="Q220" s="143">
-        <f t="shared" si="189"/>
+        <f t="shared" si="191"/>
         <v>233.48214285714289</v>
       </c>
       <c r="T220" s="49"/>
@@ -37460,7 +37388,7 @@
       </c>
       <c r="C5" s="170">
         <f ca="1">Overview!C5</f>
-        <v>212</v>
+        <v>221.56</v>
       </c>
       <c r="E5" s="12"/>
       <c r="F5" s="134" t="s">
@@ -37476,7 +37404,7 @@
       </c>
       <c r="C6" s="171">
         <f ca="1">Statement!AC154</f>
-        <v>44520</v>
+        <v>46527.6</v>
       </c>
       <c r="E6" s="20" t="s">
         <v>19</v>
@@ -37496,7 +37424,7 @@
       </c>
       <c r="C7" s="171">
         <f ca="1">Statement!AC155</f>
-        <v>43641</v>
+        <v>45648.6</v>
       </c>
       <c r="E7" s="20" t="s">
         <v>31</v>
@@ -37516,7 +37444,7 @@
       </c>
       <c r="C8" s="172">
         <f ca="1">Statement!AC151</f>
-        <v>27.42561448900388</v>
+        <v>28.662354463130658</v>
       </c>
       <c r="E8" s="20" t="s">
         <v>242</v>
@@ -37536,7 +37464,7 @@
       </c>
       <c r="C9" s="172">
         <f ca="1">Statement!AC152</f>
-        <v>5.7966623876765091</v>
+        <v>6.0580590500641858</v>
       </c>
       <c r="E9" s="20" t="s">
         <v>243</v>
@@ -37556,7 +37484,7 @@
       </c>
       <c r="C10" s="172">
         <f ca="1">Statement!AC153</f>
-        <v>13.097250960685781</v>
+        <v>13.687862843629913</v>
       </c>
       <c r="E10" s="20" t="s">
         <v>1</v>
@@ -37576,7 +37504,7 @@
       </c>
       <c r="C11" s="172">
         <f ca="1">Statement!AC156</f>
-        <v>5.6021822849807448</v>
+        <v>5.8598973042361999</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
@@ -37585,7 +37513,7 @@
       </c>
       <c r="C12" s="172">
         <f ca="1">Statement!AC157</f>
-        <v>21.38216560509554</v>
+        <v>22.365801077902987</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.2">
@@ -37821,7 +37749,7 @@
       </c>
       <c r="C38" s="173">
         <f ca="1">Statement!AC163</f>
-        <v>3.6462264150943398E-2</v>
+        <v>3.4888969128001449E-2</v>
       </c>
       <c r="E38" s="20" t="s">
         <v>269</v>
@@ -37837,7 +37765,7 @@
       </c>
       <c r="C39" s="213">
         <f ca="1">Statement!AC162</f>
-        <v>4.7124887690925425E-2</v>
+        <v>4.5091515573552045E-2</v>
       </c>
       <c r="E39" s="20" t="s">
         <v>271</v>
@@ -37869,7 +37797,7 @@
       </c>
       <c r="C41" s="173">
         <f ca="1">Statement!AC165</f>
-        <v>3.5736747529200356E-2</v>
+        <v>3.4194757520267544E-2</v>
       </c>
     </row>
     <row r="42" spans="2:6" x14ac:dyDescent="0.2">
@@ -37878,7 +37806,7 @@
       </c>
       <c r="C42" s="173">
         <f ca="1">Statement!AC166</f>
-        <v>3.5736747529200356E-2</v>
+        <v>3.4194757520267544E-2</v>
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.2">
@@ -37922,7 +37850,7 @@
       </c>
       <c r="F48" s="173">
         <f ca="1">Statement!AC177</f>
-        <v>1.9743935309973044E-2</v>
+        <v>1.8892012482913369E-2</v>
       </c>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.2">
@@ -38101,7 +38029,7 @@
       </c>
       <c r="I6" s="170">
         <f ca="1">Statement!AC117</f>
-        <v>212</v>
+        <v>221.56</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -38130,7 +38058,7 @@
       </c>
       <c r="I7" s="171">
         <f ca="1">Statement!AC154</f>
-        <v>44520</v>
+        <v>46527.6</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
@@ -38159,7 +38087,7 @@
       </c>
       <c r="I8" s="171">
         <f ca="1">Statement!AC155</f>
-        <v>43641</v>
+        <v>45648.6</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -38188,7 +38116,7 @@
       </c>
       <c r="I9" s="172">
         <f ca="1">Statement!AC151</f>
-        <v>27.42561448900388</v>
+        <v>28.662354463130658</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -38217,7 +38145,7 @@
       </c>
       <c r="I10" s="172">
         <f ca="1">Statement!AC152</f>
-        <v>5.7966623876765091</v>
+        <v>6.0580590500641858</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -38246,7 +38174,7 @@
       </c>
       <c r="I11" s="172">
         <f ca="1">Statement!AC153</f>
-        <v>13.097250960685781</v>
+        <v>13.687862843629913</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
@@ -38275,7 +38203,7 @@
       </c>
       <c r="I12" s="172">
         <f ca="1">Statement!AC156</f>
-        <v>5.6021822849807448</v>
+        <v>5.8598973042361999</v>
       </c>
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.2">
@@ -38304,7 +38232,7 @@
       </c>
       <c r="I13" s="172">
         <f ca="1">Statement!AC157</f>
-        <v>21.38216560509554</v>
+        <v>22.365801077902987</v>
       </c>
     </row>
     <row r="15" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -39077,7 +39005,7 @@
       </c>
       <c r="I51" s="173">
         <f ca="1">Statement!AC163</f>
-        <v>3.6462264150943398E-2</v>
+        <v>3.4888969128001449E-2</v>
       </c>
     </row>
     <row r="52" spans="2:9" x14ac:dyDescent="0.2">
@@ -39106,7 +39034,7 @@
       </c>
       <c r="I52" s="173">
         <f ca="1">Statement!AC162</f>
-        <v>4.7124887690925425E-2</v>
+        <v>4.5091515573552045E-2</v>
       </c>
     </row>
     <row r="53" spans="2:9" x14ac:dyDescent="0.2">
@@ -39164,7 +39092,7 @@
       </c>
       <c r="I54" s="173">
         <f ca="1">Statement!AC165</f>
-        <v>3.5736747529200356E-2</v>
+        <v>3.4194757520267544E-2</v>
       </c>
     </row>
     <row r="55" spans="2:9" x14ac:dyDescent="0.2">
@@ -39193,7 +39121,7 @@
       </c>
       <c r="I55" s="173">
         <f ca="1">Statement!AC166</f>
-        <v>3.5736747529200356E-2</v>
+        <v>3.4194757520267544E-2</v>
       </c>
     </row>
     <row r="57" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -39429,7 +39357,7 @@
       </c>
       <c r="I68" s="194">
         <f ca="1">Statement!AC177</f>
-        <v>1.9743935309973044E-2</v>
+        <v>1.8892012482913369E-2</v>
       </c>
     </row>
     <row r="70" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -40582,6 +40510,30 @@
     </row>
   </sheetData>
   <mergeCells count="32">
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="F25:G25"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="F27:G27"/>
+    <mergeCell ref="C30:D30"/>
+    <mergeCell ref="F30:G30"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="F9:G9"/>
     <mergeCell ref="C38:D38"/>
     <mergeCell ref="F38:G38"/>
     <mergeCell ref="C32:D32"/>
@@ -40590,30 +40542,6 @@
     <mergeCell ref="F34:G34"/>
     <mergeCell ref="C36:D36"/>
     <mergeCell ref="F36:G36"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="F9:G9"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="F19:G19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="F21:G21"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="F25:G25"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="F27:G27"/>
-    <mergeCell ref="C30:D30"/>
-    <mergeCell ref="F30:G30"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>

--- a/ADSK.xlsx
+++ b/ADSK.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10927"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11004"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CA66BC9-D0B0-0B42-97A4-FF6D27B9CC4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F788D65B-0B22-4046-96BF-AFC3EC9BD705}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" activeTab="2" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>
@@ -2416,14 +2416,14 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -15142,13 +15142,13 @@
     <v>268435456</v>
     <v>1</v>
     <v>Powered by Refinitiv</v>
-    <v>326.2</v>
+    <v>320</v>
     <v>185.5</v>
-    <v>1.3087</v>
-    <v>9.56</v>
-    <v>4.5094000000000002E-2</v>
-    <v>0.24</v>
-    <v>1.083E-3</v>
+    <v>1.3194999999999999</v>
+    <v>1.75</v>
+    <v>7.4910000000000003E-3</v>
+    <v>-0.61</v>
+    <v>-2.5919999999999997E-3</v>
     <v>USD</v>
     <v>Autodesk, Inc. is engaged in three-dimensional (3D) design, engineering and entertainment technology solutions, spanning architecture, engineering, construction, product design, manufacturing, media and entertainment. Its architecture, engineering, construction and operations products improve the way building, infrastructure, and industrial projects are designed, built, and operated. Its product development and manufacturing software provides manufacturers in the automotive, transportation, industrial machinery, consumer products, and building product industries with comprehensive digital design, engineering, manufacturing, and production solutions. Its product offerings include AutoCAD Civil 3D, Autodesk Build, BIM Collaborate Pro, Building Connected, Revit, Tandem, AutoCAD, AutoCAD LT, Inventor, Vault, Maya, 3ds Max, Flow Production Tracking, among others. AutoCAD Civil 3D solution offers surveying, design, analysis, and documentation solution.</v>
     <v>14300</v>
@@ -15156,25 +15156,25 @@
     <v>XNAS</v>
     <v>XNAS</v>
     <v>One Market, Ste. 400., SAN FRANCISCO, CA, 94105 US</v>
-    <v>226.93</v>
+    <v>238.59</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46300.890108888285</v>
+    <v>46304.999692557809</v>
     <v>0</v>
-    <v>218.21</v>
-    <v>46306040000</v>
+    <v>233.52</v>
+    <v>49188150000</v>
     <v>AUTODESK, INC.</v>
     <v>AUTODESK, INC.</v>
-    <v>219.23</v>
-    <v>27.4864</v>
-    <v>212</v>
-    <v>221.56</v>
-    <v>221.8</v>
+    <v>235.5</v>
+    <v>30.286899999999999</v>
+    <v>233.6</v>
+    <v>235.35</v>
+    <v>234.74</v>
     <v>209000000</v>
     <v>ADSK</v>
     <v>AUTODESK, INC. (XNAS:ADSK)</v>
-    <v>3212083</v>
-    <v>2286438</v>
+    <v>1777405</v>
+    <v>2340149</v>
     <v>1994</v>
   </rv>
   <rv s="2">
@@ -15196,19 +15196,19 @@
     <v>268435456</v>
     <v>1</v>
     <v>Powered by Refinitiv</v>
-    <v>53.42</v>
+    <v>53.64</v>
     <v>39.47</v>
-    <v>0.4</v>
-    <v>7.6380000000000007E-3</v>
+    <v>0.13</v>
+    <v>2.4849999999999998E-3</v>
     <v>US</v>
-    <v>52.98</v>
+    <v>52.8</v>
     <v>Index</v>
     <v>3</v>
-    <v>51.57</v>
+    <v>52.34</v>
     <v>10 Y TSY YLD NDX</v>
-    <v>52.16</v>
-    <v>52.37</v>
-    <v>52.77</v>
+    <v>52.36</v>
+    <v>52.31</v>
+    <v>52.44</v>
     <v>TNX</v>
     <v>10 Y TSY YLD NDX</v>
   </rv>
@@ -15430,9 +15430,9 @@
       <v>at close</v>
       <v>from previous close</v>
       <v>from previous close</v>
-      <v>Source: Nasdaq Last Sale</v>
+      <v>Source: Nasdaq</v>
       <v>GMT</v>
-      <v>Real-Time Nasdaq Last Sale</v>
+      <v>Delayed 15 minutes</v>
       <v>from close</v>
       <v>from close</v>
     </spb>
@@ -16029,7 +16029,7 @@
       </c>
       <c r="F3" s="185">
         <f ca="1">Statement!AC154</f>
-        <v>46527.6</v>
+        <v>49423.5</v>
       </c>
       <c r="H3" s="183" t="str">
         <f>'AVG target price'!B5</f>
@@ -16037,7 +16037,7 @@
       </c>
       <c r="I3" s="209">
         <f ca="1">'AVG target price'!C5</f>
-        <v>117.94549730051374</v>
+        <v>117.40628980771197</v>
       </c>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.2">
@@ -16053,7 +16053,7 @@
       </c>
       <c r="F4" s="186">
         <f ca="1">Statement!AC155</f>
-        <v>45648.6</v>
+        <v>48544.5</v>
       </c>
       <c r="H4" s="183" t="str">
         <f>'AVG target price'!B6</f>
@@ -16061,7 +16061,7 @@
       </c>
       <c r="I4" s="209">
         <f ca="1">'AVG target price'!C6</f>
-        <v>347.05184206395262</v>
+        <v>346.47563818543853</v>
       </c>
     </row>
     <row r="5" spans="2:9" x14ac:dyDescent="0.2">
@@ -16070,7 +16070,7 @@
       </c>
       <c r="C5" s="206" cm="1">
         <f t="array" aca="1" ref="C5" ca="1">_FV(C3,"Price",TRUE)</f>
-        <v>221.56</v>
+        <v>235.35</v>
       </c>
       <c r="E5" s="183" t="s">
         <v>242</v>
@@ -16085,7 +16085,7 @@
       </c>
       <c r="I5" s="209">
         <f ca="1">'AVG target price'!C7</f>
-        <v>188.3934512292424</v>
+        <v>188.26132013643894</v>
       </c>
     </row>
     <row r="6" spans="2:9" x14ac:dyDescent="0.2">
@@ -16094,14 +16094,14 @@
       </c>
       <c r="C6" s="206" cm="1">
         <f t="array" aca="1" ref="C6" ca="1">_FV(C3,"Price (Extended hours)",TRUE)</f>
-        <v>221.8</v>
+        <v>234.74</v>
       </c>
       <c r="E6" s="183" t="s">
         <v>236</v>
       </c>
       <c r="F6" s="188">
         <f ca="1">Statement!AC151</f>
-        <v>28.662354463130658</v>
+        <v>30.44631306597671</v>
       </c>
       <c r="H6" s="183" t="str">
         <f>'AVG target price'!B8</f>
@@ -16109,7 +16109,7 @@
       </c>
       <c r="I6" s="209">
         <f ca="1">'AVG target price'!C8</f>
-        <v>345.51162031984416</v>
+        <v>344.93810808304579</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -16118,14 +16118,14 @@
       </c>
       <c r="C7" s="6" cm="1">
         <f t="array" aca="1" ref="C7" ca="1">_FV(C3,"Change")</f>
-        <v>9.56</v>
+        <v>1.75</v>
       </c>
       <c r="E7" s="184" t="s">
         <v>200</v>
       </c>
       <c r="F7" s="189">
         <f ca="1">Statement!AC152</f>
-        <v>6.0580590500641858</v>
+        <v>6.4351155327342751</v>
       </c>
       <c r="H7" s="183" t="str">
         <f>'AVG target price'!B9</f>
@@ -16133,7 +16133,7 @@
       </c>
       <c r="I7" s="209">
         <f ca="1">'AVG target price'!C9</f>
-        <v>220.05252078330085</v>
+        <v>219.69825681203739</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
@@ -16142,14 +16142,14 @@
       </c>
       <c r="C8" s="6" cm="1">
         <f t="array" aca="1" ref="C8" ca="1">_FV(C3,"Change (extended hours)",TRUE)</f>
-        <v>0.24</v>
+        <v>-0.61</v>
       </c>
       <c r="E8" s="183" t="s">
         <v>264</v>
       </c>
       <c r="F8" s="190">
         <f ca="1">Statement!AC162</f>
-        <v>4.5091515573552045E-2</v>
+        <v>4.244944206703289E-2</v>
       </c>
       <c r="H8" s="182" t="str">
         <f>'AVG target price'!B10</f>
@@ -16157,7 +16157,7 @@
       </c>
       <c r="I8" s="210">
         <f ca="1">'AVG target price'!C10</f>
-        <v>243.79098633937073</v>
+        <v>243.35592260493453</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -16166,14 +16166,14 @@
       </c>
       <c r="C9" s="73" cm="1">
         <f t="array" aca="1" ref="C9" ca="1">_FV(C3,"Change (%)",TRUE)</f>
-        <v>4.5094000000000002E-2</v>
+        <v>7.4910000000000003E-3</v>
       </c>
       <c r="E9" s="183" t="s">
         <v>287</v>
       </c>
       <c r="F9" s="190">
         <f ca="1">Statement!AC163</f>
-        <v>3.4888969128001449E-2</v>
+        <v>3.2844699383896329E-2</v>
       </c>
       <c r="H9" s="182" t="str">
         <f>'AVG target price'!B12</f>
@@ -16181,7 +16181,7 @@
       </c>
       <c r="I9" s="211">
         <f ca="1">'AVG target price'!C12</f>
-        <v>0.10033844709952487</v>
+        <v>3.4017092011619038E-2</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -16190,14 +16190,14 @@
       </c>
       <c r="C10" s="73" cm="1">
         <f t="array" aca="1" ref="C10" ca="1">_FV(C3,"Change % (extended hours)",TRUE)</f>
-        <v>1.083E-3</v>
+        <v>-2.5919999999999997E-3</v>
       </c>
       <c r="E10" s="183" t="s">
         <v>292</v>
       </c>
       <c r="F10" s="190">
         <f ca="1">Statement!AC165</f>
-        <v>3.4194757520267544E-2</v>
+        <v>3.2191164122330473E-2</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -16206,7 +16206,7 @@
       </c>
       <c r="C11" s="207" cm="1">
         <f t="array" aca="1" ref="C11" ca="1">_FV(C3,"52 week high",TRUE)</f>
-        <v>326.2</v>
+        <v>320</v>
       </c>
       <c r="E11" s="184" t="s">
         <v>288</v>
@@ -16245,7 +16245,7 @@
       </c>
       <c r="C13" s="207" cm="1">
         <f t="array" aca="1" ref="C13" ca="1">_FV(C3,"Beta")</f>
-        <v>1.3087</v>
+        <v>1.3194999999999999</v>
       </c>
       <c r="E13" s="183" t="s">
         <v>103</v>
@@ -16268,7 +16268,7 @@
       </c>
       <c r="C14" s="208" cm="1">
         <f t="array" aca="1" ref="C14" ca="1">_FV(C3,"Volume average",TRUE)</f>
-        <v>2286438</v>
+        <v>2340149</v>
       </c>
       <c r="E14" s="184" t="s">
         <v>104</v>
@@ -16284,7 +16284,7 @@
       </c>
       <c r="F15" s="190">
         <f ca="1">Statement!AC177</f>
-        <v>1.8892012482913369E-2</v>
+        <v>1.7785061762117211E-2</v>
       </c>
     </row>
     <row r="16" spans="2:9" x14ac:dyDescent="0.2">
@@ -16394,7 +16394,7 @@
       </c>
       <c r="F26" s="217" cm="1">
         <f t="array" aca="1" ref="F26" ca="1">_FV(E26,"Price")</f>
-        <v>52.77</v>
+        <v>52.44</v>
       </c>
     </row>
     <row r="27" spans="2:9" x14ac:dyDescent="0.2">
@@ -16409,7 +16409,7 @@
       </c>
       <c r="F27" s="218">
         <f ca="1">F26/1000</f>
-        <v>5.2770000000000004E-2</v>
+        <v>5.2440000000000001E-2</v>
       </c>
     </row>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
@@ -22109,6 +22109,12 @@
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="H3:L3"/>
+    <mergeCell ref="P3:W3"/>
+    <mergeCell ref="X3:Z3"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="P5:Z5"/>
     <mergeCell ref="C40:L40"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="P11:Z11"/>
@@ -22116,12 +22122,6 @@
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="C26:L26"/>
     <mergeCell ref="C33:L33"/>
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="H3:L3"/>
-    <mergeCell ref="P3:W3"/>
-    <mergeCell ref="X3:Z3"/>
-    <mergeCell ref="C5:L5"/>
-    <mergeCell ref="P5:Z5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -23181,16 +23181,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="AA2:AC2"/>
+    <mergeCell ref="C4:L4"/>
+    <mergeCell ref="S4:AC4"/>
+    <mergeCell ref="C13:L13"/>
+    <mergeCell ref="C18:L18"/>
     <mergeCell ref="C31:L31"/>
     <mergeCell ref="C25:L25"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="H2:L2"/>
     <mergeCell ref="S2:Z2"/>
-    <mergeCell ref="AA2:AC2"/>
-    <mergeCell ref="C4:L4"/>
-    <mergeCell ref="S4:AC4"/>
-    <mergeCell ref="C13:L13"/>
-    <mergeCell ref="C18:L18"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -23273,7 +23273,7 @@
       </c>
       <c r="C6" s="135">
         <f ca="1">Overview!C5</f>
-        <v>221.56</v>
+        <v>235.35</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -23282,7 +23282,7 @@
       </c>
       <c r="C7" s="136">
         <f ca="1">C5*C6</f>
-        <v>46527.6</v>
+        <v>49423.5</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -23300,7 +23300,7 @@
       </c>
       <c r="C9" s="137">
         <f ca="1">Overview!F27</f>
-        <v>5.2770000000000004E-2</v>
+        <v>5.2440000000000001E-2</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -23309,7 +23309,7 @@
       </c>
       <c r="C10" s="135">
         <f ca="1">Overview!C13</f>
-        <v>1.3087</v>
+        <v>1.3194999999999999</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -23352,7 +23352,7 @@
       </c>
       <c r="C16" s="46">
         <f ca="1">C8/(C8+C7)</f>
-        <v>6.955221015246292E-2</v>
+        <v>6.5744827651389851E-2</v>
       </c>
     </row>
     <row r="17" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -23361,7 +23361,7 @@
       </c>
       <c r="C17" s="46">
         <f ca="1">C7/(C8+C7)</f>
-        <v>0.93044778984753707</v>
+        <v>0.93425517234861011</v>
       </c>
     </row>
     <row r="18" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -23379,7 +23379,7 @@
       </c>
       <c r="C19" s="46">
         <f ca="1">C9+C10*C11</f>
-        <v>0.1116615</v>
+        <v>0.11181749999999999</v>
       </c>
     </row>
     <row r="20" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -23388,7 +23388,7 @@
       </c>
       <c r="C20" s="46">
         <f ca="1">(C17*C19)+(C16*C18)</f>
-        <v>0.10724691689330795</v>
+        <v>0.10763432097861117</v>
       </c>
     </row>
   </sheetData>
@@ -23639,7 +23639,7 @@
       </c>
       <c r="L8" s="128">
         <f ca="1">L7*(1+C14)/(C15-C14)</f>
-        <v>28778.973504620913</v>
+        <v>28651.750610873107</v>
       </c>
       <c r="N8" s="91"/>
       <c r="O8" s="16"/>
@@ -23693,23 +23693,23 @@
       <c r="G10" s="140"/>
       <c r="H10" s="128">
         <f ca="1">H7/(1+$C$15)^H9</f>
-        <v>1861.2976133995592</v>
+        <v>1860.6466094664568</v>
       </c>
       <c r="I10" s="128">
         <f t="shared" ref="I10:L10" ca="1" si="0">I7/(1+$C$15)^I9</f>
-        <v>1269.4007229464412</v>
+        <v>1268.5129118409311</v>
       </c>
       <c r="J10" s="128">
         <f t="shared" ca="1" si="0"/>
-        <v>569.3156433333728</v>
+        <v>568.71848395531697</v>
       </c>
       <c r="K10" s="128">
         <f t="shared" ca="1" si="0"/>
-        <v>1418.1169093360447</v>
+        <v>1416.1339584162217</v>
       </c>
       <c r="L10" s="128">
         <f t="shared" ca="1" si="0"/>
-        <v>1479.1179861811524</v>
+        <v>1476.5331274169041</v>
       </c>
       <c r="N10" s="91"/>
     </row>
@@ -23728,7 +23728,7 @@
       <c r="K11" s="139"/>
       <c r="L11" s="128">
         <f ca="1">L8/(1+C15)^L9</f>
-        <v>17292.305557911313</v>
+        <v>17185.775768523683</v>
       </c>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.2">
@@ -23751,7 +23751,7 @@
       </c>
       <c r="C15" s="137">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.10724691689330795</v>
+        <v>0.10763432097861117</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.2">
@@ -23766,7 +23766,7 @@
       </c>
       <c r="C19" s="64">
         <f ca="1">SUM(H10:L10)</f>
-        <v>6597.2488751965702</v>
+        <v>6590.5450910958307</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.2">
@@ -23775,7 +23775,7 @@
       </c>
       <c r="C20" s="64">
         <f ca="1">L11</f>
-        <v>17292.305557911313</v>
+        <v>17185.775768523683</v>
       </c>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.2">
@@ -23784,7 +23784,7 @@
       </c>
       <c r="C21" s="94">
         <f ca="1">C19+C20</f>
-        <v>23889.554433107885</v>
+        <v>23776.320859619515</v>
       </c>
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.2">
@@ -23811,7 +23811,7 @@
       </c>
       <c r="C24" s="94">
         <f ca="1">C21+C22-C23</f>
-        <v>24768.554433107885</v>
+        <v>24655.320859619515</v>
       </c>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.2">
@@ -23829,7 +23829,7 @@
       </c>
       <c r="C26" s="234">
         <f ca="1">C24/C25</f>
-        <v>117.94549730051374</v>
+        <v>117.40628980771197</v>
       </c>
     </row>
   </sheetData>
@@ -24098,23 +24098,23 @@
       <c r="G9" s="140"/>
       <c r="H9" s="92">
         <f ca="1">DCF!H10</f>
-        <v>1861.2976133995592</v>
+        <v>1860.6466094664568</v>
       </c>
       <c r="I9" s="92">
         <f ca="1">DCF!I10</f>
-        <v>1269.4007229464412</v>
+        <v>1268.5129118409311</v>
       </c>
       <c r="J9" s="92">
         <f ca="1">DCF!J10</f>
-        <v>569.3156433333728</v>
+        <v>568.71848395531697</v>
       </c>
       <c r="K9" s="92">
         <f ca="1">DCF!K10</f>
-        <v>1418.1169093360447</v>
+        <v>1416.1339584162217</v>
       </c>
       <c r="L9" s="92">
         <f ca="1">DCF!L10</f>
-        <v>1479.1179861811524</v>
+        <v>1476.5331274169041</v>
       </c>
       <c r="N9" s="91"/>
     </row>
@@ -24900,7 +24900,7 @@
       </c>
       <c r="C41" s="137">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.10724691689330795</v>
+        <v>0.10763432097861117</v>
       </c>
     </row>
     <row r="42" spans="2:14" x14ac:dyDescent="0.2">
@@ -24926,7 +24926,7 @@
       </c>
       <c r="C44" s="24">
         <f ca="1">C43/(1+C41)^5</f>
-        <v>66883.755944414632</v>
+        <v>66766.872055263157</v>
       </c>
     </row>
     <row r="45" spans="2:14" x14ac:dyDescent="0.2">
@@ -24935,7 +24935,7 @@
       </c>
       <c r="C45" s="108">
         <f ca="1">SUM(H9:K9)+C44</f>
-        <v>72001.88683343005</v>
+        <v>71880.884018942088</v>
       </c>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.2">
@@ -24962,7 +24962,7 @@
       </c>
       <c r="C48" s="108">
         <f ca="1">C45+C46-C47</f>
-        <v>72880.88683343005</v>
+        <v>72759.884018942088</v>
       </c>
     </row>
     <row r="49" spans="2:3" x14ac:dyDescent="0.2">
@@ -24980,7 +24980,7 @@
       </c>
       <c r="C50" s="234">
         <f ca="1">C48/C49</f>
-        <v>347.05184206395262</v>
+        <v>346.47563818543853</v>
       </c>
     </row>
     <row r="52" spans="2:3" x14ac:dyDescent="0.2">
@@ -25004,7 +25004,7 @@
       </c>
       <c r="C54" s="137">
         <f ca="1">IF(Overview!C29&gt;0,Overview!C29,WACC!C19)</f>
-        <v>0.1116615</v>
+        <v>0.11181749999999999</v>
       </c>
     </row>
     <row r="55" spans="2:3" x14ac:dyDescent="0.2">
@@ -25039,7 +25039,7 @@
       </c>
       <c r="C58" s="234">
         <f ca="1">C57/(1+C54)^5</f>
-        <v>188.3934512292424</v>
+        <v>188.26132013643894</v>
       </c>
     </row>
     <row r="60" spans="2:3" x14ac:dyDescent="0.2">
@@ -25063,7 +25063,7 @@
       </c>
       <c r="C62" s="137">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.10724691689330795</v>
+        <v>0.10763432097861117</v>
       </c>
     </row>
     <row r="63" spans="2:3" x14ac:dyDescent="0.2">
@@ -25089,7 +25089,7 @@
       </c>
       <c r="C65" s="24">
         <f ca="1">C64/(1+C62)^5</f>
-        <v>66560.309378151855</v>
+        <v>66443.990733760686</v>
       </c>
     </row>
     <row r="66" spans="2:3" x14ac:dyDescent="0.2">
@@ -25098,7 +25098,7 @@
       </c>
       <c r="C66" s="108">
         <f ca="1">SUM(H9:K9)+C65</f>
-        <v>71678.440267167272</v>
+        <v>71558.002697439617</v>
       </c>
     </row>
     <row r="67" spans="2:3" x14ac:dyDescent="0.2">
@@ -25125,7 +25125,7 @@
       </c>
       <c r="C69" s="108">
         <f ca="1">C66+C67-C68</f>
-        <v>72557.440267167272</v>
+        <v>72437.002697439617</v>
       </c>
     </row>
     <row r="70" spans="2:3" x14ac:dyDescent="0.2">
@@ -25143,7 +25143,7 @@
       </c>
       <c r="C71" s="234">
         <f ca="1">C69/C70</f>
-        <v>345.51162031984416</v>
+        <v>344.93810808304579</v>
       </c>
     </row>
     <row r="73" spans="2:3" x14ac:dyDescent="0.2">
@@ -25167,7 +25167,7 @@
       </c>
       <c r="C75" s="137">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.10724691689330795</v>
+        <v>0.10763432097861117</v>
       </c>
     </row>
     <row r="76" spans="2:3" x14ac:dyDescent="0.2">
@@ -25193,7 +25193,7 @@
       </c>
       <c r="C78" s="24">
         <f ca="1">C77/(1+C75)^5</f>
-        <v>40213.898475477763</v>
+        <v>40143.621966848928</v>
       </c>
     </row>
     <row r="79" spans="2:3" x14ac:dyDescent="0.2">
@@ -25202,7 +25202,7 @@
       </c>
       <c r="C79" s="108">
         <f ca="1">SUM(H9:K9)+C78</f>
-        <v>45332.029364493181</v>
+        <v>45257.633930527852</v>
       </c>
     </row>
     <row r="80" spans="2:3" x14ac:dyDescent="0.2">
@@ -25229,7 +25229,7 @@
       </c>
       <c r="C82" s="108">
         <f ca="1">C79+C80-C81</f>
-        <v>46211.029364493181</v>
+        <v>46136.633930527852</v>
       </c>
     </row>
     <row r="83" spans="2:3" x14ac:dyDescent="0.2">
@@ -25247,22 +25247,22 @@
       </c>
       <c r="C84" s="234">
         <f ca="1">C82/C83</f>
-        <v>220.05252078330085</v>
+        <v>219.69825681203739</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="B73:C73"/>
-    <mergeCell ref="C27:L27"/>
-    <mergeCell ref="B39:C39"/>
-    <mergeCell ref="B52:C52"/>
-    <mergeCell ref="B60:C60"/>
     <mergeCell ref="C22:L22"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="H2:L2"/>
     <mergeCell ref="C4:L4"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="C17:L17"/>
+    <mergeCell ref="B73:C73"/>
+    <mergeCell ref="C27:L27"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="B60:C60"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -25312,7 +25312,7 @@
       </c>
       <c r="C5" s="135">
         <f ca="1">DCF!C26</f>
-        <v>117.94549730051374</v>
+        <v>117.40628980771197</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.2">
@@ -25321,7 +25321,7 @@
       </c>
       <c r="C6" s="135">
         <f ca="1">Multiples!C50</f>
-        <v>347.05184206395262</v>
+        <v>346.47563818543853</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.2">
@@ -25330,7 +25330,7 @@
       </c>
       <c r="C7" s="135">
         <f ca="1">Multiples!C58</f>
-        <v>188.3934512292424</v>
+        <v>188.26132013643894</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.2">
@@ -25339,7 +25339,7 @@
       </c>
       <c r="C8" s="135">
         <f ca="1">Multiples!C71</f>
-        <v>345.51162031984416</v>
+        <v>344.93810808304579</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
@@ -25348,7 +25348,7 @@
       </c>
       <c r="C9" s="135">
         <f ca="1">Multiples!C84</f>
-        <v>220.05252078330085</v>
+        <v>219.69825681203739</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
@@ -25357,7 +25357,7 @@
       </c>
       <c r="C10" s="234">
         <f ca="1">AVERAGE(C5:C9)</f>
-        <v>243.79098633937073</v>
+        <v>243.35592260493453</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -25366,7 +25366,7 @@
       </c>
       <c r="C11" s="135">
         <f ca="1">Overview!C5</f>
-        <v>221.56</v>
+        <v>235.35</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.2">
@@ -25375,7 +25375,7 @@
       </c>
       <c r="C12" s="154">
         <f ca="1">(C10-C11)/C11</f>
-        <v>0.10033844709952487</v>
+        <v>3.4017092011619038E-2</v>
       </c>
     </row>
   </sheetData>
@@ -25845,7 +25845,7 @@
       </c>
       <c r="C24" s="137">
         <f ca="1">IF(Overview!C29&gt;0,Overview!C29,WACC!C19)</f>
-        <v>0.1116615</v>
+        <v>0.11181749999999999</v>
       </c>
     </row>
     <row r="25" spans="2:14" x14ac:dyDescent="0.2">
@@ -26099,7 +26099,7 @@
       <c r="K8" s="139"/>
       <c r="L8" s="128">
         <f ca="1">L7*(1+C20)/(C21-C20)</f>
-        <v>57155.605917528395</v>
+        <v>56902.938754901152</v>
       </c>
       <c r="N8" s="91"/>
       <c r="O8" s="16"/>
@@ -26153,23 +26153,23 @@
       <c r="G10" s="140"/>
       <c r="H10" s="128">
         <f ca="1">H7/(1+$C$21)^H9</f>
-        <v>958.54779364448223</v>
+        <v>958.21253378102085</v>
       </c>
       <c r="I10" s="128">
         <f t="shared" ref="I10:L10" ca="1" si="1">I7/(1+$C$21)^I9</f>
-        <v>1268.255974583562</v>
+        <v>1267.3689641080587</v>
       </c>
       <c r="J10" s="128">
         <f t="shared" ca="1" si="1"/>
-        <v>1678.0313175114049</v>
+        <v>1676.2712180838603</v>
       </c>
       <c r="K10" s="128">
         <f t="shared" ca="1" si="1"/>
-        <v>2220.2056674510354</v>
+        <v>2217.1011569262091</v>
       </c>
       <c r="L10" s="128">
         <f t="shared" ca="1" si="1"/>
-        <v>2937.5573353971072</v>
+        <v>2932.4237551859114</v>
       </c>
       <c r="N10" s="91"/>
     </row>
@@ -26188,15 +26188,15 @@
       <c r="K11" s="139"/>
       <c r="L11" s="128">
         <f ca="1">L8/(1+C21)^L9</f>
-        <v>34342.858049289687</v>
+        <v>34131.287797844161</v>
       </c>
     </row>
     <row r="13" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B14" s="250" t="s">
+      <c r="B14" s="251" t="s">
         <v>221</v>
       </c>
-      <c r="C14" s="251"/>
+      <c r="C14" s="252"/>
     </row>
     <row r="15" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B15" s="155" t="s">
@@ -26204,7 +26204,7 @@
       </c>
       <c r="C15" s="156">
         <f ca="1">Overview!C5</f>
-        <v>221.56</v>
+        <v>235.35</v>
       </c>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.2">
@@ -26213,7 +26213,7 @@
       </c>
       <c r="C16" s="156">
         <f ca="1">C36</f>
-        <v>211.88734994199655</v>
+        <v>210.82136567430248</v>
       </c>
     </row>
     <row r="17" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -26223,20 +26223,20 @@
       <c r="C17" s="158">
         <v>0.46500000000000002</v>
       </c>
-      <c r="E17" s="252" t="s">
+      <c r="E17" s="250" t="s">
         <v>224</v>
       </c>
-      <c r="F17" s="252"/>
-      <c r="G17" s="252"/>
-      <c r="H17" s="252"/>
-      <c r="I17" s="252"/>
+      <c r="F17" s="250"/>
+      <c r="G17" s="250"/>
+      <c r="H17" s="250"/>
+      <c r="I17" s="250"/>
     </row>
     <row r="18" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="19" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B19" s="250" t="s">
+      <c r="B19" s="251" t="s">
         <v>183</v>
       </c>
-      <c r="C19" s="251"/>
+      <c r="C19" s="252"/>
     </row>
     <row r="20" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B20" s="159" t="s">
@@ -26252,7 +26252,7 @@
       </c>
       <c r="C21" s="220">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.10724691689330795</v>
+        <v>0.10763432097861117</v>
       </c>
     </row>
     <row r="22" spans="2:9" x14ac:dyDescent="0.2">
@@ -26270,7 +26270,7 @@
       </c>
       <c r="C23" s="161">
         <f ca="1">C15*C22</f>
-        <v>46306.04</v>
+        <v>49188.15</v>
       </c>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.2">
@@ -26297,15 +26297,15 @@
       </c>
       <c r="C26" s="162">
         <f ca="1">C23+C25-C24</f>
-        <v>45427.040000000001</v>
+        <v>48309.15</v>
       </c>
     </row>
     <row r="27" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B28" s="250" t="s">
+      <c r="B28" s="251" t="s">
         <v>185</v>
       </c>
-      <c r="C28" s="251"/>
+      <c r="C28" s="252"/>
     </row>
     <row r="29" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B29" s="159" t="s">
@@ -26313,7 +26313,7 @@
       </c>
       <c r="C29" s="161">
         <f ca="1">SUM(H10:L10)</f>
-        <v>9062.5980885875906</v>
+        <v>9051.3776280850598</v>
       </c>
     </row>
     <row r="30" spans="2:9" x14ac:dyDescent="0.2">
@@ -26322,7 +26322,7 @@
       </c>
       <c r="C30" s="161">
         <f ca="1">L11</f>
-        <v>34342.858049289687</v>
+        <v>34131.287797844161</v>
       </c>
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.2">
@@ -26331,7 +26331,7 @@
       </c>
       <c r="C31" s="164">
         <f ca="1">C29+C30</f>
-        <v>43405.456137877278</v>
+        <v>43182.665425929219</v>
       </c>
     </row>
     <row r="32" spans="2:9" x14ac:dyDescent="0.2">
@@ -26358,7 +26358,7 @@
       </c>
       <c r="C34" s="164">
         <f ca="1">C31+C32-C33</f>
-        <v>44284.456137877278</v>
+        <v>44061.665425929219</v>
       </c>
     </row>
     <row r="35" spans="2:3" x14ac:dyDescent="0.2">
@@ -26376,21 +26376,21 @@
       </c>
       <c r="C36" s="167">
         <f ca="1">C34/C35</f>
-        <v>211.88734994199655</v>
+        <v>210.82136567430248</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="P3:W3"/>
+    <mergeCell ref="X3:Z3"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="P5:Z5"/>
+    <mergeCell ref="B14:C14"/>
     <mergeCell ref="E17:I17"/>
     <mergeCell ref="B19:C19"/>
     <mergeCell ref="B28:C28"/>
     <mergeCell ref="C3:G3"/>
     <mergeCell ref="H3:L3"/>
-    <mergeCell ref="P3:W3"/>
-    <mergeCell ref="X3:Z3"/>
-    <mergeCell ref="C5:L5"/>
-    <mergeCell ref="P5:Z5"/>
-    <mergeCell ref="B14:C14"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -33046,7 +33046,7 @@
       </c>
       <c r="AC117" s="63">
         <f ca="1">Overview!C5</f>
-        <v>221.56</v>
+        <v>235.35</v>
       </c>
     </row>
     <row r="118" spans="1:31" x14ac:dyDescent="0.2">
@@ -33117,7 +33117,7 @@
       </c>
       <c r="AC118" s="65">
         <f ca="1">AC117/AC86</f>
-        <v>221.56</v>
+        <v>235.35</v>
       </c>
     </row>
     <row r="120" spans="1:31" x14ac:dyDescent="0.2">
@@ -34423,7 +34423,7 @@
       <c r="AA151" s="49"/>
       <c r="AC151" s="72">
         <f ca="1">AC118/Statement!AC27</f>
-        <v>28.662354463130658</v>
+        <v>30.44631306597671</v>
       </c>
     </row>
     <row r="152" spans="2:29" x14ac:dyDescent="0.2">
@@ -34460,7 +34460,7 @@
       <c r="AA152" s="49"/>
       <c r="AC152" s="72">
         <f ca="1">AC118/(Statement!AC5/Statement!AC23)</f>
-        <v>6.0580590500641858</v>
+        <v>6.4351155327342751</v>
       </c>
     </row>
     <row r="153" spans="2:29" x14ac:dyDescent="0.2">
@@ -34521,7 +34521,7 @@
       </c>
       <c r="AC153" s="72">
         <f ca="1">AC118/(Statement!AC50/Statement!AC76)</f>
-        <v>13.687862843629913</v>
+        <v>14.539801950931125</v>
       </c>
     </row>
     <row r="154" spans="2:29" x14ac:dyDescent="0.2">
@@ -34582,7 +34582,7 @@
       </c>
       <c r="AC154" s="143">
         <f ca="1">Statement!AC118*Statement!AC79</f>
-        <v>46527.6</v>
+        <v>49423.5</v>
       </c>
     </row>
     <row r="155" spans="2:29" x14ac:dyDescent="0.2">
@@ -34643,7 +34643,7 @@
       </c>
       <c r="AC155" s="143">
         <f ca="1">AC154+AC109-AC108+AC49+AC46</f>
-        <v>45648.6</v>
+        <v>48544.5</v>
       </c>
     </row>
     <row r="156" spans="2:29" x14ac:dyDescent="0.2">
@@ -34680,7 +34680,7 @@
       <c r="AA156" s="49"/>
       <c r="AC156" s="181">
         <f ca="1">AC155/AC5</f>
-        <v>5.8598973042361999</v>
+        <v>6.2316431322207961</v>
       </c>
     </row>
     <row r="157" spans="2:29" x14ac:dyDescent="0.2">
@@ -34717,7 +34717,7 @@
       <c r="AA157" s="49"/>
       <c r="AC157" s="181">
         <f ca="1">AC155/AC13</f>
-        <v>22.365801077902987</v>
+        <v>23.784664380205783</v>
       </c>
     </row>
     <row r="158" spans="2:29" x14ac:dyDescent="0.2">
@@ -34852,7 +34852,7 @@
       <c r="AA160" s="49"/>
       <c r="AC160" s="72">
         <f t="shared" ref="AC160:AC161" ca="1" si="155">AC154/AC158</f>
-        <v>22.177121067683508</v>
+        <v>23.557435653002859</v>
       </c>
     </row>
     <row r="161" spans="2:29" x14ac:dyDescent="0.2">
@@ -34889,7 +34889,7 @@
       <c r="AA161" s="49"/>
       <c r="AC161" s="72">
         <f t="shared" ca="1" si="155"/>
-        <v>37.537591382593135</v>
+        <v>39.918937379728895</v>
       </c>
     </row>
     <row r="162" spans="2:29" x14ac:dyDescent="0.2">
@@ -34926,7 +34926,7 @@
       <c r="AA162" s="49"/>
       <c r="AC162" s="74">
         <f t="shared" ref="AC162" ca="1" si="158">AC158/AC154</f>
-        <v>4.5091515573552045E-2</v>
+        <v>4.244944206703289E-2</v>
       </c>
     </row>
     <row r="163" spans="2:29" x14ac:dyDescent="0.2">
@@ -34963,7 +34963,7 @@
       <c r="AA163" s="49"/>
       <c r="AC163" s="74">
         <f ca="1">AC27/AC118</f>
-        <v>3.4888969128001449E-2</v>
+        <v>3.2844699383896329E-2</v>
       </c>
     </row>
     <row r="164" spans="2:29" x14ac:dyDescent="0.2">
@@ -35037,7 +35037,7 @@
       <c r="AA165" s="49"/>
       <c r="AC165" s="154">
         <f ca="1">-AC64/AC154</f>
-        <v>3.4194757520267544E-2</v>
+        <v>3.2191164122330473E-2</v>
       </c>
     </row>
     <row r="166" spans="2:29" x14ac:dyDescent="0.2">
@@ -35074,7 +35074,7 @@
       <c r="AA166" s="49"/>
       <c r="AC166" s="154">
         <f ca="1">-(AC64+AC65)/AC154</f>
-        <v>3.4194757520267544E-2</v>
+        <v>3.2191164122330473E-2</v>
       </c>
     </row>
     <row r="167" spans="2:29" x14ac:dyDescent="0.2">
@@ -35577,7 +35577,7 @@
       <c r="AA177" s="49"/>
       <c r="AC177" s="154">
         <f ca="1">(AC108-AC109)/AC154</f>
-        <v>1.8892012482913369E-2</v>
+        <v>1.7785061762117211E-2</v>
       </c>
     </row>
     <row r="178" spans="1:31" x14ac:dyDescent="0.2">
@@ -37388,7 +37388,7 @@
       </c>
       <c r="C5" s="170">
         <f ca="1">Overview!C5</f>
-        <v>221.56</v>
+        <v>235.35</v>
       </c>
       <c r="E5" s="12"/>
       <c r="F5" s="134" t="s">
@@ -37404,7 +37404,7 @@
       </c>
       <c r="C6" s="171">
         <f ca="1">Statement!AC154</f>
-        <v>46527.6</v>
+        <v>49423.5</v>
       </c>
       <c r="E6" s="20" t="s">
         <v>19</v>
@@ -37424,7 +37424,7 @@
       </c>
       <c r="C7" s="171">
         <f ca="1">Statement!AC155</f>
-        <v>45648.6</v>
+        <v>48544.5</v>
       </c>
       <c r="E7" s="20" t="s">
         <v>31</v>
@@ -37444,7 +37444,7 @@
       </c>
       <c r="C8" s="172">
         <f ca="1">Statement!AC151</f>
-        <v>28.662354463130658</v>
+        <v>30.44631306597671</v>
       </c>
       <c r="E8" s="20" t="s">
         <v>242</v>
@@ -37464,7 +37464,7 @@
       </c>
       <c r="C9" s="172">
         <f ca="1">Statement!AC152</f>
-        <v>6.0580590500641858</v>
+        <v>6.4351155327342751</v>
       </c>
       <c r="E9" s="20" t="s">
         <v>243</v>
@@ -37484,7 +37484,7 @@
       </c>
       <c r="C10" s="172">
         <f ca="1">Statement!AC153</f>
-        <v>13.687862843629913</v>
+        <v>14.539801950931125</v>
       </c>
       <c r="E10" s="20" t="s">
         <v>1</v>
@@ -37504,7 +37504,7 @@
       </c>
       <c r="C11" s="172">
         <f ca="1">Statement!AC156</f>
-        <v>5.8598973042361999</v>
+        <v>6.2316431322207961</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
@@ -37513,7 +37513,7 @@
       </c>
       <c r="C12" s="172">
         <f ca="1">Statement!AC157</f>
-        <v>22.365801077902987</v>
+        <v>23.784664380205783</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.2">
@@ -37749,7 +37749,7 @@
       </c>
       <c r="C38" s="173">
         <f ca="1">Statement!AC163</f>
-        <v>3.4888969128001449E-2</v>
+        <v>3.2844699383896329E-2</v>
       </c>
       <c r="E38" s="20" t="s">
         <v>269</v>
@@ -37765,7 +37765,7 @@
       </c>
       <c r="C39" s="213">
         <f ca="1">Statement!AC162</f>
-        <v>4.5091515573552045E-2</v>
+        <v>4.244944206703289E-2</v>
       </c>
       <c r="E39" s="20" t="s">
         <v>271</v>
@@ -37797,7 +37797,7 @@
       </c>
       <c r="C41" s="173">
         <f ca="1">Statement!AC165</f>
-        <v>3.4194757520267544E-2</v>
+        <v>3.2191164122330473E-2</v>
       </c>
     </row>
     <row r="42" spans="2:6" x14ac:dyDescent="0.2">
@@ -37806,7 +37806,7 @@
       </c>
       <c r="C42" s="173">
         <f ca="1">Statement!AC166</f>
-        <v>3.4194757520267544E-2</v>
+        <v>3.2191164122330473E-2</v>
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.2">
@@ -37850,7 +37850,7 @@
       </c>
       <c r="F48" s="173">
         <f ca="1">Statement!AC177</f>
-        <v>1.8892012482913369E-2</v>
+        <v>1.7785061762117211E-2</v>
       </c>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.2">
@@ -38029,7 +38029,7 @@
       </c>
       <c r="I6" s="170">
         <f ca="1">Statement!AC117</f>
-        <v>221.56</v>
+        <v>235.35</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -38058,7 +38058,7 @@
       </c>
       <c r="I7" s="171">
         <f ca="1">Statement!AC154</f>
-        <v>46527.6</v>
+        <v>49423.5</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
@@ -38087,7 +38087,7 @@
       </c>
       <c r="I8" s="171">
         <f ca="1">Statement!AC155</f>
-        <v>45648.6</v>
+        <v>48544.5</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -38116,7 +38116,7 @@
       </c>
       <c r="I9" s="172">
         <f ca="1">Statement!AC151</f>
-        <v>28.662354463130658</v>
+        <v>30.44631306597671</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -38145,7 +38145,7 @@
       </c>
       <c r="I10" s="172">
         <f ca="1">Statement!AC152</f>
-        <v>6.0580590500641858</v>
+        <v>6.4351155327342751</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -38174,7 +38174,7 @@
       </c>
       <c r="I11" s="172">
         <f ca="1">Statement!AC153</f>
-        <v>13.687862843629913</v>
+        <v>14.539801950931125</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
@@ -38203,7 +38203,7 @@
       </c>
       <c r="I12" s="172">
         <f ca="1">Statement!AC156</f>
-        <v>5.8598973042361999</v>
+        <v>6.2316431322207961</v>
       </c>
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.2">
@@ -38232,7 +38232,7 @@
       </c>
       <c r="I13" s="172">
         <f ca="1">Statement!AC157</f>
-        <v>22.365801077902987</v>
+        <v>23.784664380205783</v>
       </c>
     </row>
     <row r="15" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -39005,7 +39005,7 @@
       </c>
       <c r="I51" s="173">
         <f ca="1">Statement!AC163</f>
-        <v>3.4888969128001449E-2</v>
+        <v>3.2844699383896329E-2</v>
       </c>
     </row>
     <row r="52" spans="2:9" x14ac:dyDescent="0.2">
@@ -39034,7 +39034,7 @@
       </c>
       <c r="I52" s="173">
         <f ca="1">Statement!AC162</f>
-        <v>4.5091515573552045E-2</v>
+        <v>4.244944206703289E-2</v>
       </c>
     </row>
     <row r="53" spans="2:9" x14ac:dyDescent="0.2">
@@ -39092,7 +39092,7 @@
       </c>
       <c r="I54" s="173">
         <f ca="1">Statement!AC165</f>
-        <v>3.4194757520267544E-2</v>
+        <v>3.2191164122330473E-2</v>
       </c>
     </row>
     <row r="55" spans="2:9" x14ac:dyDescent="0.2">
@@ -39121,7 +39121,7 @@
       </c>
       <c r="I55" s="173">
         <f ca="1">Statement!AC166</f>
-        <v>3.4194757520267544E-2</v>
+        <v>3.2191164122330473E-2</v>
       </c>
     </row>
     <row r="57" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -39357,7 +39357,7 @@
       </c>
       <c r="I68" s="194">
         <f ca="1">Statement!AC177</f>
-        <v>1.8892012482913369E-2</v>
+        <v>1.7785061762117211E-2</v>
       </c>
     </row>
     <row r="70" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -40510,30 +40510,6 @@
     </row>
   </sheetData>
   <mergeCells count="32">
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="F25:G25"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="F27:G27"/>
-    <mergeCell ref="C30:D30"/>
-    <mergeCell ref="F30:G30"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="F19:G19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="F21:G21"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="F9:G9"/>
     <mergeCell ref="C38:D38"/>
     <mergeCell ref="F38:G38"/>
     <mergeCell ref="C32:D32"/>
@@ -40542,6 +40518,30 @@
     <mergeCell ref="F34:G34"/>
     <mergeCell ref="C36:D36"/>
     <mergeCell ref="F36:G36"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="F25:G25"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="F27:G27"/>
+    <mergeCell ref="C30:D30"/>
+    <mergeCell ref="F30:G30"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>

--- a/ADSK.xlsx
+++ b/ADSK.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F788D65B-0B22-4046-96BF-AFC3EC9BD705}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D175357-C428-6843-9B65-299E65BA7B1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
@@ -151,7 +151,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="784" uniqueCount="433">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="816" uniqueCount="441">
   <si>
     <t>Ticker</t>
   </si>
@@ -1450,6 +1450,30 @@
   </si>
   <si>
     <t>M&amp;E will be placed into the Other category</t>
+  </si>
+  <si>
+    <t>Discount rates used</t>
+  </si>
+  <si>
+    <t>Cost of Equity</t>
+  </si>
+  <si>
+    <t>Links</t>
+  </si>
+  <si>
+    <t>Financials -&gt;'!B13</t>
+  </si>
+  <si>
+    <t>Analysis -&gt;'!B13</t>
+  </si>
+  <si>
+    <t>Forecast -&gt;'!B13</t>
+  </si>
+  <si>
+    <t>Valuation -&gt;'!B13</t>
+  </si>
+  <si>
+    <t>Overview'!B3</t>
   </si>
 </sst>
 </file>
@@ -1466,7 +1490,7 @@
     <numFmt numFmtId="169" formatCode="#,##0.0_);\(#,##0.0\)"/>
     <numFmt numFmtId="170" formatCode="0.0"/>
   </numFmts>
-  <fonts count="25" x14ac:knownFonts="1">
+  <fonts count="26" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1638,6 +1662,14 @@
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="12"/>
+      <color theme="10"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -2055,11 +2087,12 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="253">
+  <cellXfs count="257">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
@@ -2371,6 +2404,14 @@
     <xf numFmtId="39" fontId="10" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="7" fillId="9" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="167" fontId="7" fillId="9" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="0" fillId="17" borderId="25" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="0" fillId="17" borderId="26" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="25" fillId="8" borderId="25" xfId="2" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="8" borderId="26" xfId="2" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2416,17 +2457,18 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
+    <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
@@ -15145,10 +15187,10 @@
     <v>320</v>
     <v>185.5</v>
     <v>1.3194999999999999</v>
-    <v>1.75</v>
-    <v>7.4910000000000003E-3</v>
-    <v>-0.61</v>
-    <v>-2.5919999999999997E-3</v>
+    <v>-1.81</v>
+    <v>-7.6909999999999999E-3</v>
+    <v>0.11</v>
+    <v>4.7100000000000001E-4</v>
     <v>USD</v>
     <v>Autodesk, Inc. is engaged in three-dimensional (3D) design, engineering and entertainment technology solutions, spanning architecture, engineering, construction, product design, manufacturing, media and entertainment. Its architecture, engineering, construction and operations products improve the way building, infrastructure, and industrial projects are designed, built, and operated. Its product development and manufacturing software provides manufacturers in the automotive, transportation, industrial machinery, consumer products, and building product industries with comprehensive digital design, engineering, manufacturing, and production solutions. Its product offerings include AutoCAD Civil 3D, Autodesk Build, BIM Collaborate Pro, Building Connected, Revit, Tandem, AutoCAD, AutoCAD LT, Inventor, Vault, Maya, 3ds Max, Flow Production Tracking, among others. AutoCAD Civil 3D solution offers surveying, design, analysis, and documentation solution.</v>
     <v>14300</v>
@@ -15156,25 +15198,25 @@
     <v>XNAS</v>
     <v>XNAS</v>
     <v>One Market, Ste. 400., SAN FRANCISCO, CA, 94105 US</v>
-    <v>238.59</v>
+    <v>237.27</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46304.999692557809</v>
+    <v>46307.844219339844</v>
     <v>0</v>
-    <v>233.52</v>
-    <v>49188150000</v>
+    <v>229.315</v>
+    <v>48809860000</v>
     <v>AUTODESK, INC.</v>
     <v>AUTODESK, INC.</v>
-    <v>235.5</v>
-    <v>30.286899999999999</v>
-    <v>233.6</v>
+    <v>234.703</v>
+    <v>30.2791</v>
     <v>235.35</v>
-    <v>234.74</v>
+    <v>233.54</v>
+    <v>233.65</v>
     <v>209000000</v>
     <v>ADSK</v>
     <v>AUTODESK, INC. (XNAS:ADSK)</v>
-    <v>1777405</v>
-    <v>2340149</v>
+    <v>1524104</v>
+    <v>2316106</v>
     <v>1994</v>
   </rv>
   <rv s="2">
@@ -15986,7 +16028,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{825B172E-7ADE-4B4A-B533-F037BCFCDCB0}">
-  <dimension ref="B1:I71"/>
+  <dimension ref="B1:K71"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="2" style="1" customWidth="1"/>
@@ -15998,25 +16040,30 @@
     <col min="7" max="7" width="1.6640625" style="1" customWidth="1"/>
     <col min="8" max="8" width="15.1640625" style="1" customWidth="1"/>
     <col min="9" max="9" width="8.6640625" style="1" customWidth="1"/>
-    <col min="10" max="16384" width="10.83203125" style="1"/>
+    <col min="10" max="10" width="2" style="1" customWidth="1"/>
+    <col min="11" max="11" width="16.5" style="1" customWidth="1"/>
+    <col min="12" max="16384" width="10.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:9" ht="11" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="2" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B2" s="235" t="s">
+    <row r="1" spans="2:11" ht="11" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="2" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B2" s="239" t="s">
         <v>17</v>
       </c>
-      <c r="C2" s="236"/>
-      <c r="E2" s="235" t="s">
+      <c r="C2" s="240"/>
+      <c r="E2" s="239" t="s">
         <v>286</v>
       </c>
-      <c r="F2" s="236"/>
-      <c r="H2" s="235" t="s">
+      <c r="F2" s="240"/>
+      <c r="H2" s="239" t="s">
         <v>324</v>
       </c>
-      <c r="I2" s="236"/>
-    </row>
-    <row r="3" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="I2" s="240"/>
+      <c r="K2" s="134" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="3" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B3" s="183" t="s">
         <v>11</v>
       </c>
@@ -16029,7 +16076,7 @@
       </c>
       <c r="F3" s="185">
         <f ca="1">Statement!AC154</f>
-        <v>49423.5</v>
+        <v>49043.4</v>
       </c>
       <c r="H3" s="183" t="str">
         <f>'AVG target price'!B5</f>
@@ -16037,10 +16084,13 @@
       </c>
       <c r="I3" s="209">
         <f ca="1">'AVG target price'!C5</f>
-        <v>117.40628980771197</v>
-      </c>
-    </row>
-    <row r="4" spans="2:9" x14ac:dyDescent="0.2">
+        <v>117.44825208935085</v>
+      </c>
+      <c r="K3" s="237" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="4" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B4" s="183" t="s">
         <v>0</v>
       </c>
@@ -16053,7 +16103,7 @@
       </c>
       <c r="F4" s="186">
         <f ca="1">Statement!AC155</f>
-        <v>48544.5</v>
+        <v>48164.4</v>
       </c>
       <c r="H4" s="183" t="str">
         <f>'AVG target price'!B6</f>
@@ -16061,16 +16111,19 @@
       </c>
       <c r="I4" s="209">
         <f ca="1">'AVG target price'!C6</f>
-        <v>346.47563818543853</v>
-      </c>
-    </row>
-    <row r="5" spans="2:9" x14ac:dyDescent="0.2">
+        <v>346.52062287016844</v>
+      </c>
+      <c r="K4" s="237" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="5" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B5" s="183" t="s">
         <v>1</v>
       </c>
       <c r="C5" s="206" cm="1">
         <f t="array" aca="1" ref="C5" ca="1">_FV(C3,"Price",TRUE)</f>
-        <v>235.35</v>
+        <v>233.54</v>
       </c>
       <c r="E5" s="183" t="s">
         <v>242</v>
@@ -16087,21 +16140,24 @@
         <f ca="1">'AVG target price'!C7</f>
         <v>188.26132013643894</v>
       </c>
-    </row>
-    <row r="6" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="K5" s="237" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="6" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B6" s="183" t="s">
         <v>2</v>
       </c>
       <c r="C6" s="206" cm="1">
         <f t="array" aca="1" ref="C6" ca="1">_FV(C3,"Price (Extended hours)",TRUE)</f>
-        <v>234.74</v>
+        <v>233.65</v>
       </c>
       <c r="E6" s="183" t="s">
         <v>236</v>
       </c>
       <c r="F6" s="188">
         <f ca="1">Statement!AC151</f>
-        <v>30.44631306597671</v>
+        <v>30.212160413971535</v>
       </c>
       <c r="H6" s="183" t="str">
         <f>'AVG target price'!B8</f>
@@ -16109,23 +16165,26 @@
       </c>
       <c r="I6" s="209">
         <f ca="1">'AVG target price'!C8</f>
-        <v>344.93810808304579</v>
-      </c>
-    </row>
-    <row r="7" spans="2:9" x14ac:dyDescent="0.2">
+        <v>344.98288263158031</v>
+      </c>
+      <c r="K6" s="238" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="7" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B7" s="183" t="s">
         <v>3</v>
       </c>
       <c r="C7" s="6" cm="1">
         <f t="array" aca="1" ref="C7" ca="1">_FV(C3,"Change")</f>
-        <v>1.75</v>
+        <v>-1.81</v>
       </c>
       <c r="E7" s="184" t="s">
         <v>200</v>
       </c>
       <c r="F7" s="189">
         <f ca="1">Statement!AC152</f>
-        <v>6.4351155327342751</v>
+        <v>6.3856251604621308</v>
       </c>
       <c r="H7" s="183" t="str">
         <f>'AVG target price'!B9</f>
@@ -16133,23 +16192,23 @@
       </c>
       <c r="I7" s="209">
         <f ca="1">'AVG target price'!C9</f>
-        <v>219.69825681203739</v>
-      </c>
-    </row>
-    <row r="8" spans="2:9" x14ac:dyDescent="0.2">
+        <v>219.72591467074224</v>
+      </c>
+    </row>
+    <row r="8" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B8" s="183" t="s">
         <v>4</v>
       </c>
       <c r="C8" s="6" cm="1">
         <f t="array" aca="1" ref="C8" ca="1">_FV(C3,"Change (extended hours)",TRUE)</f>
-        <v>-0.61</v>
+        <v>0.11</v>
       </c>
       <c r="E8" s="183" t="s">
         <v>264</v>
       </c>
       <c r="F8" s="190">
         <f ca="1">Statement!AC162</f>
-        <v>4.244944206703289E-2</v>
+        <v>4.277843705778963E-2</v>
       </c>
       <c r="H8" s="182" t="str">
         <f>'AVG target price'!B10</f>
@@ -16157,23 +16216,23 @@
       </c>
       <c r="I8" s="210">
         <f ca="1">'AVG target price'!C10</f>
-        <v>243.35592260493453</v>
-      </c>
-    </row>
-    <row r="9" spans="2:9" x14ac:dyDescent="0.2">
+        <v>243.38779847965617</v>
+      </c>
+    </row>
+    <row r="9" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B9" s="183" t="s">
         <v>5</v>
       </c>
       <c r="C9" s="73" cm="1">
         <f t="array" aca="1" ref="C9" ca="1">_FV(C3,"Change (%)",TRUE)</f>
-        <v>7.4910000000000003E-3</v>
+        <v>-7.6909999999999999E-3</v>
       </c>
       <c r="E9" s="183" t="s">
         <v>287</v>
       </c>
       <c r="F9" s="190">
         <f ca="1">Statement!AC163</f>
-        <v>3.2844699383896329E-2</v>
+        <v>3.3099254945619598E-2</v>
       </c>
       <c r="H9" s="182" t="str">
         <f>'AVG target price'!B12</f>
@@ -16181,26 +16240,26 @@
       </c>
       <c r="I9" s="211">
         <f ca="1">'AVG target price'!C12</f>
-        <v>3.4017092011619038E-2</v>
-      </c>
-    </row>
-    <row r="10" spans="2:9" x14ac:dyDescent="0.2">
+        <v>4.2167502267946293E-2</v>
+      </c>
+    </row>
+    <row r="10" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B10" s="183" t="s">
         <v>6</v>
       </c>
       <c r="C10" s="73" cm="1">
         <f t="array" aca="1" ref="C10" ca="1">_FV(C3,"Change % (extended hours)",TRUE)</f>
-        <v>-2.5919999999999997E-3</v>
+        <v>4.7100000000000001E-4</v>
       </c>
       <c r="E10" s="183" t="s">
         <v>292</v>
       </c>
       <c r="F10" s="190">
         <f ca="1">Statement!AC165</f>
-        <v>3.2191164122330473E-2</v>
-      </c>
-    </row>
-    <row r="11" spans="2:9" x14ac:dyDescent="0.2">
+        <v>3.2440654603881458E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B11" s="183" t="s">
         <v>7</v>
       </c>
@@ -16223,7 +16282,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="12" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B12" s="183" t="s">
         <v>8</v>
       </c>
@@ -16239,7 +16298,7 @@
         <v>0.12647308018177617</v>
       </c>
     </row>
-    <row r="13" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="13" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B13" s="183" t="s">
         <v>9</v>
       </c>
@@ -16262,13 +16321,13 @@
         <v>0.46500000000000002</v>
       </c>
     </row>
-    <row r="14" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="14" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B14" s="184" t="s">
         <v>10</v>
       </c>
       <c r="C14" s="208" cm="1">
         <f t="array" aca="1" ref="C14" ca="1">_FV(C3,"Volume average",TRUE)</f>
-        <v>2340149</v>
+        <v>2316106</v>
       </c>
       <c r="E14" s="184" t="s">
         <v>104</v>
@@ -16278,16 +16337,16 @@
         <v>0.63581348227633894</v>
       </c>
     </row>
-    <row r="15" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="15" spans="2:11" x14ac:dyDescent="0.2">
       <c r="E15" s="183" t="s">
         <v>289</v>
       </c>
       <c r="F15" s="190">
         <f ca="1">Statement!AC177</f>
-        <v>1.7785061762117211E-2</v>
-      </c>
-    </row>
-    <row r="16" spans="2:9" x14ac:dyDescent="0.2">
+        <v>1.7922900940799374E-2</v>
+      </c>
+    </row>
+    <row r="16" spans="2:11" x14ac:dyDescent="0.2">
       <c r="E16" s="184" t="s">
         <v>294</v>
       </c>
@@ -16295,12 +16354,16 @@
         <f>Statement!AC176</f>
         <v>4.205741626794258</v>
       </c>
+      <c r="H16" s="239" t="s">
+        <v>433</v>
+      </c>
+      <c r="I16" s="240"/>
     </row>
     <row r="17" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B17" s="237" t="s">
+      <c r="B17" s="241" t="s">
         <v>89</v>
       </c>
-      <c r="C17" s="237"/>
+      <c r="C17" s="241"/>
       <c r="E17" s="182" t="s">
         <v>295</v>
       </c>
@@ -16308,6 +16371,13 @@
         <f>Statement!AC172</f>
         <v>4.7619047619047623E-3</v>
       </c>
+      <c r="H17" s="183" t="s">
+        <v>164</v>
+      </c>
+      <c r="I17" s="235">
+        <f ca="1">DCF!C15</f>
+        <v>0.10760404710270478</v>
+      </c>
     </row>
     <row r="18" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B18" s="182" t="s">
@@ -16323,6 +16393,13 @@
         <f>Statement!AC145</f>
         <v>-212.53333094914524</v>
       </c>
+      <c r="H18" s="184" t="s">
+        <v>434</v>
+      </c>
+      <c r="I18" s="236">
+        <f ca="1">Multiples!C54</f>
+        <v>0.11181749999999999</v>
+      </c>
     </row>
     <row r="19" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B19" s="182" t="s">
@@ -16373,14 +16450,14 @@
       <c r="I22" s="50"/>
     </row>
     <row r="25" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B25" s="237" t="s">
+      <c r="B25" s="241" t="s">
         <v>106</v>
       </c>
-      <c r="C25" s="237"/>
-      <c r="E25" s="235" t="s">
+      <c r="C25" s="241"/>
+      <c r="E25" s="239" t="s">
         <v>337</v>
       </c>
-      <c r="F25" s="236"/>
+      <c r="F25" s="240"/>
     </row>
     <row r="26" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B26" s="182" t="s">
@@ -16622,13 +16699,14 @@
       <c r="H71" s="134"/>
     </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="7">
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="B17:C17"/>
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="E2:F2"/>
     <mergeCell ref="H2:I2"/>
     <mergeCell ref="E25:F25"/>
+    <mergeCell ref="H16:I16"/>
   </mergeCells>
   <conditionalFormatting sqref="C7:C10">
     <cfRule type="cellIs" dxfId="2" priority="4" operator="lessThan">
@@ -16641,6 +16719,12 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
+  <hyperlinks>
+    <hyperlink ref="K3" location="'Financials -&gt;'!B13" display="'Financials -&gt;'!B13" xr:uid="{F362CAA9-8511-1147-87FF-4ACF12A3D9A8}"/>
+    <hyperlink ref="K4" location="'Analysis -&gt;'!B13" display="'Analysis -&gt;'!B13" xr:uid="{C9467FF6-CFF6-214A-93C7-45D507C7A6BB}"/>
+    <hyperlink ref="K5" location="'Forecast -&gt;'!B13" display="'Forecast -&gt;'!B13" xr:uid="{DD466B6E-3A26-9A47-AD60-D0651981787C}"/>
+    <hyperlink ref="K6" location="'Valuation -&gt;'!B13" display="'Valuation -&gt;'!B13" xr:uid="{E4DA1016-67A4-544F-BD13-5C30B0A455D0}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -16650,18 +16734,57 @@
   <sheetPr>
     <tabColor theme="6" tint="0.59999389629810485"/>
   </sheetPr>
-  <dimension ref="B13"/>
+  <dimension ref="B5:H13"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="16384" width="10.83203125" style="1"/>
+    <col min="1" max="7" width="10.83203125" style="1"/>
+    <col min="8" max="8" width="18.5" style="1" customWidth="1"/>
+    <col min="9" max="16384" width="10.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="13" spans="2:2" s="4" customFormat="1" ht="49" x14ac:dyDescent="0.2">
+    <row r="5" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H5" s="134" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="6" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H6" s="237" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="7" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H7" s="237" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="8" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H8" s="237" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="9" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H9" s="237" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="10" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H10" s="238" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="13" spans="2:8" s="4" customFormat="1" ht="49" x14ac:dyDescent="0.2">
       <c r="B13" s="3" t="s">
         <v>110</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="H6" location="Overview!B3" display="Overview'!B3" xr:uid="{AD7E74EC-B8D8-8A43-A375-64EBE06E0A03}"/>
+    <hyperlink ref="H8" location="'Analysis -&gt;'!B13" display="'Analysis -&gt;'!B13" xr:uid="{0E406DBD-50D8-714F-8A42-D33BCB44E174}"/>
+    <hyperlink ref="H9" location="'Forecast -&gt;'!B13" display="'Forecast -&gt;'!B13" xr:uid="{E6F95179-D9F9-D345-877D-C8D2E2DDD008}"/>
+    <hyperlink ref="H10" location="'Valuation -&gt;'!B13" display="'Valuation -&gt;'!B13" xr:uid="{A457EABD-1994-474E-856F-AA4AE084E84C}"/>
+    <hyperlink ref="H7" location="'Financials -&gt;'!B13" display="'Financials -&gt;'!B13" xr:uid="{4385EA5F-C232-F440-A016-4F8C3B01C07F}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -16698,36 +16821,36 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="238" t="s">
+      <c r="C2" s="242" t="s">
         <v>112</v>
       </c>
-      <c r="D2" s="238"/>
-      <c r="E2" s="238"/>
-      <c r="F2" s="238"/>
-      <c r="G2" s="247"/>
-      <c r="H2" s="248" t="s">
+      <c r="D2" s="242"/>
+      <c r="E2" s="242"/>
+      <c r="F2" s="242"/>
+      <c r="G2" s="251"/>
+      <c r="H2" s="252" t="s">
         <v>113</v>
       </c>
-      <c r="I2" s="238"/>
-      <c r="J2" s="238"/>
-      <c r="K2" s="238"/>
-      <c r="L2" s="238"/>
+      <c r="I2" s="242"/>
+      <c r="J2" s="242"/>
+      <c r="K2" s="242"/>
+      <c r="L2" s="242"/>
       <c r="O2" s="5"/>
-      <c r="S2" s="238" t="s">
+      <c r="S2" s="242" t="s">
         <v>112</v>
       </c>
-      <c r="T2" s="238"/>
-      <c r="U2" s="238"/>
-      <c r="V2" s="238"/>
-      <c r="W2" s="238"/>
-      <c r="X2" s="238"/>
-      <c r="Y2" s="238"/>
-      <c r="Z2" s="238"/>
-      <c r="AA2" s="238" t="s">
+      <c r="T2" s="242"/>
+      <c r="U2" s="242"/>
+      <c r="V2" s="242"/>
+      <c r="W2" s="242"/>
+      <c r="X2" s="242"/>
+      <c r="Y2" s="242"/>
+      <c r="Z2" s="242"/>
+      <c r="AA2" s="242" t="s">
         <v>113</v>
       </c>
-      <c r="AB2" s="238"/>
-      <c r="AC2" s="238"/>
+      <c r="AB2" s="242"/>
+      <c r="AC2" s="242"/>
       <c r="AE2" s="85" t="s">
         <v>114</v>
       </c>
@@ -16738,32 +16861,32 @@
     <row r="4" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="86"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="244" t="s">
+      <c r="C4" s="248" t="s">
         <v>115</v>
       </c>
-      <c r="D4" s="244"/>
-      <c r="E4" s="244"/>
-      <c r="F4" s="244"/>
-      <c r="G4" s="244"/>
-      <c r="H4" s="244"/>
-      <c r="I4" s="244"/>
-      <c r="J4" s="244"/>
-      <c r="K4" s="244"/>
-      <c r="L4" s="244"/>
+      <c r="D4" s="248"/>
+      <c r="E4" s="248"/>
+      <c r="F4" s="248"/>
+      <c r="G4" s="248"/>
+      <c r="H4" s="248"/>
+      <c r="I4" s="248"/>
+      <c r="J4" s="248"/>
+      <c r="K4" s="248"/>
+      <c r="L4" s="248"/>
       <c r="O4" s="5"/>
-      <c r="S4" s="245" t="s">
+      <c r="S4" s="249" t="s">
         <v>115</v>
       </c>
-      <c r="T4" s="246"/>
-      <c r="U4" s="246"/>
-      <c r="V4" s="246"/>
-      <c r="W4" s="246"/>
-      <c r="X4" s="246"/>
-      <c r="Y4" s="246"/>
-      <c r="Z4" s="246"/>
-      <c r="AA4" s="246"/>
-      <c r="AB4" s="246"/>
-      <c r="AC4" s="246"/>
+      <c r="T4" s="250"/>
+      <c r="U4" s="250"/>
+      <c r="V4" s="250"/>
+      <c r="W4" s="250"/>
+      <c r="X4" s="250"/>
+      <c r="Y4" s="250"/>
+      <c r="Z4" s="250"/>
+      <c r="AA4" s="250"/>
+      <c r="AB4" s="250"/>
+      <c r="AC4" s="250"/>
       <c r="AE4" s="87"/>
     </row>
     <row r="5" spans="1:31" x14ac:dyDescent="0.2">
@@ -17676,33 +17799,33 @@
       <c r="Q15" s="91"/>
     </row>
     <row r="16" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="C16" s="244" t="s">
+      <c r="C16" s="248" t="s">
         <v>121</v>
       </c>
-      <c r="D16" s="244"/>
-      <c r="E16" s="244"/>
-      <c r="F16" s="244"/>
-      <c r="G16" s="244"/>
-      <c r="H16" s="244"/>
-      <c r="I16" s="244"/>
-      <c r="J16" s="244"/>
-      <c r="K16" s="244"/>
-      <c r="L16" s="244"/>
+      <c r="D16" s="248"/>
+      <c r="E16" s="248"/>
+      <c r="F16" s="248"/>
+      <c r="G16" s="248"/>
+      <c r="H16" s="248"/>
+      <c r="I16" s="248"/>
+      <c r="J16" s="248"/>
+      <c r="K16" s="248"/>
+      <c r="L16" s="248"/>
       <c r="O16" s="5"/>
       <c r="Q16" s="91"/>
-      <c r="S16" s="245" t="s">
+      <c r="S16" s="249" t="s">
         <v>121</v>
       </c>
-      <c r="T16" s="246"/>
-      <c r="U16" s="246"/>
-      <c r="V16" s="246"/>
-      <c r="W16" s="246"/>
-      <c r="X16" s="246"/>
-      <c r="Y16" s="246"/>
-      <c r="Z16" s="246"/>
-      <c r="AA16" s="246"/>
-      <c r="AB16" s="246"/>
-      <c r="AC16" s="246"/>
+      <c r="T16" s="250"/>
+      <c r="U16" s="250"/>
+      <c r="V16" s="250"/>
+      <c r="W16" s="250"/>
+      <c r="X16" s="250"/>
+      <c r="Y16" s="250"/>
+      <c r="Z16" s="250"/>
+      <c r="AA16" s="250"/>
+      <c r="AB16" s="250"/>
+      <c r="AC16" s="250"/>
     </row>
     <row r="17" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B17" s="16" t="s">
@@ -18470,33 +18593,33 @@
       <c r="Q27" s="91"/>
     </row>
     <row r="28" spans="2:31" x14ac:dyDescent="0.2">
-      <c r="C28" s="244" t="s">
+      <c r="C28" s="248" t="s">
         <v>422</v>
       </c>
-      <c r="D28" s="244"/>
-      <c r="E28" s="244"/>
-      <c r="F28" s="244"/>
-      <c r="G28" s="244"/>
-      <c r="H28" s="244"/>
-      <c r="I28" s="244"/>
-      <c r="J28" s="244"/>
-      <c r="K28" s="244"/>
-      <c r="L28" s="244"/>
+      <c r="D28" s="248"/>
+      <c r="E28" s="248"/>
+      <c r="F28" s="248"/>
+      <c r="G28" s="248"/>
+      <c r="H28" s="248"/>
+      <c r="I28" s="248"/>
+      <c r="J28" s="248"/>
+      <c r="K28" s="248"/>
+      <c r="L28" s="248"/>
       <c r="O28" s="5"/>
       <c r="Q28" s="91"/>
-      <c r="S28" s="245" t="s">
+      <c r="S28" s="249" t="s">
         <v>422</v>
       </c>
-      <c r="T28" s="246"/>
-      <c r="U28" s="246"/>
-      <c r="V28" s="246"/>
-      <c r="W28" s="246"/>
-      <c r="X28" s="246"/>
-      <c r="Y28" s="246"/>
-      <c r="Z28" s="246"/>
-      <c r="AA28" s="246"/>
-      <c r="AB28" s="246"/>
-      <c r="AC28" s="246"/>
+      <c r="T28" s="250"/>
+      <c r="U28" s="250"/>
+      <c r="V28" s="250"/>
+      <c r="W28" s="250"/>
+      <c r="X28" s="250"/>
+      <c r="Y28" s="250"/>
+      <c r="Z28" s="250"/>
+      <c r="AA28" s="250"/>
+      <c r="AB28" s="250"/>
+      <c r="AC28" s="250"/>
       <c r="AE28" s="87"/>
     </row>
     <row r="29" spans="2:31" x14ac:dyDescent="0.2">
@@ -18737,35 +18860,35 @@
     </row>
     <row r="2" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="238" t="s">
+      <c r="C2" s="242" t="s">
         <v>112</v>
       </c>
-      <c r="D2" s="238"/>
-      <c r="E2" s="238"/>
-      <c r="F2" s="238"/>
-      <c r="G2" s="247"/>
-      <c r="H2" s="248" t="s">
+      <c r="D2" s="242"/>
+      <c r="E2" s="242"/>
+      <c r="F2" s="242"/>
+      <c r="G2" s="251"/>
+      <c r="H2" s="252" t="s">
         <v>113</v>
       </c>
-      <c r="I2" s="238"/>
-      <c r="J2" s="238"/>
-      <c r="K2" s="238"/>
-      <c r="L2" s="238"/>
-      <c r="P2" s="238" t="s">
+      <c r="I2" s="242"/>
+      <c r="J2" s="242"/>
+      <c r="K2" s="242"/>
+      <c r="L2" s="242"/>
+      <c r="P2" s="242" t="s">
         <v>112</v>
       </c>
-      <c r="Q2" s="238"/>
-      <c r="R2" s="238"/>
-      <c r="S2" s="238"/>
-      <c r="T2" s="238"/>
-      <c r="U2" s="238"/>
-      <c r="V2" s="238"/>
-      <c r="W2" s="238"/>
-      <c r="X2" s="238" t="s">
+      <c r="Q2" s="242"/>
+      <c r="R2" s="242"/>
+      <c r="S2" s="242"/>
+      <c r="T2" s="242"/>
+      <c r="U2" s="242"/>
+      <c r="V2" s="242"/>
+      <c r="W2" s="242"/>
+      <c r="X2" s="242" t="s">
         <v>113</v>
       </c>
-      <c r="Y2" s="238"/>
-      <c r="Z2" s="238"/>
+      <c r="Y2" s="242"/>
+      <c r="Z2" s="242"/>
       <c r="AB2" s="85" t="s">
         <v>114</v>
       </c>
@@ -18774,31 +18897,31 @@
     <row r="4" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="86"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="244" t="s">
+      <c r="C4" s="248" t="s">
         <v>115</v>
       </c>
-      <c r="D4" s="244"/>
-      <c r="E4" s="244"/>
-      <c r="F4" s="244"/>
-      <c r="G4" s="244"/>
-      <c r="H4" s="244"/>
-      <c r="I4" s="244"/>
-      <c r="J4" s="244"/>
-      <c r="K4" s="244"/>
-      <c r="L4" s="244"/>
-      <c r="P4" s="246" t="s">
+      <c r="D4" s="248"/>
+      <c r="E4" s="248"/>
+      <c r="F4" s="248"/>
+      <c r="G4" s="248"/>
+      <c r="H4" s="248"/>
+      <c r="I4" s="248"/>
+      <c r="J4" s="248"/>
+      <c r="K4" s="248"/>
+      <c r="L4" s="248"/>
+      <c r="P4" s="250" t="s">
         <v>115</v>
       </c>
-      <c r="Q4" s="246"/>
-      <c r="R4" s="246"/>
-      <c r="S4" s="246"/>
-      <c r="T4" s="246"/>
-      <c r="U4" s="246"/>
-      <c r="V4" s="246"/>
-      <c r="W4" s="246"/>
-      <c r="X4" s="246"/>
-      <c r="Y4" s="246"/>
-      <c r="Z4" s="246"/>
+      <c r="Q4" s="250"/>
+      <c r="R4" s="250"/>
+      <c r="S4" s="250"/>
+      <c r="T4" s="250"/>
+      <c r="U4" s="250"/>
+      <c r="V4" s="250"/>
+      <c r="W4" s="250"/>
+      <c r="X4" s="250"/>
+      <c r="Y4" s="250"/>
+      <c r="Z4" s="250"/>
       <c r="AB4" s="87"/>
     </row>
     <row r="5" spans="1:28" x14ac:dyDescent="0.2">
@@ -18993,32 +19116,32 @@
       <c r="N8" s="91"/>
     </row>
     <row r="9" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="C9" s="244" t="s">
+      <c r="C9" s="248" t="s">
         <v>124</v>
       </c>
-      <c r="D9" s="244"/>
-      <c r="E9" s="244"/>
-      <c r="F9" s="244"/>
-      <c r="G9" s="244"/>
-      <c r="H9" s="244"/>
-      <c r="I9" s="244"/>
-      <c r="J9" s="244"/>
-      <c r="K9" s="244"/>
-      <c r="L9" s="244"/>
+      <c r="D9" s="248"/>
+      <c r="E9" s="248"/>
+      <c r="F9" s="248"/>
+      <c r="G9" s="248"/>
+      <c r="H9" s="248"/>
+      <c r="I9" s="248"/>
+      <c r="J9" s="248"/>
+      <c r="K9" s="248"/>
+      <c r="L9" s="248"/>
       <c r="N9" s="91"/>
-      <c r="P9" s="246" t="s">
+      <c r="P9" s="250" t="s">
         <v>125</v>
       </c>
-      <c r="Q9" s="246"/>
-      <c r="R9" s="246"/>
-      <c r="S9" s="246"/>
-      <c r="T9" s="246"/>
-      <c r="U9" s="246"/>
-      <c r="V9" s="246"/>
-      <c r="W9" s="246"/>
-      <c r="X9" s="246"/>
-      <c r="Y9" s="246"/>
-      <c r="Z9" s="246"/>
+      <c r="Q9" s="250"/>
+      <c r="R9" s="250"/>
+      <c r="S9" s="250"/>
+      <c r="T9" s="250"/>
+      <c r="U9" s="250"/>
+      <c r="V9" s="250"/>
+      <c r="W9" s="250"/>
+      <c r="X9" s="250"/>
+      <c r="Y9" s="250"/>
+      <c r="Z9" s="250"/>
       <c r="AB9" s="87"/>
     </row>
     <row r="10" spans="1:28" x14ac:dyDescent="0.2">
@@ -19864,31 +19987,31 @@
       </c>
     </row>
     <row r="21" spans="2:28" x14ac:dyDescent="0.2">
-      <c r="C21" s="244" t="s">
+      <c r="C21" s="248" t="s">
         <v>127</v>
       </c>
-      <c r="D21" s="244"/>
-      <c r="E21" s="244"/>
-      <c r="F21" s="244"/>
-      <c r="G21" s="244"/>
-      <c r="H21" s="244"/>
-      <c r="I21" s="244"/>
-      <c r="J21" s="244"/>
-      <c r="K21" s="244"/>
-      <c r="L21" s="244"/>
-      <c r="P21" s="246" t="s">
+      <c r="D21" s="248"/>
+      <c r="E21" s="248"/>
+      <c r="F21" s="248"/>
+      <c r="G21" s="248"/>
+      <c r="H21" s="248"/>
+      <c r="I21" s="248"/>
+      <c r="J21" s="248"/>
+      <c r="K21" s="248"/>
+      <c r="L21" s="248"/>
+      <c r="P21" s="250" t="s">
         <v>127</v>
       </c>
-      <c r="Q21" s="246"/>
-      <c r="R21" s="246"/>
-      <c r="S21" s="246"/>
-      <c r="T21" s="246"/>
-      <c r="U21" s="246"/>
-      <c r="V21" s="246"/>
-      <c r="W21" s="246"/>
-      <c r="X21" s="246"/>
-      <c r="Y21" s="246"/>
-      <c r="Z21" s="246"/>
+      <c r="Q21" s="250"/>
+      <c r="R21" s="250"/>
+      <c r="S21" s="250"/>
+      <c r="T21" s="250"/>
+      <c r="U21" s="250"/>
+      <c r="V21" s="250"/>
+      <c r="W21" s="250"/>
+      <c r="X21" s="250"/>
+      <c r="Y21" s="250"/>
+      <c r="Z21" s="250"/>
     </row>
     <row r="22" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B22" s="16" t="s">
@@ -20703,60 +20826,60 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="238" t="s">
+      <c r="C3" s="242" t="s">
         <v>112</v>
       </c>
-      <c r="D3" s="238"/>
-      <c r="E3" s="238"/>
-      <c r="F3" s="238"/>
-      <c r="G3" s="247"/>
-      <c r="H3" s="248" t="s">
+      <c r="D3" s="242"/>
+      <c r="E3" s="242"/>
+      <c r="F3" s="242"/>
+      <c r="G3" s="251"/>
+      <c r="H3" s="252" t="s">
         <v>113</v>
       </c>
-      <c r="I3" s="238"/>
-      <c r="J3" s="238"/>
-      <c r="K3" s="238"/>
-      <c r="L3" s="238"/>
-      <c r="P3" s="249"/>
-      <c r="Q3" s="249"/>
-      <c r="R3" s="249"/>
-      <c r="S3" s="249"/>
-      <c r="T3" s="249"/>
-      <c r="U3" s="249"/>
-      <c r="V3" s="249"/>
-      <c r="W3" s="249"/>
-      <c r="X3" s="249"/>
-      <c r="Y3" s="249"/>
-      <c r="Z3" s="249"/>
+      <c r="I3" s="242"/>
+      <c r="J3" s="242"/>
+      <c r="K3" s="242"/>
+      <c r="L3" s="242"/>
+      <c r="P3" s="253"/>
+      <c r="Q3" s="253"/>
+      <c r="R3" s="253"/>
+      <c r="S3" s="253"/>
+      <c r="T3" s="253"/>
+      <c r="U3" s="253"/>
+      <c r="V3" s="253"/>
+      <c r="W3" s="253"/>
+      <c r="X3" s="253"/>
+      <c r="Y3" s="253"/>
+      <c r="Z3" s="253"/>
       <c r="AB3" s="111"/>
     </row>
     <row r="4" spans="1:28" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="86"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="244" t="s">
+      <c r="C5" s="248" t="s">
         <v>115</v>
       </c>
-      <c r="D5" s="244"/>
-      <c r="E5" s="244"/>
-      <c r="F5" s="244"/>
-      <c r="G5" s="244"/>
-      <c r="H5" s="244"/>
-      <c r="I5" s="244"/>
-      <c r="J5" s="244"/>
-      <c r="K5" s="244"/>
-      <c r="L5" s="244"/>
-      <c r="P5" s="249"/>
-      <c r="Q5" s="249"/>
-      <c r="R5" s="249"/>
-      <c r="S5" s="249"/>
-      <c r="T5" s="249"/>
-      <c r="U5" s="249"/>
-      <c r="V5" s="249"/>
-      <c r="W5" s="249"/>
-      <c r="X5" s="249"/>
-      <c r="Y5" s="249"/>
-      <c r="Z5" s="249"/>
+      <c r="D5" s="248"/>
+      <c r="E5" s="248"/>
+      <c r="F5" s="248"/>
+      <c r="G5" s="248"/>
+      <c r="H5" s="248"/>
+      <c r="I5" s="248"/>
+      <c r="J5" s="248"/>
+      <c r="K5" s="248"/>
+      <c r="L5" s="248"/>
+      <c r="P5" s="253"/>
+      <c r="Q5" s="253"/>
+      <c r="R5" s="253"/>
+      <c r="S5" s="253"/>
+      <c r="T5" s="253"/>
+      <c r="U5" s="253"/>
+      <c r="V5" s="253"/>
+      <c r="W5" s="253"/>
+      <c r="X5" s="253"/>
+      <c r="Y5" s="253"/>
+      <c r="Z5" s="253"/>
       <c r="AB5" s="112"/>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.2">
@@ -20942,30 +21065,30 @@
       <c r="N10" s="91"/>
     </row>
     <row r="11" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="C11" s="244" t="s">
+      <c r="C11" s="248" t="s">
         <v>131</v>
       </c>
-      <c r="D11" s="244"/>
-      <c r="E11" s="244"/>
-      <c r="F11" s="244"/>
-      <c r="G11" s="244"/>
-      <c r="H11" s="244"/>
-      <c r="I11" s="244"/>
-      <c r="J11" s="244"/>
-      <c r="K11" s="244"/>
-      <c r="L11" s="244"/>
+      <c r="D11" s="248"/>
+      <c r="E11" s="248"/>
+      <c r="F11" s="248"/>
+      <c r="G11" s="248"/>
+      <c r="H11" s="248"/>
+      <c r="I11" s="248"/>
+      <c r="J11" s="248"/>
+      <c r="K11" s="248"/>
+      <c r="L11" s="248"/>
       <c r="N11" s="91"/>
-      <c r="P11" s="249"/>
-      <c r="Q11" s="249"/>
-      <c r="R11" s="249"/>
-      <c r="S11" s="249"/>
-      <c r="T11" s="249"/>
-      <c r="U11" s="249"/>
-      <c r="V11" s="249"/>
-      <c r="W11" s="249"/>
-      <c r="X11" s="249"/>
-      <c r="Y11" s="249"/>
-      <c r="Z11" s="249"/>
+      <c r="P11" s="253"/>
+      <c r="Q11" s="253"/>
+      <c r="R11" s="253"/>
+      <c r="S11" s="253"/>
+      <c r="T11" s="253"/>
+      <c r="U11" s="253"/>
+      <c r="V11" s="253"/>
+      <c r="W11" s="253"/>
+      <c r="X11" s="253"/>
+      <c r="Y11" s="253"/>
+      <c r="Z11" s="253"/>
       <c r="AB11" s="112"/>
     </row>
     <row r="12" spans="1:28" x14ac:dyDescent="0.2">
@@ -21207,18 +21330,18 @@
       <c r="D16" s="24"/>
     </row>
     <row r="18" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C18" s="244" t="s">
+      <c r="C18" s="248" t="s">
         <v>136</v>
       </c>
-      <c r="D18" s="244"/>
-      <c r="E18" s="244"/>
-      <c r="F18" s="244"/>
-      <c r="G18" s="244"/>
-      <c r="H18" s="244"/>
-      <c r="I18" s="244"/>
-      <c r="J18" s="244"/>
-      <c r="K18" s="244"/>
-      <c r="L18" s="244"/>
+      <c r="D18" s="248"/>
+      <c r="E18" s="248"/>
+      <c r="F18" s="248"/>
+      <c r="G18" s="248"/>
+      <c r="H18" s="248"/>
+      <c r="I18" s="248"/>
+      <c r="J18" s="248"/>
+      <c r="K18" s="248"/>
+      <c r="L18" s="248"/>
     </row>
     <row r="19" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B19" s="16" t="s">
@@ -21431,23 +21554,23 @@
       </c>
     </row>
     <row r="25" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B25" s="249"/>
-      <c r="C25" s="249"/>
+      <c r="B25" s="253"/>
+      <c r="C25" s="253"/>
     </row>
     <row r="26" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B26" s="111"/>
-      <c r="C26" s="244" t="s">
+      <c r="C26" s="248" t="s">
         <v>142</v>
       </c>
-      <c r="D26" s="244"/>
-      <c r="E26" s="244"/>
-      <c r="F26" s="244"/>
-      <c r="G26" s="244"/>
-      <c r="H26" s="244"/>
-      <c r="I26" s="244"/>
-      <c r="J26" s="244"/>
-      <c r="K26" s="244"/>
-      <c r="L26" s="244"/>
+      <c r="D26" s="248"/>
+      <c r="E26" s="248"/>
+      <c r="F26" s="248"/>
+      <c r="G26" s="248"/>
+      <c r="H26" s="248"/>
+      <c r="I26" s="248"/>
+      <c r="J26" s="248"/>
+      <c r="K26" s="248"/>
+      <c r="L26" s="248"/>
     </row>
     <row r="27" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B27" s="16" t="s">
@@ -21639,18 +21762,18 @@
     </row>
     <row r="33" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B33" s="111"/>
-      <c r="C33" s="244" t="s">
+      <c r="C33" s="248" t="s">
         <v>146</v>
       </c>
-      <c r="D33" s="244"/>
-      <c r="E33" s="244"/>
-      <c r="F33" s="244"/>
-      <c r="G33" s="244"/>
-      <c r="H33" s="244"/>
-      <c r="I33" s="244"/>
-      <c r="J33" s="244"/>
-      <c r="K33" s="244"/>
-      <c r="L33" s="244"/>
+      <c r="D33" s="248"/>
+      <c r="E33" s="248"/>
+      <c r="F33" s="248"/>
+      <c r="G33" s="248"/>
+      <c r="H33" s="248"/>
+      <c r="I33" s="248"/>
+      <c r="J33" s="248"/>
+      <c r="K33" s="248"/>
+      <c r="L33" s="248"/>
     </row>
     <row r="34" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B34" s="16" t="s">
@@ -21834,18 +21957,18 @@
       <c r="C39" s="127"/>
     </row>
     <row r="40" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C40" s="244" t="s">
+      <c r="C40" s="248" t="s">
         <v>149</v>
       </c>
-      <c r="D40" s="244"/>
-      <c r="E40" s="244"/>
-      <c r="F40" s="244"/>
-      <c r="G40" s="244"/>
-      <c r="H40" s="244"/>
-      <c r="I40" s="244"/>
-      <c r="J40" s="244"/>
-      <c r="K40" s="244"/>
-      <c r="L40" s="244"/>
+      <c r="D40" s="248"/>
+      <c r="E40" s="248"/>
+      <c r="F40" s="248"/>
+      <c r="G40" s="248"/>
+      <c r="H40" s="248"/>
+      <c r="I40" s="248"/>
+      <c r="J40" s="248"/>
+      <c r="K40" s="248"/>
+      <c r="L40" s="248"/>
     </row>
     <row r="41" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B41" s="16" t="s">
@@ -22109,12 +22232,6 @@
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="H3:L3"/>
-    <mergeCell ref="P3:W3"/>
-    <mergeCell ref="X3:Z3"/>
-    <mergeCell ref="C5:L5"/>
-    <mergeCell ref="P5:Z5"/>
     <mergeCell ref="C40:L40"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="P11:Z11"/>
@@ -22122,6 +22239,12 @@
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="C26:L26"/>
     <mergeCell ref="C33:L33"/>
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="H3:L3"/>
+    <mergeCell ref="P3:W3"/>
+    <mergeCell ref="X3:Z3"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="P5:Z5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -22159,60 +22282,60 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="238" t="s">
+      <c r="C2" s="242" t="s">
         <v>112</v>
       </c>
-      <c r="D2" s="238"/>
-      <c r="E2" s="238"/>
-      <c r="F2" s="238"/>
-      <c r="G2" s="247"/>
-      <c r="H2" s="248" t="s">
+      <c r="D2" s="242"/>
+      <c r="E2" s="242"/>
+      <c r="F2" s="242"/>
+      <c r="G2" s="251"/>
+      <c r="H2" s="252" t="s">
         <v>113</v>
       </c>
-      <c r="I2" s="238"/>
-      <c r="J2" s="238"/>
-      <c r="K2" s="238"/>
-      <c r="L2" s="238"/>
-      <c r="S2" s="249"/>
-      <c r="T2" s="249"/>
-      <c r="U2" s="249"/>
-      <c r="V2" s="249"/>
-      <c r="W2" s="249"/>
-      <c r="X2" s="249"/>
-      <c r="Y2" s="249"/>
-      <c r="Z2" s="249"/>
-      <c r="AA2" s="249"/>
-      <c r="AB2" s="249"/>
-      <c r="AC2" s="249"/>
+      <c r="I2" s="242"/>
+      <c r="J2" s="242"/>
+      <c r="K2" s="242"/>
+      <c r="L2" s="242"/>
+      <c r="S2" s="253"/>
+      <c r="T2" s="253"/>
+      <c r="U2" s="253"/>
+      <c r="V2" s="253"/>
+      <c r="W2" s="253"/>
+      <c r="X2" s="253"/>
+      <c r="Y2" s="253"/>
+      <c r="Z2" s="253"/>
+      <c r="AA2" s="253"/>
+      <c r="AB2" s="253"/>
+      <c r="AC2" s="253"/>
       <c r="AE2" s="111"/>
     </row>
     <row r="3" spans="1:31" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="86"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="244" t="s">
+      <c r="C4" s="248" t="s">
         <v>18</v>
       </c>
-      <c r="D4" s="244"/>
-      <c r="E4" s="244"/>
-      <c r="F4" s="244"/>
-      <c r="G4" s="244"/>
-      <c r="H4" s="244"/>
-      <c r="I4" s="244"/>
-      <c r="J4" s="244"/>
-      <c r="K4" s="244"/>
-      <c r="L4" s="244"/>
-      <c r="S4" s="249"/>
-      <c r="T4" s="249"/>
-      <c r="U4" s="249"/>
-      <c r="V4" s="249"/>
-      <c r="W4" s="249"/>
-      <c r="X4" s="249"/>
-      <c r="Y4" s="249"/>
-      <c r="Z4" s="249"/>
-      <c r="AA4" s="249"/>
-      <c r="AB4" s="249"/>
-      <c r="AC4" s="249"/>
+      <c r="D4" s="248"/>
+      <c r="E4" s="248"/>
+      <c r="F4" s="248"/>
+      <c r="G4" s="248"/>
+      <c r="H4" s="248"/>
+      <c r="I4" s="248"/>
+      <c r="J4" s="248"/>
+      <c r="K4" s="248"/>
+      <c r="L4" s="248"/>
+      <c r="S4" s="253"/>
+      <c r="T4" s="253"/>
+      <c r="U4" s="253"/>
+      <c r="V4" s="253"/>
+      <c r="W4" s="253"/>
+      <c r="X4" s="253"/>
+      <c r="Y4" s="253"/>
+      <c r="Z4" s="253"/>
+      <c r="AA4" s="253"/>
+      <c r="AB4" s="253"/>
+      <c r="AC4" s="253"/>
       <c r="AE4" s="112"/>
     </row>
     <row r="5" spans="1:31" x14ac:dyDescent="0.2">
@@ -22575,18 +22698,18 @@
       <c r="AE10" s="64"/>
     </row>
     <row r="13" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="C13" s="244" t="s">
+      <c r="C13" s="248" t="s">
         <v>157</v>
       </c>
-      <c r="D13" s="244"/>
-      <c r="E13" s="244"/>
-      <c r="F13" s="244"/>
-      <c r="G13" s="244"/>
-      <c r="H13" s="244"/>
-      <c r="I13" s="244"/>
-      <c r="J13" s="244"/>
-      <c r="K13" s="244"/>
-      <c r="L13" s="244"/>
+      <c r="D13" s="248"/>
+      <c r="E13" s="248"/>
+      <c r="F13" s="248"/>
+      <c r="G13" s="248"/>
+      <c r="H13" s="248"/>
+      <c r="I13" s="248"/>
+      <c r="J13" s="248"/>
+      <c r="K13" s="248"/>
+      <c r="L13" s="248"/>
     </row>
     <row r="14" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C14" s="12">
@@ -22679,18 +22802,18 @@
       </c>
     </row>
     <row r="18" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C18" s="244" t="s">
+      <c r="C18" s="248" t="s">
         <v>158</v>
       </c>
-      <c r="D18" s="244"/>
-      <c r="E18" s="244"/>
-      <c r="F18" s="244"/>
-      <c r="G18" s="244"/>
-      <c r="H18" s="244"/>
-      <c r="I18" s="244"/>
-      <c r="J18" s="244"/>
-      <c r="K18" s="244"/>
-      <c r="L18" s="244"/>
+      <c r="D18" s="248"/>
+      <c r="E18" s="248"/>
+      <c r="F18" s="248"/>
+      <c r="G18" s="248"/>
+      <c r="H18" s="248"/>
+      <c r="I18" s="248"/>
+      <c r="J18" s="248"/>
+      <c r="K18" s="248"/>
+      <c r="L18" s="248"/>
     </row>
     <row r="19" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B19" s="16" t="s">
@@ -22882,18 +23005,18 @@
       </c>
     </row>
     <row r="25" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C25" s="244" t="s">
+      <c r="C25" s="248" t="s">
         <v>261</v>
       </c>
-      <c r="D25" s="244"/>
-      <c r="E25" s="244"/>
-      <c r="F25" s="244"/>
-      <c r="G25" s="244"/>
-      <c r="H25" s="244"/>
-      <c r="I25" s="244"/>
-      <c r="J25" s="244"/>
-      <c r="K25" s="244"/>
-      <c r="L25" s="244"/>
+      <c r="D25" s="248"/>
+      <c r="E25" s="248"/>
+      <c r="F25" s="248"/>
+      <c r="G25" s="248"/>
+      <c r="H25" s="248"/>
+      <c r="I25" s="248"/>
+      <c r="J25" s="248"/>
+      <c r="K25" s="248"/>
+      <c r="L25" s="248"/>
     </row>
     <row r="26" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B26" s="16" t="s">
@@ -23031,18 +23154,18 @@
       </c>
     </row>
     <row r="31" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C31" s="244" t="s">
+      <c r="C31" s="248" t="s">
         <v>77</v>
       </c>
-      <c r="D31" s="244"/>
-      <c r="E31" s="244"/>
-      <c r="F31" s="244"/>
-      <c r="G31" s="244"/>
-      <c r="H31" s="244"/>
-      <c r="I31" s="244"/>
-      <c r="J31" s="244"/>
-      <c r="K31" s="244"/>
-      <c r="L31" s="244"/>
+      <c r="D31" s="248"/>
+      <c r="E31" s="248"/>
+      <c r="F31" s="248"/>
+      <c r="G31" s="248"/>
+      <c r="H31" s="248"/>
+      <c r="I31" s="248"/>
+      <c r="J31" s="248"/>
+      <c r="K31" s="248"/>
+      <c r="L31" s="248"/>
     </row>
     <row r="32" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B32" s="16" t="s">
@@ -23181,16 +23304,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="C31:L31"/>
+    <mergeCell ref="C25:L25"/>
+    <mergeCell ref="C2:G2"/>
+    <mergeCell ref="H2:L2"/>
+    <mergeCell ref="S2:Z2"/>
     <mergeCell ref="AA2:AC2"/>
     <mergeCell ref="C4:L4"/>
     <mergeCell ref="S4:AC4"/>
     <mergeCell ref="C13:L13"/>
     <mergeCell ref="C18:L18"/>
-    <mergeCell ref="C31:L31"/>
-    <mergeCell ref="C25:L25"/>
-    <mergeCell ref="C2:G2"/>
-    <mergeCell ref="H2:L2"/>
-    <mergeCell ref="S2:Z2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -23204,18 +23327,57 @@
   <sheetPr>
     <tabColor theme="6" tint="0.59999389629810485"/>
   </sheetPr>
-  <dimension ref="B13"/>
+  <dimension ref="B5:H13"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="16384" width="10.83203125" style="1"/>
+    <col min="1" max="7" width="10.83203125" style="1"/>
+    <col min="8" max="8" width="17" style="1" customWidth="1"/>
+    <col min="9" max="16384" width="10.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="13" spans="2:2" s="4" customFormat="1" ht="49" x14ac:dyDescent="0.2">
+    <row r="5" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H5" s="134" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="6" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H6" s="237" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="7" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H7" s="237" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="8" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H8" s="237" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="9" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H9" s="237" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="10" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H10" s="238" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="13" spans="2:8" s="4" customFormat="1" ht="49" x14ac:dyDescent="0.2">
       <c r="B13" s="3" t="s">
         <v>163</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="H6" location="Overview!B3" display="Overview'!B3" xr:uid="{3F1BD722-EB05-7242-9EDC-1F73528A64FB}"/>
+    <hyperlink ref="H8" location="'Analysis -&gt;'!B13" display="'Analysis -&gt;'!B13" xr:uid="{F95DEF6B-BD13-2A4F-B51B-3125CDE9F316}"/>
+    <hyperlink ref="H9" location="'Forecast -&gt;'!B13" display="'Forecast -&gt;'!B13" xr:uid="{9E581C8E-6290-CC41-BA81-976C5BB26121}"/>
+    <hyperlink ref="H10" location="'Valuation -&gt;'!B13" display="'Valuation -&gt;'!B13" xr:uid="{81F63A6C-25C5-A94E-AF54-5E57564326C4}"/>
+    <hyperlink ref="H7" location="'Financials -&gt;'!B13" display="'Financials -&gt;'!B13" xr:uid="{993BE835-95C3-AC40-ABD4-B3D7AA934040}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -23253,10 +23415,10 @@
     </row>
     <row r="3" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="238" t="s">
+      <c r="B4" s="242" t="s">
         <v>165</v>
       </c>
-      <c r="C4" s="238"/>
+      <c r="C4" s="242"/>
     </row>
     <row r="5" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" s="1" t="s">
@@ -23273,7 +23435,7 @@
       </c>
       <c r="C6" s="135">
         <f ca="1">Overview!C5</f>
-        <v>235.35</v>
+        <v>233.54</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -23282,7 +23444,7 @@
       </c>
       <c r="C7" s="136">
         <f ca="1">C5*C6</f>
-        <v>49423.5</v>
+        <v>49043.4</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -23341,10 +23503,10 @@
     </row>
     <row r="14" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="15" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="238" t="s">
+      <c r="B15" s="242" t="s">
         <v>172</v>
       </c>
-      <c r="C15" s="238"/>
+      <c r="C15" s="242"/>
     </row>
     <row r="16" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B16" s="1" t="s">
@@ -23352,7 +23514,7 @@
       </c>
       <c r="C16" s="46">
         <f ca="1">C8/(C8+C7)</f>
-        <v>6.5744827651389851E-2</v>
+        <v>6.6220626259010609E-2</v>
       </c>
     </row>
     <row r="17" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -23361,7 +23523,7 @@
       </c>
       <c r="C17" s="46">
         <f ca="1">C7/(C8+C7)</f>
-        <v>0.93425517234861011</v>
+        <v>0.9337793737409894</v>
       </c>
     </row>
     <row r="18" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -23388,7 +23550,7 @@
       </c>
       <c r="C20" s="46">
         <f ca="1">(C17*C19)+(C16*C18)</f>
-        <v>0.10763432097861117</v>
+        <v>0.10760404710270478</v>
       </c>
     </row>
   </sheetData>
@@ -23433,60 +23595,60 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="238" t="s">
+      <c r="C3" s="242" t="s">
         <v>112</v>
       </c>
-      <c r="D3" s="238"/>
-      <c r="E3" s="238"/>
-      <c r="F3" s="238"/>
-      <c r="G3" s="247"/>
-      <c r="H3" s="248" t="s">
+      <c r="D3" s="242"/>
+      <c r="E3" s="242"/>
+      <c r="F3" s="242"/>
+      <c r="G3" s="251"/>
+      <c r="H3" s="252" t="s">
         <v>113</v>
       </c>
-      <c r="I3" s="238"/>
-      <c r="J3" s="238"/>
-      <c r="K3" s="238"/>
-      <c r="L3" s="238"/>
-      <c r="P3" s="249"/>
-      <c r="Q3" s="249"/>
-      <c r="R3" s="249"/>
-      <c r="S3" s="249"/>
-      <c r="T3" s="249"/>
-      <c r="U3" s="249"/>
-      <c r="V3" s="249"/>
-      <c r="W3" s="249"/>
-      <c r="X3" s="249"/>
-      <c r="Y3" s="249"/>
-      <c r="Z3" s="249"/>
+      <c r="I3" s="242"/>
+      <c r="J3" s="242"/>
+      <c r="K3" s="242"/>
+      <c r="L3" s="242"/>
+      <c r="P3" s="253"/>
+      <c r="Q3" s="253"/>
+      <c r="R3" s="253"/>
+      <c r="S3" s="253"/>
+      <c r="T3" s="253"/>
+      <c r="U3" s="253"/>
+      <c r="V3" s="253"/>
+      <c r="W3" s="253"/>
+      <c r="X3" s="253"/>
+      <c r="Y3" s="253"/>
+      <c r="Z3" s="253"/>
       <c r="AB3" s="111"/>
     </row>
     <row r="4" spans="1:28" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="86"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="244" t="s">
+      <c r="C5" s="248" t="s">
         <v>179</v>
       </c>
-      <c r="D5" s="244"/>
-      <c r="E5" s="244"/>
-      <c r="F5" s="244"/>
-      <c r="G5" s="244"/>
-      <c r="H5" s="244"/>
-      <c r="I5" s="244"/>
-      <c r="J5" s="244"/>
-      <c r="K5" s="244"/>
-      <c r="L5" s="244"/>
-      <c r="P5" s="249"/>
-      <c r="Q5" s="249"/>
-      <c r="R5" s="249"/>
-      <c r="S5" s="249"/>
-      <c r="T5" s="249"/>
-      <c r="U5" s="249"/>
-      <c r="V5" s="249"/>
-      <c r="W5" s="249"/>
-      <c r="X5" s="249"/>
-      <c r="Y5" s="249"/>
-      <c r="Z5" s="249"/>
+      <c r="D5" s="248"/>
+      <c r="E5" s="248"/>
+      <c r="F5" s="248"/>
+      <c r="G5" s="248"/>
+      <c r="H5" s="248"/>
+      <c r="I5" s="248"/>
+      <c r="J5" s="248"/>
+      <c r="K5" s="248"/>
+      <c r="L5" s="248"/>
+      <c r="P5" s="253"/>
+      <c r="Q5" s="253"/>
+      <c r="R5" s="253"/>
+      <c r="S5" s="253"/>
+      <c r="T5" s="253"/>
+      <c r="U5" s="253"/>
+      <c r="V5" s="253"/>
+      <c r="W5" s="253"/>
+      <c r="X5" s="253"/>
+      <c r="Y5" s="253"/>
+      <c r="Z5" s="253"/>
       <c r="AB5" s="112"/>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.2">
@@ -23639,7 +23801,7 @@
       </c>
       <c r="L8" s="128">
         <f ca="1">L7*(1+C14)/(C15-C14)</f>
-        <v>28651.750610873107</v>
+        <v>28661.651974693403</v>
       </c>
       <c r="N8" s="91"/>
       <c r="O8" s="16"/>
@@ -23693,23 +23855,23 @@
       <c r="G10" s="140"/>
       <c r="H10" s="128">
         <f ca="1">H7/(1+$C$15)^H9</f>
-        <v>1860.6466094664568</v>
+        <v>1860.6974660742021</v>
       </c>
       <c r="I10" s="128">
         <f t="shared" ref="I10:L10" ca="1" si="0">I7/(1+$C$15)^I9</f>
-        <v>1268.5129118409311</v>
+        <v>1268.5822567072785</v>
       </c>
       <c r="J10" s="128">
         <f t="shared" ca="1" si="0"/>
-        <v>568.71848395531697</v>
+        <v>568.76511916793174</v>
       </c>
       <c r="K10" s="128">
         <f t="shared" ca="1" si="0"/>
-        <v>1416.1339584162217</v>
+        <v>1416.2887921641759</v>
       </c>
       <c r="L10" s="128">
         <f t="shared" ca="1" si="0"/>
-        <v>1476.5331274169041</v>
+        <v>1476.7349270781838</v>
       </c>
       <c r="N10" s="91"/>
     </row>
@@ -23728,14 +23890,14 @@
       <c r="K11" s="139"/>
       <c r="L11" s="128">
         <f ca="1">L8/(1+C15)^L9</f>
-        <v>17185.775768523683</v>
+        <v>17194.064377571904</v>
       </c>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B13" s="238" t="s">
+      <c r="B13" s="242" t="s">
         <v>183</v>
       </c>
-      <c r="C13" s="238"/>
+      <c r="C13" s="242"/>
     </row>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B14" s="1" t="s">
@@ -23751,14 +23913,14 @@
       </c>
       <c r="C15" s="137">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.10763432097861117</v>
+        <v>0.10760404710270478</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B18" s="238" t="s">
+      <c r="B18" s="242" t="s">
         <v>185</v>
       </c>
-      <c r="C18" s="238"/>
+      <c r="C18" s="242"/>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B19" s="1" t="s">
@@ -23766,7 +23928,7 @@
       </c>
       <c r="C19" s="64">
         <f ca="1">SUM(H10:L10)</f>
-        <v>6590.5450910958307</v>
+        <v>6591.0685611917725</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.2">
@@ -23775,7 +23937,7 @@
       </c>
       <c r="C20" s="64">
         <f ca="1">L11</f>
-        <v>17185.775768523683</v>
+        <v>17194.064377571904</v>
       </c>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.2">
@@ -23784,7 +23946,7 @@
       </c>
       <c r="C21" s="94">
         <f ca="1">C19+C20</f>
-        <v>23776.320859619515</v>
+        <v>23785.132938763676</v>
       </c>
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.2">
@@ -23811,7 +23973,7 @@
       </c>
       <c r="C24" s="94">
         <f ca="1">C21+C22-C23</f>
-        <v>24655.320859619515</v>
+        <v>24664.132938763676</v>
       </c>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.2">
@@ -23829,7 +23991,7 @@
       </c>
       <c r="C26" s="234">
         <f ca="1">C24/C25</f>
-        <v>117.40628980771197</v>
+        <v>117.44825208935085</v>
       </c>
     </row>
   </sheetData>
@@ -23872,37 +24034,37 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="238" t="s">
+      <c r="C2" s="242" t="s">
         <v>112</v>
       </c>
-      <c r="D2" s="238"/>
-      <c r="E2" s="238"/>
-      <c r="F2" s="238"/>
-      <c r="G2" s="247"/>
-      <c r="H2" s="248" t="s">
+      <c r="D2" s="242"/>
+      <c r="E2" s="242"/>
+      <c r="F2" s="242"/>
+      <c r="G2" s="251"/>
+      <c r="H2" s="252" t="s">
         <v>113</v>
       </c>
-      <c r="I2" s="238"/>
-      <c r="J2" s="238"/>
-      <c r="K2" s="238"/>
-      <c r="L2" s="238"/>
+      <c r="I2" s="242"/>
+      <c r="J2" s="242"/>
+      <c r="K2" s="242"/>
+      <c r="L2" s="242"/>
     </row>
     <row r="3" spans="1:14" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="86"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="244" t="s">
+      <c r="C4" s="248" t="s">
         <v>193</v>
       </c>
-      <c r="D4" s="244"/>
-      <c r="E4" s="244"/>
-      <c r="F4" s="244"/>
-      <c r="G4" s="244"/>
-      <c r="H4" s="244"/>
-      <c r="I4" s="244"/>
-      <c r="J4" s="244"/>
-      <c r="K4" s="244"/>
-      <c r="L4" s="244"/>
+      <c r="D4" s="248"/>
+      <c r="E4" s="248"/>
+      <c r="F4" s="248"/>
+      <c r="G4" s="248"/>
+      <c r="H4" s="248"/>
+      <c r="I4" s="248"/>
+      <c r="J4" s="248"/>
+      <c r="K4" s="248"/>
+      <c r="L4" s="248"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B5" s="16" t="s">
@@ -24098,23 +24260,23 @@
       <c r="G9" s="140"/>
       <c r="H9" s="92">
         <f ca="1">DCF!H10</f>
-        <v>1860.6466094664568</v>
+        <v>1860.6974660742021</v>
       </c>
       <c r="I9" s="92">
         <f ca="1">DCF!I10</f>
-        <v>1268.5129118409311</v>
+        <v>1268.5822567072785</v>
       </c>
       <c r="J9" s="92">
         <f ca="1">DCF!J10</f>
-        <v>568.71848395531697</v>
+        <v>568.76511916793174</v>
       </c>
       <c r="K9" s="92">
         <f ca="1">DCF!K10</f>
-        <v>1416.1339584162217</v>
+        <v>1416.2887921641759</v>
       </c>
       <c r="L9" s="92">
         <f ca="1">DCF!L10</f>
-        <v>1476.5331274169041</v>
+        <v>1476.7349270781838</v>
       </c>
       <c r="N9" s="91"/>
     </row>
@@ -24122,18 +24284,18 @@
       <c r="N10" s="91"/>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C11" s="244" t="s">
+      <c r="C11" s="248" t="s">
         <v>121</v>
       </c>
-      <c r="D11" s="244"/>
-      <c r="E11" s="244"/>
-      <c r="F11" s="244"/>
-      <c r="G11" s="244"/>
-      <c r="H11" s="244"/>
-      <c r="I11" s="244"/>
-      <c r="J11" s="244"/>
-      <c r="K11" s="244"/>
-      <c r="L11" s="244"/>
+      <c r="D11" s="248"/>
+      <c r="E11" s="248"/>
+      <c r="F11" s="248"/>
+      <c r="G11" s="248"/>
+      <c r="H11" s="248"/>
+      <c r="I11" s="248"/>
+      <c r="J11" s="248"/>
+      <c r="K11" s="248"/>
+      <c r="L11" s="248"/>
       <c r="N11" s="91"/>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.2">
@@ -24327,18 +24489,18 @@
       <c r="N16" s="91"/>
     </row>
     <row r="17" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C17" s="244" t="s">
+      <c r="C17" s="248" t="s">
         <v>195</v>
       </c>
-      <c r="D17" s="244"/>
-      <c r="E17" s="244"/>
-      <c r="F17" s="244"/>
-      <c r="G17" s="244"/>
-      <c r="H17" s="244"/>
-      <c r="I17" s="244"/>
-      <c r="J17" s="244"/>
-      <c r="K17" s="244"/>
-      <c r="L17" s="244"/>
+      <c r="D17" s="248"/>
+      <c r="E17" s="248"/>
+      <c r="F17" s="248"/>
+      <c r="G17" s="248"/>
+      <c r="H17" s="248"/>
+      <c r="I17" s="248"/>
+      <c r="J17" s="248"/>
+      <c r="K17" s="248"/>
+      <c r="L17" s="248"/>
       <c r="N17" s="91"/>
     </row>
     <row r="18" spans="2:14" x14ac:dyDescent="0.2">
@@ -24472,18 +24634,18 @@
       <c r="N21" s="91"/>
     </row>
     <row r="22" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C22" s="244" t="s">
+      <c r="C22" s="248" t="s">
         <v>198</v>
       </c>
-      <c r="D22" s="244"/>
-      <c r="E22" s="244"/>
-      <c r="F22" s="244"/>
-      <c r="G22" s="244"/>
-      <c r="H22" s="244"/>
-      <c r="I22" s="244"/>
-      <c r="J22" s="244"/>
-      <c r="K22" s="244"/>
-      <c r="L22" s="244"/>
+      <c r="D22" s="248"/>
+      <c r="E22" s="248"/>
+      <c r="F22" s="248"/>
+      <c r="G22" s="248"/>
+      <c r="H22" s="248"/>
+      <c r="I22" s="248"/>
+      <c r="J22" s="248"/>
+      <c r="K22" s="248"/>
+      <c r="L22" s="248"/>
       <c r="N22" s="91"/>
     </row>
     <row r="23" spans="2:14" x14ac:dyDescent="0.2">
@@ -24567,18 +24729,18 @@
       <c r="N26" s="91"/>
     </row>
     <row r="27" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C27" s="244" t="s">
+      <c r="C27" s="248" t="s">
         <v>199</v>
       </c>
-      <c r="D27" s="244"/>
-      <c r="E27" s="244"/>
-      <c r="F27" s="244"/>
-      <c r="G27" s="244"/>
-      <c r="H27" s="244"/>
-      <c r="I27" s="244"/>
-      <c r="J27" s="244"/>
-      <c r="K27" s="244"/>
-      <c r="L27" s="244"/>
+      <c r="D27" s="248"/>
+      <c r="E27" s="248"/>
+      <c r="F27" s="248"/>
+      <c r="G27" s="248"/>
+      <c r="H27" s="248"/>
+      <c r="I27" s="248"/>
+      <c r="J27" s="248"/>
+      <c r="K27" s="248"/>
+      <c r="L27" s="248"/>
       <c r="N27" s="91"/>
     </row>
     <row r="28" spans="2:14" x14ac:dyDescent="0.2">
@@ -24879,10 +25041,10 @@
       <c r="N38" s="91"/>
     </row>
     <row r="39" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B39" s="238" t="s">
+      <c r="B39" s="242" t="s">
         <v>204</v>
       </c>
-      <c r="C39" s="238"/>
+      <c r="C39" s="242"/>
       <c r="N39" s="91"/>
     </row>
     <row r="40" spans="2:14" x14ac:dyDescent="0.2">
@@ -24900,7 +25062,7 @@
       </c>
       <c r="C41" s="137">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.10763432097861117</v>
+        <v>0.10760404710270478</v>
       </c>
     </row>
     <row r="42" spans="2:14" x14ac:dyDescent="0.2">
@@ -24926,7 +25088,7 @@
       </c>
       <c r="C44" s="24">
         <f ca="1">C43/(1+C41)^5</f>
-        <v>66766.872055263157</v>
+        <v>66775.99716862179</v>
       </c>
     </row>
     <row r="45" spans="2:14" x14ac:dyDescent="0.2">
@@ -24935,7 +25097,7 @@
       </c>
       <c r="C45" s="108">
         <f ca="1">SUM(H9:K9)+C44</f>
-        <v>71880.884018942088</v>
+        <v>71890.330802735378</v>
       </c>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.2">
@@ -24962,7 +25124,7 @@
       </c>
       <c r="C48" s="108">
         <f ca="1">C45+C46-C47</f>
-        <v>72759.884018942088</v>
+        <v>72769.330802735378</v>
       </c>
     </row>
     <row r="49" spans="2:3" x14ac:dyDescent="0.2">
@@ -24980,14 +25142,14 @@
       </c>
       <c r="C50" s="234">
         <f ca="1">C48/C49</f>
-        <v>346.47563818543853</v>
+        <v>346.52062287016844</v>
       </c>
     </row>
     <row r="52" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B52" s="238" t="s">
+      <c r="B52" s="242" t="s">
         <v>209</v>
       </c>
-      <c r="C52" s="238"/>
+      <c r="C52" s="242"/>
     </row>
     <row r="53" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B53" s="1" t="s">
@@ -25043,10 +25205,10 @@
       </c>
     </row>
     <row r="60" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B60" s="238" t="s">
+      <c r="B60" s="242" t="s">
         <v>321</v>
       </c>
-      <c r="C60" s="238"/>
+      <c r="C60" s="242"/>
     </row>
     <row r="61" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B61" s="1" t="s">
@@ -25063,7 +25225,7 @@
       </c>
       <c r="C62" s="137">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.10763432097861117</v>
+        <v>0.10760404710270478</v>
       </c>
     </row>
     <row r="63" spans="2:3" x14ac:dyDescent="0.2">
@@ -25089,7 +25251,7 @@
       </c>
       <c r="C65" s="24">
         <f ca="1">C64/(1+C62)^5</f>
-        <v>66443.990733760686</v>
+        <v>66453.071718518273</v>
       </c>
     </row>
     <row r="66" spans="2:3" x14ac:dyDescent="0.2">
@@ -25098,7 +25260,7 @@
       </c>
       <c r="C66" s="108">
         <f ca="1">SUM(H9:K9)+C65</f>
-        <v>71558.002697439617</v>
+        <v>71567.40535263186</v>
       </c>
     </row>
     <row r="67" spans="2:3" x14ac:dyDescent="0.2">
@@ -25125,7 +25287,7 @@
       </c>
       <c r="C69" s="108">
         <f ca="1">C66+C67-C68</f>
-        <v>72437.002697439617</v>
+        <v>72446.40535263186</v>
       </c>
     </row>
     <row r="70" spans="2:3" x14ac:dyDescent="0.2">
@@ -25143,14 +25305,14 @@
       </c>
       <c r="C71" s="234">
         <f ca="1">C69/C70</f>
-        <v>344.93810808304579</v>
+        <v>344.98288263158031</v>
       </c>
     </row>
     <row r="73" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B73" s="238" t="s">
+      <c r="B73" s="242" t="s">
         <v>379</v>
       </c>
-      <c r="C73" s="238"/>
+      <c r="C73" s="242"/>
     </row>
     <row r="74" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B74" s="1" t="s">
@@ -25167,7 +25329,7 @@
       </c>
       <c r="C75" s="137">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.10763432097861117</v>
+        <v>0.10760404710270478</v>
       </c>
     </row>
     <row r="76" spans="2:3" x14ac:dyDescent="0.2">
@@ -25193,7 +25355,7 @@
       </c>
       <c r="C78" s="24">
         <f ca="1">C77/(1+C75)^5</f>
-        <v>40143.621966848928</v>
+        <v>40149.108446742284</v>
       </c>
     </row>
     <row r="79" spans="2:3" x14ac:dyDescent="0.2">
@@ -25202,7 +25364,7 @@
       </c>
       <c r="C79" s="108">
         <f ca="1">SUM(H9:K9)+C78</f>
-        <v>45257.633930527852</v>
+        <v>45263.442080855872</v>
       </c>
     </row>
     <row r="80" spans="2:3" x14ac:dyDescent="0.2">
@@ -25229,7 +25391,7 @@
       </c>
       <c r="C82" s="108">
         <f ca="1">C79+C80-C81</f>
-        <v>46136.633930527852</v>
+        <v>46142.442080855872</v>
       </c>
     </row>
     <row r="83" spans="2:3" x14ac:dyDescent="0.2">
@@ -25247,22 +25409,22 @@
       </c>
       <c r="C84" s="234">
         <f ca="1">C82/C83</f>
-        <v>219.69825681203739</v>
+        <v>219.72591467074224</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="B73:C73"/>
+    <mergeCell ref="C27:L27"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="B60:C60"/>
     <mergeCell ref="C22:L22"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="H2:L2"/>
     <mergeCell ref="C4:L4"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="C17:L17"/>
-    <mergeCell ref="B73:C73"/>
-    <mergeCell ref="C27:L27"/>
-    <mergeCell ref="B39:C39"/>
-    <mergeCell ref="B52:C52"/>
-    <mergeCell ref="B60:C60"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -25300,10 +25462,10 @@
       <c r="N3" s="91"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B4" s="238" t="s">
+      <c r="B4" s="242" t="s">
         <v>213</v>
       </c>
-      <c r="C4" s="238"/>
+      <c r="C4" s="242"/>
       <c r="N4" s="91"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
@@ -25312,7 +25474,7 @@
       </c>
       <c r="C5" s="135">
         <f ca="1">DCF!C26</f>
-        <v>117.40628980771197</v>
+        <v>117.44825208935085</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.2">
@@ -25321,7 +25483,7 @@
       </c>
       <c r="C6" s="135">
         <f ca="1">Multiples!C50</f>
-        <v>346.47563818543853</v>
+        <v>346.52062287016844</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.2">
@@ -25339,7 +25501,7 @@
       </c>
       <c r="C8" s="135">
         <f ca="1">Multiples!C71</f>
-        <v>344.93810808304579</v>
+        <v>344.98288263158031</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
@@ -25348,7 +25510,7 @@
       </c>
       <c r="C9" s="135">
         <f ca="1">Multiples!C84</f>
-        <v>219.69825681203739</v>
+        <v>219.72591467074224</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
@@ -25357,7 +25519,7 @@
       </c>
       <c r="C10" s="234">
         <f ca="1">AVERAGE(C5:C9)</f>
-        <v>243.35592260493453</v>
+        <v>243.38779847965617</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -25366,7 +25528,7 @@
       </c>
       <c r="C11" s="135">
         <f ca="1">Overview!C5</f>
-        <v>235.35</v>
+        <v>233.54</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.2">
@@ -25375,7 +25537,7 @@
       </c>
       <c r="C12" s="154">
         <f ca="1">(C10-C11)/C11</f>
-        <v>3.4017092011619038E-2</v>
+        <v>4.2167502267946293E-2</v>
       </c>
     </row>
   </sheetData>
@@ -25391,18 +25553,57 @@
   <sheetPr>
     <tabColor theme="6" tint="0.59999389629810485"/>
   </sheetPr>
-  <dimension ref="B13"/>
+  <dimension ref="B5:H13"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="16384" width="10.83203125" style="1"/>
+    <col min="1" max="7" width="10.83203125" style="1"/>
+    <col min="8" max="8" width="17.1640625" style="1" customWidth="1"/>
+    <col min="9" max="16384" width="10.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="13" spans="2:2" s="4" customFormat="1" ht="49" x14ac:dyDescent="0.2">
+    <row r="5" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H5" s="134" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="6" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H6" s="237" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="7" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H7" s="237" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="8" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H8" s="237" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="9" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H9" s="237" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="10" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H10" s="238" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="13" spans="2:8" s="4" customFormat="1" ht="49" x14ac:dyDescent="0.2">
       <c r="B13" s="3" t="s">
         <v>14</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="H6" location="Overview!B3" display="Overview'!B3" xr:uid="{91129D30-5528-2248-85DB-C9607A2D03AD}"/>
+    <hyperlink ref="H8" location="'Analysis -&gt;'!B13" display="'Analysis -&gt;'!B13" xr:uid="{4617514C-0F58-7C45-9397-29D85A4DFCAC}"/>
+    <hyperlink ref="H9" location="'Forecast -&gt;'!B13" display="'Forecast -&gt;'!B13" xr:uid="{6076256E-B478-D248-A480-D7855B180EE4}"/>
+    <hyperlink ref="H10" location="'Valuation -&gt;'!B13" display="'Valuation -&gt;'!B13" xr:uid="{9559CE97-633C-314C-8A02-98D2E6E533A5}"/>
+    <hyperlink ref="H7" location="'Financials -&gt;'!B13" display="'Financials -&gt;'!B13" xr:uid="{4E254FFE-5ADE-A24D-A746-D07E81A1B570}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -25431,37 +25632,37 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="238" t="s">
+      <c r="C2" s="242" t="s">
         <v>112</v>
       </c>
-      <c r="D2" s="238"/>
-      <c r="E2" s="238"/>
-      <c r="F2" s="238"/>
-      <c r="G2" s="247"/>
-      <c r="H2" s="248" t="s">
+      <c r="D2" s="242"/>
+      <c r="E2" s="242"/>
+      <c r="F2" s="242"/>
+      <c r="G2" s="251"/>
+      <c r="H2" s="252" t="s">
         <v>113</v>
       </c>
-      <c r="I2" s="238"/>
-      <c r="J2" s="238"/>
-      <c r="K2" s="238"/>
-      <c r="L2" s="238"/>
+      <c r="I2" s="242"/>
+      <c r="J2" s="242"/>
+      <c r="K2" s="242"/>
+      <c r="L2" s="242"/>
     </row>
     <row r="3" spans="1:14" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="86"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="244" t="s">
+      <c r="C4" s="248" t="s">
         <v>193</v>
       </c>
-      <c r="D4" s="244"/>
-      <c r="E4" s="244"/>
-      <c r="F4" s="244"/>
-      <c r="G4" s="244"/>
-      <c r="H4" s="244"/>
-      <c r="I4" s="244"/>
-      <c r="J4" s="244"/>
-      <c r="K4" s="244"/>
-      <c r="L4" s="244"/>
+      <c r="D4" s="248"/>
+      <c r="E4" s="248"/>
+      <c r="F4" s="248"/>
+      <c r="G4" s="248"/>
+      <c r="H4" s="248"/>
+      <c r="I4" s="248"/>
+      <c r="J4" s="248"/>
+      <c r="K4" s="248"/>
+      <c r="L4" s="248"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B5" s="16" t="s">
@@ -25574,18 +25775,18 @@
       <c r="N8" s="91"/>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C9" s="244" t="s">
+      <c r="C9" s="248" t="s">
         <v>121</v>
       </c>
-      <c r="D9" s="244"/>
-      <c r="E9" s="244"/>
-      <c r="F9" s="244"/>
-      <c r="G9" s="244"/>
-      <c r="H9" s="244"/>
-      <c r="I9" s="244"/>
-      <c r="J9" s="244"/>
-      <c r="K9" s="244"/>
-      <c r="L9" s="244"/>
+      <c r="D9" s="248"/>
+      <c r="E9" s="248"/>
+      <c r="F9" s="248"/>
+      <c r="G9" s="248"/>
+      <c r="H9" s="248"/>
+      <c r="I9" s="248"/>
+      <c r="J9" s="248"/>
+      <c r="K9" s="248"/>
+      <c r="L9" s="248"/>
       <c r="N9" s="91"/>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
@@ -25706,18 +25907,18 @@
       <c r="N13" s="91"/>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C14" s="244" t="s">
+      <c r="C14" s="248" t="s">
         <v>367</v>
       </c>
-      <c r="D14" s="244"/>
-      <c r="E14" s="244"/>
-      <c r="F14" s="244"/>
-      <c r="G14" s="244"/>
-      <c r="H14" s="244"/>
-      <c r="I14" s="244"/>
-      <c r="J14" s="244"/>
-      <c r="K14" s="244"/>
-      <c r="L14" s="244"/>
+      <c r="D14" s="248"/>
+      <c r="E14" s="248"/>
+      <c r="F14" s="248"/>
+      <c r="G14" s="248"/>
+      <c r="H14" s="248"/>
+      <c r="I14" s="248"/>
+      <c r="J14" s="248"/>
+      <c r="K14" s="248"/>
+      <c r="L14" s="248"/>
       <c r="N14" s="91"/>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.2">
@@ -25807,10 +26008,10 @@
       <c r="N19" s="91"/>
     </row>
     <row r="20" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B20" s="238" t="s">
+      <c r="B20" s="242" t="s">
         <v>369</v>
       </c>
-      <c r="C20" s="238"/>
+      <c r="C20" s="242"/>
       <c r="N20" s="91"/>
     </row>
     <row r="21" spans="2:14" x14ac:dyDescent="0.2">
@@ -25911,60 +26112,60 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="238" t="s">
+      <c r="C3" s="242" t="s">
         <v>112</v>
       </c>
-      <c r="D3" s="238"/>
-      <c r="E3" s="238"/>
-      <c r="F3" s="238"/>
-      <c r="G3" s="247"/>
-      <c r="H3" s="248" t="s">
+      <c r="D3" s="242"/>
+      <c r="E3" s="242"/>
+      <c r="F3" s="242"/>
+      <c r="G3" s="251"/>
+      <c r="H3" s="252" t="s">
         <v>113</v>
       </c>
-      <c r="I3" s="238"/>
-      <c r="J3" s="238"/>
-      <c r="K3" s="238"/>
-      <c r="L3" s="238"/>
-      <c r="P3" s="249"/>
-      <c r="Q3" s="249"/>
-      <c r="R3" s="249"/>
-      <c r="S3" s="249"/>
-      <c r="T3" s="249"/>
-      <c r="U3" s="249"/>
-      <c r="V3" s="249"/>
-      <c r="W3" s="249"/>
-      <c r="X3" s="249"/>
-      <c r="Y3" s="249"/>
-      <c r="Z3" s="249"/>
+      <c r="I3" s="242"/>
+      <c r="J3" s="242"/>
+      <c r="K3" s="242"/>
+      <c r="L3" s="242"/>
+      <c r="P3" s="253"/>
+      <c r="Q3" s="253"/>
+      <c r="R3" s="253"/>
+      <c r="S3" s="253"/>
+      <c r="T3" s="253"/>
+      <c r="U3" s="253"/>
+      <c r="V3" s="253"/>
+      <c r="W3" s="253"/>
+      <c r="X3" s="253"/>
+      <c r="Y3" s="253"/>
+      <c r="Z3" s="253"/>
       <c r="AB3" s="111"/>
     </row>
     <row r="4" spans="1:28" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="86"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="244" t="s">
+      <c r="C5" s="248" t="s">
         <v>179</v>
       </c>
-      <c r="D5" s="244"/>
-      <c r="E5" s="244"/>
-      <c r="F5" s="244"/>
-      <c r="G5" s="244"/>
-      <c r="H5" s="244"/>
-      <c r="I5" s="244"/>
-      <c r="J5" s="244"/>
-      <c r="K5" s="244"/>
-      <c r="L5" s="244"/>
-      <c r="P5" s="249"/>
-      <c r="Q5" s="249"/>
-      <c r="R5" s="249"/>
-      <c r="S5" s="249"/>
-      <c r="T5" s="249"/>
-      <c r="U5" s="249"/>
-      <c r="V5" s="249"/>
-      <c r="W5" s="249"/>
-      <c r="X5" s="249"/>
-      <c r="Y5" s="249"/>
-      <c r="Z5" s="249"/>
+      <c r="D5" s="248"/>
+      <c r="E5" s="248"/>
+      <c r="F5" s="248"/>
+      <c r="G5" s="248"/>
+      <c r="H5" s="248"/>
+      <c r="I5" s="248"/>
+      <c r="J5" s="248"/>
+      <c r="K5" s="248"/>
+      <c r="L5" s="248"/>
+      <c r="P5" s="253"/>
+      <c r="Q5" s="253"/>
+      <c r="R5" s="253"/>
+      <c r="S5" s="253"/>
+      <c r="T5" s="253"/>
+      <c r="U5" s="253"/>
+      <c r="V5" s="253"/>
+      <c r="W5" s="253"/>
+      <c r="X5" s="253"/>
+      <c r="Y5" s="253"/>
+      <c r="Z5" s="253"/>
       <c r="AB5" s="112"/>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.2">
@@ -26099,7 +26300,7 @@
       <c r="K8" s="139"/>
       <c r="L8" s="128">
         <f ca="1">L7*(1+C20)/(C21-C20)</f>
-        <v>56902.938754901152</v>
+        <v>56922.603057676512</v>
       </c>
       <c r="N8" s="91"/>
       <c r="O8" s="16"/>
@@ -26153,23 +26354,23 @@
       <c r="G10" s="140"/>
       <c r="H10" s="128">
         <f ca="1">H7/(1+$C$21)^H9</f>
-        <v>958.21253378102085</v>
+        <v>958.23872437450552</v>
       </c>
       <c r="I10" s="128">
         <f t="shared" ref="I10:L10" ca="1" si="1">I7/(1+$C$21)^I9</f>
-        <v>1267.3689641080587</v>
+        <v>1267.438246439053</v>
       </c>
       <c r="J10" s="128">
         <f t="shared" ca="1" si="1"/>
-        <v>1676.2712180838603</v>
+        <v>1676.4086731989319</v>
       </c>
       <c r="K10" s="128">
         <f t="shared" ca="1" si="1"/>
-        <v>2217.1011569262091</v>
+        <v>2217.3435648422683</v>
       </c>
       <c r="L10" s="128">
         <f t="shared" ca="1" si="1"/>
-        <v>2932.4237551859114</v>
+        <v>2932.8245332717784</v>
       </c>
       <c r="N10" s="91"/>
     </row>
@@ -26188,15 +26389,15 @@
       <c r="K11" s="139"/>
       <c r="L11" s="128">
         <f ca="1">L8/(1+C21)^L9</f>
-        <v>34131.287797844161</v>
+        <v>34147.749138005885</v>
       </c>
     </row>
     <row r="13" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B14" s="251" t="s">
+      <c r="B14" s="254" t="s">
         <v>221</v>
       </c>
-      <c r="C14" s="252"/>
+      <c r="C14" s="255"/>
     </row>
     <row r="15" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B15" s="155" t="s">
@@ -26204,7 +26405,7 @@
       </c>
       <c r="C15" s="156">
         <f ca="1">Overview!C5</f>
-        <v>235.35</v>
+        <v>233.54</v>
       </c>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.2">
@@ -26213,7 +26414,7 @@
       </c>
       <c r="C16" s="156">
         <f ca="1">C36</f>
-        <v>210.82136567430248</v>
+        <v>210.90432000063359</v>
       </c>
     </row>
     <row r="17" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -26223,20 +26424,20 @@
       <c r="C17" s="158">
         <v>0.46500000000000002</v>
       </c>
-      <c r="E17" s="250" t="s">
+      <c r="E17" s="256" t="s">
         <v>224</v>
       </c>
-      <c r="F17" s="250"/>
-      <c r="G17" s="250"/>
-      <c r="H17" s="250"/>
-      <c r="I17" s="250"/>
+      <c r="F17" s="256"/>
+      <c r="G17" s="256"/>
+      <c r="H17" s="256"/>
+      <c r="I17" s="256"/>
     </row>
     <row r="18" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="19" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B19" s="251" t="s">
+      <c r="B19" s="254" t="s">
         <v>183</v>
       </c>
-      <c r="C19" s="252"/>
+      <c r="C19" s="255"/>
     </row>
     <row r="20" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B20" s="159" t="s">
@@ -26252,7 +26453,7 @@
       </c>
       <c r="C21" s="220">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.10763432097861117</v>
+        <v>0.10760404710270478</v>
       </c>
     </row>
     <row r="22" spans="2:9" x14ac:dyDescent="0.2">
@@ -26270,7 +26471,7 @@
       </c>
       <c r="C23" s="161">
         <f ca="1">C15*C22</f>
-        <v>49188.15</v>
+        <v>48809.86</v>
       </c>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.2">
@@ -26297,15 +26498,15 @@
       </c>
       <c r="C26" s="162">
         <f ca="1">C23+C25-C24</f>
-        <v>48309.15</v>
+        <v>47930.86</v>
       </c>
     </row>
     <row r="27" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B28" s="251" t="s">
+      <c r="B28" s="254" t="s">
         <v>185</v>
       </c>
-      <c r="C28" s="252"/>
+      <c r="C28" s="255"/>
     </row>
     <row r="29" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B29" s="159" t="s">
@@ -26313,7 +26514,7 @@
       </c>
       <c r="C29" s="161">
         <f ca="1">SUM(H10:L10)</f>
-        <v>9051.3776280850598</v>
+        <v>9052.253742126537</v>
       </c>
     </row>
     <row r="30" spans="2:9" x14ac:dyDescent="0.2">
@@ -26322,7 +26523,7 @@
       </c>
       <c r="C30" s="161">
         <f ca="1">L11</f>
-        <v>34131.287797844161</v>
+        <v>34147.749138005885</v>
       </c>
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.2">
@@ -26331,7 +26532,7 @@
       </c>
       <c r="C31" s="164">
         <f ca="1">C29+C30</f>
-        <v>43182.665425929219</v>
+        <v>43200.002880132422</v>
       </c>
     </row>
     <row r="32" spans="2:9" x14ac:dyDescent="0.2">
@@ -26358,7 +26559,7 @@
       </c>
       <c r="C34" s="164">
         <f ca="1">C31+C32-C33</f>
-        <v>44061.665425929219</v>
+        <v>44079.002880132422</v>
       </c>
     </row>
     <row r="35" spans="2:3" x14ac:dyDescent="0.2">
@@ -26376,21 +26577,21 @@
       </c>
       <c r="C36" s="167">
         <f ca="1">C34/C35</f>
-        <v>210.82136567430248</v>
+        <v>210.90432000063359</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="E17:I17"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="H3:L3"/>
     <mergeCell ref="P3:W3"/>
     <mergeCell ref="X3:Z3"/>
     <mergeCell ref="C5:L5"/>
     <mergeCell ref="P5:Z5"/>
     <mergeCell ref="B14:C14"/>
-    <mergeCell ref="E17:I17"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="H3:L3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -33046,7 +33247,7 @@
       </c>
       <c r="AC117" s="63">
         <f ca="1">Overview!C5</f>
-        <v>235.35</v>
+        <v>233.54</v>
       </c>
     </row>
     <row r="118" spans="1:31" x14ac:dyDescent="0.2">
@@ -33117,7 +33318,7 @@
       </c>
       <c r="AC118" s="65">
         <f ca="1">AC117/AC86</f>
-        <v>235.35</v>
+        <v>233.54</v>
       </c>
     </row>
     <row r="120" spans="1:31" x14ac:dyDescent="0.2">
@@ -34423,7 +34624,7 @@
       <c r="AA151" s="49"/>
       <c r="AC151" s="72">
         <f ca="1">AC118/Statement!AC27</f>
-        <v>30.44631306597671</v>
+        <v>30.212160413971535</v>
       </c>
     </row>
     <row r="152" spans="2:29" x14ac:dyDescent="0.2">
@@ -34460,7 +34661,7 @@
       <c r="AA152" s="49"/>
       <c r="AC152" s="72">
         <f ca="1">AC118/(Statement!AC5/Statement!AC23)</f>
-        <v>6.4351155327342751</v>
+        <v>6.3856251604621308</v>
       </c>
     </row>
     <row r="153" spans="2:29" x14ac:dyDescent="0.2">
@@ -34521,7 +34722,7 @@
       </c>
       <c r="AC153" s="72">
         <f ca="1">AC118/(Statement!AC50/Statement!AC76)</f>
-        <v>14.539801950931125</v>
+        <v>14.427981081879986</v>
       </c>
     </row>
     <row r="154" spans="2:29" x14ac:dyDescent="0.2">
@@ -34582,7 +34783,7 @@
       </c>
       <c r="AC154" s="143">
         <f ca="1">Statement!AC118*Statement!AC79</f>
-        <v>49423.5</v>
+        <v>49043.4</v>
       </c>
     </row>
     <row r="155" spans="2:29" x14ac:dyDescent="0.2">
@@ -34643,7 +34844,7 @@
       </c>
       <c r="AC155" s="143">
         <f ca="1">AC154+AC109-AC108+AC49+AC46</f>
-        <v>48544.5</v>
+        <v>48164.4</v>
       </c>
     </row>
     <row r="156" spans="2:29" x14ac:dyDescent="0.2">
@@ -34680,7 +34881,7 @@
       <c r="AA156" s="49"/>
       <c r="AC156" s="181">
         <f ca="1">AC155/AC5</f>
-        <v>6.2316431322207961</v>
+        <v>6.182849807445443</v>
       </c>
     </row>
     <row r="157" spans="2:29" x14ac:dyDescent="0.2">
@@ -34717,7 +34918,7 @@
       <c r="AA157" s="49"/>
       <c r="AC157" s="181">
         <f ca="1">AC155/AC13</f>
-        <v>23.784664380205783</v>
+        <v>23.598432141107303</v>
       </c>
     </row>
     <row r="158" spans="2:29" x14ac:dyDescent="0.2">
@@ -34852,7 +35053,7 @@
       <c r="AA160" s="49"/>
       <c r="AC160" s="72">
         <f t="shared" ref="AC160:AC161" ca="1" si="155">AC154/AC158</f>
-        <v>23.557435653002859</v>
+        <v>23.376263107721641</v>
       </c>
     </row>
     <row r="161" spans="2:29" x14ac:dyDescent="0.2">
@@ -34889,7 +35090,7 @@
       <c r="AA161" s="49"/>
       <c r="AC161" s="72">
         <f t="shared" ca="1" si="155"/>
-        <v>39.918937379728895</v>
+        <v>39.606374924702379</v>
       </c>
     </row>
     <row r="162" spans="2:29" x14ac:dyDescent="0.2">
@@ -34926,7 +35127,7 @@
       <c r="AA162" s="49"/>
       <c r="AC162" s="74">
         <f t="shared" ref="AC162" ca="1" si="158">AC158/AC154</f>
-        <v>4.244944206703289E-2</v>
+        <v>4.277843705778963E-2</v>
       </c>
     </row>
     <row r="163" spans="2:29" x14ac:dyDescent="0.2">
@@ -34963,7 +35164,7 @@
       <c r="AA163" s="49"/>
       <c r="AC163" s="74">
         <f ca="1">AC27/AC118</f>
-        <v>3.2844699383896329E-2</v>
+        <v>3.3099254945619598E-2</v>
       </c>
     </row>
     <row r="164" spans="2:29" x14ac:dyDescent="0.2">
@@ -35037,7 +35238,7 @@
       <c r="AA165" s="49"/>
       <c r="AC165" s="154">
         <f ca="1">-AC64/AC154</f>
-        <v>3.2191164122330473E-2</v>
+        <v>3.2440654603881458E-2</v>
       </c>
     </row>
     <row r="166" spans="2:29" x14ac:dyDescent="0.2">
@@ -35074,7 +35275,7 @@
       <c r="AA166" s="49"/>
       <c r="AC166" s="154">
         <f ca="1">-(AC64+AC65)/AC154</f>
-        <v>3.2191164122330473E-2</v>
+        <v>3.2440654603881458E-2</v>
       </c>
     </row>
     <row r="167" spans="2:29" x14ac:dyDescent="0.2">
@@ -35577,7 +35778,7 @@
       <c r="AA177" s="49"/>
       <c r="AC177" s="154">
         <f ca="1">(AC108-AC109)/AC154</f>
-        <v>1.7785061762117211E-2</v>
+        <v>1.7922900940799374E-2</v>
       </c>
     </row>
     <row r="178" spans="1:31" x14ac:dyDescent="0.2">
@@ -37337,18 +37538,57 @@
   <sheetPr>
     <tabColor theme="6" tint="0.59999389629810485"/>
   </sheetPr>
-  <dimension ref="B13"/>
+  <dimension ref="B5:H13"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="16384" width="10.83203125" style="1"/>
+    <col min="1" max="7" width="10.83203125" style="1"/>
+    <col min="8" max="8" width="18" style="1" customWidth="1"/>
+    <col min="9" max="16384" width="10.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="13" spans="2:2" s="4" customFormat="1" ht="49" x14ac:dyDescent="0.2">
+    <row r="5" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H5" s="134" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="6" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H6" s="237" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="7" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H7" s="237" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="8" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H8" s="237" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="9" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H9" s="237" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="10" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H10" s="238" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="13" spans="2:8" s="4" customFormat="1" ht="49" x14ac:dyDescent="0.2">
       <c r="B13" s="3" t="s">
         <v>231</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="H6" location="Overview!B3" display="Overview'!B3" xr:uid="{CECC5A3C-052F-194E-A17C-0CA5912D6036}"/>
+    <hyperlink ref="H8" location="'Analysis -&gt;'!B13" display="'Analysis -&gt;'!B13" xr:uid="{39DEEBD0-B241-F540-ACFA-9E159BC0B081}"/>
+    <hyperlink ref="H9" location="'Forecast -&gt;'!B13" display="'Forecast -&gt;'!B13" xr:uid="{8F54FD61-F3EA-B841-B0EF-CA76279C51CF}"/>
+    <hyperlink ref="H10" location="'Valuation -&gt;'!B13" display="'Valuation -&gt;'!B13" xr:uid="{1210F6FC-253C-8741-8222-D7981B81890F}"/>
+    <hyperlink ref="H7" location="'Financials -&gt;'!B13" display="'Financials -&gt;'!B13" xr:uid="{DACFBE39-6A45-4B4D-AD35-F054CFBC10FB}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -37372,15 +37612,15 @@
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B4" s="238" t="s">
+      <c r="B4" s="242" t="s">
         <v>232</v>
       </c>
-      <c r="C4" s="238"/>
-      <c r="E4" s="238" t="s">
+      <c r="C4" s="242"/>
+      <c r="E4" s="242" t="s">
         <v>239</v>
       </c>
-      <c r="F4" s="238"/>
-      <c r="G4" s="238"/>
+      <c r="F4" s="242"/>
+      <c r="G4" s="242"/>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B5" s="20" t="s">
@@ -37388,7 +37628,7 @@
       </c>
       <c r="C5" s="170">
         <f ca="1">Overview!C5</f>
-        <v>235.35</v>
+        <v>233.54</v>
       </c>
       <c r="E5" s="12"/>
       <c r="F5" s="134" t="s">
@@ -37404,7 +37644,7 @@
       </c>
       <c r="C6" s="171">
         <f ca="1">Statement!AC154</f>
-        <v>49423.5</v>
+        <v>49043.4</v>
       </c>
       <c r="E6" s="20" t="s">
         <v>19</v>
@@ -37424,7 +37664,7 @@
       </c>
       <c r="C7" s="171">
         <f ca="1">Statement!AC155</f>
-        <v>48544.5</v>
+        <v>48164.4</v>
       </c>
       <c r="E7" s="20" t="s">
         <v>31</v>
@@ -37444,7 +37684,7 @@
       </c>
       <c r="C8" s="172">
         <f ca="1">Statement!AC151</f>
-        <v>30.44631306597671</v>
+        <v>30.212160413971535</v>
       </c>
       <c r="E8" s="20" t="s">
         <v>242</v>
@@ -37464,7 +37704,7 @@
       </c>
       <c r="C9" s="172">
         <f ca="1">Statement!AC152</f>
-        <v>6.4351155327342751</v>
+        <v>6.3856251604621308</v>
       </c>
       <c r="E9" s="20" t="s">
         <v>243</v>
@@ -37484,7 +37724,7 @@
       </c>
       <c r="C10" s="172">
         <f ca="1">Statement!AC153</f>
-        <v>14.539801950931125</v>
+        <v>14.427981081879986</v>
       </c>
       <c r="E10" s="20" t="s">
         <v>1</v>
@@ -37504,7 +37744,7 @@
       </c>
       <c r="C11" s="172">
         <f ca="1">Statement!AC156</f>
-        <v>6.2316431322207961</v>
+        <v>6.182849807445443</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
@@ -37513,18 +37753,18 @@
       </c>
       <c r="C12" s="172">
         <f ca="1">Statement!AC157</f>
-        <v>23.784664380205783</v>
+        <v>23.598432141107303</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B15" s="238" t="s">
+      <c r="B15" s="242" t="s">
         <v>77</v>
       </c>
-      <c r="C15" s="238"/>
-      <c r="E15" s="238" t="s">
+      <c r="C15" s="242"/>
+      <c r="E15" s="242" t="s">
         <v>245</v>
       </c>
-      <c r="F15" s="238"/>
+      <c r="F15" s="242"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="20" t="s">
@@ -37575,14 +37815,14 @@
       </c>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B21" s="238" t="s">
+      <c r="B21" s="242" t="s">
         <v>244</v>
       </c>
-      <c r="C21" s="238"/>
-      <c r="E21" s="238" t="s">
+      <c r="C21" s="242"/>
+      <c r="E21" s="242" t="s">
         <v>248</v>
       </c>
-      <c r="F21" s="238"/>
+      <c r="F21" s="242"/>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B22" s="20" t="s">
@@ -37651,14 +37891,14 @@
       </c>
     </row>
     <row r="29" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B29" s="238" t="s">
+      <c r="B29" s="242" t="s">
         <v>249</v>
       </c>
-      <c r="C29" s="238"/>
-      <c r="E29" s="238" t="s">
+      <c r="C29" s="242"/>
+      <c r="E29" s="242" t="s">
         <v>255</v>
       </c>
-      <c r="F29" s="238"/>
+      <c r="F29" s="242"/>
     </row>
     <row r="30" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B30" s="20" t="s">
@@ -37734,14 +37974,14 @@
       </c>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B37" s="238" t="s">
+      <c r="B37" s="242" t="s">
         <v>267</v>
       </c>
-      <c r="C37" s="238"/>
-      <c r="E37" s="238" t="s">
+      <c r="C37" s="242"/>
+      <c r="E37" s="242" t="s">
         <v>270</v>
       </c>
-      <c r="F37" s="238"/>
+      <c r="F37" s="242"/>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B38" s="20" t="s">
@@ -37749,7 +37989,7 @@
       </c>
       <c r="C38" s="173">
         <f ca="1">Statement!AC163</f>
-        <v>3.2844699383896329E-2</v>
+        <v>3.3099254945619598E-2</v>
       </c>
       <c r="E38" s="20" t="s">
         <v>269</v>
@@ -37765,7 +38005,7 @@
       </c>
       <c r="C39" s="213">
         <f ca="1">Statement!AC162</f>
-        <v>4.244944206703289E-2</v>
+        <v>4.277843705778963E-2</v>
       </c>
       <c r="E39" s="20" t="s">
         <v>271</v>
@@ -37797,7 +38037,7 @@
       </c>
       <c r="C41" s="173">
         <f ca="1">Statement!AC165</f>
-        <v>3.2191164122330473E-2</v>
+        <v>3.2440654603881458E-2</v>
       </c>
     </row>
     <row r="42" spans="2:6" x14ac:dyDescent="0.2">
@@ -37806,18 +38046,18 @@
       </c>
       <c r="C42" s="173">
         <f ca="1">Statement!AC166</f>
-        <v>3.2191164122330473E-2</v>
+        <v>3.2440654603881458E-2</v>
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B45" s="238" t="s">
+      <c r="B45" s="242" t="s">
         <v>278</v>
       </c>
-      <c r="C45" s="238"/>
-      <c r="E45" s="238" t="s">
+      <c r="C45" s="242"/>
+      <c r="E45" s="242" t="s">
         <v>284</v>
       </c>
-      <c r="F45" s="238"/>
+      <c r="F45" s="242"/>
     </row>
     <row r="46" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B46" s="20" t="s">
@@ -37850,18 +38090,18 @@
       </c>
       <c r="F48" s="173">
         <f ca="1">Statement!AC177</f>
-        <v>1.7785061762117211E-2</v>
+        <v>1.7922900940799374E-2</v>
       </c>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B51" s="238" t="s">
+      <c r="B51" s="242" t="s">
         <v>281</v>
       </c>
-      <c r="C51" s="238"/>
-      <c r="E51" s="238" t="s">
+      <c r="C51" s="242"/>
+      <c r="E51" s="242" t="s">
         <v>302</v>
       </c>
-      <c r="F51" s="238"/>
+      <c r="F51" s="242"/>
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B52" s="20" t="s">
@@ -38029,7 +38269,7 @@
       </c>
       <c r="I6" s="170">
         <f ca="1">Statement!AC117</f>
-        <v>235.35</v>
+        <v>233.54</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -38058,7 +38298,7 @@
       </c>
       <c r="I7" s="171">
         <f ca="1">Statement!AC154</f>
-        <v>49423.5</v>
+        <v>49043.4</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
@@ -38087,7 +38327,7 @@
       </c>
       <c r="I8" s="171">
         <f ca="1">Statement!AC155</f>
-        <v>48544.5</v>
+        <v>48164.4</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -38116,7 +38356,7 @@
       </c>
       <c r="I9" s="172">
         <f ca="1">Statement!AC151</f>
-        <v>30.44631306597671</v>
+        <v>30.212160413971535</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -38145,7 +38385,7 @@
       </c>
       <c r="I10" s="172">
         <f ca="1">Statement!AC152</f>
-        <v>6.4351155327342751</v>
+        <v>6.3856251604621308</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -38174,7 +38414,7 @@
       </c>
       <c r="I11" s="172">
         <f ca="1">Statement!AC153</f>
-        <v>14.539801950931125</v>
+        <v>14.427981081879986</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
@@ -38203,7 +38443,7 @@
       </c>
       <c r="I12" s="172">
         <f ca="1">Statement!AC156</f>
-        <v>6.2316431322207961</v>
+        <v>6.182849807445443</v>
       </c>
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.2">
@@ -38232,7 +38472,7 @@
       </c>
       <c r="I13" s="172">
         <f ca="1">Statement!AC157</f>
-        <v>23.784664380205783</v>
+        <v>23.598432141107303</v>
       </c>
     </row>
     <row r="15" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -39005,7 +39245,7 @@
       </c>
       <c r="I51" s="173">
         <f ca="1">Statement!AC163</f>
-        <v>3.2844699383896329E-2</v>
+        <v>3.3099254945619598E-2</v>
       </c>
     </row>
     <row r="52" spans="2:9" x14ac:dyDescent="0.2">
@@ -39034,7 +39274,7 @@
       </c>
       <c r="I52" s="173">
         <f ca="1">Statement!AC162</f>
-        <v>4.244944206703289E-2</v>
+        <v>4.277843705778963E-2</v>
       </c>
     </row>
     <row r="53" spans="2:9" x14ac:dyDescent="0.2">
@@ -39092,7 +39332,7 @@
       </c>
       <c r="I54" s="173">
         <f ca="1">Statement!AC165</f>
-        <v>3.2191164122330473E-2</v>
+        <v>3.2440654603881458E-2</v>
       </c>
     </row>
     <row r="55" spans="2:9" x14ac:dyDescent="0.2">
@@ -39121,7 +39361,7 @@
       </c>
       <c r="I55" s="173">
         <f ca="1">Statement!AC166</f>
-        <v>3.2191164122330473E-2</v>
+        <v>3.2440654603881458E-2</v>
       </c>
     </row>
     <row r="57" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -39357,7 +39597,7 @@
       </c>
       <c r="I68" s="194">
         <f ca="1">Statement!AC177</f>
-        <v>1.7785061762117211E-2</v>
+        <v>1.7922900940799374E-2</v>
       </c>
     </row>
     <row r="70" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -39819,14 +40059,14 @@
     <row r="1" spans="2:7" ht="12" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="3" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B3" s="8"/>
-      <c r="C3" s="241" t="s">
+      <c r="C3" s="245" t="s">
         <v>312</v>
       </c>
-      <c r="D3" s="242"/>
-      <c r="F3" s="243" t="s">
+      <c r="D3" s="246"/>
+      <c r="F3" s="247" t="s">
         <v>313</v>
       </c>
-      <c r="G3" s="242"/>
+      <c r="G3" s="246"/>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B4" s="8"/>
@@ -39893,19 +40133,19 @@
       <c r="B7" s="204" t="s">
         <v>314</v>
       </c>
-      <c r="C7" s="239">
+      <c r="C7" s="243">
         <f>Statement!AA90</f>
         <v>5.7911065149948295E-2</v>
       </c>
-      <c r="D7" s="240"/>
-      <c r="F7" s="239">
+      <c r="D7" s="244"/>
+      <c r="F7" s="243">
         <f>IF(F6=0,
 IF(G6=0,0,IF(G6&gt;0,1,-1)),
 (G6-F6)/ABS(F6)
 )</f>
         <v>0.1605218377765173</v>
       </c>
-      <c r="G7" s="240"/>
+      <c r="G7" s="244"/>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B8" s="205" t="s">
@@ -39932,19 +40172,19 @@
       <c r="B9" s="204" t="s">
         <v>314</v>
       </c>
-      <c r="C9" s="239">
+      <c r="C9" s="243">
         <f>Statement!AA91</f>
         <v>5.7142857142857143E-3</v>
       </c>
-      <c r="D9" s="240"/>
-      <c r="F9" s="239">
+      <c r="D9" s="244"/>
+      <c r="F9" s="243">
         <f>IF(F8=0,
 IF(G8=0,0,IF(G8&gt;0,1,-1)),
 (G8-F8)/ABS(F8)
 )</f>
         <v>0.1069182389937107</v>
       </c>
-      <c r="G9" s="240"/>
+      <c r="G9" s="244"/>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B10" s="205" t="s">
@@ -39971,19 +40211,19 @@
       <c r="B11" s="204" t="s">
         <v>314</v>
       </c>
-      <c r="C11" s="239">
+      <c r="C11" s="243">
         <f>Statement!AA92</f>
         <v>6.3104036384309267E-2</v>
       </c>
-      <c r="D11" s="240"/>
-      <c r="F11" s="239">
+      <c r="D11" s="244"/>
+      <c r="F11" s="243">
         <f>IF(F10=0,
 IF(G10=0,0,IF(G10&gt;0,1,-1)),
 (G10-F10)/ABS(F10)
 )</f>
         <v>0.16583541147132169</v>
       </c>
-      <c r="G11" s="240"/>
+      <c r="G11" s="244"/>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B12" s="205" t="s">
@@ -40010,19 +40250,19 @@
       <c r="B13" s="204" t="s">
         <v>314</v>
       </c>
-      <c r="C13" s="239">
+      <c r="C13" s="243">
         <f>Statement!AA96</f>
         <v>4.3513957307060758E-2</v>
       </c>
-      <c r="D13" s="240"/>
-      <c r="F13" s="239">
+      <c r="D13" s="244"/>
+      <c r="F13" s="243">
         <f>IF(F12=0,
 IF(G12=0,0,IF(G12&gt;0,1,-1)),
 (G12-F12)/ABS(F12)
 )</f>
         <v>9.568965517241379E-2</v>
       </c>
-      <c r="G13" s="240"/>
+      <c r="G13" s="244"/>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B14" s="205" t="s">
@@ -40049,19 +40289,19 @@
       <c r="B15" s="204" t="s">
         <v>314</v>
       </c>
-      <c r="C15" s="239">
+      <c r="C15" s="243">
         <f>Statement!AA97</f>
         <v>0.10720887245841035</v>
       </c>
-      <c r="D15" s="240"/>
-      <c r="F15" s="239">
+      <c r="D15" s="244"/>
+      <c r="F15" s="243">
         <f>IF(F14=0,
 IF(G14=0,0,IF(G14&gt;0,1,-1)),
 (G14-F14)/ABS(F14)
 )</f>
         <v>0.34909909909909909</v>
       </c>
-      <c r="G15" s="240"/>
+      <c r="G15" s="244"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="205" t="s">
@@ -40088,19 +40328,19 @@
       <c r="B17" s="204" t="s">
         <v>314</v>
       </c>
-      <c r="C17" s="239">
+      <c r="C17" s="243">
         <f>Statement!AA99</f>
         <v>2.0366598778004071E-3</v>
       </c>
-      <c r="D17" s="240"/>
-      <c r="F17" s="239">
+      <c r="D17" s="244"/>
+      <c r="F17" s="243">
         <f>IF(F16=0,
 IF(G16=0,0,IF(G16&gt;0,1,-1)),
 (G16-F16)/ABS(F16)
 )</f>
         <v>0.5718849840255591</v>
       </c>
-      <c r="G17" s="240"/>
+      <c r="G17" s="244"/>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B18" s="205" t="s">
@@ -40127,22 +40367,22 @@
       <c r="B19" s="204" t="s">
         <v>314</v>
       </c>
-      <c r="C19" s="239">
+      <c r="C19" s="243">
         <f>IF(C18=0,
 IF(D18=0,0,IF(D18&gt;0,1,-1)),
 (D18-C18)/ABS(C18)
 )</f>
         <v>-4.7169811320754715E-3</v>
       </c>
-      <c r="D19" s="240"/>
-      <c r="F19" s="239">
+      <c r="D19" s="244"/>
+      <c r="F19" s="243">
         <f>IF(F18=0,
 IF(G18=0,0,IF(G18&gt;0,1,-1)),
 (G18-F18)/ABS(F18)
 )</f>
         <v>-1.8604651162790697E-2</v>
       </c>
-      <c r="G19" s="240"/>
+      <c r="G19" s="244"/>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B20" s="205" t="s">
@@ -40169,22 +40409,22 @@
       <c r="B21" s="204" t="s">
         <v>314</v>
       </c>
-      <c r="C21" s="239">
+      <c r="C21" s="243">
         <f>IF(C20=0,
 IF(D20=0,0,IF(D20&gt;0,1,-1)),
 (D20-C20)/ABS(C20)
 )</f>
         <v>4.3103448275863066E-3</v>
       </c>
-      <c r="D21" s="240"/>
-      <c r="F21" s="239">
+      <c r="D21" s="244"/>
+      <c r="F21" s="243">
         <f>IF(F20=0,
 IF(G20=0,0,IF(G20&gt;0,1,-1)),
 (G20-F20)/ABS(F20)
 )</f>
         <v>0.59589041095890416</v>
       </c>
-      <c r="G21" s="240"/>
+      <c r="G21" s="244"/>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B23" s="8" t="s">
@@ -40233,22 +40473,22 @@
       <c r="B25" s="204" t="s">
         <v>314</v>
       </c>
-      <c r="C25" s="239">
+      <c r="C25" s="243">
         <f>IF(C24=0,
 IF(D24=0,0,IF(D24&gt;0,1,-1)),
 (D24-C24)/ABS(C24)
 )</f>
         <v>6.3180827886710242E-2</v>
       </c>
-      <c r="D25" s="240"/>
-      <c r="F25" s="239">
+      <c r="D25" s="244"/>
+      <c r="F25" s="243">
         <f>IF(F24=0,
 IF(G24=0,0,IF(G24&gt;0,1,-1)),
 (G24-F24)/ABS(F24)
 )</f>
         <v>0.17096580683863227</v>
       </c>
-      <c r="G25" s="240"/>
+      <c r="G25" s="244"/>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B26" s="20" t="str">
@@ -40276,22 +40516,22 @@
       <c r="B27" s="204" t="s">
         <v>314</v>
       </c>
-      <c r="C27" s="239">
+      <c r="C27" s="243">
         <f>IF(C26=0,
 IF(D26=0,0,IF(D26&gt;0,1,-1)),
 (D26-C26)/ABS(C26)
 )</f>
         <v>-4.0816326530612242E-2</v>
       </c>
-      <c r="D27" s="240"/>
-      <c r="F27" s="239">
+      <c r="D27" s="244"/>
+      <c r="F27" s="243">
         <f>IF(F26=0,
 IF(G26=0,0,IF(G26&gt;0,1,-1)),
 (G26-F26)/ABS(F26)
 )</f>
         <v>-2.0833333333333332E-2</v>
       </c>
-      <c r="G27" s="240"/>
+      <c r="G27" s="244"/>
     </row>
     <row r="29" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B29" s="205" t="str">
@@ -40319,22 +40559,22 @@
       <c r="B30" s="204" t="s">
         <v>314</v>
       </c>
-      <c r="C30" s="239">
+      <c r="C30" s="243">
         <f>IF(C29=0,
 IF(D29=0,0,IF(D29&gt;0,1,-1)),
 (D29-C29)/ABS(C29)
 )</f>
         <v>6.0824742268041236E-2</v>
       </c>
-      <c r="D30" s="240"/>
-      <c r="F30" s="239">
+      <c r="D30" s="244"/>
+      <c r="F30" s="243">
         <f>IF(F29=0,
 IF(G29=0,0,IF(G29&gt;0,1,-1)),
 (G29-F29)/ABS(F29)
 )</f>
         <v>0.17198177676537585</v>
       </c>
-      <c r="G30" s="240"/>
+      <c r="G30" s="244"/>
     </row>
     <row r="31" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B31" s="20" t="str">
@@ -40362,22 +40602,22 @@
       <c r="B32" s="204" t="s">
         <v>314</v>
       </c>
-      <c r="C32" s="239">
+      <c r="C32" s="243">
         <f>IF(C31=0,
 IF(D31=0,0,IF(D31&gt;0,1,-1)),
 (D31-C31)/ABS(C31)
 )</f>
         <v>5.4852320675105488E-2</v>
       </c>
-      <c r="D32" s="240"/>
-      <c r="F32" s="239">
+      <c r="D32" s="244"/>
+      <c r="F32" s="243">
         <f>IF(F31=0,
 IF(G31=0,0,IF(G31&gt;0,1,-1)),
 (G31-F31)/ABS(F31)
 )</f>
         <v>0.13636363636363635</v>
       </c>
-      <c r="G32" s="240"/>
+      <c r="G32" s="244"/>
     </row>
     <row r="33" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B33" s="20" t="str">
@@ -40405,22 +40645,22 @@
       <c r="B34" s="204" t="s">
         <v>314</v>
       </c>
-      <c r="C34" s="239">
+      <c r="C34" s="243">
         <f>IF(C33=0,
 IF(D33=0,0,IF(D33&gt;0,1,-1)),
 (D33-C33)/ABS(C33)
 )</f>
         <v>4.9046321525885561E-2</v>
       </c>
-      <c r="D34" s="240"/>
-      <c r="F34" s="239">
+      <c r="D34" s="244"/>
+      <c r="F34" s="243">
         <f>IF(F33=0,
 IF(G33=0,0,IF(G33&gt;0,1,-1)),
 (G33-F33)/ABS(F33)
 )</f>
         <v>0.15269461077844312</v>
       </c>
-      <c r="G34" s="240"/>
+      <c r="G34" s="244"/>
     </row>
     <row r="35" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B35" s="20" t="str">
@@ -40448,22 +40688,22 @@
       <c r="B36" s="204" t="s">
         <v>314</v>
       </c>
-      <c r="C36" s="239">
+      <c r="C36" s="243">
         <f>IF(C35=0,
 IF(D35=0,0,IF(D35&gt;0,1,-1)),
 (D35-C35)/ABS(C35)
 )</f>
         <v>6.9767441860465115E-2</v>
       </c>
-      <c r="D36" s="240"/>
-      <c r="F36" s="239">
+      <c r="D36" s="244"/>
+      <c r="F36" s="243">
         <f>IF(F35=0,
 IF(G35=0,0,IF(G35&gt;0,1,-1)),
 (G35-F35)/ABS(F35)
 )</f>
         <v>0.15</v>
       </c>
-      <c r="G36" s="240"/>
+      <c r="G36" s="244"/>
     </row>
     <row r="37" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B37" s="20" t="str">
@@ -40491,25 +40731,49 @@
       <c r="B38" s="204" t="s">
         <v>314</v>
       </c>
-      <c r="C38" s="239">
+      <c r="C38" s="243">
         <f>IF(C37=0,
 IF(D37=0,0,IF(D37&gt;0,1,-1)),
 (D37-C37)/ABS(C37)
 )</f>
         <v>8.1081081081081086E-2</v>
       </c>
-      <c r="D38" s="240"/>
-      <c r="F38" s="239">
+      <c r="D38" s="244"/>
+      <c r="F38" s="243">
         <f>IF(F37=0,
 IF(G37=0,0,IF(G37&gt;0,1,-1)),
 (G37-F37)/ABS(F37)
 )</f>
         <v>0.29032258064516131</v>
       </c>
-      <c r="G38" s="240"/>
+      <c r="G38" s="244"/>
     </row>
   </sheetData>
   <mergeCells count="32">
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="F25:G25"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="F27:G27"/>
+    <mergeCell ref="C30:D30"/>
+    <mergeCell ref="F30:G30"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="F9:G9"/>
     <mergeCell ref="C38:D38"/>
     <mergeCell ref="F38:G38"/>
     <mergeCell ref="C32:D32"/>
@@ -40518,30 +40782,6 @@
     <mergeCell ref="F34:G34"/>
     <mergeCell ref="C36:D36"/>
     <mergeCell ref="F36:G36"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="F9:G9"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="F19:G19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="F21:G21"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="F25:G25"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="F27:G27"/>
-    <mergeCell ref="C30:D30"/>
-    <mergeCell ref="F30:G30"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>

--- a/ADSK.xlsx
+++ b/ADSK.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11004"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11011"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D175357-C428-6843-9B65-299E65BA7B1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8CB6418-049C-8640-8E35-4E414F2C0810}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
@@ -2457,14 +2457,14 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -15186,11 +15186,11 @@
     <v>Powered by Refinitiv</v>
     <v>320</v>
     <v>185.5</v>
-    <v>1.3194999999999999</v>
-    <v>-1.81</v>
-    <v>-7.6909999999999999E-3</v>
-    <v>0.11</v>
-    <v>4.7100000000000001E-4</v>
+    <v>1.3080000000000001</v>
+    <v>14.02</v>
+    <v>6.0656000000000002E-2</v>
+    <v>-1.52</v>
+    <v>-6.1999999999999998E-3</v>
     <v>USD</v>
     <v>Autodesk, Inc. is engaged in three-dimensional (3D) design, engineering and entertainment technology solutions, spanning architecture, engineering, construction, product design, manufacturing, media and entertainment. Its architecture, engineering, construction and operations products improve the way building, infrastructure, and industrial projects are designed, built, and operated. Its product development and manufacturing software provides manufacturers in the automotive, transportation, industrial machinery, consumer products, and building product industries with comprehensive digital design, engineering, manufacturing, and production solutions. Its product offerings include AutoCAD Civil 3D, Autodesk Build, BIM Collaborate Pro, Building Connected, Revit, Tandem, AutoCAD, AutoCAD LT, Inventor, Vault, Maya, 3ds Max, Flow Production Tracking, among others. AutoCAD Civil 3D solution offers surveying, design, analysis, and documentation solution.</v>
     <v>14300</v>
@@ -15198,25 +15198,25 @@
     <v>XNAS</v>
     <v>XNAS</v>
     <v>One Market, Ste. 400., SAN FRANCISCO, CA, 94105 US</v>
-    <v>237.27</v>
+    <v>246.74</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46307.844219339844</v>
+    <v>46310.894717499999</v>
     <v>0</v>
-    <v>229.315</v>
-    <v>48809860000</v>
+    <v>234.02500000000001</v>
+    <v>51238440000</v>
     <v>AUTODESK, INC.</v>
     <v>AUTODESK, INC.</v>
-    <v>234.703</v>
-    <v>30.2791</v>
-    <v>235.35</v>
-    <v>233.54</v>
-    <v>233.65</v>
+    <v>234.18</v>
+    <v>31.785699999999999</v>
+    <v>231.14</v>
+    <v>245.16</v>
+    <v>243.64</v>
     <v>209000000</v>
     <v>ADSK</v>
     <v>AUTODESK, INC. (XNAS:ADSK)</v>
-    <v>1524104</v>
-    <v>2316106</v>
+    <v>2427911</v>
+    <v>2117039</v>
     <v>1994</v>
   </rv>
   <rv s="2">
@@ -15240,17 +15240,17 @@
     <v>Powered by Refinitiv</v>
     <v>53.64</v>
     <v>39.47</v>
-    <v>0.13</v>
-    <v>2.4849999999999998E-3</v>
+    <v>-0.27</v>
+    <v>-5.1749999999999999E-3</v>
     <v>US</v>
-    <v>52.8</v>
+    <v>53.29</v>
     <v>Index</v>
     <v>3</v>
-    <v>52.34</v>
+    <v>51.77</v>
     <v>10 Y TSY YLD NDX</v>
-    <v>52.36</v>
-    <v>52.31</v>
-    <v>52.44</v>
+    <v>51.96</v>
+    <v>52.17</v>
+    <v>51.9</v>
     <v>TNX</v>
     <v>10 Y TSY YLD NDX</v>
   </rv>
@@ -15472,9 +15472,9 @@
       <v>at close</v>
       <v>from previous close</v>
       <v>from previous close</v>
-      <v>Source: Nasdaq</v>
+      <v>Source: Nasdaq Last Sale</v>
       <v>GMT</v>
-      <v>Delayed 15 minutes</v>
+      <v>Real-Time Nasdaq Last Sale</v>
       <v>from close</v>
       <v>from close</v>
     </spb>
@@ -16076,7 +16076,7 @@
       </c>
       <c r="F3" s="185">
         <f ca="1">Statement!AC154</f>
-        <v>49043.4</v>
+        <v>51483.6</v>
       </c>
       <c r="H3" s="183" t="str">
         <f>'AVG target price'!B5</f>
@@ -16084,7 +16084,7 @@
       </c>
       <c r="I3" s="209">
         <f ca="1">'AVG target price'!C5</f>
-        <v>117.44825208935085</v>
+        <v>118.57284844015848</v>
       </c>
       <c r="K3" s="237" t="s">
         <v>436</v>
@@ -16103,7 +16103,7 @@
       </c>
       <c r="F4" s="186">
         <f ca="1">Statement!AC155</f>
-        <v>48164.4</v>
+        <v>50604.6</v>
       </c>
       <c r="H4" s="183" t="str">
         <f>'AVG target price'!B6</f>
@@ -16111,7 +16111,7 @@
       </c>
       <c r="I4" s="209">
         <f ca="1">'AVG target price'!C6</f>
-        <v>346.52062287016844</v>
+        <v>347.71724854292682</v>
       </c>
       <c r="K4" s="237" t="s">
         <v>437</v>
@@ -16123,7 +16123,7 @@
       </c>
       <c r="C5" s="206" cm="1">
         <f t="array" aca="1" ref="C5" ca="1">_FV(C3,"Price",TRUE)</f>
-        <v>233.54</v>
+        <v>245.16</v>
       </c>
       <c r="E5" s="183" t="s">
         <v>242</v>
@@ -16138,7 +16138,7 @@
       </c>
       <c r="I5" s="209">
         <f ca="1">'AVG target price'!C7</f>
-        <v>188.26132013643894</v>
+        <v>189.15919991140987</v>
       </c>
       <c r="K5" s="237" t="s">
         <v>438</v>
@@ -16150,14 +16150,14 @@
       </c>
       <c r="C6" s="206" cm="1">
         <f t="array" aca="1" ref="C6" ca="1">_FV(C3,"Price (Extended hours)",TRUE)</f>
-        <v>233.65</v>
+        <v>243.64</v>
       </c>
       <c r="E6" s="183" t="s">
         <v>236</v>
       </c>
       <c r="F6" s="188">
         <f ca="1">Statement!AC151</f>
-        <v>30.212160413971535</v>
+        <v>31.715394566623541</v>
       </c>
       <c r="H6" s="183" t="str">
         <f>'AVG target price'!B8</f>
@@ -16165,7 +16165,7 @@
       </c>
       <c r="I6" s="209">
         <f ca="1">'AVG target price'!C8</f>
-        <v>344.98288263158031</v>
+        <v>346.17391838017352</v>
       </c>
       <c r="K6" s="238" t="s">
         <v>439</v>
@@ -16177,14 +16177,14 @@
       </c>
       <c r="C7" s="6" cm="1">
         <f t="array" aca="1" ref="C7" ca="1">_FV(C3,"Change")</f>
-        <v>-1.81</v>
+        <v>14.02</v>
       </c>
       <c r="E7" s="184" t="s">
         <v>200</v>
       </c>
       <c r="F7" s="189">
         <f ca="1">Statement!AC152</f>
-        <v>6.3856251604621308</v>
+        <v>6.7033478818998722</v>
       </c>
       <c r="H7" s="183" t="str">
         <f>'AVG target price'!B9</f>
@@ -16192,7 +16192,7 @@
       </c>
       <c r="I7" s="209">
         <f ca="1">'AVG target price'!C9</f>
-        <v>219.72591467074224</v>
+        <v>220.46162192204596</v>
       </c>
     </row>
     <row r="8" spans="2:11" x14ac:dyDescent="0.2">
@@ -16201,14 +16201,14 @@
       </c>
       <c r="C8" s="6" cm="1">
         <f t="array" aca="1" ref="C8" ca="1">_FV(C3,"Change (extended hours)",TRUE)</f>
-        <v>0.11</v>
+        <v>-1.52</v>
       </c>
       <c r="E8" s="183" t="s">
         <v>264</v>
       </c>
       <c r="F8" s="190">
         <f ca="1">Statement!AC162</f>
-        <v>4.277843705778963E-2</v>
+        <v>4.0750841044526802E-2</v>
       </c>
       <c r="H8" s="182" t="str">
         <f>'AVG target price'!B10</f>
@@ -16216,7 +16216,7 @@
       </c>
       <c r="I8" s="210">
         <f ca="1">'AVG target price'!C10</f>
-        <v>243.38779847965617</v>
+        <v>244.4169674393429</v>
       </c>
     </row>
     <row r="9" spans="2:11" x14ac:dyDescent="0.2">
@@ -16225,14 +16225,14 @@
       </c>
       <c r="C9" s="73" cm="1">
         <f t="array" aca="1" ref="C9" ca="1">_FV(C3,"Change (%)",TRUE)</f>
-        <v>-7.6909999999999999E-3</v>
+        <v>6.0656000000000002E-2</v>
       </c>
       <c r="E9" s="183" t="s">
         <v>287</v>
       </c>
       <c r="F9" s="190">
         <f ca="1">Statement!AC163</f>
-        <v>3.3099254945619598E-2</v>
+        <v>3.1530429107521622E-2</v>
       </c>
       <c r="H9" s="182" t="str">
         <f>'AVG target price'!B12</f>
@@ -16240,7 +16240,7 @@
       </c>
       <c r="I9" s="211">
         <f ca="1">'AVG target price'!C12</f>
-        <v>4.2167502267946293E-2</v>
+        <v>-3.0308066595574274E-3</v>
       </c>
     </row>
     <row r="10" spans="2:11" x14ac:dyDescent="0.2">
@@ -16249,14 +16249,14 @@
       </c>
       <c r="C10" s="73" cm="1">
         <f t="array" aca="1" ref="C10" ca="1">_FV(C3,"Change % (extended hours)",TRUE)</f>
-        <v>4.7100000000000001E-4</v>
+        <v>-6.1999999999999998E-3</v>
       </c>
       <c r="E10" s="183" t="s">
         <v>292</v>
       </c>
       <c r="F10" s="190">
         <f ca="1">Statement!AC165</f>
-        <v>3.2440654603881458E-2</v>
+        <v>3.0903044853118275E-2</v>
       </c>
     </row>
     <row r="11" spans="2:11" x14ac:dyDescent="0.2">
@@ -16304,7 +16304,7 @@
       </c>
       <c r="C13" s="207" cm="1">
         <f t="array" aca="1" ref="C13" ca="1">_FV(C3,"Beta")</f>
-        <v>1.3194999999999999</v>
+        <v>1.3080000000000001</v>
       </c>
       <c r="E13" s="183" t="s">
         <v>103</v>
@@ -16327,7 +16327,7 @@
       </c>
       <c r="C14" s="208" cm="1">
         <f t="array" aca="1" ref="C14" ca="1">_FV(C3,"Volume average",TRUE)</f>
-        <v>2316106</v>
+        <v>2117039</v>
       </c>
       <c r="E14" s="184" t="s">
         <v>104</v>
@@ -16343,7 +16343,7 @@
       </c>
       <c r="F15" s="190">
         <f ca="1">Statement!AC177</f>
-        <v>1.7922900940799374E-2</v>
+        <v>1.7073398130666852E-2</v>
       </c>
     </row>
     <row r="16" spans="2:11" x14ac:dyDescent="0.2">
@@ -16376,7 +16376,7 @@
       </c>
       <c r="I17" s="235">
         <f ca="1">DCF!C15</f>
-        <v>0.10760404710270478</v>
+        <v>0.10680053630170883</v>
       </c>
     </row>
     <row r="18" spans="2:9" x14ac:dyDescent="0.2">
@@ -16398,7 +16398,7 @@
       </c>
       <c r="I18" s="236">
         <f ca="1">Multiples!C54</f>
-        <v>0.11181749999999999</v>
+        <v>0.11076</v>
       </c>
     </row>
     <row r="19" spans="2:9" x14ac:dyDescent="0.2">
@@ -16471,7 +16471,7 @@
       </c>
       <c r="F26" s="217" cm="1">
         <f t="array" aca="1" ref="F26" ca="1">_FV(E26,"Price")</f>
-        <v>52.44</v>
+        <v>51.9</v>
       </c>
     </row>
     <row r="27" spans="2:9" x14ac:dyDescent="0.2">
@@ -16486,7 +16486,7 @@
       </c>
       <c r="F27" s="218">
         <f ca="1">F26/1000</f>
-        <v>5.2440000000000001E-2</v>
+        <v>5.1900000000000002E-2</v>
       </c>
     </row>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
@@ -22232,6 +22232,12 @@
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="H3:L3"/>
+    <mergeCell ref="P3:W3"/>
+    <mergeCell ref="X3:Z3"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="P5:Z5"/>
     <mergeCell ref="C40:L40"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="P11:Z11"/>
@@ -22239,12 +22245,6 @@
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="C26:L26"/>
     <mergeCell ref="C33:L33"/>
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="H3:L3"/>
-    <mergeCell ref="P3:W3"/>
-    <mergeCell ref="X3:Z3"/>
-    <mergeCell ref="C5:L5"/>
-    <mergeCell ref="P5:Z5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -23304,16 +23304,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="AA2:AC2"/>
+    <mergeCell ref="C4:L4"/>
+    <mergeCell ref="S4:AC4"/>
+    <mergeCell ref="C13:L13"/>
+    <mergeCell ref="C18:L18"/>
     <mergeCell ref="C31:L31"/>
     <mergeCell ref="C25:L25"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="H2:L2"/>
     <mergeCell ref="S2:Z2"/>
-    <mergeCell ref="AA2:AC2"/>
-    <mergeCell ref="C4:L4"/>
-    <mergeCell ref="S4:AC4"/>
-    <mergeCell ref="C13:L13"/>
-    <mergeCell ref="C18:L18"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -23435,7 +23435,7 @@
       </c>
       <c r="C6" s="135">
         <f ca="1">Overview!C5</f>
-        <v>233.54</v>
+        <v>245.16</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -23444,7 +23444,7 @@
       </c>
       <c r="C7" s="136">
         <f ca="1">C5*C6</f>
-        <v>49043.4</v>
+        <v>51483.6</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -23462,7 +23462,7 @@
       </c>
       <c r="C9" s="137">
         <f ca="1">Overview!F27</f>
-        <v>5.2440000000000001E-2</v>
+        <v>5.1900000000000002E-2</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -23471,7 +23471,7 @@
       </c>
       <c r="C10" s="135">
         <f ca="1">Overview!C13</f>
-        <v>1.3194999999999999</v>
+        <v>1.3080000000000001</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -23514,7 +23514,7 @@
       </c>
       <c r="C16" s="46">
         <f ca="1">C8/(C8+C7)</f>
-        <v>6.6220626259010609E-2</v>
+        <v>6.3280544962300955E-2</v>
       </c>
     </row>
     <row r="17" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -23523,7 +23523,7 @@
       </c>
       <c r="C17" s="46">
         <f ca="1">C7/(C8+C7)</f>
-        <v>0.9337793737409894</v>
+        <v>0.93671945503769904</v>
       </c>
     </row>
     <row r="18" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -23541,7 +23541,7 @@
       </c>
       <c r="C19" s="46">
         <f ca="1">C9+C10*C11</f>
-        <v>0.11181749999999999</v>
+        <v>0.11076</v>
       </c>
     </row>
     <row r="20" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -23550,7 +23550,7 @@
       </c>
       <c r="C20" s="46">
         <f ca="1">(C17*C19)+(C16*C18)</f>
-        <v>0.10760404710270478</v>
+        <v>0.10680053630170883</v>
       </c>
     </row>
   </sheetData>
@@ -23801,7 +23801,7 @@
       </c>
       <c r="L8" s="128">
         <f ca="1">L7*(1+C14)/(C15-C14)</f>
-        <v>28661.651974693403</v>
+        <v>28926.972304696937</v>
       </c>
       <c r="N8" s="91"/>
       <c r="O8" s="16"/>
@@ -23855,23 +23855,23 @@
       <c r="G10" s="140"/>
       <c r="H10" s="128">
         <f ca="1">H7/(1+$C$15)^H9</f>
-        <v>1860.6974660742021</v>
+        <v>1862.0482880717882</v>
       </c>
       <c r="I10" s="128">
         <f t="shared" ref="I10:L10" ca="1" si="0">I7/(1+$C$15)^I9</f>
-        <v>1268.5822567072785</v>
+        <v>1270.4248462482396</v>
       </c>
       <c r="J10" s="128">
         <f t="shared" ca="1" si="0"/>
-        <v>568.76511916793174</v>
+        <v>570.0047484218378</v>
       </c>
       <c r="K10" s="128">
         <f t="shared" ca="1" si="0"/>
-        <v>1416.2887921641759</v>
+        <v>1420.4060405726918</v>
       </c>
       <c r="L10" s="128">
         <f t="shared" ca="1" si="0"/>
-        <v>1476.7349270781838</v>
+        <v>1482.1030874782641</v>
       </c>
       <c r="N10" s="91"/>
     </row>
@@ -23890,7 +23890,7 @@
       <c r="K11" s="139"/>
       <c r="L11" s="128">
         <f ca="1">L8/(1+C15)^L9</f>
-        <v>17194.064377571904</v>
+        <v>17416.31116164046</v>
       </c>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.2">
@@ -23913,7 +23913,7 @@
       </c>
       <c r="C15" s="137">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.10760404710270478</v>
+        <v>0.10680053630170883</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.2">
@@ -23928,7 +23928,7 @@
       </c>
       <c r="C19" s="64">
         <f ca="1">SUM(H10:L10)</f>
-        <v>6591.0685611917725</v>
+        <v>6604.9870107928218</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.2">
@@ -23937,7 +23937,7 @@
       </c>
       <c r="C20" s="64">
         <f ca="1">L11</f>
-        <v>17194.064377571904</v>
+        <v>17416.31116164046</v>
       </c>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.2">
@@ -23946,7 +23946,7 @@
       </c>
       <c r="C21" s="94">
         <f ca="1">C19+C20</f>
-        <v>23785.132938763676</v>
+        <v>24021.298172433282</v>
       </c>
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.2">
@@ -23973,7 +23973,7 @@
       </c>
       <c r="C24" s="94">
         <f ca="1">C21+C22-C23</f>
-        <v>24664.132938763676</v>
+        <v>24900.298172433282</v>
       </c>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.2">
@@ -23991,7 +23991,7 @@
       </c>
       <c r="C26" s="234">
         <f ca="1">C24/C25</f>
-        <v>117.44825208935085</v>
+        <v>118.57284844015848</v>
       </c>
     </row>
   </sheetData>
@@ -24260,23 +24260,23 @@
       <c r="G9" s="140"/>
       <c r="H9" s="92">
         <f ca="1">DCF!H10</f>
-        <v>1860.6974660742021</v>
+        <v>1862.0482880717882</v>
       </c>
       <c r="I9" s="92">
         <f ca="1">DCF!I10</f>
-        <v>1268.5822567072785</v>
+        <v>1270.4248462482396</v>
       </c>
       <c r="J9" s="92">
         <f ca="1">DCF!J10</f>
-        <v>568.76511916793174</v>
+        <v>570.0047484218378</v>
       </c>
       <c r="K9" s="92">
         <f ca="1">DCF!K10</f>
-        <v>1416.2887921641759</v>
+        <v>1420.4060405726918</v>
       </c>
       <c r="L9" s="92">
         <f ca="1">DCF!L10</f>
-        <v>1476.7349270781838</v>
+        <v>1482.1030874782641</v>
       </c>
       <c r="N9" s="91"/>
     </row>
@@ -25062,7 +25062,7 @@
       </c>
       <c r="C41" s="137">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.10760404710270478</v>
+        <v>0.10680053630170883</v>
       </c>
     </row>
     <row r="42" spans="2:14" x14ac:dyDescent="0.2">
@@ -25088,7 +25088,7 @@
       </c>
       <c r="C44" s="24">
         <f ca="1">C43/(1+C41)^5</f>
-        <v>66775.99716862179</v>
+        <v>67018.73827070008</v>
       </c>
     </row>
     <row r="45" spans="2:14" x14ac:dyDescent="0.2">
@@ -25097,7 +25097,7 @@
       </c>
       <c r="C45" s="108">
         <f ca="1">SUM(H9:K9)+C44</f>
-        <v>71890.330802735378</v>
+        <v>72141.622194014635</v>
       </c>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.2">
@@ -25124,7 +25124,7 @@
       </c>
       <c r="C48" s="108">
         <f ca="1">C45+C46-C47</f>
-        <v>72769.330802735378</v>
+        <v>73020.622194014635</v>
       </c>
     </row>
     <row r="49" spans="2:3" x14ac:dyDescent="0.2">
@@ -25142,7 +25142,7 @@
       </c>
       <c r="C50" s="234">
         <f ca="1">C48/C49</f>
-        <v>346.52062287016844</v>
+        <v>347.71724854292682</v>
       </c>
     </row>
     <row r="52" spans="2:3" x14ac:dyDescent="0.2">
@@ -25166,7 +25166,7 @@
       </c>
       <c r="C54" s="137">
         <f ca="1">IF(Overview!C29&gt;0,Overview!C29,WACC!C19)</f>
-        <v>0.11181749999999999</v>
+        <v>0.11076</v>
       </c>
     </row>
     <row r="55" spans="2:3" x14ac:dyDescent="0.2">
@@ -25201,7 +25201,7 @@
       </c>
       <c r="C58" s="234">
         <f ca="1">C57/(1+C54)^5</f>
-        <v>188.26132013643894</v>
+        <v>189.15919991140987</v>
       </c>
     </row>
     <row r="60" spans="2:3" x14ac:dyDescent="0.2">
@@ -25225,7 +25225,7 @@
       </c>
       <c r="C62" s="137">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.10760404710270478</v>
+        <v>0.10680053630170883</v>
       </c>
     </row>
     <row r="63" spans="2:3" x14ac:dyDescent="0.2">
@@ -25251,7 +25251,7 @@
       </c>
       <c r="C65" s="24">
         <f ca="1">C64/(1+C62)^5</f>
-        <v>66453.071718518273</v>
+        <v>66694.638936521878</v>
       </c>
     </row>
     <row r="66" spans="2:3" x14ac:dyDescent="0.2">
@@ -25260,7 +25260,7 @@
       </c>
       <c r="C66" s="108">
         <f ca="1">SUM(H9:K9)+C65</f>
-        <v>71567.40535263186</v>
+        <v>71817.522859836434</v>
       </c>
     </row>
     <row r="67" spans="2:3" x14ac:dyDescent="0.2">
@@ -25287,7 +25287,7 @@
       </c>
       <c r="C69" s="108">
         <f ca="1">C66+C67-C68</f>
-        <v>72446.40535263186</v>
+        <v>72696.522859836434</v>
       </c>
     </row>
     <row r="70" spans="2:3" x14ac:dyDescent="0.2">
@@ -25305,7 +25305,7 @@
       </c>
       <c r="C71" s="234">
         <f ca="1">C69/C70</f>
-        <v>344.98288263158031</v>
+        <v>346.17391838017352</v>
       </c>
     </row>
     <row r="73" spans="2:3" x14ac:dyDescent="0.2">
@@ -25329,7 +25329,7 @@
       </c>
       <c r="C75" s="137">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.10760404710270478</v>
+        <v>0.10680053630170883</v>
       </c>
     </row>
     <row r="76" spans="2:3" x14ac:dyDescent="0.2">
@@ -25355,7 +25355,7 @@
       </c>
       <c r="C78" s="24">
         <f ca="1">C77/(1+C75)^5</f>
-        <v>40149.108446742284</v>
+        <v>40295.056680315094</v>
       </c>
     </row>
     <row r="79" spans="2:3" x14ac:dyDescent="0.2">
@@ -25364,7 +25364,7 @@
       </c>
       <c r="C79" s="108">
         <f ca="1">SUM(H9:K9)+C78</f>
-        <v>45263.442080855872</v>
+        <v>45417.94060362965</v>
       </c>
     </row>
     <row r="80" spans="2:3" x14ac:dyDescent="0.2">
@@ -25391,7 +25391,7 @@
       </c>
       <c r="C82" s="108">
         <f ca="1">C79+C80-C81</f>
-        <v>46142.442080855872</v>
+        <v>46296.94060362965</v>
       </c>
     </row>
     <row r="83" spans="2:3" x14ac:dyDescent="0.2">
@@ -25409,22 +25409,22 @@
       </c>
       <c r="C84" s="234">
         <f ca="1">C82/C83</f>
-        <v>219.72591467074224</v>
+        <v>220.46162192204596</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="B73:C73"/>
-    <mergeCell ref="C27:L27"/>
-    <mergeCell ref="B39:C39"/>
-    <mergeCell ref="B52:C52"/>
-    <mergeCell ref="B60:C60"/>
     <mergeCell ref="C22:L22"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="H2:L2"/>
     <mergeCell ref="C4:L4"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="C17:L17"/>
+    <mergeCell ref="B73:C73"/>
+    <mergeCell ref="C27:L27"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="B60:C60"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -25474,7 +25474,7 @@
       </c>
       <c r="C5" s="135">
         <f ca="1">DCF!C26</f>
-        <v>117.44825208935085</v>
+        <v>118.57284844015848</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.2">
@@ -25483,7 +25483,7 @@
       </c>
       <c r="C6" s="135">
         <f ca="1">Multiples!C50</f>
-        <v>346.52062287016844</v>
+        <v>347.71724854292682</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.2">
@@ -25492,7 +25492,7 @@
       </c>
       <c r="C7" s="135">
         <f ca="1">Multiples!C58</f>
-        <v>188.26132013643894</v>
+        <v>189.15919991140987</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.2">
@@ -25501,7 +25501,7 @@
       </c>
       <c r="C8" s="135">
         <f ca="1">Multiples!C71</f>
-        <v>344.98288263158031</v>
+        <v>346.17391838017352</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
@@ -25510,7 +25510,7 @@
       </c>
       <c r="C9" s="135">
         <f ca="1">Multiples!C84</f>
-        <v>219.72591467074224</v>
+        <v>220.46162192204596</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
@@ -25519,7 +25519,7 @@
       </c>
       <c r="C10" s="234">
         <f ca="1">AVERAGE(C5:C9)</f>
-        <v>243.38779847965617</v>
+        <v>244.4169674393429</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -25528,7 +25528,7 @@
       </c>
       <c r="C11" s="135">
         <f ca="1">Overview!C5</f>
-        <v>233.54</v>
+        <v>245.16</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.2">
@@ -25537,7 +25537,7 @@
       </c>
       <c r="C12" s="154">
         <f ca="1">(C10-C11)/C11</f>
-        <v>4.2167502267946293E-2</v>
+        <v>-3.0308066595574274E-3</v>
       </c>
     </row>
   </sheetData>
@@ -26046,7 +26046,7 @@
       </c>
       <c r="C24" s="137">
         <f ca="1">IF(Overview!C29&gt;0,Overview!C29,WACC!C19)</f>
-        <v>0.11181749999999999</v>
+        <v>0.11076</v>
       </c>
     </row>
     <row r="25" spans="2:14" x14ac:dyDescent="0.2">
@@ -26300,7 +26300,7 @@
       <c r="K8" s="139"/>
       <c r="L8" s="128">
         <f ca="1">L7*(1+C20)/(C21-C20)</f>
-        <v>56922.603057676512</v>
+        <v>57449.534437670161</v>
       </c>
       <c r="N8" s="91"/>
       <c r="O8" s="16"/>
@@ -26354,23 +26354,23 @@
       <c r="G10" s="140"/>
       <c r="H10" s="128">
         <f ca="1">H7/(1+$C$21)^H9</f>
-        <v>958.23872437450552</v>
+        <v>958.93438284205592</v>
       </c>
       <c r="I10" s="128">
         <f t="shared" ref="I10:L10" ca="1" si="1">I7/(1+$C$21)^I9</f>
-        <v>1267.438246439053</v>
+        <v>1269.279174328715</v>
       </c>
       <c r="J10" s="128">
         <f t="shared" ca="1" si="1"/>
-        <v>1676.4086731989319</v>
+        <v>1680.0624226339171</v>
       </c>
       <c r="K10" s="128">
         <f t="shared" ca="1" si="1"/>
-        <v>2217.3435648422683</v>
+        <v>2223.7895342758957</v>
       </c>
       <c r="L10" s="128">
         <f t="shared" ca="1" si="1"/>
-        <v>2932.8245332717784</v>
+        <v>2943.4858051298525</v>
       </c>
       <c r="N10" s="91"/>
     </row>
@@ -26389,15 +26389,15 @@
       <c r="K11" s="139"/>
       <c r="L11" s="128">
         <f ca="1">L8/(1+C21)^L9</f>
-        <v>34147.749138005885</v>
+        <v>34589.135610828511</v>
       </c>
     </row>
     <row r="13" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B14" s="254" t="s">
+      <c r="B14" s="255" t="s">
         <v>221</v>
       </c>
-      <c r="C14" s="255"/>
+      <c r="C14" s="256"/>
     </row>
     <row r="15" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B15" s="155" t="s">
@@ -26405,7 +26405,7 @@
       </c>
       <c r="C15" s="156">
         <f ca="1">Overview!C5</f>
-        <v>233.54</v>
+        <v>245.16</v>
       </c>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.2">
@@ -26414,7 +26414,7 @@
       </c>
       <c r="C16" s="156">
         <f ca="1">C36</f>
-        <v>210.90432000063359</v>
+        <v>213.12768866047347</v>
       </c>
     </row>
     <row r="17" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -26424,20 +26424,20 @@
       <c r="C17" s="158">
         <v>0.46500000000000002</v>
       </c>
-      <c r="E17" s="256" t="s">
+      <c r="E17" s="254" t="s">
         <v>224</v>
       </c>
-      <c r="F17" s="256"/>
-      <c r="G17" s="256"/>
-      <c r="H17" s="256"/>
-      <c r="I17" s="256"/>
+      <c r="F17" s="254"/>
+      <c r="G17" s="254"/>
+      <c r="H17" s="254"/>
+      <c r="I17" s="254"/>
     </row>
     <row r="18" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="19" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B19" s="254" t="s">
+      <c r="B19" s="255" t="s">
         <v>183</v>
       </c>
-      <c r="C19" s="255"/>
+      <c r="C19" s="256"/>
     </row>
     <row r="20" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B20" s="159" t="s">
@@ -26453,7 +26453,7 @@
       </c>
       <c r="C21" s="220">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.10760404710270478</v>
+        <v>0.10680053630170883</v>
       </c>
     </row>
     <row r="22" spans="2:9" x14ac:dyDescent="0.2">
@@ -26471,7 +26471,7 @@
       </c>
       <c r="C23" s="161">
         <f ca="1">C15*C22</f>
-        <v>48809.86</v>
+        <v>51238.44</v>
       </c>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.2">
@@ -26498,15 +26498,15 @@
       </c>
       <c r="C26" s="162">
         <f ca="1">C23+C25-C24</f>
-        <v>47930.86</v>
+        <v>50359.44</v>
       </c>
     </row>
     <row r="27" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B28" s="254" t="s">
+      <c r="B28" s="255" t="s">
         <v>185</v>
       </c>
-      <c r="C28" s="255"/>
+      <c r="C28" s="256"/>
     </row>
     <row r="29" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B29" s="159" t="s">
@@ -26514,7 +26514,7 @@
       </c>
       <c r="C29" s="161">
         <f ca="1">SUM(H10:L10)</f>
-        <v>9052.253742126537</v>
+        <v>9075.5513192104372</v>
       </c>
     </row>
     <row r="30" spans="2:9" x14ac:dyDescent="0.2">
@@ -26523,7 +26523,7 @@
       </c>
       <c r="C30" s="161">
         <f ca="1">L11</f>
-        <v>34147.749138005885</v>
+        <v>34589.135610828511</v>
       </c>
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.2">
@@ -26532,7 +26532,7 @@
       </c>
       <c r="C31" s="164">
         <f ca="1">C29+C30</f>
-        <v>43200.002880132422</v>
+        <v>43664.686930038952</v>
       </c>
     </row>
     <row r="32" spans="2:9" x14ac:dyDescent="0.2">
@@ -26559,7 +26559,7 @@
       </c>
       <c r="C34" s="164">
         <f ca="1">C31+C32-C33</f>
-        <v>44079.002880132422</v>
+        <v>44543.686930038952</v>
       </c>
     </row>
     <row r="35" spans="2:3" x14ac:dyDescent="0.2">
@@ -26577,21 +26577,21 @@
       </c>
       <c r="C36" s="167">
         <f ca="1">C34/C35</f>
-        <v>210.90432000063359</v>
+        <v>213.12768866047347</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="P3:W3"/>
+    <mergeCell ref="X3:Z3"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="P5:Z5"/>
+    <mergeCell ref="B14:C14"/>
     <mergeCell ref="E17:I17"/>
     <mergeCell ref="B19:C19"/>
     <mergeCell ref="B28:C28"/>
     <mergeCell ref="C3:G3"/>
     <mergeCell ref="H3:L3"/>
-    <mergeCell ref="P3:W3"/>
-    <mergeCell ref="X3:Z3"/>
-    <mergeCell ref="C5:L5"/>
-    <mergeCell ref="P5:Z5"/>
-    <mergeCell ref="B14:C14"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -33247,7 +33247,7 @@
       </c>
       <c r="AC117" s="63">
         <f ca="1">Overview!C5</f>
-        <v>233.54</v>
+        <v>245.16</v>
       </c>
     </row>
     <row r="118" spans="1:31" x14ac:dyDescent="0.2">
@@ -33318,7 +33318,7 @@
       </c>
       <c r="AC118" s="65">
         <f ca="1">AC117/AC86</f>
-        <v>233.54</v>
+        <v>245.16</v>
       </c>
     </row>
     <row r="120" spans="1:31" x14ac:dyDescent="0.2">
@@ -34624,7 +34624,7 @@
       <c r="AA151" s="49"/>
       <c r="AC151" s="72">
         <f ca="1">AC118/Statement!AC27</f>
-        <v>30.212160413971535</v>
+        <v>31.715394566623541</v>
       </c>
     </row>
     <row r="152" spans="2:29" x14ac:dyDescent="0.2">
@@ -34661,7 +34661,7 @@
       <c r="AA152" s="49"/>
       <c r="AC152" s="72">
         <f ca="1">AC118/(Statement!AC5/Statement!AC23)</f>
-        <v>6.3856251604621308</v>
+        <v>6.7033478818998722</v>
       </c>
     </row>
     <row r="153" spans="2:29" x14ac:dyDescent="0.2">
@@ -34722,7 +34722,7 @@
       </c>
       <c r="AC153" s="72">
         <f ca="1">AC118/(Statement!AC50/Statement!AC76)</f>
-        <v>14.427981081879986</v>
+        <v>15.145858705291159</v>
       </c>
     </row>
     <row r="154" spans="2:29" x14ac:dyDescent="0.2">
@@ -34783,7 +34783,7 @@
       </c>
       <c r="AC154" s="143">
         <f ca="1">Statement!AC118*Statement!AC79</f>
-        <v>49043.4</v>
+        <v>51483.6</v>
       </c>
     </row>
     <row r="155" spans="2:29" x14ac:dyDescent="0.2">
@@ -34844,7 +34844,7 @@
       </c>
       <c r="AC155" s="143">
         <f ca="1">AC154+AC109-AC108+AC49+AC46</f>
-        <v>48164.4</v>
+        <v>50604.6</v>
       </c>
     </row>
     <row r="156" spans="2:29" x14ac:dyDescent="0.2">
@@ -34881,7 +34881,7 @@
       <c r="AA156" s="49"/>
       <c r="AC156" s="181">
         <f ca="1">AC155/AC5</f>
-        <v>6.182849807445443</v>
+        <v>6.4960975609756098</v>
       </c>
     </row>
     <row r="157" spans="2:29" x14ac:dyDescent="0.2">
@@ -34918,7 +34918,7 @@
       <c r="AA157" s="49"/>
       <c r="AC157" s="181">
         <f ca="1">AC155/AC13</f>
-        <v>23.598432141107303</v>
+        <v>24.794022537971582</v>
       </c>
     </row>
     <row r="158" spans="2:29" x14ac:dyDescent="0.2">
@@ -35053,7 +35053,7 @@
       <c r="AA160" s="49"/>
       <c r="AC160" s="72">
         <f t="shared" ref="AC160:AC161" ca="1" si="155">AC154/AC158</f>
-        <v>23.376263107721641</v>
+        <v>24.539370829361296</v>
       </c>
     </row>
     <row r="161" spans="2:29" x14ac:dyDescent="0.2">
@@ -35090,7 +35090,7 @@
       <c r="AA161" s="49"/>
       <c r="AC161" s="72">
         <f t="shared" ca="1" si="155"/>
-        <v>39.606374924702379</v>
+        <v>41.612991348684794</v>
       </c>
     </row>
     <row r="162" spans="2:29" x14ac:dyDescent="0.2">
@@ -35127,7 +35127,7 @@
       <c r="AA162" s="49"/>
       <c r="AC162" s="74">
         <f t="shared" ref="AC162" ca="1" si="158">AC158/AC154</f>
-        <v>4.277843705778963E-2</v>
+        <v>4.0750841044526802E-2</v>
       </c>
     </row>
     <row r="163" spans="2:29" x14ac:dyDescent="0.2">
@@ -35164,7 +35164,7 @@
       <c r="AA163" s="49"/>
       <c r="AC163" s="74">
         <f ca="1">AC27/AC118</f>
-        <v>3.3099254945619598E-2</v>
+        <v>3.1530429107521622E-2</v>
       </c>
     </row>
     <row r="164" spans="2:29" x14ac:dyDescent="0.2">
@@ -35238,7 +35238,7 @@
       <c r="AA165" s="49"/>
       <c r="AC165" s="154">
         <f ca="1">-AC64/AC154</f>
-        <v>3.2440654603881458E-2</v>
+        <v>3.0903044853118275E-2</v>
       </c>
     </row>
     <row r="166" spans="2:29" x14ac:dyDescent="0.2">
@@ -35275,7 +35275,7 @@
       <c r="AA166" s="49"/>
       <c r="AC166" s="154">
         <f ca="1">-(AC64+AC65)/AC154</f>
-        <v>3.2440654603881458E-2</v>
+        <v>3.0903044853118275E-2</v>
       </c>
     </row>
     <row r="167" spans="2:29" x14ac:dyDescent="0.2">
@@ -35778,7 +35778,7 @@
       <c r="AA177" s="49"/>
       <c r="AC177" s="154">
         <f ca="1">(AC108-AC109)/AC154</f>
-        <v>1.7922900940799374E-2</v>
+        <v>1.7073398130666852E-2</v>
       </c>
     </row>
     <row r="178" spans="1:31" x14ac:dyDescent="0.2">
@@ -37628,7 +37628,7 @@
       </c>
       <c r="C5" s="170">
         <f ca="1">Overview!C5</f>
-        <v>233.54</v>
+        <v>245.16</v>
       </c>
       <c r="E5" s="12"/>
       <c r="F5" s="134" t="s">
@@ -37644,7 +37644,7 @@
       </c>
       <c r="C6" s="171">
         <f ca="1">Statement!AC154</f>
-        <v>49043.4</v>
+        <v>51483.6</v>
       </c>
       <c r="E6" s="20" t="s">
         <v>19</v>
@@ -37664,7 +37664,7 @@
       </c>
       <c r="C7" s="171">
         <f ca="1">Statement!AC155</f>
-        <v>48164.4</v>
+        <v>50604.6</v>
       </c>
       <c r="E7" s="20" t="s">
         <v>31</v>
@@ -37684,7 +37684,7 @@
       </c>
       <c r="C8" s="172">
         <f ca="1">Statement!AC151</f>
-        <v>30.212160413971535</v>
+        <v>31.715394566623541</v>
       </c>
       <c r="E8" s="20" t="s">
         <v>242</v>
@@ -37704,7 +37704,7 @@
       </c>
       <c r="C9" s="172">
         <f ca="1">Statement!AC152</f>
-        <v>6.3856251604621308</v>
+        <v>6.7033478818998722</v>
       </c>
       <c r="E9" s="20" t="s">
         <v>243</v>
@@ -37724,7 +37724,7 @@
       </c>
       <c r="C10" s="172">
         <f ca="1">Statement!AC153</f>
-        <v>14.427981081879986</v>
+        <v>15.145858705291159</v>
       </c>
       <c r="E10" s="20" t="s">
         <v>1</v>
@@ -37744,7 +37744,7 @@
       </c>
       <c r="C11" s="172">
         <f ca="1">Statement!AC156</f>
-        <v>6.182849807445443</v>
+        <v>6.4960975609756098</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
@@ -37753,7 +37753,7 @@
       </c>
       <c r="C12" s="172">
         <f ca="1">Statement!AC157</f>
-        <v>23.598432141107303</v>
+        <v>24.794022537971582</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.2">
@@ -37989,7 +37989,7 @@
       </c>
       <c r="C38" s="173">
         <f ca="1">Statement!AC163</f>
-        <v>3.3099254945619598E-2</v>
+        <v>3.1530429107521622E-2</v>
       </c>
       <c r="E38" s="20" t="s">
         <v>269</v>
@@ -38005,7 +38005,7 @@
       </c>
       <c r="C39" s="213">
         <f ca="1">Statement!AC162</f>
-        <v>4.277843705778963E-2</v>
+        <v>4.0750841044526802E-2</v>
       </c>
       <c r="E39" s="20" t="s">
         <v>271</v>
@@ -38037,7 +38037,7 @@
       </c>
       <c r="C41" s="173">
         <f ca="1">Statement!AC165</f>
-        <v>3.2440654603881458E-2</v>
+        <v>3.0903044853118275E-2</v>
       </c>
     </row>
     <row r="42" spans="2:6" x14ac:dyDescent="0.2">
@@ -38046,7 +38046,7 @@
       </c>
       <c r="C42" s="173">
         <f ca="1">Statement!AC166</f>
-        <v>3.2440654603881458E-2</v>
+        <v>3.0903044853118275E-2</v>
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.2">
@@ -38090,7 +38090,7 @@
       </c>
       <c r="F48" s="173">
         <f ca="1">Statement!AC177</f>
-        <v>1.7922900940799374E-2</v>
+        <v>1.7073398130666852E-2</v>
       </c>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.2">
@@ -38269,7 +38269,7 @@
       </c>
       <c r="I6" s="170">
         <f ca="1">Statement!AC117</f>
-        <v>233.54</v>
+        <v>245.16</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -38298,7 +38298,7 @@
       </c>
       <c r="I7" s="171">
         <f ca="1">Statement!AC154</f>
-        <v>49043.4</v>
+        <v>51483.6</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
@@ -38327,7 +38327,7 @@
       </c>
       <c r="I8" s="171">
         <f ca="1">Statement!AC155</f>
-        <v>48164.4</v>
+        <v>50604.6</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -38356,7 +38356,7 @@
       </c>
       <c r="I9" s="172">
         <f ca="1">Statement!AC151</f>
-        <v>30.212160413971535</v>
+        <v>31.715394566623541</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -38385,7 +38385,7 @@
       </c>
       <c r="I10" s="172">
         <f ca="1">Statement!AC152</f>
-        <v>6.3856251604621308</v>
+        <v>6.7033478818998722</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -38414,7 +38414,7 @@
       </c>
       <c r="I11" s="172">
         <f ca="1">Statement!AC153</f>
-        <v>14.427981081879986</v>
+        <v>15.145858705291159</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
@@ -38443,7 +38443,7 @@
       </c>
       <c r="I12" s="172">
         <f ca="1">Statement!AC156</f>
-        <v>6.182849807445443</v>
+        <v>6.4960975609756098</v>
       </c>
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.2">
@@ -38472,7 +38472,7 @@
       </c>
       <c r="I13" s="172">
         <f ca="1">Statement!AC157</f>
-        <v>23.598432141107303</v>
+        <v>24.794022537971582</v>
       </c>
     </row>
     <row r="15" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -39245,7 +39245,7 @@
       </c>
       <c r="I51" s="173">
         <f ca="1">Statement!AC163</f>
-        <v>3.3099254945619598E-2</v>
+        <v>3.1530429107521622E-2</v>
       </c>
     </row>
     <row r="52" spans="2:9" x14ac:dyDescent="0.2">
@@ -39274,7 +39274,7 @@
       </c>
       <c r="I52" s="173">
         <f ca="1">Statement!AC162</f>
-        <v>4.277843705778963E-2</v>
+        <v>4.0750841044526802E-2</v>
       </c>
     </row>
     <row r="53" spans="2:9" x14ac:dyDescent="0.2">
@@ -39332,7 +39332,7 @@
       </c>
       <c r="I54" s="173">
         <f ca="1">Statement!AC165</f>
-        <v>3.2440654603881458E-2</v>
+        <v>3.0903044853118275E-2</v>
       </c>
     </row>
     <row r="55" spans="2:9" x14ac:dyDescent="0.2">
@@ -39361,7 +39361,7 @@
       </c>
       <c r="I55" s="173">
         <f ca="1">Statement!AC166</f>
-        <v>3.2440654603881458E-2</v>
+        <v>3.0903044853118275E-2</v>
       </c>
     </row>
     <row r="57" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -39597,7 +39597,7 @@
       </c>
       <c r="I68" s="194">
         <f ca="1">Statement!AC177</f>
-        <v>1.7922900940799374E-2</v>
+        <v>1.7073398130666852E-2</v>
       </c>
     </row>
     <row r="70" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -40750,30 +40750,6 @@
     </row>
   </sheetData>
   <mergeCells count="32">
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="F25:G25"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="F27:G27"/>
-    <mergeCell ref="C30:D30"/>
-    <mergeCell ref="F30:G30"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="F19:G19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="F21:G21"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="F9:G9"/>
     <mergeCell ref="C38:D38"/>
     <mergeCell ref="F38:G38"/>
     <mergeCell ref="C32:D32"/>
@@ -40782,6 +40758,30 @@
     <mergeCell ref="F34:G34"/>
     <mergeCell ref="C36:D36"/>
     <mergeCell ref="F36:G36"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="F25:G25"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="F27:G27"/>
+    <mergeCell ref="C30:D30"/>
+    <mergeCell ref="F30:G30"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>

--- a/ADSK.xlsx
+++ b/ADSK.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8CB6418-049C-8640-8E35-4E414F2C0810}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8A264DC-642A-5C45-9FCB-9D6AF5A87731}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
@@ -118,7 +118,7 @@
       </extLst>
     </bk>
   </futureMetadata>
-  <futureMetadata name="XLRICHVALUE" count="2">
+  <futureMetadata name="XLRICHVALUE" count="5">
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
@@ -129,7 +129,28 @@
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="3"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="4"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
           <xlrd:rvb i="5"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="8"/>
         </ext>
       </extLst>
     </bk>
@@ -139,19 +160,28 @@
       <rc t="1" v="0"/>
     </bk>
   </cellMetadata>
-  <valueMetadata count="2">
+  <valueMetadata count="5">
     <bk>
       <rc t="2" v="0"/>
     </bk>
     <bk>
       <rc t="2" v="1"/>
     </bk>
+    <bk>
+      <rc t="2" v="2"/>
+    </bk>
+    <bk>
+      <rc t="2" v="3"/>
+    </bk>
+    <bk>
+      <rc t="2" v="4"/>
+    </bk>
   </valueMetadata>
 </metadata>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="816" uniqueCount="441">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="817" uniqueCount="442">
   <si>
     <t>Ticker</t>
   </si>
@@ -1474,6 +1504,9 @@
   </si>
   <si>
     <t>Overview'!B3</t>
+  </si>
+  <si>
+    <t>Reverse DCF price</t>
   </si>
 </sst>
 </file>
@@ -2092,7 +2125,7 @@
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="257">
+  <cellXfs count="260">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
@@ -2466,6 +2499,9 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="168" fontId="0" fillId="17" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="27" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
@@ -15167,7 +15203,7 @@
 </file>
 
 <file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
-<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="6">
+<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="9">
   <rv s="0">
     <v>https://www.bing.com/financeapi/forcetrigger?t=a1mwoc&amp;q=XNAS%3aADSK&amp;form=skydnc</v>
     <v>Learn more on Bing</v>
@@ -15186,11 +15222,9 @@
     <v>Powered by Refinitiv</v>
     <v>320</v>
     <v>185.5</v>
-    <v>1.3080000000000001</v>
-    <v>14.02</v>
-    <v>6.0656000000000002E-2</v>
-    <v>-1.52</v>
-    <v>-6.1999999999999998E-3</v>
+    <v>1.3027</v>
+    <v>3.37</v>
+    <v>1.4001E-2</v>
     <v>USD</v>
     <v>Autodesk, Inc. is engaged in three-dimensional (3D) design, engineering and entertainment technology solutions, spanning architecture, engineering, construction, product design, manufacturing, media and entertainment. Its architecture, engineering, construction and operations products improve the way building, infrastructure, and industrial projects are designed, built, and operated. Its product development and manufacturing software provides manufacturers in the automotive, transportation, industrial machinery, consumer products, and building product industries with comprehensive digital design, engineering, manufacturing, and production solutions. Its product offerings include AutoCAD Civil 3D, Autodesk Build, BIM Collaborate Pro, Building Connected, Revit, Tandem, AutoCAD, AutoCAD LT, Inventor, Vault, Maya, 3ds Max, Flow Production Tracking, among others. AutoCAD Civil 3D solution offers surveying, design, analysis, and documentation solution.</v>
     <v>14300</v>
@@ -15198,35 +15232,49 @@
     <v>XNAS</v>
     <v>XNAS</v>
     <v>One Market, Ste. 400., SAN FRANCISCO, CA, 94105 US</v>
-    <v>246.74</v>
+    <v>247.68</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46310.894717499999</v>
+    <v>46315.717840462501</v>
     <v>0</v>
-    <v>234.02500000000001</v>
-    <v>51238440000</v>
+    <v>241.1</v>
+    <v>51010630000</v>
     <v>AUTODESK, INC.</v>
     <v>AUTODESK, INC.</v>
-    <v>234.18</v>
-    <v>31.785699999999999</v>
-    <v>231.14</v>
-    <v>245.16</v>
-    <v>243.64</v>
+    <v>241.1</v>
+    <v>31.644400000000001</v>
+    <v>240.7</v>
+    <v>244.07</v>
     <v>209000000</v>
     <v>ADSK</v>
     <v>AUTODESK, INC. (XNAS:ADSK)</v>
-    <v>2427911</v>
-    <v>2117039</v>
+    <v>684901</v>
+    <v>2072616</v>
     <v>1994</v>
   </rv>
   <rv s="2">
     <v>1</v>
   </rv>
+  <rv s="3">
+    <v>12</v>
+    <v>Price (Extended hours)</v>
+    <v>0</v>
+  </rv>
+  <rv s="3">
+    <v>12</v>
+    <v>Change (extended hours)</v>
+    <v>0</v>
+  </rv>
+  <rv s="3">
+    <v>12</v>
+    <v>Change % (extended hours)</v>
+    <v>0</v>
+  </rv>
   <rv s="0">
     <v>https://www.bing.com/financeapi/forcetrigger?t=a33knm&amp;q=10+Y+TSY+YLD+NDX&amp;form=skydnc</v>
     <v>Learn more on Bing</v>
   </rv>
-  <rv s="3">
+  <rv s="4">
     <v>5</v>
     <v>10 Y TSY YLD NDX</v>
     <v>6</v>
@@ -15240,28 +15288,28 @@
     <v>Powered by Refinitiv</v>
     <v>53.64</v>
     <v>39.47</v>
-    <v>-0.27</v>
-    <v>-5.1749999999999999E-3</v>
+    <v>0.38</v>
+    <v>7.4539999999999997E-3</v>
     <v>US</v>
-    <v>53.29</v>
+    <v>51.5</v>
     <v>Index</v>
-    <v>3</v>
-    <v>51.77</v>
+    <v>6</v>
+    <v>50.9</v>
     <v>10 Y TSY YLD NDX</v>
-    <v>51.96</v>
-    <v>52.17</v>
-    <v>51.9</v>
+    <v>50.9</v>
+    <v>50.98</v>
+    <v>51.36</v>
     <v>TNX</v>
     <v>10 Y TSY YLD NDX</v>
   </rv>
   <rv s="2">
-    <v>4</v>
+    <v>7</v>
   </rv>
 </rvData>
 </file>
 
 <file path=xl/richData/rdrichvaluestructure.xml><?xml version="1.0" encoding="utf-8"?>
-<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="4">
+<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="5">
   <s t="_hyperlink">
     <k n="Address" t="s"/>
     <k n="Text" t="s"/>
@@ -15283,8 +15331,6 @@
     <k n="Beta"/>
     <k n="Change"/>
     <k n="Change (%)"/>
-    <k n="Change (Extended hours)"/>
-    <k n="Change % (Extended hours)"/>
     <k n="Currency" t="s"/>
     <k n="Description" t="s"/>
     <k n="Employees"/>
@@ -15305,7 +15351,6 @@
     <k n="P/E"/>
     <k n="Previous close"/>
     <k n="Price"/>
-    <k n="Price (Extended hours)"/>
     <k n="Shares outstanding"/>
     <k n="Ticker symbol" t="s"/>
     <k n="UniqueName" t="s"/>
@@ -15315,6 +15360,11 @@
   </s>
   <s t="_linkedentity">
     <k n="%cvi" t="r"/>
+  </s>
+  <s t="_error">
+    <k n="errorType" t="i"/>
+    <k n="field" t="s"/>
+    <k n="subType" t="i"/>
   </s>
   <s t="_linkedentitycore">
     <k n="_Display" t="spb"/>
@@ -15350,7 +15400,7 @@
 <file path=xl/richData/rdsupportingpropertybag.xml><?xml version="1.0" encoding="utf-8"?>
 <supportingPropertyBags xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2">
   <spbArrays count="2">
-    <a count="45">
+    <a count="42">
       <v t="s">%EntityServiceId</v>
       <v t="s">_Format</v>
       <v t="s">%IsRefreshable</v>
@@ -15361,16 +15411,13 @@
       <v t="s">Name</v>
       <v t="s">_SubLabel</v>
       <v t="s">Price</v>
-      <v t="s">Price (Extended hours)</v>
       <v t="s">Exchange</v>
       <v t="s">Official name</v>
       <v t="s">Last trade time</v>
       <v t="s">Ticker symbol</v>
       <v t="s">Exchange abbreviation</v>
       <v t="s">Change</v>
-      <v t="s">Change (Extended hours)</v>
       <v t="s">Change (%)</v>
-      <v t="s">Change % (Extended hours)</v>
       <v t="s">Currency</v>
       <v t="s">Previous close</v>
       <v t="s">Open</v>
@@ -15464,19 +15511,13 @@
       <v>8</v>
       <v>9</v>
       <v>4</v>
-      <v>1</v>
-      <v>1</v>
-      <v>5</v>
     </spb>
     <spb s="4">
-      <v>at close</v>
+      <v>Real-Time Nasdaq Last Sale</v>
       <v>from previous close</v>
       <v>from previous close</v>
       <v>Source: Nasdaq Last Sale</v>
       <v>GMT</v>
-      <v>Real-Time Nasdaq Last Sale</v>
-      <v>from close</v>
-      <v>from close</v>
     </spb>
     <spb s="0">
       <v>1</v>
@@ -15548,9 +15589,6 @@
     <k n="Year incorporated" t="i"/>
     <k n="`%EntityServiceId" t="i"/>
     <k n="Shares outstanding" t="i"/>
-    <k n="Price (Extended hours)" t="i"/>
-    <k n="Change (Extended hours)" t="i"/>
-    <k n="Change % (Extended hours)" t="i"/>
   </s>
   <s>
     <k n="Price" t="s"/>
@@ -15558,9 +15596,6 @@
     <k n="Change (%)" t="s"/>
     <k n="ExchangeID" t="s"/>
     <k n="Last trade time" t="s"/>
-    <k n="Price (Extended hours)" t="s"/>
-    <k n="Change (Extended hours)" t="s"/>
-    <k n="Change % (Extended hours)" t="s"/>
   </s>
   <s>
     <k n="UniqueName" t="spb"/>
@@ -16038,7 +16073,7 @@
     <col min="5" max="5" width="19.1640625" style="1" customWidth="1"/>
     <col min="6" max="6" width="14.5" style="1" customWidth="1"/>
     <col min="7" max="7" width="1.6640625" style="1" customWidth="1"/>
-    <col min="8" max="8" width="15.1640625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="15.83203125" style="1" customWidth="1"/>
     <col min="9" max="9" width="8.6640625" style="1" customWidth="1"/>
     <col min="10" max="10" width="2" style="1" customWidth="1"/>
     <col min="11" max="11" width="16.5" style="1" customWidth="1"/>
@@ -16076,7 +16111,7 @@
       </c>
       <c r="F3" s="185">
         <f ca="1">Statement!AC154</f>
-        <v>51483.6</v>
+        <v>51254.7</v>
       </c>
       <c r="H3" s="183" t="str">
         <f>'AVG target price'!B5</f>
@@ -16084,7 +16119,7 @@
       </c>
       <c r="I3" s="209">
         <f ca="1">'AVG target price'!C5</f>
-        <v>118.57284844015848</v>
+        <v>119.63544251297965</v>
       </c>
       <c r="K3" s="237" t="s">
         <v>436</v>
@@ -16103,7 +16138,7 @@
       </c>
       <c r="F4" s="186">
         <f ca="1">Statement!AC155</f>
-        <v>50604.6</v>
+        <v>50375.7</v>
       </c>
       <c r="H4" s="183" t="str">
         <f>'AVG target price'!B6</f>
@@ -16111,7 +16146,7 @@
       </c>
       <c r="I4" s="209">
         <f ca="1">'AVG target price'!C6</f>
-        <v>347.71724854292682</v>
+        <v>348.83223203863969</v>
       </c>
       <c r="K4" s="237" t="s">
         <v>437</v>
@@ -16123,7 +16158,7 @@
       </c>
       <c r="C5" s="206" cm="1">
         <f t="array" aca="1" ref="C5" ca="1">_FV(C3,"Price",TRUE)</f>
-        <v>245.16</v>
+        <v>244.07</v>
       </c>
       <c r="E5" s="183" t="s">
         <v>242</v>
@@ -16138,7 +16173,7 @@
       </c>
       <c r="I5" s="209">
         <f ca="1">'AVG target price'!C7</f>
-        <v>189.15919991140987</v>
+        <v>189.82347741565462</v>
       </c>
       <c r="K5" s="237" t="s">
         <v>438</v>
@@ -16148,16 +16183,16 @@
       <c r="B6" s="183" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="206" cm="1">
-        <f t="array" aca="1" ref="C6" ca="1">_FV(C3,"Price (Extended hours)",TRUE)</f>
-        <v>243.64</v>
+      <c r="C6" s="206" t="e" cm="1" vm="2">
+        <f t="array" ref="C6">_FV(C3,"Price (Extended hours)",TRUE)</f>
+        <v>#VALUE!</v>
       </c>
       <c r="E6" s="183" t="s">
         <v>236</v>
       </c>
       <c r="F6" s="188">
         <f ca="1">Statement!AC151</f>
-        <v>31.715394566623541</v>
+        <v>31.574385510996116</v>
       </c>
       <c r="H6" s="183" t="str">
         <f>'AVG target price'!B8</f>
@@ -16165,7 +16200,7 @@
       </c>
       <c r="I6" s="209">
         <f ca="1">'AVG target price'!C8</f>
-        <v>346.17391838017352</v>
+        <v>347.28369308146864</v>
       </c>
       <c r="K6" s="238" t="s">
         <v>439</v>
@@ -16177,14 +16212,14 @@
       </c>
       <c r="C7" s="6" cm="1">
         <f t="array" aca="1" ref="C7" ca="1">_FV(C3,"Change")</f>
-        <v>14.02</v>
+        <v>3.37</v>
       </c>
       <c r="E7" s="184" t="s">
         <v>200</v>
       </c>
       <c r="F7" s="189">
         <f ca="1">Statement!AC152</f>
-        <v>6.7033478818998722</v>
+        <v>6.6735442875481388</v>
       </c>
       <c r="H7" s="183" t="str">
         <f>'AVG target price'!B9</f>
@@ -16192,23 +16227,23 @@
       </c>
       <c r="I7" s="209">
         <f ca="1">'AVG target price'!C9</f>
-        <v>220.46162192204596</v>
+        <v>221.14711313311457</v>
       </c>
     </row>
     <row r="8" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B8" s="183" t="s">
         <v>4</v>
       </c>
-      <c r="C8" s="6" cm="1">
-        <f t="array" aca="1" ref="C8" ca="1">_FV(C3,"Change (extended hours)",TRUE)</f>
-        <v>-1.52</v>
+      <c r="C8" s="6" t="e" cm="1" vm="3">
+        <f t="array" ref="C8">_FV(C3,"Change (extended hours)",TRUE)</f>
+        <v>#VALUE!</v>
       </c>
       <c r="E8" s="183" t="s">
         <v>264</v>
       </c>
       <c r="F8" s="190">
         <f ca="1">Statement!AC162</f>
-        <v>4.0750841044526802E-2</v>
+        <v>4.0932831525694234E-2</v>
       </c>
       <c r="H8" s="182" t="str">
         <f>'AVG target price'!B10</f>
@@ -16216,7 +16251,7 @@
       </c>
       <c r="I8" s="210">
         <f ca="1">'AVG target price'!C10</f>
-        <v>244.4169674393429</v>
+        <v>245.34439163637143</v>
       </c>
     </row>
     <row r="9" spans="2:11" x14ac:dyDescent="0.2">
@@ -16225,14 +16260,14 @@
       </c>
       <c r="C9" s="73" cm="1">
         <f t="array" aca="1" ref="C9" ca="1">_FV(C3,"Change (%)",TRUE)</f>
-        <v>6.0656000000000002E-2</v>
+        <v>1.4001E-2</v>
       </c>
       <c r="E9" s="183" t="s">
         <v>287</v>
       </c>
       <c r="F9" s="190">
         <f ca="1">Statement!AC163</f>
-        <v>3.1530429107521622E-2</v>
+        <v>3.1671241856844348E-2</v>
       </c>
       <c r="H9" s="182" t="str">
         <f>'AVG target price'!B12</f>
@@ -16240,23 +16275,23 @@
       </c>
       <c r="I9" s="211">
         <f ca="1">'AVG target price'!C12</f>
-        <v>-3.0308066595574274E-3</v>
+        <v>5.221418594548422E-3</v>
       </c>
     </row>
     <row r="10" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B10" s="183" t="s">
         <v>6</v>
       </c>
-      <c r="C10" s="73" cm="1">
-        <f t="array" aca="1" ref="C10" ca="1">_FV(C3,"Change % (extended hours)",TRUE)</f>
-        <v>-6.1999999999999998E-3</v>
+      <c r="C10" s="73" t="e" cm="1" vm="4">
+        <f t="array" ref="C10">_FV(C3,"Change % (extended hours)",TRUE)</f>
+        <v>#VALUE!</v>
       </c>
       <c r="E10" s="183" t="s">
         <v>292</v>
       </c>
       <c r="F10" s="190">
         <f ca="1">Statement!AC165</f>
-        <v>3.0903044853118275E-2</v>
+        <v>3.104105574708271E-2</v>
       </c>
     </row>
     <row r="11" spans="2:11" x14ac:dyDescent="0.2">
@@ -16304,7 +16339,7 @@
       </c>
       <c r="C13" s="207" cm="1">
         <f t="array" aca="1" ref="C13" ca="1">_FV(C3,"Beta")</f>
-        <v>1.3080000000000001</v>
+        <v>1.3027</v>
       </c>
       <c r="E13" s="183" t="s">
         <v>103</v>
@@ -16313,12 +16348,12 @@
         <f>Statement!AC126</f>
         <v>0.48536801655335504</v>
       </c>
-      <c r="H13" s="182" t="s">
+      <c r="H13" s="259" t="s">
         <v>383</v>
       </c>
-      <c r="I13" s="211">
+      <c r="I13" s="257">
         <f>'Reverse DCF'!C17</f>
-        <v>0.46500000000000002</v>
+        <v>0.51</v>
       </c>
     </row>
     <row r="14" spans="2:11" x14ac:dyDescent="0.2">
@@ -16327,7 +16362,7 @@
       </c>
       <c r="C14" s="208" cm="1">
         <f t="array" aca="1" ref="C14" ca="1">_FV(C3,"Volume average",TRUE)</f>
-        <v>2117039</v>
+        <v>2072616</v>
       </c>
       <c r="E14" s="184" t="s">
         <v>104</v>
@@ -16336,6 +16371,13 @@
         <f>Statement!AC141</f>
         <v>0.63581348227633894</v>
       </c>
+      <c r="H14" s="184" t="s">
+        <v>441</v>
+      </c>
+      <c r="I14" s="258">
+        <f ca="1">'Reverse DCF'!C16</f>
+        <v>247.54895652923278</v>
+      </c>
     </row>
     <row r="15" spans="2:11" x14ac:dyDescent="0.2">
       <c r="E15" s="183" t="s">
@@ -16343,7 +16385,7 @@
       </c>
       <c r="F15" s="190">
         <f ca="1">Statement!AC177</f>
-        <v>1.7073398130666852E-2</v>
+        <v>1.7149646764101634E-2</v>
       </c>
     </row>
     <row r="16" spans="2:11" x14ac:dyDescent="0.2">
@@ -16376,7 +16418,7 @@
       </c>
       <c r="I17" s="235">
         <f ca="1">DCF!C15</f>
-        <v>0.10680053630170883</v>
+        <v>0.10605494718970561</v>
       </c>
     </row>
     <row r="18" spans="2:9" x14ac:dyDescent="0.2">
@@ -16398,7 +16440,7 @@
       </c>
       <c r="I18" s="236">
         <f ca="1">Multiples!C54</f>
-        <v>0.11076</v>
+        <v>0.1099815</v>
       </c>
     </row>
     <row r="19" spans="2:9" x14ac:dyDescent="0.2">
@@ -16466,12 +16508,12 @@
       <c r="C26" s="168">
         <v>0.21</v>
       </c>
-      <c r="E26" s="183" t="e" vm="2">
+      <c r="E26" s="183" t="e" vm="5">
         <v>#VALUE!</v>
       </c>
       <c r="F26" s="217" cm="1">
         <f t="array" aca="1" ref="F26" ca="1">_FV(E26,"Price")</f>
-        <v>51.9</v>
+        <v>51.36</v>
       </c>
     </row>
     <row r="27" spans="2:9" x14ac:dyDescent="0.2">
@@ -16486,7 +16528,7 @@
       </c>
       <c r="F27" s="218">
         <f ca="1">F26/1000</f>
-        <v>5.1900000000000002E-2</v>
+        <v>5.1360000000000003E-2</v>
       </c>
     </row>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
@@ -23435,7 +23477,7 @@
       </c>
       <c r="C6" s="135">
         <f ca="1">Overview!C5</f>
-        <v>245.16</v>
+        <v>244.07</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -23444,7 +23486,7 @@
       </c>
       <c r="C7" s="136">
         <f ca="1">C5*C6</f>
-        <v>51483.6</v>
+        <v>51254.7</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -23462,7 +23504,7 @@
       </c>
       <c r="C9" s="137">
         <f ca="1">Overview!F27</f>
-        <v>5.1900000000000002E-2</v>
+        <v>5.1360000000000003E-2</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -23471,7 +23513,7 @@
       </c>
       <c r="C10" s="135">
         <f ca="1">Overview!C13</f>
-        <v>1.3080000000000001</v>
+        <v>1.3027</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -23514,7 +23556,7 @@
       </c>
       <c r="C16" s="46">
         <f ca="1">C8/(C8+C7)</f>
-        <v>6.3280544962300955E-2</v>
+        <v>6.3545193275683462E-2</v>
       </c>
     </row>
     <row r="17" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -23523,7 +23565,7 @@
       </c>
       <c r="C17" s="46">
         <f ca="1">C7/(C8+C7)</f>
-        <v>0.93671945503769904</v>
+        <v>0.93645480672431658</v>
       </c>
     </row>
     <row r="18" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -23541,7 +23583,7 @@
       </c>
       <c r="C19" s="46">
         <f ca="1">C9+C10*C11</f>
-        <v>0.11076</v>
+        <v>0.1099815</v>
       </c>
     </row>
     <row r="20" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -23550,7 +23592,7 @@
       </c>
       <c r="C20" s="46">
         <f ca="1">(C17*C19)+(C16*C18)</f>
-        <v>0.10680053630170883</v>
+        <v>0.10605494718970561</v>
       </c>
     </row>
   </sheetData>
@@ -23801,7 +23843,7 @@
       </c>
       <c r="L8" s="128">
         <f ca="1">L7*(1+C14)/(C15-C14)</f>
-        <v>28926.972304696937</v>
+        <v>29177.598634709731</v>
       </c>
       <c r="N8" s="91"/>
       <c r="O8" s="16"/>
@@ -23855,23 +23897,23 @@
       <c r="G10" s="140"/>
       <c r="H10" s="128">
         <f ca="1">H7/(1+$C$15)^H9</f>
-        <v>1862.0482880717882</v>
+        <v>1863.3034905670513</v>
       </c>
       <c r="I10" s="128">
         <f t="shared" ref="I10:L10" ca="1" si="0">I7/(1+$C$15)^I9</f>
-        <v>1270.4248462482396</v>
+        <v>1272.138204509688</v>
       </c>
       <c r="J10" s="128">
         <f t="shared" ca="1" si="0"/>
-        <v>570.0047484218378</v>
+        <v>571.15824233461035</v>
       </c>
       <c r="K10" s="128">
         <f t="shared" ca="1" si="0"/>
-        <v>1420.4060405726918</v>
+        <v>1424.2398848366518</v>
       </c>
       <c r="L10" s="128">
         <f t="shared" ca="1" si="0"/>
-        <v>1482.1030874782641</v>
+        <v>1487.1052383302315</v>
       </c>
       <c r="N10" s="91"/>
     </row>
@@ -23890,7 +23932,7 @@
       <c r="K11" s="139"/>
       <c r="L11" s="128">
         <f ca="1">L8/(1+C15)^L9</f>
-        <v>17416.31116164046</v>
+        <v>17626.497867147493</v>
       </c>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.2">
@@ -23913,7 +23955,7 @@
       </c>
       <c r="C15" s="137">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.10680053630170883</v>
+        <v>0.10605494718970561</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.2">
@@ -23928,7 +23970,7 @@
       </c>
       <c r="C19" s="64">
         <f ca="1">SUM(H10:L10)</f>
-        <v>6604.9870107928218</v>
+        <v>6617.9450605782322</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.2">
@@ -23937,7 +23979,7 @@
       </c>
       <c r="C20" s="64">
         <f ca="1">L11</f>
-        <v>17416.31116164046</v>
+        <v>17626.497867147493</v>
       </c>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.2">
@@ -23946,7 +23988,7 @@
       </c>
       <c r="C21" s="94">
         <f ca="1">C19+C20</f>
-        <v>24021.298172433282</v>
+        <v>24244.442927725726</v>
       </c>
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.2">
@@ -23973,7 +24015,7 @@
       </c>
       <c r="C24" s="94">
         <f ca="1">C21+C22-C23</f>
-        <v>24900.298172433282</v>
+        <v>25123.442927725726</v>
       </c>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.2">
@@ -23991,7 +24033,7 @@
       </c>
       <c r="C26" s="234">
         <f ca="1">C24/C25</f>
-        <v>118.57284844015848</v>
+        <v>119.63544251297965</v>
       </c>
     </row>
   </sheetData>
@@ -24260,23 +24302,23 @@
       <c r="G9" s="140"/>
       <c r="H9" s="92">
         <f ca="1">DCF!H10</f>
-        <v>1862.0482880717882</v>
+        <v>1863.3034905670513</v>
       </c>
       <c r="I9" s="92">
         <f ca="1">DCF!I10</f>
-        <v>1270.4248462482396</v>
+        <v>1272.138204509688</v>
       </c>
       <c r="J9" s="92">
         <f ca="1">DCF!J10</f>
-        <v>570.0047484218378</v>
+        <v>571.15824233461035</v>
       </c>
       <c r="K9" s="92">
         <f ca="1">DCF!K10</f>
-        <v>1420.4060405726918</v>
+        <v>1424.2398848366518</v>
       </c>
       <c r="L9" s="92">
         <f ca="1">DCF!L10</f>
-        <v>1482.1030874782641</v>
+        <v>1487.1052383302315</v>
       </c>
       <c r="N9" s="91"/>
     </row>
@@ -25062,7 +25104,7 @@
       </c>
       <c r="C41" s="137">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.10680053630170883</v>
+        <v>0.10605494718970561</v>
       </c>
     </row>
     <row r="42" spans="2:14" x14ac:dyDescent="0.2">
@@ -25088,7 +25130,7 @@
       </c>
       <c r="C44" s="24">
         <f ca="1">C43/(1+C41)^5</f>
-        <v>67018.73827070008</v>
+        <v>67244.928905866327</v>
       </c>
     </row>
     <row r="45" spans="2:14" x14ac:dyDescent="0.2">
@@ -25097,7 +25139,7 @@
       </c>
       <c r="C45" s="108">
         <f ca="1">SUM(H9:K9)+C44</f>
-        <v>72141.622194014635</v>
+        <v>72375.76872811433</v>
       </c>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.2">
@@ -25124,7 +25166,7 @@
       </c>
       <c r="C48" s="108">
         <f ca="1">C45+C46-C47</f>
-        <v>73020.622194014635</v>
+        <v>73254.76872811433</v>
       </c>
     </row>
     <row r="49" spans="2:3" x14ac:dyDescent="0.2">
@@ -25142,7 +25184,7 @@
       </c>
       <c r="C50" s="234">
         <f ca="1">C48/C49</f>
-        <v>347.71724854292682</v>
+        <v>348.83223203863969</v>
       </c>
     </row>
     <row r="52" spans="2:3" x14ac:dyDescent="0.2">
@@ -25166,7 +25208,7 @@
       </c>
       <c r="C54" s="137">
         <f ca="1">IF(Overview!C29&gt;0,Overview!C29,WACC!C19)</f>
-        <v>0.11076</v>
+        <v>0.1099815</v>
       </c>
     </row>
     <row r="55" spans="2:3" x14ac:dyDescent="0.2">
@@ -25201,7 +25243,7 @@
       </c>
       <c r="C58" s="234">
         <f ca="1">C57/(1+C54)^5</f>
-        <v>189.15919991140987</v>
+        <v>189.82347741565462</v>
       </c>
     </row>
     <row r="60" spans="2:3" x14ac:dyDescent="0.2">
@@ -25225,7 +25267,7 @@
       </c>
       <c r="C62" s="137">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.10680053630170883</v>
+        <v>0.10605494718970561</v>
       </c>
     </row>
     <row r="63" spans="2:3" x14ac:dyDescent="0.2">
@@ -25251,7 +25293,7 @@
       </c>
       <c r="C65" s="24">
         <f ca="1">C64/(1+C62)^5</f>
-        <v>66694.638936521878</v>
+        <v>66919.735724860409</v>
       </c>
     </row>
     <row r="66" spans="2:3" x14ac:dyDescent="0.2">
@@ -25260,7 +25302,7 @@
       </c>
       <c r="C66" s="108">
         <f ca="1">SUM(H9:K9)+C65</f>
-        <v>71817.522859836434</v>
+        <v>72050.575547108412</v>
       </c>
     </row>
     <row r="67" spans="2:3" x14ac:dyDescent="0.2">
@@ -25287,7 +25329,7 @@
       </c>
       <c r="C69" s="108">
         <f ca="1">C66+C67-C68</f>
-        <v>72696.522859836434</v>
+        <v>72929.575547108412</v>
       </c>
     </row>
     <row r="70" spans="2:3" x14ac:dyDescent="0.2">
@@ -25305,7 +25347,7 @@
       </c>
       <c r="C71" s="234">
         <f ca="1">C69/C70</f>
-        <v>346.17391838017352</v>
+        <v>347.28369308146864</v>
       </c>
     </row>
     <row r="73" spans="2:3" x14ac:dyDescent="0.2">
@@ -25329,7 +25371,7 @@
       </c>
       <c r="C75" s="137">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.10680053630170883</v>
+        <v>0.10605494718970561</v>
       </c>
     </row>
     <row r="76" spans="2:3" x14ac:dyDescent="0.2">
@@ -25355,7 +25397,7 @@
       </c>
       <c r="C78" s="24">
         <f ca="1">C77/(1+C75)^5</f>
-        <v>40295.056680315094</v>
+        <v>40431.053935706055</v>
       </c>
     </row>
     <row r="79" spans="2:3" x14ac:dyDescent="0.2">
@@ -25364,7 +25406,7 @@
       </c>
       <c r="C79" s="108">
         <f ca="1">SUM(H9:K9)+C78</f>
-        <v>45417.94060362965</v>
+        <v>45561.893757954058</v>
       </c>
     </row>
     <row r="80" spans="2:3" x14ac:dyDescent="0.2">
@@ -25391,7 +25433,7 @@
       </c>
       <c r="C82" s="108">
         <f ca="1">C79+C80-C81</f>
-        <v>46296.94060362965</v>
+        <v>46440.893757954058</v>
       </c>
     </row>
     <row r="83" spans="2:3" x14ac:dyDescent="0.2">
@@ -25409,7 +25451,7 @@
       </c>
       <c r="C84" s="234">
         <f ca="1">C82/C83</f>
-        <v>220.46162192204596</v>
+        <v>221.14711313311457</v>
       </c>
     </row>
   </sheetData>
@@ -25474,7 +25516,7 @@
       </c>
       <c r="C5" s="135">
         <f ca="1">DCF!C26</f>
-        <v>118.57284844015848</v>
+        <v>119.63544251297965</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.2">
@@ -25483,7 +25525,7 @@
       </c>
       <c r="C6" s="135">
         <f ca="1">Multiples!C50</f>
-        <v>347.71724854292682</v>
+        <v>348.83223203863969</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.2">
@@ -25492,7 +25534,7 @@
       </c>
       <c r="C7" s="135">
         <f ca="1">Multiples!C58</f>
-        <v>189.15919991140987</v>
+        <v>189.82347741565462</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.2">
@@ -25501,7 +25543,7 @@
       </c>
       <c r="C8" s="135">
         <f ca="1">Multiples!C71</f>
-        <v>346.17391838017352</v>
+        <v>347.28369308146864</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
@@ -25510,7 +25552,7 @@
       </c>
       <c r="C9" s="135">
         <f ca="1">Multiples!C84</f>
-        <v>220.46162192204596</v>
+        <v>221.14711313311457</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
@@ -25519,7 +25561,7 @@
       </c>
       <c r="C10" s="234">
         <f ca="1">AVERAGE(C5:C9)</f>
-        <v>244.4169674393429</v>
+        <v>245.34439163637143</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -25528,7 +25570,7 @@
       </c>
       <c r="C11" s="135">
         <f ca="1">Overview!C5</f>
-        <v>245.16</v>
+        <v>244.07</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.2">
@@ -25537,7 +25579,7 @@
       </c>
       <c r="C12" s="154">
         <f ca="1">(C10-C11)/C11</f>
-        <v>-3.0308066595574274E-3</v>
+        <v>5.221418594548422E-3</v>
       </c>
     </row>
   </sheetData>
@@ -26046,7 +26088,7 @@
       </c>
       <c r="C24" s="137">
         <f ca="1">IF(Overview!C29&gt;0,Overview!C29,WACC!C19)</f>
-        <v>0.11076</v>
+        <v>0.1099815</v>
       </c>
     </row>
     <row r="25" spans="2:14" x14ac:dyDescent="0.2">
@@ -26252,23 +26294,23 @@
       </c>
       <c r="H7" s="128">
         <f>G7*(1+$C$17)</f>
-        <v>1061.3490892077357</v>
+        <v>1093.9502557704304</v>
       </c>
       <c r="I7" s="128">
         <f t="shared" ref="I7:L7" si="0">H7*(1+$C$17)</f>
-        <v>1554.8764156893328</v>
+        <v>1651.86488621335</v>
       </c>
       <c r="J7" s="128">
         <f t="shared" si="0"/>
-        <v>2277.8939489848726</v>
+        <v>2494.3159781821587</v>
       </c>
       <c r="K7" s="128">
         <f t="shared" si="0"/>
-        <v>3337.1146352628384</v>
+        <v>3766.4171270550596</v>
       </c>
       <c r="L7" s="128">
         <f t="shared" si="0"/>
-        <v>4888.8729406600587</v>
+        <v>5687.2898618531399</v>
       </c>
       <c r="N7" s="91"/>
       <c r="O7" s="16"/>
@@ -26300,7 +26342,7 @@
       <c r="K8" s="139"/>
       <c r="L8" s="128">
         <f ca="1">L7*(1+C20)/(C21-C20)</f>
-        <v>57449.534437670161</v>
+        <v>67410.832828727333</v>
       </c>
       <c r="N8" s="91"/>
       <c r="O8" s="16"/>
@@ -26354,23 +26396,23 @@
       <c r="G10" s="140"/>
       <c r="H10" s="128">
         <f ca="1">H7/(1+$C$21)^H9</f>
-        <v>958.93438284205592</v>
+        <v>989.0559764232047</v>
       </c>
       <c r="I10" s="128">
         <f t="shared" ref="I10:L10" ca="1" si="1">I7/(1+$C$21)^I9</f>
-        <v>1269.279174328715</v>
+        <v>1350.2715468103097</v>
       </c>
       <c r="J10" s="128">
         <f t="shared" ca="1" si="1"/>
-        <v>1680.0624226339171</v>
+        <v>1843.4075457680337</v>
       </c>
       <c r="K10" s="128">
         <f t="shared" ca="1" si="1"/>
-        <v>2223.7895342758957</v>
+        <v>2516.6429580937534</v>
       </c>
       <c r="L10" s="128">
         <f t="shared" ca="1" si="1"/>
-        <v>2943.4858051298525</v>
+        <v>3435.7523343456337</v>
       </c>
       <c r="N10" s="91"/>
     </row>
@@ -26389,7 +26431,7 @@
       <c r="K11" s="139"/>
       <c r="L11" s="128">
         <f ca="1">L8/(1+C21)^L9</f>
-        <v>34589.135610828511</v>
+        <v>40723.601553168715</v>
       </c>
     </row>
     <row r="13" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
@@ -26405,7 +26447,7 @@
       </c>
       <c r="C15" s="156">
         <f ca="1">Overview!C5</f>
-        <v>245.16</v>
+        <v>244.07</v>
       </c>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.2">
@@ -26414,7 +26456,7 @@
       </c>
       <c r="C16" s="156">
         <f ca="1">C36</f>
-        <v>213.12768866047347</v>
+        <v>247.54895652923278</v>
       </c>
     </row>
     <row r="17" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -26422,7 +26464,7 @@
         <v>323</v>
       </c>
       <c r="C17" s="158">
-        <v>0.46500000000000002</v>
+        <v>0.51</v>
       </c>
       <c r="E17" s="254" t="s">
         <v>224</v>
@@ -26453,7 +26495,7 @@
       </c>
       <c r="C21" s="220">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.10680053630170883</v>
+        <v>0.10605494718970561</v>
       </c>
     </row>
     <row r="22" spans="2:9" x14ac:dyDescent="0.2">
@@ -26471,7 +26513,7 @@
       </c>
       <c r="C23" s="161">
         <f ca="1">C15*C22</f>
-        <v>51238.44</v>
+        <v>51010.63</v>
       </c>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.2">
@@ -26498,7 +26540,7 @@
       </c>
       <c r="C26" s="162">
         <f ca="1">C23+C25-C24</f>
-        <v>50359.44</v>
+        <v>50131.63</v>
       </c>
     </row>
     <row r="27" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
@@ -26514,7 +26556,7 @@
       </c>
       <c r="C29" s="161">
         <f ca="1">SUM(H10:L10)</f>
-        <v>9075.5513192104372</v>
+        <v>10135.130361440935</v>
       </c>
     </row>
     <row r="30" spans="2:9" x14ac:dyDescent="0.2">
@@ -26523,7 +26565,7 @@
       </c>
       <c r="C30" s="161">
         <f ca="1">L11</f>
-        <v>34589.135610828511</v>
+        <v>40723.601553168715</v>
       </c>
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.2">
@@ -26532,7 +26574,7 @@
       </c>
       <c r="C31" s="164">
         <f ca="1">C29+C30</f>
-        <v>43664.686930038952</v>
+        <v>50858.731914609649</v>
       </c>
     </row>
     <row r="32" spans="2:9" x14ac:dyDescent="0.2">
@@ -26559,7 +26601,7 @@
       </c>
       <c r="C34" s="164">
         <f ca="1">C31+C32-C33</f>
-        <v>44543.686930038952</v>
+        <v>51737.731914609649</v>
       </c>
     </row>
     <row r="35" spans="2:3" x14ac:dyDescent="0.2">
@@ -26577,7 +26619,7 @@
       </c>
       <c r="C36" s="167">
         <f ca="1">C34/C35</f>
-        <v>213.12768866047347</v>
+        <v>247.54895652923278</v>
       </c>
     </row>
   </sheetData>
@@ -33247,7 +33289,7 @@
       </c>
       <c r="AC117" s="63">
         <f ca="1">Overview!C5</f>
-        <v>245.16</v>
+        <v>244.07</v>
       </c>
     </row>
     <row r="118" spans="1:31" x14ac:dyDescent="0.2">
@@ -33318,7 +33360,7 @@
       </c>
       <c r="AC118" s="65">
         <f ca="1">AC117/AC86</f>
-        <v>245.16</v>
+        <v>244.07</v>
       </c>
     </row>
     <row r="120" spans="1:31" x14ac:dyDescent="0.2">
@@ -34624,7 +34666,7 @@
       <c r="AA151" s="49"/>
       <c r="AC151" s="72">
         <f ca="1">AC118/Statement!AC27</f>
-        <v>31.715394566623541</v>
+        <v>31.574385510996116</v>
       </c>
     </row>
     <row r="152" spans="2:29" x14ac:dyDescent="0.2">
@@ -34661,7 +34703,7 @@
       <c r="AA152" s="49"/>
       <c r="AC152" s="72">
         <f ca="1">AC118/(Statement!AC5/Statement!AC23)</f>
-        <v>6.7033478818998722</v>
+        <v>6.6735442875481388</v>
       </c>
     </row>
     <row r="153" spans="2:29" x14ac:dyDescent="0.2">
@@ -34722,7 +34764,7 @@
       </c>
       <c r="AC153" s="72">
         <f ca="1">AC118/(Statement!AC50/Statement!AC76)</f>
-        <v>15.145858705291159</v>
+        <v>15.078519065917822</v>
       </c>
     </row>
     <row r="154" spans="2:29" x14ac:dyDescent="0.2">
@@ -34783,7 +34825,7 @@
       </c>
       <c r="AC154" s="143">
         <f ca="1">Statement!AC118*Statement!AC79</f>
-        <v>51483.6</v>
+        <v>51254.7</v>
       </c>
     </row>
     <row r="155" spans="2:29" x14ac:dyDescent="0.2">
@@ -34844,7 +34886,7 @@
       </c>
       <c r="AC155" s="143">
         <f ca="1">AC154+AC109-AC108+AC49+AC46</f>
-        <v>50604.6</v>
+        <v>50375.7</v>
       </c>
     </row>
     <row r="156" spans="2:29" x14ac:dyDescent="0.2">
@@ -34881,7 +34923,7 @@
       <c r="AA156" s="49"/>
       <c r="AC156" s="181">
         <f ca="1">AC155/AC5</f>
-        <v>6.4960975609756098</v>
+        <v>6.4667137355584074</v>
       </c>
     </row>
     <row r="157" spans="2:29" x14ac:dyDescent="0.2">
@@ -34918,7 +34960,7 @@
       <c r="AA157" s="49"/>
       <c r="AC157" s="181">
         <f ca="1">AC155/AC13</f>
-        <v>24.794022537971582</v>
+        <v>24.681871631553157</v>
       </c>
     </row>
     <row r="158" spans="2:29" x14ac:dyDescent="0.2">
@@ -35053,7 +35095,7 @@
       <c r="AA160" s="49"/>
       <c r="AC160" s="72">
         <f t="shared" ref="AC160:AC161" ca="1" si="155">AC154/AC158</f>
-        <v>24.539370829361296</v>
+        <v>24.430266920877024</v>
       </c>
     </row>
     <row r="161" spans="2:29" x14ac:dyDescent="0.2">
@@ -35090,7 +35132,7 @@
       <c r="AA161" s="49"/>
       <c r="AC161" s="72">
         <f t="shared" ca="1" si="155"/>
-        <v>41.612991348684794</v>
+        <v>41.424763129911916</v>
       </c>
     </row>
     <row r="162" spans="2:29" x14ac:dyDescent="0.2">
@@ -35127,7 +35169,7 @@
       <c r="AA162" s="49"/>
       <c r="AC162" s="74">
         <f t="shared" ref="AC162" ca="1" si="158">AC158/AC154</f>
-        <v>4.0750841044526802E-2</v>
+        <v>4.0932831525694234E-2</v>
       </c>
     </row>
     <row r="163" spans="2:29" x14ac:dyDescent="0.2">
@@ -35164,7 +35206,7 @@
       <c r="AA163" s="49"/>
       <c r="AC163" s="74">
         <f ca="1">AC27/AC118</f>
-        <v>3.1530429107521622E-2</v>
+        <v>3.1671241856844348E-2</v>
       </c>
     </row>
     <row r="164" spans="2:29" x14ac:dyDescent="0.2">
@@ -35238,7 +35280,7 @@
       <c r="AA165" s="49"/>
       <c r="AC165" s="154">
         <f ca="1">-AC64/AC154</f>
-        <v>3.0903044853118275E-2</v>
+        <v>3.104105574708271E-2</v>
       </c>
     </row>
     <row r="166" spans="2:29" x14ac:dyDescent="0.2">
@@ -35275,7 +35317,7 @@
       <c r="AA166" s="49"/>
       <c r="AC166" s="154">
         <f ca="1">-(AC64+AC65)/AC154</f>
-        <v>3.0903044853118275E-2</v>
+        <v>3.104105574708271E-2</v>
       </c>
     </row>
     <row r="167" spans="2:29" x14ac:dyDescent="0.2">
@@ -35778,7 +35820,7 @@
       <c r="AA177" s="49"/>
       <c r="AC177" s="154">
         <f ca="1">(AC108-AC109)/AC154</f>
-        <v>1.7073398130666852E-2</v>
+        <v>1.7149646764101634E-2</v>
       </c>
     </row>
     <row r="178" spans="1:31" x14ac:dyDescent="0.2">
@@ -37628,7 +37670,7 @@
       </c>
       <c r="C5" s="170">
         <f ca="1">Overview!C5</f>
-        <v>245.16</v>
+        <v>244.07</v>
       </c>
       <c r="E5" s="12"/>
       <c r="F5" s="134" t="s">
@@ -37644,7 +37686,7 @@
       </c>
       <c r="C6" s="171">
         <f ca="1">Statement!AC154</f>
-        <v>51483.6</v>
+        <v>51254.7</v>
       </c>
       <c r="E6" s="20" t="s">
         <v>19</v>
@@ -37664,7 +37706,7 @@
       </c>
       <c r="C7" s="171">
         <f ca="1">Statement!AC155</f>
-        <v>50604.6</v>
+        <v>50375.7</v>
       </c>
       <c r="E7" s="20" t="s">
         <v>31</v>
@@ -37684,7 +37726,7 @@
       </c>
       <c r="C8" s="172">
         <f ca="1">Statement!AC151</f>
-        <v>31.715394566623541</v>
+        <v>31.574385510996116</v>
       </c>
       <c r="E8" s="20" t="s">
         <v>242</v>
@@ -37704,7 +37746,7 @@
       </c>
       <c r="C9" s="172">
         <f ca="1">Statement!AC152</f>
-        <v>6.7033478818998722</v>
+        <v>6.6735442875481388</v>
       </c>
       <c r="E9" s="20" t="s">
         <v>243</v>
@@ -37724,7 +37766,7 @@
       </c>
       <c r="C10" s="172">
         <f ca="1">Statement!AC153</f>
-        <v>15.145858705291159</v>
+        <v>15.078519065917822</v>
       </c>
       <c r="E10" s="20" t="s">
         <v>1</v>
@@ -37744,7 +37786,7 @@
       </c>
       <c r="C11" s="172">
         <f ca="1">Statement!AC156</f>
-        <v>6.4960975609756098</v>
+        <v>6.4667137355584074</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
@@ -37753,7 +37795,7 @@
       </c>
       <c r="C12" s="172">
         <f ca="1">Statement!AC157</f>
-        <v>24.794022537971582</v>
+        <v>24.681871631553157</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.2">
@@ -37989,7 +38031,7 @@
       </c>
       <c r="C38" s="173">
         <f ca="1">Statement!AC163</f>
-        <v>3.1530429107521622E-2</v>
+        <v>3.1671241856844348E-2</v>
       </c>
       <c r="E38" s="20" t="s">
         <v>269</v>
@@ -38005,7 +38047,7 @@
       </c>
       <c r="C39" s="213">
         <f ca="1">Statement!AC162</f>
-        <v>4.0750841044526802E-2</v>
+        <v>4.0932831525694234E-2</v>
       </c>
       <c r="E39" s="20" t="s">
         <v>271</v>
@@ -38037,7 +38079,7 @@
       </c>
       <c r="C41" s="173">
         <f ca="1">Statement!AC165</f>
-        <v>3.0903044853118275E-2</v>
+        <v>3.104105574708271E-2</v>
       </c>
     </row>
     <row r="42" spans="2:6" x14ac:dyDescent="0.2">
@@ -38046,7 +38088,7 @@
       </c>
       <c r="C42" s="173">
         <f ca="1">Statement!AC166</f>
-        <v>3.0903044853118275E-2</v>
+        <v>3.104105574708271E-2</v>
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.2">
@@ -38090,7 +38132,7 @@
       </c>
       <c r="F48" s="173">
         <f ca="1">Statement!AC177</f>
-        <v>1.7073398130666852E-2</v>
+        <v>1.7149646764101634E-2</v>
       </c>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.2">
@@ -38269,7 +38311,7 @@
       </c>
       <c r="I6" s="170">
         <f ca="1">Statement!AC117</f>
-        <v>245.16</v>
+        <v>244.07</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -38298,7 +38340,7 @@
       </c>
       <c r="I7" s="171">
         <f ca="1">Statement!AC154</f>
-        <v>51483.6</v>
+        <v>51254.7</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
@@ -38327,7 +38369,7 @@
       </c>
       <c r="I8" s="171">
         <f ca="1">Statement!AC155</f>
-        <v>50604.6</v>
+        <v>50375.7</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -38356,7 +38398,7 @@
       </c>
       <c r="I9" s="172">
         <f ca="1">Statement!AC151</f>
-        <v>31.715394566623541</v>
+        <v>31.574385510996116</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -38385,7 +38427,7 @@
       </c>
       <c r="I10" s="172">
         <f ca="1">Statement!AC152</f>
-        <v>6.7033478818998722</v>
+        <v>6.6735442875481388</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -38414,7 +38456,7 @@
       </c>
       <c r="I11" s="172">
         <f ca="1">Statement!AC153</f>
-        <v>15.145858705291159</v>
+        <v>15.078519065917822</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
@@ -38443,7 +38485,7 @@
       </c>
       <c r="I12" s="172">
         <f ca="1">Statement!AC156</f>
-        <v>6.4960975609756098</v>
+        <v>6.4667137355584074</v>
       </c>
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.2">
@@ -38472,7 +38514,7 @@
       </c>
       <c r="I13" s="172">
         <f ca="1">Statement!AC157</f>
-        <v>24.794022537971582</v>
+        <v>24.681871631553157</v>
       </c>
     </row>
     <row r="15" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -39245,7 +39287,7 @@
       </c>
       <c r="I51" s="173">
         <f ca="1">Statement!AC163</f>
-        <v>3.1530429107521622E-2</v>
+        <v>3.1671241856844348E-2</v>
       </c>
     </row>
     <row r="52" spans="2:9" x14ac:dyDescent="0.2">
@@ -39274,7 +39316,7 @@
       </c>
       <c r="I52" s="173">
         <f ca="1">Statement!AC162</f>
-        <v>4.0750841044526802E-2</v>
+        <v>4.0932831525694234E-2</v>
       </c>
     </row>
     <row r="53" spans="2:9" x14ac:dyDescent="0.2">
@@ -39332,7 +39374,7 @@
       </c>
       <c r="I54" s="173">
         <f ca="1">Statement!AC165</f>
-        <v>3.0903044853118275E-2</v>
+        <v>3.104105574708271E-2</v>
       </c>
     </row>
     <row r="55" spans="2:9" x14ac:dyDescent="0.2">
@@ -39361,7 +39403,7 @@
       </c>
       <c r="I55" s="173">
         <f ca="1">Statement!AC166</f>
-        <v>3.0903044853118275E-2</v>
+        <v>3.104105574708271E-2</v>
       </c>
     </row>
     <row r="57" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -39597,7 +39639,7 @@
       </c>
       <c r="I68" s="194">
         <f ca="1">Statement!AC177</f>
-        <v>1.7073398130666852E-2</v>
+        <v>1.7149646764101634E-2</v>
       </c>
     </row>
     <row r="70" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">

--- a/ADSK.xlsx
+++ b/ADSK.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11011"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11020"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8A264DC-642A-5C45-9FCB-9D6AF5A87731}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7EED8353-4B1C-CE46-A69F-1FA38B10EE76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
@@ -118,7 +118,7 @@
       </extLst>
     </bk>
   </futureMetadata>
-  <futureMetadata name="XLRICHVALUE" count="5">
+  <futureMetadata name="XLRICHVALUE" count="2">
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
@@ -129,28 +129,7 @@
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="3"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="4"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
           <xlrd:rvb i="5"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="8"/>
         </ext>
       </extLst>
     </bk>
@@ -160,21 +139,12 @@
       <rc t="1" v="0"/>
     </bk>
   </cellMetadata>
-  <valueMetadata count="5">
+  <valueMetadata count="2">
     <bk>
       <rc t="2" v="0"/>
     </bk>
     <bk>
       <rc t="2" v="1"/>
-    </bk>
-    <bk>
-      <rc t="2" v="2"/>
-    </bk>
-    <bk>
-      <rc t="2" v="3"/>
-    </bk>
-    <bk>
-      <rc t="2" v="4"/>
     </bk>
   </valueMetadata>
 </metadata>
@@ -2445,6 +2415,9 @@
     <xf numFmtId="0" fontId="25" fillId="8" borderId="26" xfId="2" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="168" fontId="0" fillId="17" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="27" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2499,9 +2472,6 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="168" fontId="0" fillId="17" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="17" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="27" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
@@ -15203,7 +15173,7 @@
 </file>
 
 <file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
-<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="9">
+<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="6">
   <rv s="0">
     <v>https://www.bing.com/financeapi/forcetrigger?t=a1mwoc&amp;q=XNAS%3aADSK&amp;form=skydnc</v>
     <v>Learn more on Bing</v>
@@ -15222,9 +15192,11 @@
     <v>Powered by Refinitiv</v>
     <v>320</v>
     <v>185.5</v>
-    <v>1.3027</v>
-    <v>3.37</v>
-    <v>1.4001E-2</v>
+    <v>1.2928999999999999</v>
+    <v>-2.75</v>
+    <v>-1.0786E-2</v>
+    <v>0</v>
+    <v>0</v>
     <v>USD</v>
     <v>Autodesk, Inc. is engaged in three-dimensional (3D) design, engineering and entertainment technology solutions, spanning architecture, engineering, construction, product design, manufacturing, media and entertainment. Its architecture, engineering, construction and operations products improve the way building, infrastructure, and industrial projects are designed, built, and operated. Its product development and manufacturing software provides manufacturers in the automotive, transportation, industrial machinery, consumer products, and building product industries with comprehensive digital design, engineering, manufacturing, and production solutions. Its product offerings include AutoCAD Civil 3D, Autodesk Build, BIM Collaborate Pro, Building Connected, Revit, Tandem, AutoCAD, AutoCAD LT, Inventor, Vault, Maya, 3ds Max, Flow Production Tracking, among others. AutoCAD Civil 3D solution offers surveying, design, analysis, and documentation solution.</v>
     <v>14300</v>
@@ -15232,49 +15204,35 @@
     <v>XNAS</v>
     <v>XNAS</v>
     <v>One Market, Ste. 400., SAN FRANCISCO, CA, 94105 US</v>
-    <v>247.68</v>
+    <v>255.02</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46315.717840462501</v>
+    <v>46318.932775253903</v>
     <v>0</v>
-    <v>241.1</v>
-    <v>51010630000</v>
+    <v>248.92500000000001</v>
+    <v>52709800000</v>
     <v>AUTODESK, INC.</v>
     <v>AUTODESK, INC.</v>
-    <v>241.1</v>
-    <v>31.644400000000001</v>
-    <v>240.7</v>
-    <v>244.07</v>
+    <v>254.06</v>
+    <v>32.698500000000003</v>
+    <v>254.95</v>
+    <v>252.2</v>
+    <v>252.2</v>
     <v>209000000</v>
     <v>ADSK</v>
     <v>AUTODESK, INC. (XNAS:ADSK)</v>
-    <v>684901</v>
-    <v>2072616</v>
+    <v>1320307</v>
+    <v>1977465</v>
     <v>1994</v>
   </rv>
   <rv s="2">
     <v>1</v>
   </rv>
-  <rv s="3">
-    <v>12</v>
-    <v>Price (Extended hours)</v>
-    <v>0</v>
-  </rv>
-  <rv s="3">
-    <v>12</v>
-    <v>Change (extended hours)</v>
-    <v>0</v>
-  </rv>
-  <rv s="3">
-    <v>12</v>
-    <v>Change % (extended hours)</v>
-    <v>0</v>
-  </rv>
   <rv s="0">
     <v>https://www.bing.com/financeapi/forcetrigger?t=a33knm&amp;q=10+Y+TSY+YLD+NDX&amp;form=skydnc</v>
     <v>Learn more on Bing</v>
   </rv>
-  <rv s="4">
+  <rv s="3">
     <v>5</v>
     <v>10 Y TSY YLD NDX</v>
     <v>6</v>
@@ -15288,28 +15246,28 @@
     <v>Powered by Refinitiv</v>
     <v>53.64</v>
     <v>39.47</v>
-    <v>0.38</v>
-    <v>7.4539999999999997E-3</v>
+    <v>-1.93</v>
+    <v>-3.7505000000000004E-2</v>
     <v>US</v>
-    <v>51.5</v>
+    <v>50.54</v>
     <v>Index</v>
-    <v>6</v>
-    <v>50.9</v>
+    <v>3</v>
+    <v>49.39</v>
     <v>10 Y TSY YLD NDX</v>
-    <v>50.9</v>
-    <v>50.98</v>
-    <v>51.36</v>
+    <v>50.4</v>
+    <v>51.46</v>
+    <v>49.53</v>
     <v>TNX</v>
     <v>10 Y TSY YLD NDX</v>
   </rv>
   <rv s="2">
-    <v>7</v>
+    <v>4</v>
   </rv>
 </rvData>
 </file>
 
 <file path=xl/richData/rdrichvaluestructure.xml><?xml version="1.0" encoding="utf-8"?>
-<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="5">
+<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="4">
   <s t="_hyperlink">
     <k n="Address" t="s"/>
     <k n="Text" t="s"/>
@@ -15331,6 +15289,8 @@
     <k n="Beta"/>
     <k n="Change"/>
     <k n="Change (%)"/>
+    <k n="Change (Extended hours)"/>
+    <k n="Change % (Extended hours)"/>
     <k n="Currency" t="s"/>
     <k n="Description" t="s"/>
     <k n="Employees"/>
@@ -15351,6 +15311,7 @@
     <k n="P/E"/>
     <k n="Previous close"/>
     <k n="Price"/>
+    <k n="Price (Extended hours)"/>
     <k n="Shares outstanding"/>
     <k n="Ticker symbol" t="s"/>
     <k n="UniqueName" t="s"/>
@@ -15360,11 +15321,6 @@
   </s>
   <s t="_linkedentity">
     <k n="%cvi" t="r"/>
-  </s>
-  <s t="_error">
-    <k n="errorType" t="i"/>
-    <k n="field" t="s"/>
-    <k n="subType" t="i"/>
   </s>
   <s t="_linkedentitycore">
     <k n="_Display" t="spb"/>
@@ -15400,7 +15356,7 @@
 <file path=xl/richData/rdsupportingpropertybag.xml><?xml version="1.0" encoding="utf-8"?>
 <supportingPropertyBags xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2">
   <spbArrays count="2">
-    <a count="42">
+    <a count="45">
       <v t="s">%EntityServiceId</v>
       <v t="s">_Format</v>
       <v t="s">%IsRefreshable</v>
@@ -15411,13 +15367,16 @@
       <v t="s">Name</v>
       <v t="s">_SubLabel</v>
       <v t="s">Price</v>
+      <v t="s">Price (Extended hours)</v>
       <v t="s">Exchange</v>
       <v t="s">Official name</v>
       <v t="s">Last trade time</v>
       <v t="s">Ticker symbol</v>
       <v t="s">Exchange abbreviation</v>
       <v t="s">Change</v>
+      <v t="s">Change (Extended hours)</v>
       <v t="s">Change (%)</v>
+      <v t="s">Change % (Extended hours)</v>
       <v t="s">Currency</v>
       <v t="s">Previous close</v>
       <v t="s">Open</v>
@@ -15511,13 +15470,19 @@
       <v>8</v>
       <v>9</v>
       <v>4</v>
+      <v>1</v>
+      <v>1</v>
+      <v>5</v>
     </spb>
     <spb s="4">
-      <v>Real-Time Nasdaq Last Sale</v>
+      <v>at close</v>
       <v>from previous close</v>
       <v>from previous close</v>
-      <v>Source: Nasdaq Last Sale</v>
+      <v>Source: Nasdaq</v>
       <v>GMT</v>
+      <v>Delayed 15 minutes</v>
+      <v>from close</v>
+      <v>from close</v>
     </spb>
     <spb s="0">
       <v>1</v>
@@ -15589,6 +15554,9 @@
     <k n="Year incorporated" t="i"/>
     <k n="`%EntityServiceId" t="i"/>
     <k n="Shares outstanding" t="i"/>
+    <k n="Price (Extended hours)" t="i"/>
+    <k n="Change (Extended hours)" t="i"/>
+    <k n="Change % (Extended hours)" t="i"/>
   </s>
   <s>
     <k n="Price" t="s"/>
@@ -15596,6 +15564,9 @@
     <k n="Change (%)" t="s"/>
     <k n="ExchangeID" t="s"/>
     <k n="Last trade time" t="s"/>
+    <k n="Price (Extended hours)" t="s"/>
+    <k n="Change (Extended hours)" t="s"/>
+    <k n="Change % (Extended hours)" t="s"/>
   </s>
   <s>
     <k n="UniqueName" t="spb"/>
@@ -16082,18 +16053,18 @@
   <sheetData>
     <row r="1" spans="2:11" ht="11" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="2" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B2" s="239" t="s">
+      <c r="B2" s="242" t="s">
         <v>17</v>
       </c>
-      <c r="C2" s="240"/>
-      <c r="E2" s="239" t="s">
+      <c r="C2" s="243"/>
+      <c r="E2" s="242" t="s">
         <v>286</v>
       </c>
-      <c r="F2" s="240"/>
-      <c r="H2" s="239" t="s">
+      <c r="F2" s="243"/>
+      <c r="H2" s="242" t="s">
         <v>324</v>
       </c>
-      <c r="I2" s="240"/>
+      <c r="I2" s="243"/>
       <c r="K2" s="134" t="s">
         <v>435</v>
       </c>
@@ -16111,7 +16082,7 @@
       </c>
       <c r="F3" s="185">
         <f ca="1">Statement!AC154</f>
-        <v>51254.7</v>
+        <v>52962</v>
       </c>
       <c r="H3" s="183" t="str">
         <f>'AVG target price'!B5</f>
@@ -16119,7 +16090,7 @@
       </c>
       <c r="I3" s="209">
         <f ca="1">'AVG target price'!C5</f>
-        <v>119.63544251297965</v>
+        <v>122.59878263521894</v>
       </c>
       <c r="K3" s="237" t="s">
         <v>436</v>
@@ -16138,7 +16109,7 @@
       </c>
       <c r="F4" s="186">
         <f ca="1">Statement!AC155</f>
-        <v>50375.7</v>
+        <v>52083</v>
       </c>
       <c r="H4" s="183" t="str">
         <f>'AVG target price'!B6</f>
@@ -16146,7 +16117,7 @@
       </c>
       <c r="I4" s="209">
         <f ca="1">'AVG target price'!C6</f>
-        <v>348.83223203863969</v>
+        <v>351.86382334060107</v>
       </c>
       <c r="K4" s="237" t="s">
         <v>437</v>
@@ -16158,7 +16129,7 @@
       </c>
       <c r="C5" s="206" cm="1">
         <f t="array" aca="1" ref="C5" ca="1">_FV(C3,"Price",TRUE)</f>
-        <v>244.07</v>
+        <v>252.2</v>
       </c>
       <c r="E5" s="183" t="s">
         <v>242</v>
@@ -16173,7 +16144,7 @@
       </c>
       <c r="I5" s="209">
         <f ca="1">'AVG target price'!C7</f>
-        <v>189.82347741565462</v>
+        <v>191.77732889949982</v>
       </c>
       <c r="K5" s="237" t="s">
         <v>438</v>
@@ -16183,16 +16154,16 @@
       <c r="B6" s="183" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="206" t="e" cm="1" vm="2">
-        <f t="array" ref="C6">_FV(C3,"Price (Extended hours)",TRUE)</f>
-        <v>#VALUE!</v>
+      <c r="C6" s="206" cm="1">
+        <f t="array" aca="1" ref="C6" ca="1">_FV(C3,"Price (Extended hours)",TRUE)</f>
+        <v>252.2</v>
       </c>
       <c r="E6" s="183" t="s">
         <v>236</v>
       </c>
       <c r="F6" s="188">
         <f ca="1">Statement!AC151</f>
-        <v>31.574385510996116</v>
+        <v>32.626131953428199</v>
       </c>
       <c r="H6" s="183" t="str">
         <f>'AVG target price'!B8</f>
@@ -16200,7 +16171,7 @@
       </c>
       <c r="I6" s="209">
         <f ca="1">'AVG target price'!C8</f>
-        <v>347.28369308146864</v>
+        <v>350.30112067060702</v>
       </c>
       <c r="K6" s="238" t="s">
         <v>439</v>
@@ -16212,14 +16183,14 @@
       </c>
       <c r="C7" s="6" cm="1">
         <f t="array" aca="1" ref="C7" ca="1">_FV(C3,"Change")</f>
-        <v>3.37</v>
+        <v>-2.75</v>
       </c>
       <c r="E7" s="184" t="s">
         <v>200</v>
       </c>
       <c r="F7" s="189">
         <f ca="1">Statement!AC152</f>
-        <v>6.6735442875481388</v>
+        <v>6.8958408215661109</v>
       </c>
       <c r="H7" s="183" t="str">
         <f>'AVG target price'!B9</f>
@@ -16227,23 +16198,23 @@
       </c>
       <c r="I7" s="209">
         <f ca="1">'AVG target price'!C9</f>
-        <v>221.14711313311457</v>
+        <v>223.01083239183876</v>
       </c>
     </row>
     <row r="8" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B8" s="183" t="s">
         <v>4</v>
       </c>
-      <c r="C8" s="6" t="e" cm="1" vm="3">
-        <f t="array" ref="C8">_FV(C3,"Change (extended hours)",TRUE)</f>
-        <v>#VALUE!</v>
+      <c r="C8" s="6" cm="1">
+        <f t="array" aca="1" ref="C8" ca="1">_FV(C3,"Change (extended hours)",TRUE)</f>
+        <v>0</v>
       </c>
       <c r="E8" s="183" t="s">
         <v>264</v>
       </c>
       <c r="F8" s="190">
         <f ca="1">Statement!AC162</f>
-        <v>4.0932831525694234E-2</v>
+        <v>3.9613307654544766E-2</v>
       </c>
       <c r="H8" s="182" t="str">
         <f>'AVG target price'!B10</f>
@@ -16251,7 +16222,7 @@
       </c>
       <c r="I8" s="210">
         <f ca="1">'AVG target price'!C10</f>
-        <v>245.34439163637143</v>
+        <v>247.91037758755311</v>
       </c>
     </row>
     <row r="9" spans="2:11" x14ac:dyDescent="0.2">
@@ -16260,14 +16231,14 @@
       </c>
       <c r="C9" s="73" cm="1">
         <f t="array" aca="1" ref="C9" ca="1">_FV(C3,"Change (%)",TRUE)</f>
-        <v>1.4001E-2</v>
+        <v>-1.0786E-2</v>
       </c>
       <c r="E9" s="183" t="s">
         <v>287</v>
       </c>
       <c r="F9" s="190">
         <f ca="1">Statement!AC163</f>
-        <v>3.1671241856844348E-2</v>
+        <v>3.0650277557494054E-2</v>
       </c>
       <c r="H9" s="182" t="str">
         <f>'AVG target price'!B12</f>
@@ -16275,23 +16246,23 @@
       </c>
       <c r="I9" s="211">
         <f ca="1">'AVG target price'!C12</f>
-        <v>5.221418594548422E-3</v>
+        <v>-1.7008812103278648E-2</v>
       </c>
     </row>
     <row r="10" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B10" s="183" t="s">
         <v>6</v>
       </c>
-      <c r="C10" s="73" t="e" cm="1" vm="4">
-        <f t="array" ref="C10">_FV(C3,"Change % (extended hours)",TRUE)</f>
-        <v>#VALUE!</v>
+      <c r="C10" s="73" cm="1">
+        <f t="array" aca="1" ref="C10" ca="1">_FV(C3,"Change % (extended hours)",TRUE)</f>
+        <v>0</v>
       </c>
       <c r="E10" s="183" t="s">
         <v>292</v>
       </c>
       <c r="F10" s="190">
         <f ca="1">Statement!AC165</f>
-        <v>3.104105574708271E-2</v>
+        <v>3.0040406329066124E-2</v>
       </c>
     </row>
     <row r="11" spans="2:11" x14ac:dyDescent="0.2">
@@ -16339,7 +16310,7 @@
       </c>
       <c r="C13" s="207" cm="1">
         <f t="array" aca="1" ref="C13" ca="1">_FV(C3,"Beta")</f>
-        <v>1.3027</v>
+        <v>1.2928999999999999</v>
       </c>
       <c r="E13" s="183" t="s">
         <v>103</v>
@@ -16348,10 +16319,10 @@
         <f>Statement!AC126</f>
         <v>0.48536801655335504</v>
       </c>
-      <c r="H13" s="259" t="s">
+      <c r="H13" s="241" t="s">
         <v>383</v>
       </c>
-      <c r="I13" s="257">
+      <c r="I13" s="239">
         <f>'Reverse DCF'!C17</f>
         <v>0.51</v>
       </c>
@@ -16362,7 +16333,7 @@
       </c>
       <c r="C14" s="208" cm="1">
         <f t="array" aca="1" ref="C14" ca="1">_FV(C3,"Volume average",TRUE)</f>
-        <v>2072616</v>
+        <v>1977465</v>
       </c>
       <c r="E14" s="184" t="s">
         <v>104</v>
@@ -16374,9 +16345,9 @@
       <c r="H14" s="184" t="s">
         <v>441</v>
       </c>
-      <c r="I14" s="258">
+      <c r="I14" s="240">
         <f ca="1">'Reverse DCF'!C16</f>
-        <v>247.54895652923278</v>
+        <v>254.35811150241574</v>
       </c>
     </row>
     <row r="15" spans="2:11" x14ac:dyDescent="0.2">
@@ -16385,7 +16356,7 @@
       </c>
       <c r="F15" s="190">
         <f ca="1">Statement!AC177</f>
-        <v>1.7149646764101634E-2</v>
+        <v>1.6596805256599071E-2</v>
       </c>
     </row>
     <row r="16" spans="2:11" x14ac:dyDescent="0.2">
@@ -16396,16 +16367,16 @@
         <f>Statement!AC176</f>
         <v>4.205741626794258</v>
       </c>
-      <c r="H16" s="239" t="s">
+      <c r="H16" s="242" t="s">
         <v>433</v>
       </c>
-      <c r="I16" s="240"/>
+      <c r="I16" s="243"/>
     </row>
     <row r="17" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B17" s="241" t="s">
+      <c r="B17" s="244" t="s">
         <v>89</v>
       </c>
-      <c r="C17" s="241"/>
+      <c r="C17" s="244"/>
       <c r="E17" s="182" t="s">
         <v>295</v>
       </c>
@@ -16418,7 +16389,7 @@
       </c>
       <c r="I17" s="235">
         <f ca="1">DCF!C15</f>
-        <v>0.10605494718970561</v>
+        <v>0.10404267046420979</v>
       </c>
     </row>
     <row r="18" spans="2:9" x14ac:dyDescent="0.2">
@@ -16440,7 +16411,7 @@
       </c>
       <c r="I18" s="236">
         <f ca="1">Multiples!C54</f>
-        <v>0.1099815</v>
+        <v>0.1077105</v>
       </c>
     </row>
     <row r="19" spans="2:9" x14ac:dyDescent="0.2">
@@ -16492,14 +16463,14 @@
       <c r="I22" s="50"/>
     </row>
     <row r="25" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B25" s="241" t="s">
+      <c r="B25" s="244" t="s">
         <v>106</v>
       </c>
-      <c r="C25" s="241"/>
-      <c r="E25" s="239" t="s">
+      <c r="C25" s="244"/>
+      <c r="E25" s="242" t="s">
         <v>337</v>
       </c>
-      <c r="F25" s="240"/>
+      <c r="F25" s="243"/>
     </row>
     <row r="26" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B26" s="182" t="s">
@@ -16508,12 +16479,12 @@
       <c r="C26" s="168">
         <v>0.21</v>
       </c>
-      <c r="E26" s="183" t="e" vm="5">
+      <c r="E26" s="183" t="e" vm="2">
         <v>#VALUE!</v>
       </c>
       <c r="F26" s="217" cm="1">
         <f t="array" aca="1" ref="F26" ca="1">_FV(E26,"Price")</f>
-        <v>51.36</v>
+        <v>49.53</v>
       </c>
     </row>
     <row r="27" spans="2:9" x14ac:dyDescent="0.2">
@@ -16528,7 +16499,7 @@
       </c>
       <c r="F27" s="218">
         <f ca="1">F26/1000</f>
-        <v>5.1360000000000003E-2</v>
+        <v>4.9530000000000005E-2</v>
       </c>
     </row>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
@@ -16863,36 +16834,36 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="242" t="s">
+      <c r="C2" s="245" t="s">
         <v>112</v>
       </c>
-      <c r="D2" s="242"/>
-      <c r="E2" s="242"/>
-      <c r="F2" s="242"/>
-      <c r="G2" s="251"/>
-      <c r="H2" s="252" t="s">
+      <c r="D2" s="245"/>
+      <c r="E2" s="245"/>
+      <c r="F2" s="245"/>
+      <c r="G2" s="254"/>
+      <c r="H2" s="255" t="s">
         <v>113</v>
       </c>
-      <c r="I2" s="242"/>
-      <c r="J2" s="242"/>
-      <c r="K2" s="242"/>
-      <c r="L2" s="242"/>
+      <c r="I2" s="245"/>
+      <c r="J2" s="245"/>
+      <c r="K2" s="245"/>
+      <c r="L2" s="245"/>
       <c r="O2" s="5"/>
-      <c r="S2" s="242" t="s">
+      <c r="S2" s="245" t="s">
         <v>112</v>
       </c>
-      <c r="T2" s="242"/>
-      <c r="U2" s="242"/>
-      <c r="V2" s="242"/>
-      <c r="W2" s="242"/>
-      <c r="X2" s="242"/>
-      <c r="Y2" s="242"/>
-      <c r="Z2" s="242"/>
-      <c r="AA2" s="242" t="s">
+      <c r="T2" s="245"/>
+      <c r="U2" s="245"/>
+      <c r="V2" s="245"/>
+      <c r="W2" s="245"/>
+      <c r="X2" s="245"/>
+      <c r="Y2" s="245"/>
+      <c r="Z2" s="245"/>
+      <c r="AA2" s="245" t="s">
         <v>113</v>
       </c>
-      <c r="AB2" s="242"/>
-      <c r="AC2" s="242"/>
+      <c r="AB2" s="245"/>
+      <c r="AC2" s="245"/>
       <c r="AE2" s="85" t="s">
         <v>114</v>
       </c>
@@ -16903,32 +16874,32 @@
     <row r="4" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="86"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="248" t="s">
+      <c r="C4" s="251" t="s">
         <v>115</v>
       </c>
-      <c r="D4" s="248"/>
-      <c r="E4" s="248"/>
-      <c r="F4" s="248"/>
-      <c r="G4" s="248"/>
-      <c r="H4" s="248"/>
-      <c r="I4" s="248"/>
-      <c r="J4" s="248"/>
-      <c r="K4" s="248"/>
-      <c r="L4" s="248"/>
+      <c r="D4" s="251"/>
+      <c r="E4" s="251"/>
+      <c r="F4" s="251"/>
+      <c r="G4" s="251"/>
+      <c r="H4" s="251"/>
+      <c r="I4" s="251"/>
+      <c r="J4" s="251"/>
+      <c r="K4" s="251"/>
+      <c r="L4" s="251"/>
       <c r="O4" s="5"/>
-      <c r="S4" s="249" t="s">
+      <c r="S4" s="252" t="s">
         <v>115</v>
       </c>
-      <c r="T4" s="250"/>
-      <c r="U4" s="250"/>
-      <c r="V4" s="250"/>
-      <c r="W4" s="250"/>
-      <c r="X4" s="250"/>
-      <c r="Y4" s="250"/>
-      <c r="Z4" s="250"/>
-      <c r="AA4" s="250"/>
-      <c r="AB4" s="250"/>
-      <c r="AC4" s="250"/>
+      <c r="T4" s="253"/>
+      <c r="U4" s="253"/>
+      <c r="V4" s="253"/>
+      <c r="W4" s="253"/>
+      <c r="X4" s="253"/>
+      <c r="Y4" s="253"/>
+      <c r="Z4" s="253"/>
+      <c r="AA4" s="253"/>
+      <c r="AB4" s="253"/>
+      <c r="AC4" s="253"/>
       <c r="AE4" s="87"/>
     </row>
     <row r="5" spans="1:31" x14ac:dyDescent="0.2">
@@ -17841,33 +17812,33 @@
       <c r="Q15" s="91"/>
     </row>
     <row r="16" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="C16" s="248" t="s">
+      <c r="C16" s="251" t="s">
         <v>121</v>
       </c>
-      <c r="D16" s="248"/>
-      <c r="E16" s="248"/>
-      <c r="F16" s="248"/>
-      <c r="G16" s="248"/>
-      <c r="H16" s="248"/>
-      <c r="I16" s="248"/>
-      <c r="J16" s="248"/>
-      <c r="K16" s="248"/>
-      <c r="L16" s="248"/>
+      <c r="D16" s="251"/>
+      <c r="E16" s="251"/>
+      <c r="F16" s="251"/>
+      <c r="G16" s="251"/>
+      <c r="H16" s="251"/>
+      <c r="I16" s="251"/>
+      <c r="J16" s="251"/>
+      <c r="K16" s="251"/>
+      <c r="L16" s="251"/>
       <c r="O16" s="5"/>
       <c r="Q16" s="91"/>
-      <c r="S16" s="249" t="s">
+      <c r="S16" s="252" t="s">
         <v>121</v>
       </c>
-      <c r="T16" s="250"/>
-      <c r="U16" s="250"/>
-      <c r="V16" s="250"/>
-      <c r="W16" s="250"/>
-      <c r="X16" s="250"/>
-      <c r="Y16" s="250"/>
-      <c r="Z16" s="250"/>
-      <c r="AA16" s="250"/>
-      <c r="AB16" s="250"/>
-      <c r="AC16" s="250"/>
+      <c r="T16" s="253"/>
+      <c r="U16" s="253"/>
+      <c r="V16" s="253"/>
+      <c r="W16" s="253"/>
+      <c r="X16" s="253"/>
+      <c r="Y16" s="253"/>
+      <c r="Z16" s="253"/>
+      <c r="AA16" s="253"/>
+      <c r="AB16" s="253"/>
+      <c r="AC16" s="253"/>
     </row>
     <row r="17" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B17" s="16" t="s">
@@ -18635,33 +18606,33 @@
       <c r="Q27" s="91"/>
     </row>
     <row r="28" spans="2:31" x14ac:dyDescent="0.2">
-      <c r="C28" s="248" t="s">
+      <c r="C28" s="251" t="s">
         <v>422</v>
       </c>
-      <c r="D28" s="248"/>
-      <c r="E28" s="248"/>
-      <c r="F28" s="248"/>
-      <c r="G28" s="248"/>
-      <c r="H28" s="248"/>
-      <c r="I28" s="248"/>
-      <c r="J28" s="248"/>
-      <c r="K28" s="248"/>
-      <c r="L28" s="248"/>
+      <c r="D28" s="251"/>
+      <c r="E28" s="251"/>
+      <c r="F28" s="251"/>
+      <c r="G28" s="251"/>
+      <c r="H28" s="251"/>
+      <c r="I28" s="251"/>
+      <c r="J28" s="251"/>
+      <c r="K28" s="251"/>
+      <c r="L28" s="251"/>
       <c r="O28" s="5"/>
       <c r="Q28" s="91"/>
-      <c r="S28" s="249" t="s">
+      <c r="S28" s="252" t="s">
         <v>422</v>
       </c>
-      <c r="T28" s="250"/>
-      <c r="U28" s="250"/>
-      <c r="V28" s="250"/>
-      <c r="W28" s="250"/>
-      <c r="X28" s="250"/>
-      <c r="Y28" s="250"/>
-      <c r="Z28" s="250"/>
-      <c r="AA28" s="250"/>
-      <c r="AB28" s="250"/>
-      <c r="AC28" s="250"/>
+      <c r="T28" s="253"/>
+      <c r="U28" s="253"/>
+      <c r="V28" s="253"/>
+      <c r="W28" s="253"/>
+      <c r="X28" s="253"/>
+      <c r="Y28" s="253"/>
+      <c r="Z28" s="253"/>
+      <c r="AA28" s="253"/>
+      <c r="AB28" s="253"/>
+      <c r="AC28" s="253"/>
       <c r="AE28" s="87"/>
     </row>
     <row r="29" spans="2:31" x14ac:dyDescent="0.2">
@@ -18902,35 +18873,35 @@
     </row>
     <row r="2" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="242" t="s">
+      <c r="C2" s="245" t="s">
         <v>112</v>
       </c>
-      <c r="D2" s="242"/>
-      <c r="E2" s="242"/>
-      <c r="F2" s="242"/>
-      <c r="G2" s="251"/>
-      <c r="H2" s="252" t="s">
+      <c r="D2" s="245"/>
+      <c r="E2" s="245"/>
+      <c r="F2" s="245"/>
+      <c r="G2" s="254"/>
+      <c r="H2" s="255" t="s">
         <v>113</v>
       </c>
-      <c r="I2" s="242"/>
-      <c r="J2" s="242"/>
-      <c r="K2" s="242"/>
-      <c r="L2" s="242"/>
-      <c r="P2" s="242" t="s">
+      <c r="I2" s="245"/>
+      <c r="J2" s="245"/>
+      <c r="K2" s="245"/>
+      <c r="L2" s="245"/>
+      <c r="P2" s="245" t="s">
         <v>112</v>
       </c>
-      <c r="Q2" s="242"/>
-      <c r="R2" s="242"/>
-      <c r="S2" s="242"/>
-      <c r="T2" s="242"/>
-      <c r="U2" s="242"/>
-      <c r="V2" s="242"/>
-      <c r="W2" s="242"/>
-      <c r="X2" s="242" t="s">
+      <c r="Q2" s="245"/>
+      <c r="R2" s="245"/>
+      <c r="S2" s="245"/>
+      <c r="T2" s="245"/>
+      <c r="U2" s="245"/>
+      <c r="V2" s="245"/>
+      <c r="W2" s="245"/>
+      <c r="X2" s="245" t="s">
         <v>113</v>
       </c>
-      <c r="Y2" s="242"/>
-      <c r="Z2" s="242"/>
+      <c r="Y2" s="245"/>
+      <c r="Z2" s="245"/>
       <c r="AB2" s="85" t="s">
         <v>114</v>
       </c>
@@ -18939,31 +18910,31 @@
     <row r="4" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="86"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="248" t="s">
+      <c r="C4" s="251" t="s">
         <v>115</v>
       </c>
-      <c r="D4" s="248"/>
-      <c r="E4" s="248"/>
-      <c r="F4" s="248"/>
-      <c r="G4" s="248"/>
-      <c r="H4" s="248"/>
-      <c r="I4" s="248"/>
-      <c r="J4" s="248"/>
-      <c r="K4" s="248"/>
-      <c r="L4" s="248"/>
-      <c r="P4" s="250" t="s">
+      <c r="D4" s="251"/>
+      <c r="E4" s="251"/>
+      <c r="F4" s="251"/>
+      <c r="G4" s="251"/>
+      <c r="H4" s="251"/>
+      <c r="I4" s="251"/>
+      <c r="J4" s="251"/>
+      <c r="K4" s="251"/>
+      <c r="L4" s="251"/>
+      <c r="P4" s="253" t="s">
         <v>115</v>
       </c>
-      <c r="Q4" s="250"/>
-      <c r="R4" s="250"/>
-      <c r="S4" s="250"/>
-      <c r="T4" s="250"/>
-      <c r="U4" s="250"/>
-      <c r="V4" s="250"/>
-      <c r="W4" s="250"/>
-      <c r="X4" s="250"/>
-      <c r="Y4" s="250"/>
-      <c r="Z4" s="250"/>
+      <c r="Q4" s="253"/>
+      <c r="R4" s="253"/>
+      <c r="S4" s="253"/>
+      <c r="T4" s="253"/>
+      <c r="U4" s="253"/>
+      <c r="V4" s="253"/>
+      <c r="W4" s="253"/>
+      <c r="X4" s="253"/>
+      <c r="Y4" s="253"/>
+      <c r="Z4" s="253"/>
       <c r="AB4" s="87"/>
     </row>
     <row r="5" spans="1:28" x14ac:dyDescent="0.2">
@@ -19158,32 +19129,32 @@
       <c r="N8" s="91"/>
     </row>
     <row r="9" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="C9" s="248" t="s">
+      <c r="C9" s="251" t="s">
         <v>124</v>
       </c>
-      <c r="D9" s="248"/>
-      <c r="E9" s="248"/>
-      <c r="F9" s="248"/>
-      <c r="G9" s="248"/>
-      <c r="H9" s="248"/>
-      <c r="I9" s="248"/>
-      <c r="J9" s="248"/>
-      <c r="K9" s="248"/>
-      <c r="L9" s="248"/>
+      <c r="D9" s="251"/>
+      <c r="E9" s="251"/>
+      <c r="F9" s="251"/>
+      <c r="G9" s="251"/>
+      <c r="H9" s="251"/>
+      <c r="I9" s="251"/>
+      <c r="J9" s="251"/>
+      <c r="K9" s="251"/>
+      <c r="L9" s="251"/>
       <c r="N9" s="91"/>
-      <c r="P9" s="250" t="s">
+      <c r="P9" s="253" t="s">
         <v>125</v>
       </c>
-      <c r="Q9" s="250"/>
-      <c r="R9" s="250"/>
-      <c r="S9" s="250"/>
-      <c r="T9" s="250"/>
-      <c r="U9" s="250"/>
-      <c r="V9" s="250"/>
-      <c r="W9" s="250"/>
-      <c r="X9" s="250"/>
-      <c r="Y9" s="250"/>
-      <c r="Z9" s="250"/>
+      <c r="Q9" s="253"/>
+      <c r="R9" s="253"/>
+      <c r="S9" s="253"/>
+      <c r="T9" s="253"/>
+      <c r="U9" s="253"/>
+      <c r="V9" s="253"/>
+      <c r="W9" s="253"/>
+      <c r="X9" s="253"/>
+      <c r="Y9" s="253"/>
+      <c r="Z9" s="253"/>
       <c r="AB9" s="87"/>
     </row>
     <row r="10" spans="1:28" x14ac:dyDescent="0.2">
@@ -20029,31 +20000,31 @@
       </c>
     </row>
     <row r="21" spans="2:28" x14ac:dyDescent="0.2">
-      <c r="C21" s="248" t="s">
+      <c r="C21" s="251" t="s">
         <v>127</v>
       </c>
-      <c r="D21" s="248"/>
-      <c r="E21" s="248"/>
-      <c r="F21" s="248"/>
-      <c r="G21" s="248"/>
-      <c r="H21" s="248"/>
-      <c r="I21" s="248"/>
-      <c r="J21" s="248"/>
-      <c r="K21" s="248"/>
-      <c r="L21" s="248"/>
-      <c r="P21" s="250" t="s">
+      <c r="D21" s="251"/>
+      <c r="E21" s="251"/>
+      <c r="F21" s="251"/>
+      <c r="G21" s="251"/>
+      <c r="H21" s="251"/>
+      <c r="I21" s="251"/>
+      <c r="J21" s="251"/>
+      <c r="K21" s="251"/>
+      <c r="L21" s="251"/>
+      <c r="P21" s="253" t="s">
         <v>127</v>
       </c>
-      <c r="Q21" s="250"/>
-      <c r="R21" s="250"/>
-      <c r="S21" s="250"/>
-      <c r="T21" s="250"/>
-      <c r="U21" s="250"/>
-      <c r="V21" s="250"/>
-      <c r="W21" s="250"/>
-      <c r="X21" s="250"/>
-      <c r="Y21" s="250"/>
-      <c r="Z21" s="250"/>
+      <c r="Q21" s="253"/>
+      <c r="R21" s="253"/>
+      <c r="S21" s="253"/>
+      <c r="T21" s="253"/>
+      <c r="U21" s="253"/>
+      <c r="V21" s="253"/>
+      <c r="W21" s="253"/>
+      <c r="X21" s="253"/>
+      <c r="Y21" s="253"/>
+      <c r="Z21" s="253"/>
     </row>
     <row r="22" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B22" s="16" t="s">
@@ -20868,60 +20839,60 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="242" t="s">
+      <c r="C3" s="245" t="s">
         <v>112</v>
       </c>
-      <c r="D3" s="242"/>
-      <c r="E3" s="242"/>
-      <c r="F3" s="242"/>
-      <c r="G3" s="251"/>
-      <c r="H3" s="252" t="s">
+      <c r="D3" s="245"/>
+      <c r="E3" s="245"/>
+      <c r="F3" s="245"/>
+      <c r="G3" s="254"/>
+      <c r="H3" s="255" t="s">
         <v>113</v>
       </c>
-      <c r="I3" s="242"/>
-      <c r="J3" s="242"/>
-      <c r="K3" s="242"/>
-      <c r="L3" s="242"/>
-      <c r="P3" s="253"/>
-      <c r="Q3" s="253"/>
-      <c r="R3" s="253"/>
-      <c r="S3" s="253"/>
-      <c r="T3" s="253"/>
-      <c r="U3" s="253"/>
-      <c r="V3" s="253"/>
-      <c r="W3" s="253"/>
-      <c r="X3" s="253"/>
-      <c r="Y3" s="253"/>
-      <c r="Z3" s="253"/>
+      <c r="I3" s="245"/>
+      <c r="J3" s="245"/>
+      <c r="K3" s="245"/>
+      <c r="L3" s="245"/>
+      <c r="P3" s="256"/>
+      <c r="Q3" s="256"/>
+      <c r="R3" s="256"/>
+      <c r="S3" s="256"/>
+      <c r="T3" s="256"/>
+      <c r="U3" s="256"/>
+      <c r="V3" s="256"/>
+      <c r="W3" s="256"/>
+      <c r="X3" s="256"/>
+      <c r="Y3" s="256"/>
+      <c r="Z3" s="256"/>
       <c r="AB3" s="111"/>
     </row>
     <row r="4" spans="1:28" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="86"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="248" t="s">
+      <c r="C5" s="251" t="s">
         <v>115</v>
       </c>
-      <c r="D5" s="248"/>
-      <c r="E5" s="248"/>
-      <c r="F5" s="248"/>
-      <c r="G5" s="248"/>
-      <c r="H5" s="248"/>
-      <c r="I5" s="248"/>
-      <c r="J5" s="248"/>
-      <c r="K5" s="248"/>
-      <c r="L5" s="248"/>
-      <c r="P5" s="253"/>
-      <c r="Q5" s="253"/>
-      <c r="R5" s="253"/>
-      <c r="S5" s="253"/>
-      <c r="T5" s="253"/>
-      <c r="U5" s="253"/>
-      <c r="V5" s="253"/>
-      <c r="W5" s="253"/>
-      <c r="X5" s="253"/>
-      <c r="Y5" s="253"/>
-      <c r="Z5" s="253"/>
+      <c r="D5" s="251"/>
+      <c r="E5" s="251"/>
+      <c r="F5" s="251"/>
+      <c r="G5" s="251"/>
+      <c r="H5" s="251"/>
+      <c r="I5" s="251"/>
+      <c r="J5" s="251"/>
+      <c r="K5" s="251"/>
+      <c r="L5" s="251"/>
+      <c r="P5" s="256"/>
+      <c r="Q5" s="256"/>
+      <c r="R5" s="256"/>
+      <c r="S5" s="256"/>
+      <c r="T5" s="256"/>
+      <c r="U5" s="256"/>
+      <c r="V5" s="256"/>
+      <c r="W5" s="256"/>
+      <c r="X5" s="256"/>
+      <c r="Y5" s="256"/>
+      <c r="Z5" s="256"/>
       <c r="AB5" s="112"/>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.2">
@@ -21107,30 +21078,30 @@
       <c r="N10" s="91"/>
     </row>
     <row r="11" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="C11" s="248" t="s">
+      <c r="C11" s="251" t="s">
         <v>131</v>
       </c>
-      <c r="D11" s="248"/>
-      <c r="E11" s="248"/>
-      <c r="F11" s="248"/>
-      <c r="G11" s="248"/>
-      <c r="H11" s="248"/>
-      <c r="I11" s="248"/>
-      <c r="J11" s="248"/>
-      <c r="K11" s="248"/>
-      <c r="L11" s="248"/>
+      <c r="D11" s="251"/>
+      <c r="E11" s="251"/>
+      <c r="F11" s="251"/>
+      <c r="G11" s="251"/>
+      <c r="H11" s="251"/>
+      <c r="I11" s="251"/>
+      <c r="J11" s="251"/>
+      <c r="K11" s="251"/>
+      <c r="L11" s="251"/>
       <c r="N11" s="91"/>
-      <c r="P11" s="253"/>
-      <c r="Q11" s="253"/>
-      <c r="R11" s="253"/>
-      <c r="S11" s="253"/>
-      <c r="T11" s="253"/>
-      <c r="U11" s="253"/>
-      <c r="V11" s="253"/>
-      <c r="W11" s="253"/>
-      <c r="X11" s="253"/>
-      <c r="Y11" s="253"/>
-      <c r="Z11" s="253"/>
+      <c r="P11" s="256"/>
+      <c r="Q11" s="256"/>
+      <c r="R11" s="256"/>
+      <c r="S11" s="256"/>
+      <c r="T11" s="256"/>
+      <c r="U11" s="256"/>
+      <c r="V11" s="256"/>
+      <c r="W11" s="256"/>
+      <c r="X11" s="256"/>
+      <c r="Y11" s="256"/>
+      <c r="Z11" s="256"/>
       <c r="AB11" s="112"/>
     </row>
     <row r="12" spans="1:28" x14ac:dyDescent="0.2">
@@ -21372,18 +21343,18 @@
       <c r="D16" s="24"/>
     </row>
     <row r="18" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C18" s="248" t="s">
+      <c r="C18" s="251" t="s">
         <v>136</v>
       </c>
-      <c r="D18" s="248"/>
-      <c r="E18" s="248"/>
-      <c r="F18" s="248"/>
-      <c r="G18" s="248"/>
-      <c r="H18" s="248"/>
-      <c r="I18" s="248"/>
-      <c r="J18" s="248"/>
-      <c r="K18" s="248"/>
-      <c r="L18" s="248"/>
+      <c r="D18" s="251"/>
+      <c r="E18" s="251"/>
+      <c r="F18" s="251"/>
+      <c r="G18" s="251"/>
+      <c r="H18" s="251"/>
+      <c r="I18" s="251"/>
+      <c r="J18" s="251"/>
+      <c r="K18" s="251"/>
+      <c r="L18" s="251"/>
     </row>
     <row r="19" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B19" s="16" t="s">
@@ -21596,23 +21567,23 @@
       </c>
     </row>
     <row r="25" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B25" s="253"/>
-      <c r="C25" s="253"/>
+      <c r="B25" s="256"/>
+      <c r="C25" s="256"/>
     </row>
     <row r="26" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B26" s="111"/>
-      <c r="C26" s="248" t="s">
+      <c r="C26" s="251" t="s">
         <v>142</v>
       </c>
-      <c r="D26" s="248"/>
-      <c r="E26" s="248"/>
-      <c r="F26" s="248"/>
-      <c r="G26" s="248"/>
-      <c r="H26" s="248"/>
-      <c r="I26" s="248"/>
-      <c r="J26" s="248"/>
-      <c r="K26" s="248"/>
-      <c r="L26" s="248"/>
+      <c r="D26" s="251"/>
+      <c r="E26" s="251"/>
+      <c r="F26" s="251"/>
+      <c r="G26" s="251"/>
+      <c r="H26" s="251"/>
+      <c r="I26" s="251"/>
+      <c r="J26" s="251"/>
+      <c r="K26" s="251"/>
+      <c r="L26" s="251"/>
     </row>
     <row r="27" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B27" s="16" t="s">
@@ -21804,18 +21775,18 @@
     </row>
     <row r="33" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B33" s="111"/>
-      <c r="C33" s="248" t="s">
+      <c r="C33" s="251" t="s">
         <v>146</v>
       </c>
-      <c r="D33" s="248"/>
-      <c r="E33" s="248"/>
-      <c r="F33" s="248"/>
-      <c r="G33" s="248"/>
-      <c r="H33" s="248"/>
-      <c r="I33" s="248"/>
-      <c r="J33" s="248"/>
-      <c r="K33" s="248"/>
-      <c r="L33" s="248"/>
+      <c r="D33" s="251"/>
+      <c r="E33" s="251"/>
+      <c r="F33" s="251"/>
+      <c r="G33" s="251"/>
+      <c r="H33" s="251"/>
+      <c r="I33" s="251"/>
+      <c r="J33" s="251"/>
+      <c r="K33" s="251"/>
+      <c r="L33" s="251"/>
     </row>
     <row r="34" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B34" s="16" t="s">
@@ -21999,18 +21970,18 @@
       <c r="C39" s="127"/>
     </row>
     <row r="40" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="C40" s="248" t="s">
+      <c r="C40" s="251" t="s">
         <v>149</v>
       </c>
-      <c r="D40" s="248"/>
-      <c r="E40" s="248"/>
-      <c r="F40" s="248"/>
-      <c r="G40" s="248"/>
-      <c r="H40" s="248"/>
-      <c r="I40" s="248"/>
-      <c r="J40" s="248"/>
-      <c r="K40" s="248"/>
-      <c r="L40" s="248"/>
+      <c r="D40" s="251"/>
+      <c r="E40" s="251"/>
+      <c r="F40" s="251"/>
+      <c r="G40" s="251"/>
+      <c r="H40" s="251"/>
+      <c r="I40" s="251"/>
+      <c r="J40" s="251"/>
+      <c r="K40" s="251"/>
+      <c r="L40" s="251"/>
     </row>
     <row r="41" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B41" s="16" t="s">
@@ -22324,60 +22295,60 @@
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="242" t="s">
+      <c r="C2" s="245" t="s">
         <v>112</v>
       </c>
-      <c r="D2" s="242"/>
-      <c r="E2" s="242"/>
-      <c r="F2" s="242"/>
-      <c r="G2" s="251"/>
-      <c r="H2" s="252" t="s">
+      <c r="D2" s="245"/>
+      <c r="E2" s="245"/>
+      <c r="F2" s="245"/>
+      <c r="G2" s="254"/>
+      <c r="H2" s="255" t="s">
         <v>113</v>
       </c>
-      <c r="I2" s="242"/>
-      <c r="J2" s="242"/>
-      <c r="K2" s="242"/>
-      <c r="L2" s="242"/>
-      <c r="S2" s="253"/>
-      <c r="T2" s="253"/>
-      <c r="U2" s="253"/>
-      <c r="V2" s="253"/>
-      <c r="W2" s="253"/>
-      <c r="X2" s="253"/>
-      <c r="Y2" s="253"/>
-      <c r="Z2" s="253"/>
-      <c r="AA2" s="253"/>
-      <c r="AB2" s="253"/>
-      <c r="AC2" s="253"/>
+      <c r="I2" s="245"/>
+      <c r="J2" s="245"/>
+      <c r="K2" s="245"/>
+      <c r="L2" s="245"/>
+      <c r="S2" s="256"/>
+      <c r="T2" s="256"/>
+      <c r="U2" s="256"/>
+      <c r="V2" s="256"/>
+      <c r="W2" s="256"/>
+      <c r="X2" s="256"/>
+      <c r="Y2" s="256"/>
+      <c r="Z2" s="256"/>
+      <c r="AA2" s="256"/>
+      <c r="AB2" s="256"/>
+      <c r="AC2" s="256"/>
       <c r="AE2" s="111"/>
     </row>
     <row r="3" spans="1:31" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="86"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="248" t="s">
+      <c r="C4" s="251" t="s">
         <v>18</v>
       </c>
-      <c r="D4" s="248"/>
-      <c r="E4" s="248"/>
-      <c r="F4" s="248"/>
-      <c r="G4" s="248"/>
-      <c r="H4" s="248"/>
-      <c r="I4" s="248"/>
-      <c r="J4" s="248"/>
-      <c r="K4" s="248"/>
-      <c r="L4" s="248"/>
-      <c r="S4" s="253"/>
-      <c r="T4" s="253"/>
-      <c r="U4" s="253"/>
-      <c r="V4" s="253"/>
-      <c r="W4" s="253"/>
-      <c r="X4" s="253"/>
-      <c r="Y4" s="253"/>
-      <c r="Z4" s="253"/>
-      <c r="AA4" s="253"/>
-      <c r="AB4" s="253"/>
-      <c r="AC4" s="253"/>
+      <c r="D4" s="251"/>
+      <c r="E4" s="251"/>
+      <c r="F4" s="251"/>
+      <c r="G4" s="251"/>
+      <c r="H4" s="251"/>
+      <c r="I4" s="251"/>
+      <c r="J4" s="251"/>
+      <c r="K4" s="251"/>
+      <c r="L4" s="251"/>
+      <c r="S4" s="256"/>
+      <c r="T4" s="256"/>
+      <c r="U4" s="256"/>
+      <c r="V4" s="256"/>
+      <c r="W4" s="256"/>
+      <c r="X4" s="256"/>
+      <c r="Y4" s="256"/>
+      <c r="Z4" s="256"/>
+      <c r="AA4" s="256"/>
+      <c r="AB4" s="256"/>
+      <c r="AC4" s="256"/>
       <c r="AE4" s="112"/>
     </row>
     <row r="5" spans="1:31" x14ac:dyDescent="0.2">
@@ -22740,18 +22711,18 @@
       <c r="AE10" s="64"/>
     </row>
     <row r="13" spans="1:31" x14ac:dyDescent="0.2">
-      <c r="C13" s="248" t="s">
+      <c r="C13" s="251" t="s">
         <v>157</v>
       </c>
-      <c r="D13" s="248"/>
-      <c r="E13" s="248"/>
-      <c r="F13" s="248"/>
-      <c r="G13" s="248"/>
-      <c r="H13" s="248"/>
-      <c r="I13" s="248"/>
-      <c r="J13" s="248"/>
-      <c r="K13" s="248"/>
-      <c r="L13" s="248"/>
+      <c r="D13" s="251"/>
+      <c r="E13" s="251"/>
+      <c r="F13" s="251"/>
+      <c r="G13" s="251"/>
+      <c r="H13" s="251"/>
+      <c r="I13" s="251"/>
+      <c r="J13" s="251"/>
+      <c r="K13" s="251"/>
+      <c r="L13" s="251"/>
     </row>
     <row r="14" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C14" s="12">
@@ -22844,18 +22815,18 @@
       </c>
     </row>
     <row r="18" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C18" s="248" t="s">
+      <c r="C18" s="251" t="s">
         <v>158</v>
       </c>
-      <c r="D18" s="248"/>
-      <c r="E18" s="248"/>
-      <c r="F18" s="248"/>
-      <c r="G18" s="248"/>
-      <c r="H18" s="248"/>
-      <c r="I18" s="248"/>
-      <c r="J18" s="248"/>
-      <c r="K18" s="248"/>
-      <c r="L18" s="248"/>
+      <c r="D18" s="251"/>
+      <c r="E18" s="251"/>
+      <c r="F18" s="251"/>
+      <c r="G18" s="251"/>
+      <c r="H18" s="251"/>
+      <c r="I18" s="251"/>
+      <c r="J18" s="251"/>
+      <c r="K18" s="251"/>
+      <c r="L18" s="251"/>
     </row>
     <row r="19" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B19" s="16" t="s">
@@ -23047,18 +23018,18 @@
       </c>
     </row>
     <row r="25" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C25" s="248" t="s">
+      <c r="C25" s="251" t="s">
         <v>261</v>
       </c>
-      <c r="D25" s="248"/>
-      <c r="E25" s="248"/>
-      <c r="F25" s="248"/>
-      <c r="G25" s="248"/>
-      <c r="H25" s="248"/>
-      <c r="I25" s="248"/>
-      <c r="J25" s="248"/>
-      <c r="K25" s="248"/>
-      <c r="L25" s="248"/>
+      <c r="D25" s="251"/>
+      <c r="E25" s="251"/>
+      <c r="F25" s="251"/>
+      <c r="G25" s="251"/>
+      <c r="H25" s="251"/>
+      <c r="I25" s="251"/>
+      <c r="J25" s="251"/>
+      <c r="K25" s="251"/>
+      <c r="L25" s="251"/>
     </row>
     <row r="26" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B26" s="16" t="s">
@@ -23196,18 +23167,18 @@
       </c>
     </row>
     <row r="31" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C31" s="248" t="s">
+      <c r="C31" s="251" t="s">
         <v>77</v>
       </c>
-      <c r="D31" s="248"/>
-      <c r="E31" s="248"/>
-      <c r="F31" s="248"/>
-      <c r="G31" s="248"/>
-      <c r="H31" s="248"/>
-      <c r="I31" s="248"/>
-      <c r="J31" s="248"/>
-      <c r="K31" s="248"/>
-      <c r="L31" s="248"/>
+      <c r="D31" s="251"/>
+      <c r="E31" s="251"/>
+      <c r="F31" s="251"/>
+      <c r="G31" s="251"/>
+      <c r="H31" s="251"/>
+      <c r="I31" s="251"/>
+      <c r="J31" s="251"/>
+      <c r="K31" s="251"/>
+      <c r="L31" s="251"/>
     </row>
     <row r="32" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B32" s="16" t="s">
@@ -23457,10 +23428,10 @@
     </row>
     <row r="3" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="242" t="s">
+      <c r="B4" s="245" t="s">
         <v>165</v>
       </c>
-      <c r="C4" s="242"/>
+      <c r="C4" s="245"/>
     </row>
     <row r="5" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" s="1" t="s">
@@ -23477,7 +23448,7 @@
       </c>
       <c r="C6" s="135">
         <f ca="1">Overview!C5</f>
-        <v>244.07</v>
+        <v>252.2</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -23486,7 +23457,7 @@
       </c>
       <c r="C7" s="136">
         <f ca="1">C5*C6</f>
-        <v>51254.7</v>
+        <v>52962</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -23504,7 +23475,7 @@
       </c>
       <c r="C9" s="137">
         <f ca="1">Overview!F27</f>
-        <v>5.1360000000000003E-2</v>
+        <v>4.9530000000000005E-2</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -23513,7 +23484,7 @@
       </c>
       <c r="C10" s="135">
         <f ca="1">Overview!C13</f>
-        <v>1.3027</v>
+        <v>1.2928999999999999</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -23545,10 +23516,10 @@
     </row>
     <row r="14" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="15" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="242" t="s">
+      <c r="B15" s="245" t="s">
         <v>172</v>
       </c>
-      <c r="C15" s="242"/>
+      <c r="C15" s="245"/>
     </row>
     <row r="16" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B16" s="1" t="s">
@@ -23556,7 +23527,7 @@
       </c>
       <c r="C16" s="46">
         <f ca="1">C8/(C8+C7)</f>
-        <v>6.3545193275683462E-2</v>
+        <v>6.162296243798724E-2</v>
       </c>
     </row>
     <row r="17" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -23565,7 +23536,7 @@
       </c>
       <c r="C17" s="46">
         <f ca="1">C7/(C8+C7)</f>
-        <v>0.93645480672431658</v>
+        <v>0.93837703756201274</v>
       </c>
     </row>
     <row r="18" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -23583,7 +23554,7 @@
       </c>
       <c r="C19" s="46">
         <f ca="1">C9+C10*C11</f>
-        <v>0.1099815</v>
+        <v>0.1077105</v>
       </c>
     </row>
     <row r="20" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -23592,7 +23563,7 @@
       </c>
       <c r="C20" s="46">
         <f ca="1">(C17*C19)+(C16*C18)</f>
-        <v>0.10605494718970561</v>
+        <v>0.10404267046420979</v>
       </c>
     </row>
   </sheetData>
@@ -23637,60 +23608,60 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="242" t="s">
+      <c r="C3" s="245" t="s">
         <v>112</v>
       </c>
-      <c r="D3" s="242"/>
-      <c r="E3" s="242"/>
-      <c r="F3" s="242"/>
-      <c r="G3" s="251"/>
-      <c r="H3" s="252" t="s">
+      <c r="D3" s="245"/>
+      <c r="E3" s="245"/>
+      <c r="F3" s="245"/>
+      <c r="G3" s="254"/>
+      <c r="H3" s="255" t="s">
         <v>113</v>
       </c>
-      <c r="I3" s="242"/>
-      <c r="J3" s="242"/>
-      <c r="K3" s="242"/>
-      <c r="L3" s="242"/>
-      <c r="P3" s="253"/>
-      <c r="Q3" s="253"/>
-      <c r="R3" s="253"/>
-      <c r="S3" s="253"/>
-      <c r="T3" s="253"/>
-      <c r="U3" s="253"/>
-      <c r="V3" s="253"/>
-      <c r="W3" s="253"/>
-      <c r="X3" s="253"/>
-      <c r="Y3" s="253"/>
-      <c r="Z3" s="253"/>
+      <c r="I3" s="245"/>
+      <c r="J3" s="245"/>
+      <c r="K3" s="245"/>
+      <c r="L3" s="245"/>
+      <c r="P3" s="256"/>
+      <c r="Q3" s="256"/>
+      <c r="R3" s="256"/>
+      <c r="S3" s="256"/>
+      <c r="T3" s="256"/>
+      <c r="U3" s="256"/>
+      <c r="V3" s="256"/>
+      <c r="W3" s="256"/>
+      <c r="X3" s="256"/>
+      <c r="Y3" s="256"/>
+      <c r="Z3" s="256"/>
       <c r="AB3" s="111"/>
     </row>
     <row r="4" spans="1:28" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="86"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="248" t="s">
+      <c r="C5" s="251" t="s">
         <v>179</v>
       </c>
-      <c r="D5" s="248"/>
-      <c r="E5" s="248"/>
-      <c r="F5" s="248"/>
-      <c r="G5" s="248"/>
-      <c r="H5" s="248"/>
-      <c r="I5" s="248"/>
-      <c r="J5" s="248"/>
-      <c r="K5" s="248"/>
-      <c r="L5" s="248"/>
-      <c r="P5" s="253"/>
-      <c r="Q5" s="253"/>
-      <c r="R5" s="253"/>
-      <c r="S5" s="253"/>
-      <c r="T5" s="253"/>
-      <c r="U5" s="253"/>
-      <c r="V5" s="253"/>
-      <c r="W5" s="253"/>
-      <c r="X5" s="253"/>
-      <c r="Y5" s="253"/>
-      <c r="Z5" s="253"/>
+      <c r="D5" s="251"/>
+      <c r="E5" s="251"/>
+      <c r="F5" s="251"/>
+      <c r="G5" s="251"/>
+      <c r="H5" s="251"/>
+      <c r="I5" s="251"/>
+      <c r="J5" s="251"/>
+      <c r="K5" s="251"/>
+      <c r="L5" s="251"/>
+      <c r="P5" s="256"/>
+      <c r="Q5" s="256"/>
+      <c r="R5" s="256"/>
+      <c r="S5" s="256"/>
+      <c r="T5" s="256"/>
+      <c r="U5" s="256"/>
+      <c r="V5" s="256"/>
+      <c r="W5" s="256"/>
+      <c r="X5" s="256"/>
+      <c r="Y5" s="256"/>
+      <c r="Z5" s="256"/>
       <c r="AB5" s="112"/>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.2">
@@ -23843,7 +23814,7 @@
       </c>
       <c r="L8" s="128">
         <f ca="1">L7*(1+C14)/(C15-C14)</f>
-        <v>29177.598634709731</v>
+        <v>29876.212830500768</v>
       </c>
       <c r="N8" s="91"/>
       <c r="O8" s="16"/>
@@ -23897,23 +23868,23 @@
       <c r="G10" s="140"/>
       <c r="H10" s="128">
         <f ca="1">H7/(1+$C$15)^H9</f>
-        <v>1863.3034905670513</v>
+        <v>1866.6996294545338</v>
       </c>
       <c r="I10" s="128">
         <f t="shared" ref="I10:L10" ca="1" si="0">I7/(1+$C$15)^I9</f>
-        <v>1272.138204509688</v>
+        <v>1276.7797406692569</v>
       </c>
       <c r="J10" s="128">
         <f t="shared" ca="1" si="0"/>
-        <v>571.15824233461035</v>
+        <v>574.28699240293599</v>
       </c>
       <c r="K10" s="128">
         <f t="shared" ca="1" si="0"/>
-        <v>1424.2398848366518</v>
+        <v>1434.6518365627037</v>
       </c>
       <c r="L10" s="128">
         <f t="shared" ca="1" si="0"/>
-        <v>1487.1052383302315</v>
+        <v>1500.7070475941791</v>
       </c>
       <c r="N10" s="91"/>
     </row>
@@ -23932,14 +23903,14 @@
       <c r="K11" s="139"/>
       <c r="L11" s="128">
         <f ca="1">L8/(1+C15)^L9</f>
-        <v>17626.497867147493</v>
+        <v>18213.619106712369</v>
       </c>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B13" s="242" t="s">
+      <c r="B13" s="245" t="s">
         <v>183</v>
       </c>
-      <c r="C13" s="242"/>
+      <c r="C13" s="245"/>
     </row>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B14" s="1" t="s">
@@ -23955,14 +23926,14 @@
       </c>
       <c r="C15" s="137">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.10605494718970561</v>
+        <v>0.10404267046420979</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B18" s="242" t="s">
+      <c r="B18" s="245" t="s">
         <v>185</v>
       </c>
-      <c r="C18" s="242"/>
+      <c r="C18" s="245"/>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B19" s="1" t="s">
@@ -23970,7 +23941,7 @@
       </c>
       <c r="C19" s="64">
         <f ca="1">SUM(H10:L10)</f>
-        <v>6617.9450605782322</v>
+        <v>6653.1252466836095</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.2">
@@ -23979,7 +23950,7 @@
       </c>
       <c r="C20" s="64">
         <f ca="1">L11</f>
-        <v>17626.497867147493</v>
+        <v>18213.619106712369</v>
       </c>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.2">
@@ -23988,7 +23959,7 @@
       </c>
       <c r="C21" s="94">
         <f ca="1">C19+C20</f>
-        <v>24244.442927725726</v>
+        <v>24866.744353395978</v>
       </c>
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.2">
@@ -24015,7 +23986,7 @@
       </c>
       <c r="C24" s="94">
         <f ca="1">C21+C22-C23</f>
-        <v>25123.442927725726</v>
+        <v>25745.744353395978</v>
       </c>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.2">
@@ -24033,7 +24004,7 @@
       </c>
       <c r="C26" s="234">
         <f ca="1">C24/C25</f>
-        <v>119.63544251297965</v>
+        <v>122.59878263521894</v>
       </c>
     </row>
   </sheetData>
@@ -24076,37 +24047,37 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="242" t="s">
+      <c r="C2" s="245" t="s">
         <v>112</v>
       </c>
-      <c r="D2" s="242"/>
-      <c r="E2" s="242"/>
-      <c r="F2" s="242"/>
-      <c r="G2" s="251"/>
-      <c r="H2" s="252" t="s">
+      <c r="D2" s="245"/>
+      <c r="E2" s="245"/>
+      <c r="F2" s="245"/>
+      <c r="G2" s="254"/>
+      <c r="H2" s="255" t="s">
         <v>113</v>
       </c>
-      <c r="I2" s="242"/>
-      <c r="J2" s="242"/>
-      <c r="K2" s="242"/>
-      <c r="L2" s="242"/>
+      <c r="I2" s="245"/>
+      <c r="J2" s="245"/>
+      <c r="K2" s="245"/>
+      <c r="L2" s="245"/>
     </row>
     <row r="3" spans="1:14" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="86"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="248" t="s">
+      <c r="C4" s="251" t="s">
         <v>193</v>
       </c>
-      <c r="D4" s="248"/>
-      <c r="E4" s="248"/>
-      <c r="F4" s="248"/>
-      <c r="G4" s="248"/>
-      <c r="H4" s="248"/>
-      <c r="I4" s="248"/>
-      <c r="J4" s="248"/>
-      <c r="K4" s="248"/>
-      <c r="L4" s="248"/>
+      <c r="D4" s="251"/>
+      <c r="E4" s="251"/>
+      <c r="F4" s="251"/>
+      <c r="G4" s="251"/>
+      <c r="H4" s="251"/>
+      <c r="I4" s="251"/>
+      <c r="J4" s="251"/>
+      <c r="K4" s="251"/>
+      <c r="L4" s="251"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B5" s="16" t="s">
@@ -24302,23 +24273,23 @@
       <c r="G9" s="140"/>
       <c r="H9" s="92">
         <f ca="1">DCF!H10</f>
-        <v>1863.3034905670513</v>
+        <v>1866.6996294545338</v>
       </c>
       <c r="I9" s="92">
         <f ca="1">DCF!I10</f>
-        <v>1272.138204509688</v>
+        <v>1276.7797406692569</v>
       </c>
       <c r="J9" s="92">
         <f ca="1">DCF!J10</f>
-        <v>571.15824233461035</v>
+        <v>574.28699240293599</v>
       </c>
       <c r="K9" s="92">
         <f ca="1">DCF!K10</f>
-        <v>1424.2398848366518</v>
+        <v>1434.6518365627037</v>
       </c>
       <c r="L9" s="92">
         <f ca="1">DCF!L10</f>
-        <v>1487.1052383302315</v>
+        <v>1500.7070475941791</v>
       </c>
       <c r="N9" s="91"/>
     </row>
@@ -24326,18 +24297,18 @@
       <c r="N10" s="91"/>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C11" s="248" t="s">
+      <c r="C11" s="251" t="s">
         <v>121</v>
       </c>
-      <c r="D11" s="248"/>
-      <c r="E11" s="248"/>
-      <c r="F11" s="248"/>
-      <c r="G11" s="248"/>
-      <c r="H11" s="248"/>
-      <c r="I11" s="248"/>
-      <c r="J11" s="248"/>
-      <c r="K11" s="248"/>
-      <c r="L11" s="248"/>
+      <c r="D11" s="251"/>
+      <c r="E11" s="251"/>
+      <c r="F11" s="251"/>
+      <c r="G11" s="251"/>
+      <c r="H11" s="251"/>
+      <c r="I11" s="251"/>
+      <c r="J11" s="251"/>
+      <c r="K11" s="251"/>
+      <c r="L11" s="251"/>
       <c r="N11" s="91"/>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.2">
@@ -24531,18 +24502,18 @@
       <c r="N16" s="91"/>
     </row>
     <row r="17" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C17" s="248" t="s">
+      <c r="C17" s="251" t="s">
         <v>195</v>
       </c>
-      <c r="D17" s="248"/>
-      <c r="E17" s="248"/>
-      <c r="F17" s="248"/>
-      <c r="G17" s="248"/>
-      <c r="H17" s="248"/>
-      <c r="I17" s="248"/>
-      <c r="J17" s="248"/>
-      <c r="K17" s="248"/>
-      <c r="L17" s="248"/>
+      <c r="D17" s="251"/>
+      <c r="E17" s="251"/>
+      <c r="F17" s="251"/>
+      <c r="G17" s="251"/>
+      <c r="H17" s="251"/>
+      <c r="I17" s="251"/>
+      <c r="J17" s="251"/>
+      <c r="K17" s="251"/>
+      <c r="L17" s="251"/>
       <c r="N17" s="91"/>
     </row>
     <row r="18" spans="2:14" x14ac:dyDescent="0.2">
@@ -24676,18 +24647,18 @@
       <c r="N21" s="91"/>
     </row>
     <row r="22" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C22" s="248" t="s">
+      <c r="C22" s="251" t="s">
         <v>198</v>
       </c>
-      <c r="D22" s="248"/>
-      <c r="E22" s="248"/>
-      <c r="F22" s="248"/>
-      <c r="G22" s="248"/>
-      <c r="H22" s="248"/>
-      <c r="I22" s="248"/>
-      <c r="J22" s="248"/>
-      <c r="K22" s="248"/>
-      <c r="L22" s="248"/>
+      <c r="D22" s="251"/>
+      <c r="E22" s="251"/>
+      <c r="F22" s="251"/>
+      <c r="G22" s="251"/>
+      <c r="H22" s="251"/>
+      <c r="I22" s="251"/>
+      <c r="J22" s="251"/>
+      <c r="K22" s="251"/>
+      <c r="L22" s="251"/>
       <c r="N22" s="91"/>
     </row>
     <row r="23" spans="2:14" x14ac:dyDescent="0.2">
@@ -24771,18 +24742,18 @@
       <c r="N26" s="91"/>
     </row>
     <row r="27" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="C27" s="248" t="s">
+      <c r="C27" s="251" t="s">
         <v>199</v>
       </c>
-      <c r="D27" s="248"/>
-      <c r="E27" s="248"/>
-      <c r="F27" s="248"/>
-      <c r="G27" s="248"/>
-      <c r="H27" s="248"/>
-      <c r="I27" s="248"/>
-      <c r="J27" s="248"/>
-      <c r="K27" s="248"/>
-      <c r="L27" s="248"/>
+      <c r="D27" s="251"/>
+      <c r="E27" s="251"/>
+      <c r="F27" s="251"/>
+      <c r="G27" s="251"/>
+      <c r="H27" s="251"/>
+      <c r="I27" s="251"/>
+      <c r="J27" s="251"/>
+      <c r="K27" s="251"/>
+      <c r="L27" s="251"/>
       <c r="N27" s="91"/>
     </row>
     <row r="28" spans="2:14" x14ac:dyDescent="0.2">
@@ -25083,10 +25054,10 @@
       <c r="N38" s="91"/>
     </row>
     <row r="39" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B39" s="242" t="s">
+      <c r="B39" s="245" t="s">
         <v>204</v>
       </c>
-      <c r="C39" s="242"/>
+      <c r="C39" s="245"/>
       <c r="N39" s="91"/>
     </row>
     <row r="40" spans="2:14" x14ac:dyDescent="0.2">
@@ -25104,7 +25075,7 @@
       </c>
       <c r="C41" s="137">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.10605494718970561</v>
+        <v>0.10404267046420979</v>
       </c>
     </row>
     <row r="42" spans="2:14" x14ac:dyDescent="0.2">
@@ -25130,7 +25101,7 @@
       </c>
       <c r="C44" s="24">
         <f ca="1">C43/(1+C41)^5</f>
-        <v>67244.928905866327</v>
+        <v>67859.984702436792</v>
       </c>
     </row>
     <row r="45" spans="2:14" x14ac:dyDescent="0.2">
@@ -25139,7 +25110,7 @@
       </c>
       <c r="C45" s="108">
         <f ca="1">SUM(H9:K9)+C44</f>
-        <v>72375.76872811433</v>
+        <v>73012.40290152622</v>
       </c>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.2">
@@ -25166,7 +25137,7 @@
       </c>
       <c r="C48" s="108">
         <f ca="1">C45+C46-C47</f>
-        <v>73254.76872811433</v>
+        <v>73891.40290152622</v>
       </c>
     </row>
     <row r="49" spans="2:3" x14ac:dyDescent="0.2">
@@ -25184,14 +25155,14 @@
       </c>
       <c r="C50" s="234">
         <f ca="1">C48/C49</f>
-        <v>348.83223203863969</v>
+        <v>351.86382334060107</v>
       </c>
     </row>
     <row r="52" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B52" s="242" t="s">
+      <c r="B52" s="245" t="s">
         <v>209</v>
       </c>
-      <c r="C52" s="242"/>
+      <c r="C52" s="245"/>
     </row>
     <row r="53" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B53" s="1" t="s">
@@ -25208,7 +25179,7 @@
       </c>
       <c r="C54" s="137">
         <f ca="1">IF(Overview!C29&gt;0,Overview!C29,WACC!C19)</f>
-        <v>0.1099815</v>
+        <v>0.1077105</v>
       </c>
     </row>
     <row r="55" spans="2:3" x14ac:dyDescent="0.2">
@@ -25243,14 +25214,14 @@
       </c>
       <c r="C58" s="234">
         <f ca="1">C57/(1+C54)^5</f>
-        <v>189.82347741565462</v>
+        <v>191.77732889949982</v>
       </c>
     </row>
     <row r="60" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B60" s="242" t="s">
+      <c r="B60" s="245" t="s">
         <v>321</v>
       </c>
-      <c r="C60" s="242"/>
+      <c r="C60" s="245"/>
     </row>
     <row r="61" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B61" s="1" t="s">
@@ -25267,7 +25238,7 @@
       </c>
       <c r="C62" s="137">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.10605494718970561</v>
+        <v>0.10404267046420979</v>
       </c>
     </row>
     <row r="63" spans="2:3" x14ac:dyDescent="0.2">
@@ -25293,7 +25264,7 @@
       </c>
       <c r="C65" s="24">
         <f ca="1">C64/(1+C62)^5</f>
-        <v>66919.735724860409</v>
+        <v>67531.817141738051</v>
       </c>
     </row>
     <row r="66" spans="2:3" x14ac:dyDescent="0.2">
@@ -25302,7 +25273,7 @@
       </c>
       <c r="C66" s="108">
         <f ca="1">SUM(H9:K9)+C65</f>
-        <v>72050.575547108412</v>
+        <v>72684.235340827479</v>
       </c>
     </row>
     <row r="67" spans="2:3" x14ac:dyDescent="0.2">
@@ -25329,7 +25300,7 @@
       </c>
       <c r="C69" s="108">
         <f ca="1">C66+C67-C68</f>
-        <v>72929.575547108412</v>
+        <v>73563.235340827479</v>
       </c>
     </row>
     <row r="70" spans="2:3" x14ac:dyDescent="0.2">
@@ -25347,14 +25318,14 @@
       </c>
       <c r="C71" s="234">
         <f ca="1">C69/C70</f>
-        <v>347.28369308146864</v>
+        <v>350.30112067060702</v>
       </c>
     </row>
     <row r="73" spans="2:3" x14ac:dyDescent="0.2">
-      <c r="B73" s="242" t="s">
+      <c r="B73" s="245" t="s">
         <v>379</v>
       </c>
-      <c r="C73" s="242"/>
+      <c r="C73" s="245"/>
     </row>
     <row r="74" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B74" s="1" t="s">
@@ -25371,7 +25342,7 @@
       </c>
       <c r="C75" s="137">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.10605494718970561</v>
+        <v>0.10404267046420979</v>
       </c>
     </row>
     <row r="76" spans="2:3" x14ac:dyDescent="0.2">
@@ -25397,7 +25368,7 @@
       </c>
       <c r="C78" s="24">
         <f ca="1">C77/(1+C75)^5</f>
-        <v>40431.053935706055</v>
+        <v>40800.856603196713</v>
       </c>
     </row>
     <row r="79" spans="2:3" x14ac:dyDescent="0.2">
@@ -25406,7 +25377,7 @@
       </c>
       <c r="C79" s="108">
         <f ca="1">SUM(H9:K9)+C78</f>
-        <v>45561.893757954058</v>
+        <v>45953.274802286141</v>
       </c>
     </row>
     <row r="80" spans="2:3" x14ac:dyDescent="0.2">
@@ -25433,7 +25404,7 @@
       </c>
       <c r="C82" s="108">
         <f ca="1">C79+C80-C81</f>
-        <v>46440.893757954058</v>
+        <v>46832.274802286141</v>
       </c>
     </row>
     <row r="83" spans="2:3" x14ac:dyDescent="0.2">
@@ -25451,7 +25422,7 @@
       </c>
       <c r="C84" s="234">
         <f ca="1">C82/C83</f>
-        <v>221.14711313311457</v>
+        <v>223.01083239183876</v>
       </c>
     </row>
   </sheetData>
@@ -25504,10 +25475,10 @@
       <c r="N3" s="91"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B4" s="242" t="s">
+      <c r="B4" s="245" t="s">
         <v>213</v>
       </c>
-      <c r="C4" s="242"/>
+      <c r="C4" s="245"/>
       <c r="N4" s="91"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
@@ -25516,7 +25487,7 @@
       </c>
       <c r="C5" s="135">
         <f ca="1">DCF!C26</f>
-        <v>119.63544251297965</v>
+        <v>122.59878263521894</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.2">
@@ -25525,7 +25496,7 @@
       </c>
       <c r="C6" s="135">
         <f ca="1">Multiples!C50</f>
-        <v>348.83223203863969</v>
+        <v>351.86382334060107</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.2">
@@ -25534,7 +25505,7 @@
       </c>
       <c r="C7" s="135">
         <f ca="1">Multiples!C58</f>
-        <v>189.82347741565462</v>
+        <v>191.77732889949982</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.2">
@@ -25543,7 +25514,7 @@
       </c>
       <c r="C8" s="135">
         <f ca="1">Multiples!C71</f>
-        <v>347.28369308146864</v>
+        <v>350.30112067060702</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
@@ -25552,7 +25523,7 @@
       </c>
       <c r="C9" s="135">
         <f ca="1">Multiples!C84</f>
-        <v>221.14711313311457</v>
+        <v>223.01083239183876</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
@@ -25561,7 +25532,7 @@
       </c>
       <c r="C10" s="234">
         <f ca="1">AVERAGE(C5:C9)</f>
-        <v>245.34439163637143</v>
+        <v>247.91037758755311</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -25570,7 +25541,7 @@
       </c>
       <c r="C11" s="135">
         <f ca="1">Overview!C5</f>
-        <v>244.07</v>
+        <v>252.2</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.2">
@@ -25579,7 +25550,7 @@
       </c>
       <c r="C12" s="154">
         <f ca="1">(C10-C11)/C11</f>
-        <v>5.221418594548422E-3</v>
+        <v>-1.7008812103278648E-2</v>
       </c>
     </row>
   </sheetData>
@@ -25674,37 +25645,37 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
-      <c r="C2" s="242" t="s">
+      <c r="C2" s="245" t="s">
         <v>112</v>
       </c>
-      <c r="D2" s="242"/>
-      <c r="E2" s="242"/>
-      <c r="F2" s="242"/>
-      <c r="G2" s="251"/>
-      <c r="H2" s="252" t="s">
+      <c r="D2" s="245"/>
+      <c r="E2" s="245"/>
+      <c r="F2" s="245"/>
+      <c r="G2" s="254"/>
+      <c r="H2" s="255" t="s">
         <v>113</v>
       </c>
-      <c r="I2" s="242"/>
-      <c r="J2" s="242"/>
-      <c r="K2" s="242"/>
-      <c r="L2" s="242"/>
+      <c r="I2" s="245"/>
+      <c r="J2" s="245"/>
+      <c r="K2" s="245"/>
+      <c r="L2" s="245"/>
     </row>
     <row r="3" spans="1:14" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="86"/>
       <c r="B4" s="60"/>
-      <c r="C4" s="248" t="s">
+      <c r="C4" s="251" t="s">
         <v>193</v>
       </c>
-      <c r="D4" s="248"/>
-      <c r="E4" s="248"/>
-      <c r="F4" s="248"/>
-      <c r="G4" s="248"/>
-      <c r="H4" s="248"/>
-      <c r="I4" s="248"/>
-      <c r="J4" s="248"/>
-      <c r="K4" s="248"/>
-      <c r="L4" s="248"/>
+      <c r="D4" s="251"/>
+      <c r="E4" s="251"/>
+      <c r="F4" s="251"/>
+      <c r="G4" s="251"/>
+      <c r="H4" s="251"/>
+      <c r="I4" s="251"/>
+      <c r="J4" s="251"/>
+      <c r="K4" s="251"/>
+      <c r="L4" s="251"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B5" s="16" t="s">
@@ -25817,18 +25788,18 @@
       <c r="N8" s="91"/>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C9" s="248" t="s">
+      <c r="C9" s="251" t="s">
         <v>121</v>
       </c>
-      <c r="D9" s="248"/>
-      <c r="E9" s="248"/>
-      <c r="F9" s="248"/>
-      <c r="G9" s="248"/>
-      <c r="H9" s="248"/>
-      <c r="I9" s="248"/>
-      <c r="J9" s="248"/>
-      <c r="K9" s="248"/>
-      <c r="L9" s="248"/>
+      <c r="D9" s="251"/>
+      <c r="E9" s="251"/>
+      <c r="F9" s="251"/>
+      <c r="G9" s="251"/>
+      <c r="H9" s="251"/>
+      <c r="I9" s="251"/>
+      <c r="J9" s="251"/>
+      <c r="K9" s="251"/>
+      <c r="L9" s="251"/>
       <c r="N9" s="91"/>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
@@ -25949,18 +25920,18 @@
       <c r="N13" s="91"/>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C14" s="248" t="s">
+      <c r="C14" s="251" t="s">
         <v>367</v>
       </c>
-      <c r="D14" s="248"/>
-      <c r="E14" s="248"/>
-      <c r="F14" s="248"/>
-      <c r="G14" s="248"/>
-      <c r="H14" s="248"/>
-      <c r="I14" s="248"/>
-      <c r="J14" s="248"/>
-      <c r="K14" s="248"/>
-      <c r="L14" s="248"/>
+      <c r="D14" s="251"/>
+      <c r="E14" s="251"/>
+      <c r="F14" s="251"/>
+      <c r="G14" s="251"/>
+      <c r="H14" s="251"/>
+      <c r="I14" s="251"/>
+      <c r="J14" s="251"/>
+      <c r="K14" s="251"/>
+      <c r="L14" s="251"/>
       <c r="N14" s="91"/>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.2">
@@ -26050,10 +26021,10 @@
       <c r="N19" s="91"/>
     </row>
     <row r="20" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B20" s="242" t="s">
+      <c r="B20" s="245" t="s">
         <v>369</v>
       </c>
-      <c r="C20" s="242"/>
+      <c r="C20" s="245"/>
       <c r="N20" s="91"/>
     </row>
     <row r="21" spans="2:14" x14ac:dyDescent="0.2">
@@ -26088,7 +26059,7 @@
       </c>
       <c r="C24" s="137">
         <f ca="1">IF(Overview!C29&gt;0,Overview!C29,WACC!C19)</f>
-        <v>0.1099815</v>
+        <v>0.1077105</v>
       </c>
     </row>
     <row r="25" spans="2:14" x14ac:dyDescent="0.2">
@@ -26154,60 +26125,60 @@
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A3" s="4"/>
-      <c r="C3" s="242" t="s">
+      <c r="C3" s="245" t="s">
         <v>112</v>
       </c>
-      <c r="D3" s="242"/>
-      <c r="E3" s="242"/>
-      <c r="F3" s="242"/>
-      <c r="G3" s="251"/>
-      <c r="H3" s="252" t="s">
+      <c r="D3" s="245"/>
+      <c r="E3" s="245"/>
+      <c r="F3" s="245"/>
+      <c r="G3" s="254"/>
+      <c r="H3" s="255" t="s">
         <v>113</v>
       </c>
-      <c r="I3" s="242"/>
-      <c r="J3" s="242"/>
-      <c r="K3" s="242"/>
-      <c r="L3" s="242"/>
-      <c r="P3" s="253"/>
-      <c r="Q3" s="253"/>
-      <c r="R3" s="253"/>
-      <c r="S3" s="253"/>
-      <c r="T3" s="253"/>
-      <c r="U3" s="253"/>
-      <c r="V3" s="253"/>
-      <c r="W3" s="253"/>
-      <c r="X3" s="253"/>
-      <c r="Y3" s="253"/>
-      <c r="Z3" s="253"/>
+      <c r="I3" s="245"/>
+      <c r="J3" s="245"/>
+      <c r="K3" s="245"/>
+      <c r="L3" s="245"/>
+      <c r="P3" s="256"/>
+      <c r="Q3" s="256"/>
+      <c r="R3" s="256"/>
+      <c r="S3" s="256"/>
+      <c r="T3" s="256"/>
+      <c r="U3" s="256"/>
+      <c r="V3" s="256"/>
+      <c r="W3" s="256"/>
+      <c r="X3" s="256"/>
+      <c r="Y3" s="256"/>
+      <c r="Z3" s="256"/>
       <c r="AB3" s="111"/>
     </row>
     <row r="4" spans="1:28" ht="10" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="5" spans="1:28" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="86"/>
       <c r="B5" s="60"/>
-      <c r="C5" s="248" t="s">
+      <c r="C5" s="251" t="s">
         <v>179</v>
       </c>
-      <c r="D5" s="248"/>
-      <c r="E5" s="248"/>
-      <c r="F5" s="248"/>
-      <c r="G5" s="248"/>
-      <c r="H5" s="248"/>
-      <c r="I5" s="248"/>
-      <c r="J5" s="248"/>
-      <c r="K5" s="248"/>
-      <c r="L5" s="248"/>
-      <c r="P5" s="253"/>
-      <c r="Q5" s="253"/>
-      <c r="R5" s="253"/>
-      <c r="S5" s="253"/>
-      <c r="T5" s="253"/>
-      <c r="U5" s="253"/>
-      <c r="V5" s="253"/>
-      <c r="W5" s="253"/>
-      <c r="X5" s="253"/>
-      <c r="Y5" s="253"/>
-      <c r="Z5" s="253"/>
+      <c r="D5" s="251"/>
+      <c r="E5" s="251"/>
+      <c r="F5" s="251"/>
+      <c r="G5" s="251"/>
+      <c r="H5" s="251"/>
+      <c r="I5" s="251"/>
+      <c r="J5" s="251"/>
+      <c r="K5" s="251"/>
+      <c r="L5" s="251"/>
+      <c r="P5" s="256"/>
+      <c r="Q5" s="256"/>
+      <c r="R5" s="256"/>
+      <c r="S5" s="256"/>
+      <c r="T5" s="256"/>
+      <c r="U5" s="256"/>
+      <c r="V5" s="256"/>
+      <c r="W5" s="256"/>
+      <c r="X5" s="256"/>
+      <c r="Y5" s="256"/>
+      <c r="Z5" s="256"/>
       <c r="AB5" s="112"/>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.2">
@@ -26342,7 +26313,7 @@
       <c r="K8" s="139"/>
       <c r="L8" s="128">
         <f ca="1">L7*(1+C20)/(C21-C20)</f>
-        <v>67410.832828727333</v>
+        <v>69024.884942948338</v>
       </c>
       <c r="N8" s="91"/>
       <c r="O8" s="16"/>
@@ -26396,23 +26367,23 @@
       <c r="G10" s="140"/>
       <c r="H10" s="128">
         <f ca="1">H7/(1+$C$21)^H9</f>
-        <v>989.0559764232047</v>
+        <v>990.85867334318175</v>
       </c>
       <c r="I10" s="128">
         <f t="shared" ref="I10:L10" ca="1" si="1">I7/(1+$C$21)^I9</f>
-        <v>1350.2715468103097</v>
+        <v>1355.1981610630216</v>
       </c>
       <c r="J10" s="128">
         <f t="shared" ca="1" si="1"/>
-        <v>1843.4075457680337</v>
+        <v>1853.5055554915716</v>
       </c>
       <c r="K10" s="128">
         <f t="shared" ca="1" si="1"/>
-        <v>2516.6429580937534</v>
+        <v>2535.0409578059903</v>
       </c>
       <c r="L10" s="128">
         <f t="shared" ca="1" si="1"/>
-        <v>3435.7523343456337</v>
+        <v>3467.1774458477657</v>
       </c>
       <c r="N10" s="91"/>
     </row>
@@ -26431,15 +26402,15 @@
       <c r="K11" s="139"/>
       <c r="L11" s="128">
         <f ca="1">L8/(1+C21)^L9</f>
-        <v>40723.601553168715</v>
+        <v>42080.064510453361</v>
       </c>
     </row>
     <row r="13" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B14" s="255" t="s">
+      <c r="B14" s="258" t="s">
         <v>221</v>
       </c>
-      <c r="C14" s="256"/>
+      <c r="C14" s="259"/>
     </row>
     <row r="15" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B15" s="155" t="s">
@@ -26447,7 +26418,7 @@
       </c>
       <c r="C15" s="156">
         <f ca="1">Overview!C5</f>
-        <v>244.07</v>
+        <v>252.2</v>
       </c>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.2">
@@ -26456,7 +26427,7 @@
       </c>
       <c r="C16" s="156">
         <f ca="1">C36</f>
-        <v>247.54895652923278</v>
+        <v>254.35811150241574</v>
       </c>
     </row>
     <row r="17" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -26466,20 +26437,20 @@
       <c r="C17" s="158">
         <v>0.51</v>
       </c>
-      <c r="E17" s="254" t="s">
+      <c r="E17" s="257" t="s">
         <v>224</v>
       </c>
-      <c r="F17" s="254"/>
-      <c r="G17" s="254"/>
-      <c r="H17" s="254"/>
-      <c r="I17" s="254"/>
+      <c r="F17" s="257"/>
+      <c r="G17" s="257"/>
+      <c r="H17" s="257"/>
+      <c r="I17" s="257"/>
     </row>
     <row r="18" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="19" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B19" s="255" t="s">
+      <c r="B19" s="258" t="s">
         <v>183</v>
       </c>
-      <c r="C19" s="256"/>
+      <c r="C19" s="259"/>
     </row>
     <row r="20" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B20" s="159" t="s">
@@ -26495,7 +26466,7 @@
       </c>
       <c r="C21" s="220">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.10605494718970561</v>
+        <v>0.10404267046420979</v>
       </c>
     </row>
     <row r="22" spans="2:9" x14ac:dyDescent="0.2">
@@ -26513,7 +26484,7 @@
       </c>
       <c r="C23" s="161">
         <f ca="1">C15*C22</f>
-        <v>51010.63</v>
+        <v>52709.799999999996</v>
       </c>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.2">
@@ -26540,15 +26511,15 @@
       </c>
       <c r="C26" s="162">
         <f ca="1">C23+C25-C24</f>
-        <v>50131.63</v>
+        <v>51830.799999999996</v>
       </c>
     </row>
     <row r="27" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B28" s="255" t="s">
+      <c r="B28" s="258" t="s">
         <v>185</v>
       </c>
-      <c r="C28" s="256"/>
+      <c r="C28" s="259"/>
     </row>
     <row r="29" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B29" s="159" t="s">
@@ -26556,7 +26527,7 @@
       </c>
       <c r="C29" s="161">
         <f ca="1">SUM(H10:L10)</f>
-        <v>10135.130361440935</v>
+        <v>10201.78079355153</v>
       </c>
     </row>
     <row r="30" spans="2:9" x14ac:dyDescent="0.2">
@@ -26565,7 +26536,7 @@
       </c>
       <c r="C30" s="161">
         <f ca="1">L11</f>
-        <v>40723.601553168715</v>
+        <v>42080.064510453361</v>
       </c>
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.2">
@@ -26574,7 +26545,7 @@
       </c>
       <c r="C31" s="164">
         <f ca="1">C29+C30</f>
-        <v>50858.731914609649</v>
+        <v>52281.845304004892</v>
       </c>
     </row>
     <row r="32" spans="2:9" x14ac:dyDescent="0.2">
@@ -26601,7 +26572,7 @@
       </c>
       <c r="C34" s="164">
         <f ca="1">C31+C32-C33</f>
-        <v>51737.731914609649</v>
+        <v>53160.845304004892</v>
       </c>
     </row>
     <row r="35" spans="2:3" x14ac:dyDescent="0.2">
@@ -26619,7 +26590,7 @@
       </c>
       <c r="C36" s="167">
         <f ca="1">C34/C35</f>
-        <v>247.54895652923278</v>
+        <v>254.35811150241574</v>
       </c>
     </row>
   </sheetData>
@@ -33289,7 +33260,7 @@
       </c>
       <c r="AC117" s="63">
         <f ca="1">Overview!C5</f>
-        <v>244.07</v>
+        <v>252.2</v>
       </c>
     </row>
     <row r="118" spans="1:31" x14ac:dyDescent="0.2">
@@ -33360,7 +33331,7 @@
       </c>
       <c r="AC118" s="65">
         <f ca="1">AC117/AC86</f>
-        <v>244.07</v>
+        <v>252.2</v>
       </c>
     </row>
     <row r="120" spans="1:31" x14ac:dyDescent="0.2">
@@ -34666,7 +34637,7 @@
       <c r="AA151" s="49"/>
       <c r="AC151" s="72">
         <f ca="1">AC118/Statement!AC27</f>
-        <v>31.574385510996116</v>
+        <v>32.626131953428199</v>
       </c>
     </row>
     <row r="152" spans="2:29" x14ac:dyDescent="0.2">
@@ -34703,7 +34674,7 @@
       <c r="AA152" s="49"/>
       <c r="AC152" s="72">
         <f ca="1">AC118/(Statement!AC5/Statement!AC23)</f>
-        <v>6.6735442875481388</v>
+        <v>6.8958408215661109</v>
       </c>
     </row>
     <row r="153" spans="2:29" x14ac:dyDescent="0.2">
@@ -34764,7 +34735,7 @@
       </c>
       <c r="AC153" s="72">
         <f ca="1">AC118/(Statement!AC50/Statement!AC76)</f>
-        <v>15.078519065917822</v>
+        <v>15.58078628436299</v>
       </c>
     </row>
     <row r="154" spans="2:29" x14ac:dyDescent="0.2">
@@ -34825,7 +34796,7 @@
       </c>
       <c r="AC154" s="143">
         <f ca="1">Statement!AC118*Statement!AC79</f>
-        <v>51254.7</v>
+        <v>52962</v>
       </c>
     </row>
     <row r="155" spans="2:29" x14ac:dyDescent="0.2">
@@ -34886,7 +34857,7 @@
       </c>
       <c r="AC155" s="143">
         <f ca="1">AC154+AC109-AC108+AC49+AC46</f>
-        <v>50375.7</v>
+        <v>52083</v>
       </c>
     </row>
     <row r="156" spans="2:29" x14ac:dyDescent="0.2">
@@ -34923,7 +34894,7 @@
       <c r="AA156" s="49"/>
       <c r="AC156" s="181">
         <f ca="1">AC155/AC5</f>
-        <v>6.4667137355584074</v>
+        <v>6.6858793324775352</v>
       </c>
     </row>
     <row r="157" spans="2:29" x14ac:dyDescent="0.2">
@@ -34960,7 +34931,7 @@
       <c r="AA157" s="49"/>
       <c r="AC157" s="181">
         <f ca="1">AC155/AC13</f>
-        <v>24.681871631553157</v>
+        <v>25.518373346398825</v>
       </c>
     </row>
     <row r="158" spans="2:29" x14ac:dyDescent="0.2">
@@ -35095,7 +35066,7 @@
       <c r="AA160" s="49"/>
       <c r="AC160" s="72">
         <f t="shared" ref="AC160:AC161" ca="1" si="155">AC154/AC158</f>
-        <v>24.430266920877024</v>
+        <v>25.244041944709245</v>
       </c>
     </row>
     <row r="161" spans="2:29" x14ac:dyDescent="0.2">
@@ -35132,7 +35103,7 @@
       <c r="AA161" s="49"/>
       <c r="AC161" s="72">
         <f t="shared" ca="1" si="155"/>
-        <v>41.424763129911916</v>
+        <v>42.828703880942641</v>
       </c>
     </row>
     <row r="162" spans="2:29" x14ac:dyDescent="0.2">
@@ -35169,7 +35140,7 @@
       <c r="AA162" s="49"/>
       <c r="AC162" s="74">
         <f t="shared" ref="AC162" ca="1" si="158">AC158/AC154</f>
-        <v>4.0932831525694234E-2</v>
+        <v>3.9613307654544766E-2</v>
       </c>
     </row>
     <row r="163" spans="2:29" x14ac:dyDescent="0.2">
@@ -35206,7 +35177,7 @@
       <c r="AA163" s="49"/>
       <c r="AC163" s="74">
         <f ca="1">AC27/AC118</f>
-        <v>3.1671241856844348E-2</v>
+        <v>3.0650277557494054E-2</v>
       </c>
     </row>
     <row r="164" spans="2:29" x14ac:dyDescent="0.2">
@@ -35280,7 +35251,7 @@
       <c r="AA165" s="49"/>
       <c r="AC165" s="154">
         <f ca="1">-AC64/AC154</f>
-        <v>3.104105574708271E-2</v>
+        <v>3.0040406329066124E-2</v>
       </c>
     </row>
     <row r="166" spans="2:29" x14ac:dyDescent="0.2">
@@ -35317,7 +35288,7 @@
       <c r="AA166" s="49"/>
       <c r="AC166" s="154">
         <f ca="1">-(AC64+AC65)/AC154</f>
-        <v>3.104105574708271E-2</v>
+        <v>3.0040406329066124E-2</v>
       </c>
     </row>
     <row r="167" spans="2:29" x14ac:dyDescent="0.2">
@@ -35820,7 +35791,7 @@
       <c r="AA177" s="49"/>
       <c r="AC177" s="154">
         <f ca="1">(AC108-AC109)/AC154</f>
-        <v>1.7149646764101634E-2</v>
+        <v>1.6596805256599071E-2</v>
       </c>
     </row>
     <row r="178" spans="1:31" x14ac:dyDescent="0.2">
@@ -37654,15 +37625,15 @@
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B4" s="242" t="s">
+      <c r="B4" s="245" t="s">
         <v>232</v>
       </c>
-      <c r="C4" s="242"/>
-      <c r="E4" s="242" t="s">
+      <c r="C4" s="245"/>
+      <c r="E4" s="245" t="s">
         <v>239</v>
       </c>
-      <c r="F4" s="242"/>
-      <c r="G4" s="242"/>
+      <c r="F4" s="245"/>
+      <c r="G4" s="245"/>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B5" s="20" t="s">
@@ -37670,7 +37641,7 @@
       </c>
       <c r="C5" s="170">
         <f ca="1">Overview!C5</f>
-        <v>244.07</v>
+        <v>252.2</v>
       </c>
       <c r="E5" s="12"/>
       <c r="F5" s="134" t="s">
@@ -37686,7 +37657,7 @@
       </c>
       <c r="C6" s="171">
         <f ca="1">Statement!AC154</f>
-        <v>51254.7</v>
+        <v>52962</v>
       </c>
       <c r="E6" s="20" t="s">
         <v>19</v>
@@ -37706,7 +37677,7 @@
       </c>
       <c r="C7" s="171">
         <f ca="1">Statement!AC155</f>
-        <v>50375.7</v>
+        <v>52083</v>
       </c>
       <c r="E7" s="20" t="s">
         <v>31</v>
@@ -37726,7 +37697,7 @@
       </c>
       <c r="C8" s="172">
         <f ca="1">Statement!AC151</f>
-        <v>31.574385510996116</v>
+        <v>32.626131953428199</v>
       </c>
       <c r="E8" s="20" t="s">
         <v>242</v>
@@ -37746,7 +37717,7 @@
       </c>
       <c r="C9" s="172">
         <f ca="1">Statement!AC152</f>
-        <v>6.6735442875481388</v>
+        <v>6.8958408215661109</v>
       </c>
       <c r="E9" s="20" t="s">
         <v>243</v>
@@ -37766,7 +37737,7 @@
       </c>
       <c r="C10" s="172">
         <f ca="1">Statement!AC153</f>
-        <v>15.078519065917822</v>
+        <v>15.58078628436299</v>
       </c>
       <c r="E10" s="20" t="s">
         <v>1</v>
@@ -37786,7 +37757,7 @@
       </c>
       <c r="C11" s="172">
         <f ca="1">Statement!AC156</f>
-        <v>6.4667137355584074</v>
+        <v>6.6858793324775352</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
@@ -37795,18 +37766,18 @@
       </c>
       <c r="C12" s="172">
         <f ca="1">Statement!AC157</f>
-        <v>24.681871631553157</v>
+        <v>25.518373346398825</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B15" s="242" t="s">
+      <c r="B15" s="245" t="s">
         <v>77</v>
       </c>
-      <c r="C15" s="242"/>
-      <c r="E15" s="242" t="s">
+      <c r="C15" s="245"/>
+      <c r="E15" s="245" t="s">
         <v>245</v>
       </c>
-      <c r="F15" s="242"/>
+      <c r="F15" s="245"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="20" t="s">
@@ -37857,14 +37828,14 @@
       </c>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B21" s="242" t="s">
+      <c r="B21" s="245" t="s">
         <v>244</v>
       </c>
-      <c r="C21" s="242"/>
-      <c r="E21" s="242" t="s">
+      <c r="C21" s="245"/>
+      <c r="E21" s="245" t="s">
         <v>248</v>
       </c>
-      <c r="F21" s="242"/>
+      <c r="F21" s="245"/>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B22" s="20" t="s">
@@ -37933,14 +37904,14 @@
       </c>
     </row>
     <row r="29" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B29" s="242" t="s">
+      <c r="B29" s="245" t="s">
         <v>249</v>
       </c>
-      <c r="C29" s="242"/>
-      <c r="E29" s="242" t="s">
+      <c r="C29" s="245"/>
+      <c r="E29" s="245" t="s">
         <v>255</v>
       </c>
-      <c r="F29" s="242"/>
+      <c r="F29" s="245"/>
     </row>
     <row r="30" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B30" s="20" t="s">
@@ -38016,14 +37987,14 @@
       </c>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B37" s="242" t="s">
+      <c r="B37" s="245" t="s">
         <v>267</v>
       </c>
-      <c r="C37" s="242"/>
-      <c r="E37" s="242" t="s">
+      <c r="C37" s="245"/>
+      <c r="E37" s="245" t="s">
         <v>270</v>
       </c>
-      <c r="F37" s="242"/>
+      <c r="F37" s="245"/>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B38" s="20" t="s">
@@ -38031,7 +38002,7 @@
       </c>
       <c r="C38" s="173">
         <f ca="1">Statement!AC163</f>
-        <v>3.1671241856844348E-2</v>
+        <v>3.0650277557494054E-2</v>
       </c>
       <c r="E38" s="20" t="s">
         <v>269</v>
@@ -38047,7 +38018,7 @@
       </c>
       <c r="C39" s="213">
         <f ca="1">Statement!AC162</f>
-        <v>4.0932831525694234E-2</v>
+        <v>3.9613307654544766E-2</v>
       </c>
       <c r="E39" s="20" t="s">
         <v>271</v>
@@ -38079,7 +38050,7 @@
       </c>
       <c r="C41" s="173">
         <f ca="1">Statement!AC165</f>
-        <v>3.104105574708271E-2</v>
+        <v>3.0040406329066124E-2</v>
       </c>
     </row>
     <row r="42" spans="2:6" x14ac:dyDescent="0.2">
@@ -38088,18 +38059,18 @@
       </c>
       <c r="C42" s="173">
         <f ca="1">Statement!AC166</f>
-        <v>3.104105574708271E-2</v>
+        <v>3.0040406329066124E-2</v>
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B45" s="242" t="s">
+      <c r="B45" s="245" t="s">
         <v>278</v>
       </c>
-      <c r="C45" s="242"/>
-      <c r="E45" s="242" t="s">
+      <c r="C45" s="245"/>
+      <c r="E45" s="245" t="s">
         <v>284</v>
       </c>
-      <c r="F45" s="242"/>
+      <c r="F45" s="245"/>
     </row>
     <row r="46" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B46" s="20" t="s">
@@ -38132,18 +38103,18 @@
       </c>
       <c r="F48" s="173">
         <f ca="1">Statement!AC177</f>
-        <v>1.7149646764101634E-2</v>
+        <v>1.6596805256599071E-2</v>
       </c>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B51" s="242" t="s">
+      <c r="B51" s="245" t="s">
         <v>281</v>
       </c>
-      <c r="C51" s="242"/>
-      <c r="E51" s="242" t="s">
+      <c r="C51" s="245"/>
+      <c r="E51" s="245" t="s">
         <v>302</v>
       </c>
-      <c r="F51" s="242"/>
+      <c r="F51" s="245"/>
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B52" s="20" t="s">
@@ -38311,7 +38282,7 @@
       </c>
       <c r="I6" s="170">
         <f ca="1">Statement!AC117</f>
-        <v>244.07</v>
+        <v>252.2</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -38340,7 +38311,7 @@
       </c>
       <c r="I7" s="171">
         <f ca="1">Statement!AC154</f>
-        <v>51254.7</v>
+        <v>52962</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
@@ -38369,7 +38340,7 @@
       </c>
       <c r="I8" s="171">
         <f ca="1">Statement!AC155</f>
-        <v>50375.7</v>
+        <v>52083</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -38398,7 +38369,7 @@
       </c>
       <c r="I9" s="172">
         <f ca="1">Statement!AC151</f>
-        <v>31.574385510996116</v>
+        <v>32.626131953428199</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -38427,7 +38398,7 @@
       </c>
       <c r="I10" s="172">
         <f ca="1">Statement!AC152</f>
-        <v>6.6735442875481388</v>
+        <v>6.8958408215661109</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -38456,7 +38427,7 @@
       </c>
       <c r="I11" s="172">
         <f ca="1">Statement!AC153</f>
-        <v>15.078519065917822</v>
+        <v>15.58078628436299</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
@@ -38485,7 +38456,7 @@
       </c>
       <c r="I12" s="172">
         <f ca="1">Statement!AC156</f>
-        <v>6.4667137355584074</v>
+        <v>6.6858793324775352</v>
       </c>
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.2">
@@ -38514,7 +38485,7 @@
       </c>
       <c r="I13" s="172">
         <f ca="1">Statement!AC157</f>
-        <v>24.681871631553157</v>
+        <v>25.518373346398825</v>
       </c>
     </row>
     <row r="15" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -39287,7 +39258,7 @@
       </c>
       <c r="I51" s="173">
         <f ca="1">Statement!AC163</f>
-        <v>3.1671241856844348E-2</v>
+        <v>3.0650277557494054E-2</v>
       </c>
     </row>
     <row r="52" spans="2:9" x14ac:dyDescent="0.2">
@@ -39316,7 +39287,7 @@
       </c>
       <c r="I52" s="173">
         <f ca="1">Statement!AC162</f>
-        <v>4.0932831525694234E-2</v>
+        <v>3.9613307654544766E-2</v>
       </c>
     </row>
     <row r="53" spans="2:9" x14ac:dyDescent="0.2">
@@ -39374,7 +39345,7 @@
       </c>
       <c r="I54" s="173">
         <f ca="1">Statement!AC165</f>
-        <v>3.104105574708271E-2</v>
+        <v>3.0040406329066124E-2</v>
       </c>
     </row>
     <row r="55" spans="2:9" x14ac:dyDescent="0.2">
@@ -39403,7 +39374,7 @@
       </c>
       <c r="I55" s="173">
         <f ca="1">Statement!AC166</f>
-        <v>3.104105574708271E-2</v>
+        <v>3.0040406329066124E-2</v>
       </c>
     </row>
     <row r="57" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -39639,7 +39610,7 @@
       </c>
       <c r="I68" s="194">
         <f ca="1">Statement!AC177</f>
-        <v>1.7149646764101634E-2</v>
+        <v>1.6596805256599071E-2</v>
       </c>
     </row>
     <row r="70" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -40101,14 +40072,14 @@
     <row r="1" spans="2:7" ht="12" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="3" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B3" s="8"/>
-      <c r="C3" s="245" t="s">
+      <c r="C3" s="248" t="s">
         <v>312</v>
       </c>
-      <c r="D3" s="246"/>
-      <c r="F3" s="247" t="s">
+      <c r="D3" s="249"/>
+      <c r="F3" s="250" t="s">
         <v>313</v>
       </c>
-      <c r="G3" s="246"/>
+      <c r="G3" s="249"/>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B4" s="8"/>
@@ -40175,19 +40146,19 @@
       <c r="B7" s="204" t="s">
         <v>314</v>
       </c>
-      <c r="C7" s="243">
+      <c r="C7" s="246">
         <f>Statement!AA90</f>
         <v>5.7911065149948295E-2</v>
       </c>
-      <c r="D7" s="244"/>
-      <c r="F7" s="243">
+      <c r="D7" s="247"/>
+      <c r="F7" s="246">
         <f>IF(F6=0,
 IF(G6=0,0,IF(G6&gt;0,1,-1)),
 (G6-F6)/ABS(F6)
 )</f>
         <v>0.1605218377765173</v>
       </c>
-      <c r="G7" s="244"/>
+      <c r="G7" s="247"/>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B8" s="205" t="s">
@@ -40214,19 +40185,19 @@
       <c r="B9" s="204" t="s">
         <v>314</v>
       </c>
-      <c r="C9" s="243">
+      <c r="C9" s="246">
         <f>Statement!AA91</f>
         <v>5.7142857142857143E-3</v>
       </c>
-      <c r="D9" s="244"/>
-      <c r="F9" s="243">
+      <c r="D9" s="247"/>
+      <c r="F9" s="246">
         <f>IF(F8=0,
 IF(G8=0,0,IF(G8&gt;0,1,-1)),
 (G8-F8)/ABS(F8)
 )</f>
         <v>0.1069182389937107</v>
       </c>
-      <c r="G9" s="244"/>
+      <c r="G9" s="247"/>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B10" s="205" t="s">
@@ -40253,19 +40224,19 @@
       <c r="B11" s="204" t="s">
         <v>314</v>
       </c>
-      <c r="C11" s="243">
+      <c r="C11" s="246">
         <f>Statement!AA92</f>
         <v>6.3104036384309267E-2</v>
       </c>
-      <c r="D11" s="244"/>
-      <c r="F11" s="243">
+      <c r="D11" s="247"/>
+      <c r="F11" s="246">
         <f>IF(F10=0,
 IF(G10=0,0,IF(G10&gt;0,1,-1)),
 (G10-F10)/ABS(F10)
 )</f>
         <v>0.16583541147132169</v>
       </c>
-      <c r="G11" s="244"/>
+      <c r="G11" s="247"/>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B12" s="205" t="s">
@@ -40292,19 +40263,19 @@
       <c r="B13" s="204" t="s">
         <v>314</v>
       </c>
-      <c r="C13" s="243">
+      <c r="C13" s="246">
         <f>Statement!AA96</f>
         <v>4.3513957307060758E-2</v>
       </c>
-      <c r="D13" s="244"/>
-      <c r="F13" s="243">
+      <c r="D13" s="247"/>
+      <c r="F13" s="246">
         <f>IF(F12=0,
 IF(G12=0,0,IF(G12&gt;0,1,-1)),
 (G12-F12)/ABS(F12)
 )</f>
         <v>9.568965517241379E-2</v>
       </c>
-      <c r="G13" s="244"/>
+      <c r="G13" s="247"/>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B14" s="205" t="s">
@@ -40331,19 +40302,19 @@
       <c r="B15" s="204" t="s">
         <v>314</v>
       </c>
-      <c r="C15" s="243">
+      <c r="C15" s="246">
         <f>Statement!AA97</f>
         <v>0.10720887245841035</v>
       </c>
-      <c r="D15" s="244"/>
-      <c r="F15" s="243">
+      <c r="D15" s="247"/>
+      <c r="F15" s="246">
         <f>IF(F14=0,
 IF(G14=0,0,IF(G14&gt;0,1,-1)),
 (G14-F14)/ABS(F14)
 )</f>
         <v>0.34909909909909909</v>
       </c>
-      <c r="G15" s="244"/>
+      <c r="G15" s="247"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="205" t="s">
@@ -40370,19 +40341,19 @@
       <c r="B17" s="204" t="s">
         <v>314</v>
       </c>
-      <c r="C17" s="243">
+      <c r="C17" s="246">
         <f>Statement!AA99</f>
         <v>2.0366598778004071E-3</v>
       </c>
-      <c r="D17" s="244"/>
-      <c r="F17" s="243">
+      <c r="D17" s="247"/>
+      <c r="F17" s="246">
         <f>IF(F16=0,
 IF(G16=0,0,IF(G16&gt;0,1,-1)),
 (G16-F16)/ABS(F16)
 )</f>
         <v>0.5718849840255591</v>
       </c>
-      <c r="G17" s="244"/>
+      <c r="G17" s="247"/>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B18" s="205" t="s">
@@ -40409,22 +40380,22 @@
       <c r="B19" s="204" t="s">
         <v>314</v>
       </c>
-      <c r="C19" s="243">
+      <c r="C19" s="246">
         <f>IF(C18=0,
 IF(D18=0,0,IF(D18&gt;0,1,-1)),
 (D18-C18)/ABS(C18)
 )</f>
         <v>-4.7169811320754715E-3</v>
       </c>
-      <c r="D19" s="244"/>
-      <c r="F19" s="243">
+      <c r="D19" s="247"/>
+      <c r="F19" s="246">
         <f>IF(F18=0,
 IF(G18=0,0,IF(G18&gt;0,1,-1)),
 (G18-F18)/ABS(F18)
 )</f>
         <v>-1.8604651162790697E-2</v>
       </c>
-      <c r="G19" s="244"/>
+      <c r="G19" s="247"/>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B20" s="205" t="s">
@@ -40451,22 +40422,22 @@
       <c r="B21" s="204" t="s">
         <v>314</v>
       </c>
-      <c r="C21" s="243">
+      <c r="C21" s="246">
         <f>IF(C20=0,
 IF(D20=0,0,IF(D20&gt;0,1,-1)),
 (D20-C20)/ABS(C20)
 )</f>
         <v>4.3103448275863066E-3</v>
       </c>
-      <c r="D21" s="244"/>
-      <c r="F21" s="243">
+      <c r="D21" s="247"/>
+      <c r="F21" s="246">
         <f>IF(F20=0,
 IF(G20=0,0,IF(G20&gt;0,1,-1)),
 (G20-F20)/ABS(F20)
 )</f>
         <v>0.59589041095890416</v>
       </c>
-      <c r="G21" s="244"/>
+      <c r="G21" s="247"/>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B23" s="8" t="s">
@@ -40515,22 +40486,22 @@
       <c r="B25" s="204" t="s">
         <v>314</v>
       </c>
-      <c r="C25" s="243">
+      <c r="C25" s="246">
         <f>IF(C24=0,
 IF(D24=0,0,IF(D24&gt;0,1,-1)),
 (D24-C24)/ABS(C24)
 )</f>
         <v>6.3180827886710242E-2</v>
       </c>
-      <c r="D25" s="244"/>
-      <c r="F25" s="243">
+      <c r="D25" s="247"/>
+      <c r="F25" s="246">
         <f>IF(F24=0,
 IF(G24=0,0,IF(G24&gt;0,1,-1)),
 (G24-F24)/ABS(F24)
 )</f>
         <v>0.17096580683863227</v>
       </c>
-      <c r="G25" s="244"/>
+      <c r="G25" s="247"/>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B26" s="20" t="str">
@@ -40558,22 +40529,22 @@
       <c r="B27" s="204" t="s">
         <v>314</v>
       </c>
-      <c r="C27" s="243">
+      <c r="C27" s="246">
         <f>IF(C26=0,
 IF(D26=0,0,IF(D26&gt;0,1,-1)),
 (D26-C26)/ABS(C26)
 )</f>
         <v>-4.0816326530612242E-2</v>
       </c>
-      <c r="D27" s="244"/>
-      <c r="F27" s="243">
+      <c r="D27" s="247"/>
+      <c r="F27" s="246">
         <f>IF(F26=0,
 IF(G26=0,0,IF(G26&gt;0,1,-1)),
 (G26-F26)/ABS(F26)
 )</f>
         <v>-2.0833333333333332E-2</v>
       </c>
-      <c r="G27" s="244"/>
+      <c r="G27" s="247"/>
     </row>
     <row r="29" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B29" s="205" t="str">
@@ -40601,22 +40572,22 @@
       <c r="B30" s="204" t="s">
         <v>314</v>
       </c>
-      <c r="C30" s="243">
+      <c r="C30" s="246">
         <f>IF(C29=0,
 IF(D29=0,0,IF(D29&gt;0,1,-1)),
 (D29-C29)/ABS(C29)
 )</f>
         <v>6.0824742268041236E-2</v>
       </c>
-      <c r="D30" s="244"/>
-      <c r="F30" s="243">
+      <c r="D30" s="247"/>
+      <c r="F30" s="246">
         <f>IF(F29=0,
 IF(G29=0,0,IF(G29&gt;0,1,-1)),
 (G29-F29)/ABS(F29)
 )</f>
         <v>0.17198177676537585</v>
       </c>
-      <c r="G30" s="244"/>
+      <c r="G30" s="247"/>
     </row>
     <row r="31" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B31" s="20" t="str">
@@ -40644,22 +40615,22 @@
       <c r="B32" s="204" t="s">
         <v>314</v>
       </c>
-      <c r="C32" s="243">
+      <c r="C32" s="246">
         <f>IF(C31=0,
 IF(D31=0,0,IF(D31&gt;0,1,-1)),
 (D31-C31)/ABS(C31)
 )</f>
         <v>5.4852320675105488E-2</v>
       </c>
-      <c r="D32" s="244"/>
-      <c r="F32" s="243">
+      <c r="D32" s="247"/>
+      <c r="F32" s="246">
         <f>IF(F31=0,
 IF(G31=0,0,IF(G31&gt;0,1,-1)),
 (G31-F31)/ABS(F31)
 )</f>
         <v>0.13636363636363635</v>
       </c>
-      <c r="G32" s="244"/>
+      <c r="G32" s="247"/>
     </row>
     <row r="33" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B33" s="20" t="str">
@@ -40687,22 +40658,22 @@
       <c r="B34" s="204" t="s">
         <v>314</v>
       </c>
-      <c r="C34" s="243">
+      <c r="C34" s="246">
         <f>IF(C33=0,
 IF(D33=0,0,IF(D33&gt;0,1,-1)),
 (D33-C33)/ABS(C33)
 )</f>
         <v>4.9046321525885561E-2</v>
       </c>
-      <c r="D34" s="244"/>
-      <c r="F34" s="243">
+      <c r="D34" s="247"/>
+      <c r="F34" s="246">
         <f>IF(F33=0,
 IF(G33=0,0,IF(G33&gt;0,1,-1)),
 (G33-F33)/ABS(F33)
 )</f>
         <v>0.15269461077844312</v>
       </c>
-      <c r="G34" s="244"/>
+      <c r="G34" s="247"/>
     </row>
     <row r="35" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B35" s="20" t="str">
@@ -40730,22 +40701,22 @@
       <c r="B36" s="204" t="s">
         <v>314</v>
       </c>
-      <c r="C36" s="243">
+      <c r="C36" s="246">
         <f>IF(C35=0,
 IF(D35=0,0,IF(D35&gt;0,1,-1)),
 (D35-C35)/ABS(C35)
 )</f>
         <v>6.9767441860465115E-2</v>
       </c>
-      <c r="D36" s="244"/>
-      <c r="F36" s="243">
+      <c r="D36" s="247"/>
+      <c r="F36" s="246">
         <f>IF(F35=0,
 IF(G35=0,0,IF(G35&gt;0,1,-1)),
 (G35-F35)/ABS(F35)
 )</f>
         <v>0.15</v>
       </c>
-      <c r="G36" s="244"/>
+      <c r="G36" s="247"/>
     </row>
     <row r="37" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B37" s="20" t="str">
@@ -40773,22 +40744,22 @@
       <c r="B38" s="204" t="s">
         <v>314</v>
       </c>
-      <c r="C38" s="243">
+      <c r="C38" s="246">
         <f>IF(C37=0,
 IF(D37=0,0,IF(D37&gt;0,1,-1)),
 (D37-C37)/ABS(C37)
 )</f>
         <v>8.1081081081081086E-2</v>
       </c>
-      <c r="D38" s="244"/>
-      <c r="F38" s="243">
+      <c r="D38" s="247"/>
+      <c r="F38" s="246">
         <f>IF(F37=0,
 IF(G37=0,0,IF(G37&gt;0,1,-1)),
 (G37-F37)/ABS(F37)
 )</f>
         <v>0.29032258064516131</v>
       </c>
-      <c r="G38" s="244"/>
+      <c r="G38" s="247"/>
     </row>
   </sheetData>
   <mergeCells count="32">

--- a/ADSK.xlsx
+++ b/ADSK.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7EED8353-4B1C-CE46-A69F-1FA38B10EE76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F5DF0EA-482D-4B4B-A086-2245244E0EEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
@@ -2463,14 +2463,14 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -15192,11 +15192,11 @@
     <v>Powered by Refinitiv</v>
     <v>320</v>
     <v>185.5</v>
-    <v>1.2928999999999999</v>
+    <v>1.2835000000000001</v>
     <v>-2.75</v>
-    <v>-1.0786E-2</v>
-    <v>0</v>
-    <v>0</v>
+    <v>-1.0904E-2</v>
+    <v>0.22</v>
+    <v>8.8190000000000002E-4</v>
     <v>USD</v>
     <v>Autodesk, Inc. is engaged in three-dimensional (3D) design, engineering and entertainment technology solutions, spanning architecture, engineering, construction, product design, manufacturing, media and entertainment. Its architecture, engineering, construction and operations products improve the way building, infrastructure, and industrial projects are designed, built, and operated. Its product development and manufacturing software provides manufacturers in the automotive, transportation, industrial machinery, consumer products, and building product industries with comprehensive digital design, engineering, manufacturing, and production solutions. Its product offerings include AutoCAD Civil 3D, Autodesk Build, BIM Collaborate Pro, Building Connected, Revit, Tandem, AutoCAD, AutoCAD LT, Inventor, Vault, Maya, 3ds Max, Flow Production Tracking, among others. AutoCAD Civil 3D solution offers surveying, design, analysis, and documentation solution.</v>
     <v>14300</v>
@@ -15204,25 +15204,25 @@
     <v>XNAS</v>
     <v>XNAS</v>
     <v>One Market, Ste. 400., SAN FRANCISCO, CA, 94105 US</v>
-    <v>255.02</v>
+    <v>252.53</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46318.932775253903</v>
+    <v>46321.855707128903</v>
     <v>0</v>
-    <v>248.92500000000001</v>
-    <v>52709800000</v>
+    <v>246.52</v>
+    <v>52135050000</v>
     <v>AUTODESK, INC.</v>
     <v>AUTODESK, INC.</v>
-    <v>254.06</v>
-    <v>32.698500000000003</v>
-    <v>254.95</v>
+    <v>252.36500000000001</v>
+    <v>32.341900000000003</v>
     <v>252.2</v>
-    <v>252.2</v>
+    <v>249.45</v>
+    <v>249.67</v>
     <v>209000000</v>
     <v>ADSK</v>
     <v>AUTODESK, INC. (XNAS:ADSK)</v>
-    <v>1320307</v>
-    <v>1977465</v>
+    <v>1171741</v>
+    <v>1836186</v>
     <v>1994</v>
   </rv>
   <rv s="2">
@@ -15246,17 +15246,17 @@
     <v>Powered by Refinitiv</v>
     <v>53.64</v>
     <v>39.47</v>
-    <v>-1.93</v>
-    <v>-3.7505000000000004E-2</v>
+    <v>0.35</v>
+    <v>7.0660000000000002E-3</v>
     <v>US</v>
-    <v>50.54</v>
+    <v>50.03</v>
     <v>Index</v>
     <v>3</v>
-    <v>49.39</v>
+    <v>49.55</v>
     <v>10 Y TSY YLD NDX</v>
-    <v>50.4</v>
-    <v>51.46</v>
+    <v>49.92</v>
     <v>49.53</v>
+    <v>49.88</v>
     <v>TNX</v>
     <v>10 Y TSY YLD NDX</v>
   </rv>
@@ -15478,9 +15478,9 @@
       <v>at close</v>
       <v>from previous close</v>
       <v>from previous close</v>
-      <v>Source: Nasdaq</v>
+      <v>Source: Nasdaq Last Sale</v>
       <v>GMT</v>
-      <v>Delayed 15 minutes</v>
+      <v>Real-Time Nasdaq Last Sale</v>
       <v>from close</v>
       <v>from close</v>
     </spb>
@@ -16082,7 +16082,7 @@
       </c>
       <c r="F3" s="185">
         <f ca="1">Statement!AC154</f>
-        <v>52962</v>
+        <v>52384.5</v>
       </c>
       <c r="H3" s="183" t="str">
         <f>'AVG target price'!B5</f>
@@ -16090,7 +16090,7 @@
       </c>
       <c r="I3" s="209">
         <f ca="1">'AVG target price'!C5</f>
-        <v>122.59878263521894</v>
+        <v>122.75944086413246</v>
       </c>
       <c r="K3" s="237" t="s">
         <v>436</v>
@@ -16109,7 +16109,7 @@
       </c>
       <c r="F4" s="186">
         <f ca="1">Statement!AC155</f>
-        <v>52083</v>
+        <v>51505.5</v>
       </c>
       <c r="H4" s="183" t="str">
         <f>'AVG target price'!B6</f>
@@ -16117,7 +16117,7 @@
       </c>
       <c r="I4" s="209">
         <f ca="1">'AVG target price'!C6</f>
-        <v>351.86382334060107</v>
+        <v>352.02499199489495</v>
       </c>
       <c r="K4" s="237" t="s">
         <v>437</v>
@@ -16129,7 +16129,7 @@
       </c>
       <c r="C5" s="206" cm="1">
         <f t="array" aca="1" ref="C5" ca="1">_FV(C3,"Price",TRUE)</f>
-        <v>252.2</v>
+        <v>249.45</v>
       </c>
       <c r="E5" s="183" t="s">
         <v>242</v>
@@ -16144,7 +16144,7 @@
       </c>
       <c r="I5" s="209">
         <f ca="1">'AVG target price'!C7</f>
-        <v>191.77732889949982</v>
+        <v>191.84053365045287</v>
       </c>
       <c r="K5" s="237" t="s">
         <v>438</v>
@@ -16156,14 +16156,14 @@
       </c>
       <c r="C6" s="206" cm="1">
         <f t="array" aca="1" ref="C6" ca="1">_FV(C3,"Price (Extended hours)",TRUE)</f>
-        <v>252.2</v>
+        <v>249.67</v>
       </c>
       <c r="E6" s="183" t="s">
         <v>236</v>
       </c>
       <c r="F6" s="188">
         <f ca="1">Statement!AC151</f>
-        <v>32.626131953428199</v>
+        <v>32.270375161707626</v>
       </c>
       <c r="H6" s="183" t="str">
         <f>'AVG target price'!B8</f>
@@ -16171,7 +16171,7 @@
       </c>
       <c r="I6" s="209">
         <f ca="1">'AVG target price'!C8</f>
-        <v>350.30112067060702</v>
+        <v>350.46153628868177</v>
       </c>
       <c r="K6" s="238" t="s">
         <v>439</v>
@@ -16190,7 +16190,7 @@
       </c>
       <c r="F7" s="189">
         <f ca="1">Statement!AC152</f>
-        <v>6.8958408215661109</v>
+        <v>6.8206482670089859</v>
       </c>
       <c r="H7" s="183" t="str">
         <f>'AVG target price'!B9</f>
@@ -16198,7 +16198,7 @@
       </c>
       <c r="I7" s="209">
         <f ca="1">'AVG target price'!C9</f>
-        <v>223.01083239183876</v>
+        <v>223.10990927972978</v>
       </c>
     </row>
     <row r="8" spans="2:11" x14ac:dyDescent="0.2">
@@ -16207,14 +16207,14 @@
       </c>
       <c r="C8" s="6" cm="1">
         <f t="array" aca="1" ref="C8" ca="1">_FV(C3,"Change (extended hours)",TRUE)</f>
-        <v>0</v>
+        <v>0.22</v>
       </c>
       <c r="E8" s="183" t="s">
         <v>264</v>
       </c>
       <c r="F8" s="190">
         <f ca="1">Statement!AC162</f>
-        <v>3.9613307654544766E-2</v>
+        <v>4.0050014794452554E-2</v>
       </c>
       <c r="H8" s="182" t="str">
         <f>'AVG target price'!B10</f>
@@ -16222,7 +16222,7 @@
       </c>
       <c r="I8" s="210">
         <f ca="1">'AVG target price'!C10</f>
-        <v>247.91037758755311</v>
+        <v>248.03928241557833</v>
       </c>
     </row>
     <row r="9" spans="2:11" x14ac:dyDescent="0.2">
@@ -16231,14 +16231,14 @@
       </c>
       <c r="C9" s="73" cm="1">
         <f t="array" aca="1" ref="C9" ca="1">_FV(C3,"Change (%)",TRUE)</f>
-        <v>-1.0786E-2</v>
+        <v>-1.0904E-2</v>
       </c>
       <c r="E9" s="183" t="s">
         <v>287</v>
       </c>
       <c r="F9" s="190">
         <f ca="1">Statement!AC163</f>
-        <v>3.0650277557494054E-2</v>
+        <v>3.0988173982762081E-2</v>
       </c>
       <c r="H9" s="182" t="str">
         <f>'AVG target price'!B12</f>
@@ -16246,7 +16246,7 @@
       </c>
       <c r="I9" s="211">
         <f ca="1">'AVG target price'!C12</f>
-        <v>-1.7008812103278648E-2</v>
+        <v>-5.6553120241397527E-3</v>
       </c>
     </row>
     <row r="10" spans="2:11" x14ac:dyDescent="0.2">
@@ -16255,14 +16255,14 @@
       </c>
       <c r="C10" s="73" cm="1">
         <f t="array" aca="1" ref="C10" ca="1">_FV(C3,"Change % (extended hours)",TRUE)</f>
-        <v>0</v>
+        <v>8.8190000000000002E-4</v>
       </c>
       <c r="E10" s="183" t="s">
         <v>292</v>
       </c>
       <c r="F10" s="190">
         <f ca="1">Statement!AC165</f>
-        <v>3.0040406329066124E-2</v>
+        <v>3.0371579379396576E-2</v>
       </c>
     </row>
     <row r="11" spans="2:11" x14ac:dyDescent="0.2">
@@ -16310,7 +16310,7 @@
       </c>
       <c r="C13" s="207" cm="1">
         <f t="array" aca="1" ref="C13" ca="1">_FV(C3,"Beta")</f>
-        <v>1.2928999999999999</v>
+        <v>1.2835000000000001</v>
       </c>
       <c r="E13" s="183" t="s">
         <v>103</v>
@@ -16333,7 +16333,7 @@
       </c>
       <c r="C14" s="208" cm="1">
         <f t="array" aca="1" ref="C14" ca="1">_FV(C3,"Volume average",TRUE)</f>
-        <v>1977465</v>
+        <v>1836186</v>
       </c>
       <c r="E14" s="184" t="s">
         <v>104</v>
@@ -16347,7 +16347,7 @@
       </c>
       <c r="I14" s="240">
         <f ca="1">'Reverse DCF'!C16</f>
-        <v>254.35811150241574</v>
+        <v>254.72735503932515</v>
       </c>
     </row>
     <row r="15" spans="2:11" x14ac:dyDescent="0.2">
@@ -16356,7 +16356,7 @@
       </c>
       <c r="F15" s="190">
         <f ca="1">Statement!AC177</f>
-        <v>1.6596805256599071E-2</v>
+        <v>1.6779772642671019E-2</v>
       </c>
     </row>
     <row r="16" spans="2:11" x14ac:dyDescent="0.2">
@@ -16389,7 +16389,7 @@
       </c>
       <c r="I17" s="235">
         <f ca="1">DCF!C15</f>
-        <v>0.10404267046420979</v>
+        <v>0.10393629785186842</v>
       </c>
     </row>
     <row r="18" spans="2:9" x14ac:dyDescent="0.2">
@@ -16411,7 +16411,7 @@
       </c>
       <c r="I18" s="236">
         <f ca="1">Multiples!C54</f>
-        <v>0.1077105</v>
+        <v>0.1076375</v>
       </c>
     </row>
     <row r="19" spans="2:9" x14ac:dyDescent="0.2">
@@ -16484,7 +16484,7 @@
       </c>
       <c r="F26" s="217" cm="1">
         <f t="array" aca="1" ref="F26" ca="1">_FV(E26,"Price")</f>
-        <v>49.53</v>
+        <v>49.88</v>
       </c>
     </row>
     <row r="27" spans="2:9" x14ac:dyDescent="0.2">
@@ -16499,7 +16499,7 @@
       </c>
       <c r="F27" s="218">
         <f ca="1">F26/1000</f>
-        <v>4.9530000000000005E-2</v>
+        <v>4.9880000000000001E-2</v>
       </c>
     </row>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
@@ -22245,12 +22245,6 @@
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="H3:L3"/>
-    <mergeCell ref="P3:W3"/>
-    <mergeCell ref="X3:Z3"/>
-    <mergeCell ref="C5:L5"/>
-    <mergeCell ref="P5:Z5"/>
     <mergeCell ref="C40:L40"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="P11:Z11"/>
@@ -22258,6 +22252,12 @@
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="C26:L26"/>
     <mergeCell ref="C33:L33"/>
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="H3:L3"/>
+    <mergeCell ref="P3:W3"/>
+    <mergeCell ref="X3:Z3"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="P5:Z5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -23317,16 +23317,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="C31:L31"/>
+    <mergeCell ref="C25:L25"/>
+    <mergeCell ref="C2:G2"/>
+    <mergeCell ref="H2:L2"/>
+    <mergeCell ref="S2:Z2"/>
     <mergeCell ref="AA2:AC2"/>
     <mergeCell ref="C4:L4"/>
     <mergeCell ref="S4:AC4"/>
     <mergeCell ref="C13:L13"/>
     <mergeCell ref="C18:L18"/>
-    <mergeCell ref="C31:L31"/>
-    <mergeCell ref="C25:L25"/>
-    <mergeCell ref="C2:G2"/>
-    <mergeCell ref="H2:L2"/>
-    <mergeCell ref="S2:Z2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -23448,7 +23448,7 @@
       </c>
       <c r="C6" s="135">
         <f ca="1">Overview!C5</f>
-        <v>252.2</v>
+        <v>249.45</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -23457,7 +23457,7 @@
       </c>
       <c r="C7" s="136">
         <f ca="1">C5*C6</f>
-        <v>52962</v>
+        <v>52384.5</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -23475,7 +23475,7 @@
       </c>
       <c r="C9" s="137">
         <f ca="1">Overview!F27</f>
-        <v>4.9530000000000005E-2</v>
+        <v>4.9880000000000001E-2</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -23484,7 +23484,7 @@
       </c>
       <c r="C10" s="135">
         <f ca="1">Overview!C13</f>
-        <v>1.2928999999999999</v>
+        <v>1.2835000000000001</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -23527,7 +23527,7 @@
       </c>
       <c r="C16" s="46">
         <f ca="1">C8/(C8+C7)</f>
-        <v>6.162296243798724E-2</v>
+        <v>6.2260013425822332E-2</v>
       </c>
     </row>
     <row r="17" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -23536,7 +23536,7 @@
       </c>
       <c r="C17" s="46">
         <f ca="1">C7/(C8+C7)</f>
-        <v>0.93837703756201274</v>
+        <v>0.93773998657417768</v>
       </c>
     </row>
     <row r="18" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -23554,7 +23554,7 @@
       </c>
       <c r="C19" s="46">
         <f ca="1">C9+C10*C11</f>
-        <v>0.1077105</v>
+        <v>0.1076375</v>
       </c>
     </row>
     <row r="20" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -23563,7 +23563,7 @@
       </c>
       <c r="C20" s="46">
         <f ca="1">(C17*C19)+(C16*C18)</f>
-        <v>0.10404267046420979</v>
+        <v>0.10393629785186842</v>
       </c>
     </row>
   </sheetData>
@@ -23814,7 +23814,7 @@
       </c>
       <c r="L8" s="128">
         <f ca="1">L7*(1+C14)/(C15-C14)</f>
-        <v>29876.212830500768</v>
+        <v>29914.07500559045</v>
       </c>
       <c r="N8" s="91"/>
       <c r="O8" s="16"/>
@@ -23868,23 +23868,23 @@
       <c r="G10" s="140"/>
       <c r="H10" s="128">
         <f ca="1">H7/(1+$C$15)^H9</f>
-        <v>1866.6996294545338</v>
+        <v>1866.8795000833261</v>
       </c>
       <c r="I10" s="128">
         <f t="shared" ref="I10:L10" ca="1" si="0">I7/(1+$C$15)^I9</f>
-        <v>1276.7797406692569</v>
+        <v>1277.0258072947236</v>
       </c>
       <c r="J10" s="128">
         <f t="shared" ca="1" si="0"/>
-        <v>574.28699240293599</v>
+        <v>574.45301908650492</v>
       </c>
       <c r="K10" s="128">
         <f t="shared" ca="1" si="0"/>
-        <v>1434.6518365627037</v>
+        <v>1435.2048747143547</v>
       </c>
       <c r="L10" s="128">
         <f t="shared" ca="1" si="0"/>
-        <v>1500.7070475941791</v>
+        <v>1501.4302093209835</v>
       </c>
       <c r="N10" s="91"/>
     </row>
@@ -23903,7 +23903,7 @@
       <c r="K11" s="139"/>
       <c r="L11" s="128">
         <f ca="1">L8/(1+C15)^L9</f>
-        <v>18213.619106712369</v>
+        <v>18245.489170967921</v>
       </c>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.2">
@@ -23926,7 +23926,7 @@
       </c>
       <c r="C15" s="137">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.10404267046420979</v>
+        <v>0.10393629785186842</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.2">
@@ -23941,7 +23941,7 @@
       </c>
       <c r="C19" s="64">
         <f ca="1">SUM(H10:L10)</f>
-        <v>6653.1252466836095</v>
+        <v>6654.9934104998929</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.2">
@@ -23950,7 +23950,7 @@
       </c>
       <c r="C20" s="64">
         <f ca="1">L11</f>
-        <v>18213.619106712369</v>
+        <v>18245.489170967921</v>
       </c>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.2">
@@ -23959,7 +23959,7 @@
       </c>
       <c r="C21" s="94">
         <f ca="1">C19+C20</f>
-        <v>24866.744353395978</v>
+        <v>24900.482581467815</v>
       </c>
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.2">
@@ -23986,7 +23986,7 @@
       </c>
       <c r="C24" s="94">
         <f ca="1">C21+C22-C23</f>
-        <v>25745.744353395978</v>
+        <v>25779.482581467815</v>
       </c>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.2">
@@ -24004,7 +24004,7 @@
       </c>
       <c r="C26" s="234">
         <f ca="1">C24/C25</f>
-        <v>122.59878263521894</v>
+        <v>122.75944086413246</v>
       </c>
     </row>
   </sheetData>
@@ -24273,23 +24273,23 @@
       <c r="G9" s="140"/>
       <c r="H9" s="92">
         <f ca="1">DCF!H10</f>
-        <v>1866.6996294545338</v>
+        <v>1866.8795000833261</v>
       </c>
       <c r="I9" s="92">
         <f ca="1">DCF!I10</f>
-        <v>1276.7797406692569</v>
+        <v>1277.0258072947236</v>
       </c>
       <c r="J9" s="92">
         <f ca="1">DCF!J10</f>
-        <v>574.28699240293599</v>
+        <v>574.45301908650492</v>
       </c>
       <c r="K9" s="92">
         <f ca="1">DCF!K10</f>
-        <v>1434.6518365627037</v>
+        <v>1435.2048747143547</v>
       </c>
       <c r="L9" s="92">
         <f ca="1">DCF!L10</f>
-        <v>1500.7070475941791</v>
+        <v>1501.4302093209835</v>
       </c>
       <c r="N9" s="91"/>
     </row>
@@ -25075,7 +25075,7 @@
       </c>
       <c r="C41" s="137">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.10404267046420979</v>
+        <v>0.10393629785186842</v>
       </c>
     </row>
     <row r="42" spans="2:14" x14ac:dyDescent="0.2">
@@ -25101,7 +25101,7 @@
       </c>
       <c r="C44" s="24">
         <f ca="1">C43/(1+C41)^5</f>
-        <v>67859.984702436792</v>
+        <v>67892.685117749032</v>
       </c>
     </row>
     <row r="45" spans="2:14" x14ac:dyDescent="0.2">
@@ -25110,7 +25110,7 @@
       </c>
       <c r="C45" s="108">
         <f ca="1">SUM(H9:K9)+C44</f>
-        <v>73012.40290152622</v>
+        <v>73046.248318927945</v>
       </c>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.2">
@@ -25137,7 +25137,7 @@
       </c>
       <c r="C48" s="108">
         <f ca="1">C45+C46-C47</f>
-        <v>73891.40290152622</v>
+        <v>73925.248318927945</v>
       </c>
     </row>
     <row r="49" spans="2:3" x14ac:dyDescent="0.2">
@@ -25155,7 +25155,7 @@
       </c>
       <c r="C50" s="234">
         <f ca="1">C48/C49</f>
-        <v>351.86382334060107</v>
+        <v>352.02499199489495</v>
       </c>
     </row>
     <row r="52" spans="2:3" x14ac:dyDescent="0.2">
@@ -25179,7 +25179,7 @@
       </c>
       <c r="C54" s="137">
         <f ca="1">IF(Overview!C29&gt;0,Overview!C29,WACC!C19)</f>
-        <v>0.1077105</v>
+        <v>0.1076375</v>
       </c>
     </row>
     <row r="55" spans="2:3" x14ac:dyDescent="0.2">
@@ -25214,7 +25214,7 @@
       </c>
       <c r="C58" s="234">
         <f ca="1">C57/(1+C54)^5</f>
-        <v>191.77732889949982</v>
+        <v>191.84053365045287</v>
       </c>
     </row>
     <row r="60" spans="2:3" x14ac:dyDescent="0.2">
@@ -25238,7 +25238,7 @@
       </c>
       <c r="C62" s="137">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.10404267046420979</v>
+        <v>0.10393629785186842</v>
       </c>
     </row>
     <row r="63" spans="2:3" x14ac:dyDescent="0.2">
@@ -25264,7 +25264,7 @@
       </c>
       <c r="C65" s="24">
         <f ca="1">C64/(1+C62)^5</f>
-        <v>67531.817141738051</v>
+        <v>67564.359419444256</v>
       </c>
     </row>
     <row r="66" spans="2:3" x14ac:dyDescent="0.2">
@@ -25273,7 +25273,7 @@
       </c>
       <c r="C66" s="108">
         <f ca="1">SUM(H9:K9)+C65</f>
-        <v>72684.235340827479</v>
+        <v>72717.922620623169</v>
       </c>
     </row>
     <row r="67" spans="2:3" x14ac:dyDescent="0.2">
@@ -25300,7 +25300,7 @@
       </c>
       <c r="C69" s="108">
         <f ca="1">C66+C67-C68</f>
-        <v>73563.235340827479</v>
+        <v>73596.922620623169</v>
       </c>
     </row>
     <row r="70" spans="2:3" x14ac:dyDescent="0.2">
@@ -25318,7 +25318,7 @@
       </c>
       <c r="C71" s="234">
         <f ca="1">C69/C70</f>
-        <v>350.30112067060702</v>
+        <v>350.46153628868177</v>
       </c>
     </row>
     <row r="73" spans="2:3" x14ac:dyDescent="0.2">
@@ -25342,7 +25342,7 @@
       </c>
       <c r="C75" s="137">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.10404267046420979</v>
+        <v>0.10393629785186842</v>
       </c>
     </row>
     <row r="76" spans="2:3" x14ac:dyDescent="0.2">
@@ -25368,7 +25368,7 @@
       </c>
       <c r="C78" s="24">
         <f ca="1">C77/(1+C75)^5</f>
-        <v>40800.856603196713</v>
+        <v>40820.517747564343</v>
       </c>
     </row>
     <row r="79" spans="2:3" x14ac:dyDescent="0.2">
@@ -25377,7 +25377,7 @@
       </c>
       <c r="C79" s="108">
         <f ca="1">SUM(H9:K9)+C78</f>
-        <v>45953.274802286141</v>
+        <v>45974.080948743256</v>
       </c>
     </row>
     <row r="80" spans="2:3" x14ac:dyDescent="0.2">
@@ -25404,7 +25404,7 @@
       </c>
       <c r="C82" s="108">
         <f ca="1">C79+C80-C81</f>
-        <v>46832.274802286141</v>
+        <v>46853.080948743256</v>
       </c>
     </row>
     <row r="83" spans="2:3" x14ac:dyDescent="0.2">
@@ -25422,22 +25422,22 @@
       </c>
       <c r="C84" s="234">
         <f ca="1">C82/C83</f>
-        <v>223.01083239183876</v>
+        <v>223.10990927972978</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="B73:C73"/>
+    <mergeCell ref="C27:L27"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="B60:C60"/>
     <mergeCell ref="C22:L22"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="H2:L2"/>
     <mergeCell ref="C4:L4"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="C17:L17"/>
-    <mergeCell ref="B73:C73"/>
-    <mergeCell ref="C27:L27"/>
-    <mergeCell ref="B39:C39"/>
-    <mergeCell ref="B52:C52"/>
-    <mergeCell ref="B60:C60"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -25487,7 +25487,7 @@
       </c>
       <c r="C5" s="135">
         <f ca="1">DCF!C26</f>
-        <v>122.59878263521894</v>
+        <v>122.75944086413246</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.2">
@@ -25496,7 +25496,7 @@
       </c>
       <c r="C6" s="135">
         <f ca="1">Multiples!C50</f>
-        <v>351.86382334060107</v>
+        <v>352.02499199489495</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.2">
@@ -25505,7 +25505,7 @@
       </c>
       <c r="C7" s="135">
         <f ca="1">Multiples!C58</f>
-        <v>191.77732889949982</v>
+        <v>191.84053365045287</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.2">
@@ -25514,7 +25514,7 @@
       </c>
       <c r="C8" s="135">
         <f ca="1">Multiples!C71</f>
-        <v>350.30112067060702</v>
+        <v>350.46153628868177</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
@@ -25523,7 +25523,7 @@
       </c>
       <c r="C9" s="135">
         <f ca="1">Multiples!C84</f>
-        <v>223.01083239183876</v>
+        <v>223.10990927972978</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
@@ -25532,7 +25532,7 @@
       </c>
       <c r="C10" s="234">
         <f ca="1">AVERAGE(C5:C9)</f>
-        <v>247.91037758755311</v>
+        <v>248.03928241557833</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -25541,7 +25541,7 @@
       </c>
       <c r="C11" s="135">
         <f ca="1">Overview!C5</f>
-        <v>252.2</v>
+        <v>249.45</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.2">
@@ -25550,7 +25550,7 @@
       </c>
       <c r="C12" s="154">
         <f ca="1">(C10-C11)/C11</f>
-        <v>-1.7008812103278648E-2</v>
+        <v>-5.6553120241397527E-3</v>
       </c>
     </row>
   </sheetData>
@@ -26059,7 +26059,7 @@
       </c>
       <c r="C24" s="137">
         <f ca="1">IF(Overview!C29&gt;0,Overview!C29,WACC!C19)</f>
-        <v>0.1077105</v>
+        <v>0.1076375</v>
       </c>
     </row>
     <row r="25" spans="2:14" x14ac:dyDescent="0.2">
@@ -26313,7 +26313,7 @@
       <c r="K8" s="139"/>
       <c r="L8" s="128">
         <f ca="1">L7*(1+C20)/(C21-C20)</f>
-        <v>69024.884942948338</v>
+        <v>69112.360296470622</v>
       </c>
       <c r="N8" s="91"/>
       <c r="O8" s="16"/>
@@ -26367,23 +26367,23 @@
       <c r="G10" s="140"/>
       <c r="H10" s="128">
         <f ca="1">H7/(1+$C$21)^H9</f>
-        <v>990.85867334318175</v>
+        <v>990.9541500710958</v>
       </c>
       <c r="I10" s="128">
         <f t="shared" ref="I10:L10" ca="1" si="1">I7/(1+$C$21)^I9</f>
-        <v>1355.1981610630216</v>
+        <v>1355.4593408324915</v>
       </c>
       <c r="J10" s="128">
         <f t="shared" ca="1" si="1"/>
-        <v>1853.5055554915716</v>
+        <v>1854.0414049613069</v>
       </c>
       <c r="K10" s="128">
         <f t="shared" ca="1" si="1"/>
-        <v>2535.0409578059903</v>
+        <v>2536.0181805229827</v>
       </c>
       <c r="L10" s="128">
         <f t="shared" ca="1" si="1"/>
-        <v>3467.1774458477657</v>
+        <v>3468.8482116597183</v>
       </c>
       <c r="N10" s="91"/>
     </row>
@@ -26402,15 +26402,15 @@
       <c r="K11" s="139"/>
       <c r="L11" s="128">
         <f ca="1">L8/(1+C21)^L9</f>
-        <v>42080.064510453361</v>
+        <v>42153.695915171367</v>
       </c>
     </row>
     <row r="13" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B14" s="258" t="s">
+      <c r="B14" s="257" t="s">
         <v>221</v>
       </c>
-      <c r="C14" s="259"/>
+      <c r="C14" s="258"/>
     </row>
     <row r="15" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B15" s="155" t="s">
@@ -26418,7 +26418,7 @@
       </c>
       <c r="C15" s="156">
         <f ca="1">Overview!C5</f>
-        <v>252.2</v>
+        <v>249.45</v>
       </c>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.2">
@@ -26427,7 +26427,7 @@
       </c>
       <c r="C16" s="156">
         <f ca="1">C36</f>
-        <v>254.35811150241574</v>
+        <v>254.72735503932515</v>
       </c>
     </row>
     <row r="17" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -26437,20 +26437,20 @@
       <c r="C17" s="158">
         <v>0.51</v>
       </c>
-      <c r="E17" s="257" t="s">
+      <c r="E17" s="259" t="s">
         <v>224</v>
       </c>
-      <c r="F17" s="257"/>
-      <c r="G17" s="257"/>
-      <c r="H17" s="257"/>
-      <c r="I17" s="257"/>
+      <c r="F17" s="259"/>
+      <c r="G17" s="259"/>
+      <c r="H17" s="259"/>
+      <c r="I17" s="259"/>
     </row>
     <row r="18" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="19" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B19" s="258" t="s">
+      <c r="B19" s="257" t="s">
         <v>183</v>
       </c>
-      <c r="C19" s="259"/>
+      <c r="C19" s="258"/>
     </row>
     <row r="20" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B20" s="159" t="s">
@@ -26466,7 +26466,7 @@
       </c>
       <c r="C21" s="220">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.10404267046420979</v>
+        <v>0.10393629785186842</v>
       </c>
     </row>
     <row r="22" spans="2:9" x14ac:dyDescent="0.2">
@@ -26484,7 +26484,7 @@
       </c>
       <c r="C23" s="161">
         <f ca="1">C15*C22</f>
-        <v>52709.799999999996</v>
+        <v>52135.049999999996</v>
       </c>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.2">
@@ -26511,15 +26511,15 @@
       </c>
       <c r="C26" s="162">
         <f ca="1">C23+C25-C24</f>
-        <v>51830.799999999996</v>
+        <v>51256.049999999996</v>
       </c>
     </row>
     <row r="27" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B28" s="258" t="s">
+      <c r="B28" s="257" t="s">
         <v>185</v>
       </c>
-      <c r="C28" s="259"/>
+      <c r="C28" s="258"/>
     </row>
     <row r="29" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B29" s="159" t="s">
@@ -26527,7 +26527,7 @@
       </c>
       <c r="C29" s="161">
         <f ca="1">SUM(H10:L10)</f>
-        <v>10201.78079355153</v>
+        <v>10205.321288047595</v>
       </c>
     </row>
     <row r="30" spans="2:9" x14ac:dyDescent="0.2">
@@ -26536,7 +26536,7 @@
       </c>
       <c r="C30" s="161">
         <f ca="1">L11</f>
-        <v>42080.064510453361</v>
+        <v>42153.695915171367</v>
       </c>
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.2">
@@ -26545,7 +26545,7 @@
       </c>
       <c r="C31" s="164">
         <f ca="1">C29+C30</f>
-        <v>52281.845304004892</v>
+        <v>52359.017203218958</v>
       </c>
     </row>
     <row r="32" spans="2:9" x14ac:dyDescent="0.2">
@@ -26572,7 +26572,7 @@
       </c>
       <c r="C34" s="164">
         <f ca="1">C31+C32-C33</f>
-        <v>53160.845304004892</v>
+        <v>53238.017203218958</v>
       </c>
     </row>
     <row r="35" spans="2:3" x14ac:dyDescent="0.2">
@@ -26590,21 +26590,21 @@
       </c>
       <c r="C36" s="167">
         <f ca="1">C34/C35</f>
-        <v>254.35811150241574</v>
+        <v>254.72735503932515</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="E17:I17"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="H3:L3"/>
     <mergeCell ref="P3:W3"/>
     <mergeCell ref="X3:Z3"/>
     <mergeCell ref="C5:L5"/>
     <mergeCell ref="P5:Z5"/>
     <mergeCell ref="B14:C14"/>
-    <mergeCell ref="E17:I17"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="H3:L3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -33260,7 +33260,7 @@
       </c>
       <c r="AC117" s="63">
         <f ca="1">Overview!C5</f>
-        <v>252.2</v>
+        <v>249.45</v>
       </c>
     </row>
     <row r="118" spans="1:31" x14ac:dyDescent="0.2">
@@ -33331,7 +33331,7 @@
       </c>
       <c r="AC118" s="65">
         <f ca="1">AC117/AC86</f>
-        <v>252.2</v>
+        <v>249.45</v>
       </c>
     </row>
     <row r="120" spans="1:31" x14ac:dyDescent="0.2">
@@ -34637,7 +34637,7 @@
       <c r="AA151" s="49"/>
       <c r="AC151" s="72">
         <f ca="1">AC118/Statement!AC27</f>
-        <v>32.626131953428199</v>
+        <v>32.270375161707626</v>
       </c>
     </row>
     <row r="152" spans="2:29" x14ac:dyDescent="0.2">
@@ -34674,7 +34674,7 @@
       <c r="AA152" s="49"/>
       <c r="AC152" s="72">
         <f ca="1">AC118/(Statement!AC5/Statement!AC23)</f>
-        <v>6.8958408215661109</v>
+        <v>6.8206482670089859</v>
       </c>
     </row>
     <row r="153" spans="2:29" x14ac:dyDescent="0.2">
@@ -34735,7 +34735,7 @@
       </c>
       <c r="AC153" s="72">
         <f ca="1">AC118/(Statement!AC50/Statement!AC76)</f>
-        <v>15.58078628436299</v>
+        <v>15.410892698788055</v>
       </c>
     </row>
     <row r="154" spans="2:29" x14ac:dyDescent="0.2">
@@ -34796,7 +34796,7 @@
       </c>
       <c r="AC154" s="143">
         <f ca="1">Statement!AC118*Statement!AC79</f>
-        <v>52962</v>
+        <v>52384.5</v>
       </c>
     </row>
     <row r="155" spans="2:29" x14ac:dyDescent="0.2">
@@ -34857,7 +34857,7 @@
       </c>
       <c r="AC155" s="143">
         <f ca="1">AC154+AC109-AC108+AC49+AC46</f>
-        <v>52083</v>
+        <v>51505.5</v>
       </c>
     </row>
     <row r="156" spans="2:29" x14ac:dyDescent="0.2">
@@ -34894,7 +34894,7 @@
       <c r="AA156" s="49"/>
       <c r="AC156" s="181">
         <f ca="1">AC155/AC5</f>
-        <v>6.6858793324775352</v>
+        <v>6.6117458279845955</v>
       </c>
     </row>
     <row r="157" spans="2:29" x14ac:dyDescent="0.2">
@@ -34931,7 +34931,7 @@
       <c r="AA157" s="49"/>
       <c r="AC157" s="181">
         <f ca="1">AC155/AC13</f>
-        <v>25.518373346398825</v>
+        <v>25.235423811856933</v>
       </c>
     </row>
     <row r="158" spans="2:29" x14ac:dyDescent="0.2">
@@ -35066,7 +35066,7 @@
       <c r="AA160" s="49"/>
       <c r="AC160" s="72">
         <f t="shared" ref="AC160:AC161" ca="1" si="155">AC154/AC158</f>
-        <v>25.244041944709245</v>
+        <v>24.968779790276454</v>
       </c>
     </row>
     <row r="161" spans="2:29" x14ac:dyDescent="0.2">
@@ -35103,7 +35103,7 @@
       <c r="AA161" s="49"/>
       <c r="AC161" s="72">
         <f t="shared" ca="1" si="155"/>
-        <v>42.828703880942641</v>
+        <v>42.353816173029422</v>
       </c>
     </row>
     <row r="162" spans="2:29" x14ac:dyDescent="0.2">
@@ -35140,7 +35140,7 @@
       <c r="AA162" s="49"/>
       <c r="AC162" s="74">
         <f t="shared" ref="AC162" ca="1" si="158">AC158/AC154</f>
-        <v>3.9613307654544766E-2</v>
+        <v>4.0050014794452554E-2</v>
       </c>
     </row>
     <row r="163" spans="2:29" x14ac:dyDescent="0.2">
@@ -35177,7 +35177,7 @@
       <c r="AA163" s="49"/>
       <c r="AC163" s="74">
         <f ca="1">AC27/AC118</f>
-        <v>3.0650277557494054E-2</v>
+        <v>3.0988173982762081E-2</v>
       </c>
     </row>
     <row r="164" spans="2:29" x14ac:dyDescent="0.2">
@@ -35251,7 +35251,7 @@
       <c r="AA165" s="49"/>
       <c r="AC165" s="154">
         <f ca="1">-AC64/AC154</f>
-        <v>3.0040406329066124E-2</v>
+        <v>3.0371579379396576E-2</v>
       </c>
     </row>
     <row r="166" spans="2:29" x14ac:dyDescent="0.2">
@@ -35288,7 +35288,7 @@
       <c r="AA166" s="49"/>
       <c r="AC166" s="154">
         <f ca="1">-(AC64+AC65)/AC154</f>
-        <v>3.0040406329066124E-2</v>
+        <v>3.0371579379396576E-2</v>
       </c>
     </row>
     <row r="167" spans="2:29" x14ac:dyDescent="0.2">
@@ -35791,7 +35791,7 @@
       <c r="AA177" s="49"/>
       <c r="AC177" s="154">
         <f ca="1">(AC108-AC109)/AC154</f>
-        <v>1.6596805256599071E-2</v>
+        <v>1.6779772642671019E-2</v>
       </c>
     </row>
     <row r="178" spans="1:31" x14ac:dyDescent="0.2">
@@ -37641,7 +37641,7 @@
       </c>
       <c r="C5" s="170">
         <f ca="1">Overview!C5</f>
-        <v>252.2</v>
+        <v>249.45</v>
       </c>
       <c r="E5" s="12"/>
       <c r="F5" s="134" t="s">
@@ -37657,7 +37657,7 @@
       </c>
       <c r="C6" s="171">
         <f ca="1">Statement!AC154</f>
-        <v>52962</v>
+        <v>52384.5</v>
       </c>
       <c r="E6" s="20" t="s">
         <v>19</v>
@@ -37677,7 +37677,7 @@
       </c>
       <c r="C7" s="171">
         <f ca="1">Statement!AC155</f>
-        <v>52083</v>
+        <v>51505.5</v>
       </c>
       <c r="E7" s="20" t="s">
         <v>31</v>
@@ -37697,7 +37697,7 @@
       </c>
       <c r="C8" s="172">
         <f ca="1">Statement!AC151</f>
-        <v>32.626131953428199</v>
+        <v>32.270375161707626</v>
       </c>
       <c r="E8" s="20" t="s">
         <v>242</v>
@@ -37717,7 +37717,7 @@
       </c>
       <c r="C9" s="172">
         <f ca="1">Statement!AC152</f>
-        <v>6.8958408215661109</v>
+        <v>6.8206482670089859</v>
       </c>
       <c r="E9" s="20" t="s">
         <v>243</v>
@@ -37737,7 +37737,7 @@
       </c>
       <c r="C10" s="172">
         <f ca="1">Statement!AC153</f>
-        <v>15.58078628436299</v>
+        <v>15.410892698788055</v>
       </c>
       <c r="E10" s="20" t="s">
         <v>1</v>
@@ -37757,7 +37757,7 @@
       </c>
       <c r="C11" s="172">
         <f ca="1">Statement!AC156</f>
-        <v>6.6858793324775352</v>
+        <v>6.6117458279845955</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
@@ -37766,7 +37766,7 @@
       </c>
       <c r="C12" s="172">
         <f ca="1">Statement!AC157</f>
-        <v>25.518373346398825</v>
+        <v>25.235423811856933</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.2">
@@ -38002,7 +38002,7 @@
       </c>
       <c r="C38" s="173">
         <f ca="1">Statement!AC163</f>
-        <v>3.0650277557494054E-2</v>
+        <v>3.0988173982762081E-2</v>
       </c>
       <c r="E38" s="20" t="s">
         <v>269</v>
@@ -38018,7 +38018,7 @@
       </c>
       <c r="C39" s="213">
         <f ca="1">Statement!AC162</f>
-        <v>3.9613307654544766E-2</v>
+        <v>4.0050014794452554E-2</v>
       </c>
       <c r="E39" s="20" t="s">
         <v>271</v>
@@ -38050,7 +38050,7 @@
       </c>
       <c r="C41" s="173">
         <f ca="1">Statement!AC165</f>
-        <v>3.0040406329066124E-2</v>
+        <v>3.0371579379396576E-2</v>
       </c>
     </row>
     <row r="42" spans="2:6" x14ac:dyDescent="0.2">
@@ -38059,7 +38059,7 @@
       </c>
       <c r="C42" s="173">
         <f ca="1">Statement!AC166</f>
-        <v>3.0040406329066124E-2</v>
+        <v>3.0371579379396576E-2</v>
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.2">
@@ -38103,7 +38103,7 @@
       </c>
       <c r="F48" s="173">
         <f ca="1">Statement!AC177</f>
-        <v>1.6596805256599071E-2</v>
+        <v>1.6779772642671019E-2</v>
       </c>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.2">
@@ -38282,7 +38282,7 @@
       </c>
       <c r="I6" s="170">
         <f ca="1">Statement!AC117</f>
-        <v>252.2</v>
+        <v>249.45</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -38311,7 +38311,7 @@
       </c>
       <c r="I7" s="171">
         <f ca="1">Statement!AC154</f>
-        <v>52962</v>
+        <v>52384.5</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
@@ -38340,7 +38340,7 @@
       </c>
       <c r="I8" s="171">
         <f ca="1">Statement!AC155</f>
-        <v>52083</v>
+        <v>51505.5</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -38369,7 +38369,7 @@
       </c>
       <c r="I9" s="172">
         <f ca="1">Statement!AC151</f>
-        <v>32.626131953428199</v>
+        <v>32.270375161707626</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -38398,7 +38398,7 @@
       </c>
       <c r="I10" s="172">
         <f ca="1">Statement!AC152</f>
-        <v>6.8958408215661109</v>
+        <v>6.8206482670089859</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -38427,7 +38427,7 @@
       </c>
       <c r="I11" s="172">
         <f ca="1">Statement!AC153</f>
-        <v>15.58078628436299</v>
+        <v>15.410892698788055</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
@@ -38456,7 +38456,7 @@
       </c>
       <c r="I12" s="172">
         <f ca="1">Statement!AC156</f>
-        <v>6.6858793324775352</v>
+        <v>6.6117458279845955</v>
       </c>
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.2">
@@ -38485,7 +38485,7 @@
       </c>
       <c r="I13" s="172">
         <f ca="1">Statement!AC157</f>
-        <v>25.518373346398825</v>
+        <v>25.235423811856933</v>
       </c>
     </row>
     <row r="15" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -39258,7 +39258,7 @@
       </c>
       <c r="I51" s="173">
         <f ca="1">Statement!AC163</f>
-        <v>3.0650277557494054E-2</v>
+        <v>3.0988173982762081E-2</v>
       </c>
     </row>
     <row r="52" spans="2:9" x14ac:dyDescent="0.2">
@@ -39287,7 +39287,7 @@
       </c>
       <c r="I52" s="173">
         <f ca="1">Statement!AC162</f>
-        <v>3.9613307654544766E-2</v>
+        <v>4.0050014794452554E-2</v>
       </c>
     </row>
     <row r="53" spans="2:9" x14ac:dyDescent="0.2">
@@ -39345,7 +39345,7 @@
       </c>
       <c r="I54" s="173">
         <f ca="1">Statement!AC165</f>
-        <v>3.0040406329066124E-2</v>
+        <v>3.0371579379396576E-2</v>
       </c>
     </row>
     <row r="55" spans="2:9" x14ac:dyDescent="0.2">
@@ -39374,7 +39374,7 @@
       </c>
       <c r="I55" s="173">
         <f ca="1">Statement!AC166</f>
-        <v>3.0040406329066124E-2</v>
+        <v>3.0371579379396576E-2</v>
       </c>
     </row>
     <row r="57" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -39610,7 +39610,7 @@
       </c>
       <c r="I68" s="194">
         <f ca="1">Statement!AC177</f>
-        <v>1.6596805256599071E-2</v>
+        <v>1.6779772642671019E-2</v>
       </c>
     </row>
     <row r="70" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -40763,6 +40763,30 @@
     </row>
   </sheetData>
   <mergeCells count="32">
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="F25:G25"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="F27:G27"/>
+    <mergeCell ref="C30:D30"/>
+    <mergeCell ref="F30:G30"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="F9:G9"/>
     <mergeCell ref="C38:D38"/>
     <mergeCell ref="F38:G38"/>
     <mergeCell ref="C32:D32"/>
@@ -40771,30 +40795,6 @@
     <mergeCell ref="F34:G34"/>
     <mergeCell ref="C36:D36"/>
     <mergeCell ref="F36:G36"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="F9:G9"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="F19:G19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="F21:G21"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="F25:G25"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="F27:G27"/>
-    <mergeCell ref="C30:D30"/>
-    <mergeCell ref="F30:G30"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>

--- a/ADSK.xlsx
+++ b/ADSK.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/KINGSTON/MyStockData/Finance-StockLists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F5DF0EA-482D-4B4B-A086-2245244E0EEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1DDC700-FF78-C84F-BA35-3D8B3A54D7B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="14400" xr2:uid="{AEC0C047-6E16-294C-82BD-58123BA913A1}"/>
   </bookViews>
@@ -151,7 +151,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="817" uniqueCount="442">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="827" uniqueCount="446">
   <si>
     <t>Ticker</t>
   </si>
@@ -1477,6 +1477,18 @@
   </si>
   <si>
     <t>Reverse DCF price</t>
+  </si>
+  <si>
+    <t>FCF ratios</t>
+  </si>
+  <si>
+    <t>FCFF/Sales</t>
+  </si>
+  <si>
+    <t>FCFE/Sales</t>
+  </si>
+  <si>
+    <t>Other standard growth rates</t>
   </si>
 </sst>
 </file>
@@ -2463,14 +2475,14 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -15192,11 +15204,11 @@
     <v>Powered by Refinitiv</v>
     <v>320</v>
     <v>185.5</v>
-    <v>1.2835000000000001</v>
-    <v>-2.75</v>
-    <v>-1.0904E-2</v>
-    <v>0.22</v>
-    <v>8.8190000000000002E-4</v>
+    <v>1.2979000000000001</v>
+    <v>-7.35</v>
+    <v>-2.9464999999999998E-2</v>
+    <v>0.05</v>
+    <v>2.065E-4</v>
     <v>USD</v>
     <v>Autodesk, Inc. is engaged in three-dimensional (3D) design, engineering and entertainment technology solutions, spanning architecture, engineering, construction, product design, manufacturing, media and entertainment. Its architecture, engineering, construction and operations products improve the way building, infrastructure, and industrial projects are designed, built, and operated. Its product development and manufacturing software provides manufacturers in the automotive, transportation, industrial machinery, consumer products, and building product industries with comprehensive digital design, engineering, manufacturing, and production solutions. Its product offerings include AutoCAD Civil 3D, Autodesk Build, BIM Collaborate Pro, Building Connected, Revit, Tandem, AutoCAD, AutoCAD LT, Inventor, Vault, Maya, 3ds Max, Flow Production Tracking, among others. AutoCAD Civil 3D solution offers surveying, design, analysis, and documentation solution.</v>
     <v>14300</v>
@@ -15204,25 +15216,25 @@
     <v>XNAS</v>
     <v>XNAS</v>
     <v>One Market, Ste. 400., SAN FRANCISCO, CA, 94105 US</v>
-    <v>252.53</v>
+    <v>248.54</v>
     <v>Software &amp; IT Services</v>
     <v>Stock</v>
-    <v>46321.855707128903</v>
+    <v>46322.912133876562</v>
     <v>0</v>
-    <v>246.52</v>
-    <v>52135050000</v>
+    <v>241.78</v>
+    <v>50598900000</v>
     <v>AUTODESK, INC.</v>
     <v>AUTODESK, INC.</v>
-    <v>252.36500000000001</v>
-    <v>32.341900000000003</v>
-    <v>252.2</v>
+    <v>245.66</v>
+    <v>31.388999999999999</v>
     <v>249.45</v>
-    <v>249.67</v>
+    <v>242.1</v>
+    <v>242.15</v>
     <v>209000000</v>
     <v>ADSK</v>
     <v>AUTODESK, INC. (XNAS:ADSK)</v>
-    <v>1171741</v>
-    <v>1836186</v>
+    <v>1438146</v>
+    <v>1822054</v>
     <v>1994</v>
   </rv>
   <rv s="2">
@@ -15246,17 +15258,17 @@
     <v>Powered by Refinitiv</v>
     <v>53.64</v>
     <v>39.47</v>
-    <v>0.35</v>
-    <v>7.0660000000000002E-3</v>
+    <v>-0.02</v>
+    <v>-4.0099999999999999E-4</v>
     <v>US</v>
     <v>50.03</v>
     <v>Index</v>
     <v>3</v>
-    <v>49.55</v>
+    <v>49.61</v>
     <v>10 Y TSY YLD NDX</v>
-    <v>49.92</v>
-    <v>49.53</v>
+    <v>50.03</v>
     <v>49.88</v>
+    <v>49.86</v>
     <v>TNX</v>
     <v>10 Y TSY YLD NDX</v>
   </rv>
@@ -15478,9 +15490,9 @@
       <v>at close</v>
       <v>from previous close</v>
       <v>from previous close</v>
-      <v>Source: Nasdaq Last Sale</v>
+      <v>Source: Nasdaq</v>
       <v>GMT</v>
-      <v>Real-Time Nasdaq Last Sale</v>
+      <v>Delayed 15 minutes</v>
       <v>from close</v>
       <v>from close</v>
     </spb>
@@ -16082,7 +16094,7 @@
       </c>
       <c r="F3" s="185">
         <f ca="1">Statement!AC154</f>
-        <v>52384.5</v>
+        <v>50841</v>
       </c>
       <c r="H3" s="183" t="str">
         <f>'AVG target price'!B5</f>
@@ -16090,7 +16102,7 @@
       </c>
       <c r="I3" s="209">
         <f ca="1">'AVG target price'!C5</f>
-        <v>122.75944086413246</v>
+        <v>122.03382006490071</v>
       </c>
       <c r="K3" s="237" t="s">
         <v>436</v>
@@ -16109,7 +16121,7 @@
       </c>
       <c r="F4" s="186">
         <f ca="1">Statement!AC155</f>
-        <v>51505.5</v>
+        <v>49962</v>
       </c>
       <c r="H4" s="183" t="str">
         <f>'AVG target price'!B6</f>
@@ -16117,7 +16129,7 @@
       </c>
       <c r="I4" s="209">
         <f ca="1">'AVG target price'!C6</f>
-        <v>352.02499199489495</v>
+        <v>351.29449944402205</v>
       </c>
       <c r="K4" s="237" t="s">
         <v>437</v>
@@ -16129,7 +16141,7 @@
       </c>
       <c r="C5" s="206" cm="1">
         <f t="array" aca="1" ref="C5" ca="1">_FV(C3,"Price",TRUE)</f>
-        <v>249.45</v>
+        <v>242.1</v>
       </c>
       <c r="E5" s="183" t="s">
         <v>242</v>
@@ -16144,7 +16156,7 @@
       </c>
       <c r="I5" s="209">
         <f ca="1">'AVG target price'!C7</f>
-        <v>191.84053365045287</v>
+        <v>191.29761592497329</v>
       </c>
       <c r="K5" s="237" t="s">
         <v>438</v>
@@ -16156,14 +16168,14 @@
       </c>
       <c r="C6" s="206" cm="1">
         <f t="array" aca="1" ref="C6" ca="1">_FV(C3,"Price (Extended hours)",TRUE)</f>
-        <v>249.67</v>
+        <v>242.15</v>
       </c>
       <c r="E6" s="183" t="s">
         <v>236</v>
       </c>
       <c r="F6" s="188">
         <f ca="1">Statement!AC151</f>
-        <v>32.270375161707626</v>
+        <v>31.319534282018108</v>
       </c>
       <c r="H6" s="183" t="str">
         <f>'AVG target price'!B8</f>
@@ -16171,7 +16183,7 @@
       </c>
       <c r="I6" s="209">
         <f ca="1">'AVG target price'!C8</f>
-        <v>350.46153628868177</v>
+        <v>349.73445681378689</v>
       </c>
       <c r="K6" s="238" t="s">
         <v>439</v>
@@ -16183,14 +16195,14 @@
       </c>
       <c r="C7" s="6" cm="1">
         <f t="array" aca="1" ref="C7" ca="1">_FV(C3,"Change")</f>
-        <v>-2.75</v>
+        <v>-7.35</v>
       </c>
       <c r="E7" s="184" t="s">
         <v>200</v>
       </c>
       <c r="F7" s="189">
         <f ca="1">Statement!AC152</f>
-        <v>6.8206482670089859</v>
+        <v>6.6196790757381265</v>
       </c>
       <c r="H7" s="183" t="str">
         <f>'AVG target price'!B9</f>
@@ -16198,7 +16210,7 @@
       </c>
       <c r="I7" s="209">
         <f ca="1">'AVG target price'!C9</f>
-        <v>223.10990927972978</v>
+        <v>222.66084265623115</v>
       </c>
     </row>
     <row r="8" spans="2:11" x14ac:dyDescent="0.2">
@@ -16207,14 +16219,14 @@
       </c>
       <c r="C8" s="6" cm="1">
         <f t="array" aca="1" ref="C8" ca="1">_FV(C3,"Change (extended hours)",TRUE)</f>
-        <v>0.22</v>
+        <v>0.05</v>
       </c>
       <c r="E8" s="183" t="s">
         <v>264</v>
       </c>
       <c r="F8" s="190">
         <f ca="1">Statement!AC162</f>
-        <v>4.0050014794452554E-2</v>
+        <v>4.1265907436911158E-2</v>
       </c>
       <c r="H8" s="182" t="str">
         <f>'AVG target price'!B10</f>
@@ -16222,7 +16234,7 @@
       </c>
       <c r="I8" s="210">
         <f ca="1">'AVG target price'!C10</f>
-        <v>248.03928241557833</v>
+        <v>247.40424698078283</v>
       </c>
     </row>
     <row r="9" spans="2:11" x14ac:dyDescent="0.2">
@@ -16231,14 +16243,14 @@
       </c>
       <c r="C9" s="73" cm="1">
         <f t="array" aca="1" ref="C9" ca="1">_FV(C3,"Change (%)",TRUE)</f>
-        <v>-1.0904E-2</v>
+        <v>-2.9464999999999998E-2</v>
       </c>
       <c r="E9" s="183" t="s">
         <v>287</v>
       </c>
       <c r="F9" s="190">
         <f ca="1">Statement!AC163</f>
-        <v>3.0988173982762081E-2</v>
+        <v>3.1928954977282119E-2</v>
       </c>
       <c r="H9" s="182" t="str">
         <f>'AVG target price'!B12</f>
@@ -16246,7 +16258,7 @@
       </c>
       <c r="I9" s="211">
         <f ca="1">'AVG target price'!C12</f>
-        <v>-5.6553120241397527E-3</v>
+        <v>2.1909322514592464E-2</v>
       </c>
     </row>
     <row r="10" spans="2:11" x14ac:dyDescent="0.2">
@@ -16255,14 +16267,14 @@
       </c>
       <c r="C10" s="73" cm="1">
         <f t="array" aca="1" ref="C10" ca="1">_FV(C3,"Change % (extended hours)",TRUE)</f>
-        <v>8.8190000000000002E-4</v>
+        <v>2.065E-4</v>
       </c>
       <c r="E10" s="183" t="s">
         <v>292</v>
       </c>
       <c r="F10" s="190">
         <f ca="1">Statement!AC165</f>
-        <v>3.0371579379396576E-2</v>
+        <v>3.1293640959068468E-2</v>
       </c>
     </row>
     <row r="11" spans="2:11" x14ac:dyDescent="0.2">
@@ -16310,7 +16322,7 @@
       </c>
       <c r="C13" s="207" cm="1">
         <f t="array" aca="1" ref="C13" ca="1">_FV(C3,"Beta")</f>
-        <v>1.2835000000000001</v>
+        <v>1.2979000000000001</v>
       </c>
       <c r="E13" s="183" t="s">
         <v>103</v>
@@ -16333,7 +16345,7 @@
       </c>
       <c r="C14" s="208" cm="1">
         <f t="array" aca="1" ref="C14" ca="1">_FV(C3,"Volume average",TRUE)</f>
-        <v>1836186</v>
+        <v>1822054</v>
       </c>
       <c r="E14" s="184" t="s">
         <v>104</v>
@@ -16347,7 +16359,7 @@
       </c>
       <c r="I14" s="240">
         <f ca="1">'Reverse DCF'!C16</f>
-        <v>254.72735503932515</v>
+        <v>253.05971544825422</v>
       </c>
     </row>
     <row r="15" spans="2:11" x14ac:dyDescent="0.2">
@@ -16356,7 +16368,7 @@
       </c>
       <c r="F15" s="190">
         <f ca="1">Statement!AC177</f>
-        <v>1.6779772642671019E-2</v>
+        <v>1.7289195727857438E-2</v>
       </c>
     </row>
     <row r="16" spans="2:11" x14ac:dyDescent="0.2">
@@ -16389,7 +16401,7 @@
       </c>
       <c r="I17" s="235">
         <f ca="1">DCF!C15</f>
-        <v>0.10393629785186842</v>
+        <v>0.10441891613431764</v>
       </c>
     </row>
     <row r="18" spans="2:9" x14ac:dyDescent="0.2">
@@ -16411,7 +16423,7 @@
       </c>
       <c r="I18" s="236">
         <f ca="1">Multiples!C54</f>
-        <v>0.1076375</v>
+        <v>0.1082655</v>
       </c>
     </row>
     <row r="19" spans="2:9" x14ac:dyDescent="0.2">
@@ -16484,7 +16496,7 @@
       </c>
       <c r="F26" s="217" cm="1">
         <f t="array" aca="1" ref="F26" ca="1">_FV(E26,"Price")</f>
-        <v>49.88</v>
+        <v>49.86</v>
       </c>
     </row>
     <row r="27" spans="2:9" x14ac:dyDescent="0.2">
@@ -16499,7 +16511,7 @@
       </c>
       <c r="F27" s="218">
         <f ca="1">F26/1000</f>
-        <v>4.9880000000000001E-2</v>
+        <v>4.9860000000000002E-2</v>
       </c>
     </row>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
@@ -22245,6 +22257,12 @@
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="H3:L3"/>
+    <mergeCell ref="P3:W3"/>
+    <mergeCell ref="X3:Z3"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="P5:Z5"/>
     <mergeCell ref="C40:L40"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="P11:Z11"/>
@@ -22252,12 +22270,6 @@
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="C26:L26"/>
     <mergeCell ref="C33:L33"/>
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="H3:L3"/>
-    <mergeCell ref="P3:W3"/>
-    <mergeCell ref="X3:Z3"/>
-    <mergeCell ref="C5:L5"/>
-    <mergeCell ref="P5:Z5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -23317,16 +23329,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="AA2:AC2"/>
+    <mergeCell ref="C4:L4"/>
+    <mergeCell ref="S4:AC4"/>
+    <mergeCell ref="C13:L13"/>
+    <mergeCell ref="C18:L18"/>
     <mergeCell ref="C31:L31"/>
     <mergeCell ref="C25:L25"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="H2:L2"/>
     <mergeCell ref="S2:Z2"/>
-    <mergeCell ref="AA2:AC2"/>
-    <mergeCell ref="C4:L4"/>
-    <mergeCell ref="S4:AC4"/>
-    <mergeCell ref="C13:L13"/>
-    <mergeCell ref="C18:L18"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -23448,7 +23460,7 @@
       </c>
       <c r="C6" s="135">
         <f ca="1">Overview!C5</f>
-        <v>249.45</v>
+        <v>242.1</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -23457,7 +23469,7 @@
       </c>
       <c r="C7" s="136">
         <f ca="1">C5*C6</f>
-        <v>52384.5</v>
+        <v>50841</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -23475,7 +23487,7 @@
       </c>
       <c r="C9" s="137">
         <f ca="1">Overview!F27</f>
-        <v>4.9880000000000001E-2</v>
+        <v>4.9860000000000002E-2</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -23484,7 +23496,7 @@
       </c>
       <c r="C10" s="135">
         <f ca="1">Overview!C13</f>
-        <v>1.2835000000000001</v>
+        <v>1.2979000000000001</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -23527,7 +23539,7 @@
       </c>
       <c r="C16" s="46">
         <f ca="1">C8/(C8+C7)</f>
-        <v>6.2260013425822332E-2</v>
+        <v>6.4029161067029952E-2</v>
       </c>
     </row>
     <row r="17" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -23536,7 +23548,7 @@
       </c>
       <c r="C17" s="46">
         <f ca="1">C7/(C8+C7)</f>
-        <v>0.93773998657417768</v>
+        <v>0.93597083893297006</v>
       </c>
     </row>
     <row r="18" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -23554,7 +23566,7 @@
       </c>
       <c r="C19" s="46">
         <f ca="1">C9+C10*C11</f>
-        <v>0.1076375</v>
+        <v>0.1082655</v>
       </c>
     </row>
     <row r="20" spans="2:3" ht="17" customHeight="1" x14ac:dyDescent="0.2">
@@ -23563,7 +23575,7 @@
       </c>
       <c r="C20" s="46">
         <f ca="1">(C17*C19)+(C16*C18)</f>
-        <v>0.10393629785186842</v>
+        <v>0.10441891613431764</v>
       </c>
     </row>
   </sheetData>
@@ -23814,7 +23826,7 @@
       </c>
       <c r="L8" s="128">
         <f ca="1">L7*(1+C14)/(C15-C14)</f>
-        <v>29914.07500559045</v>
+        <v>29743.057890453783</v>
       </c>
       <c r="N8" s="91"/>
       <c r="O8" s="16"/>
@@ -23868,23 +23880,23 @@
       <c r="G10" s="140"/>
       <c r="H10" s="128">
         <f ca="1">H7/(1+$C$15)^H9</f>
-        <v>1866.8795000833261</v>
+        <v>1866.063695351347</v>
       </c>
       <c r="I10" s="128">
         <f t="shared" ref="I10:L10" ca="1" si="0">I7/(1+$C$15)^I9</f>
-        <v>1277.0258072947236</v>
+        <v>1275.909960162302</v>
       </c>
       <c r="J10" s="128">
         <f t="shared" ca="1" si="0"/>
-        <v>574.45301908650492</v>
+        <v>573.70026016954296</v>
       </c>
       <c r="K10" s="128">
         <f t="shared" ca="1" si="0"/>
-        <v>1435.2048747143547</v>
+        <v>1432.6978469563744</v>
       </c>
       <c r="L10" s="128">
         <f t="shared" ca="1" si="0"/>
-        <v>1501.4302093209835</v>
+        <v>1498.1525370723487</v>
       </c>
       <c r="N10" s="91"/>
     </row>
@@ -23903,7 +23915,7 @@
       <c r="K11" s="139"/>
       <c r="L11" s="128">
         <f ca="1">L8/(1+C15)^L9</f>
-        <v>18245.489170967921</v>
+        <v>18101.577913917237</v>
       </c>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.2">
@@ -23926,7 +23938,7 @@
       </c>
       <c r="C15" s="137">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.10393629785186842</v>
+        <v>0.10441891613431764</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.2">
@@ -23941,7 +23953,7 @@
       </c>
       <c r="C19" s="64">
         <f ca="1">SUM(H10:L10)</f>
-        <v>6654.9934104998929</v>
+        <v>6646.5242997119149</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.2">
@@ -23950,7 +23962,7 @@
       </c>
       <c r="C20" s="64">
         <f ca="1">L11</f>
-        <v>18245.489170967921</v>
+        <v>18101.577913917237</v>
       </c>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.2">
@@ -23959,7 +23971,7 @@
       </c>
       <c r="C21" s="94">
         <f ca="1">C19+C20</f>
-        <v>24900.482581467815</v>
+        <v>24748.10221362915</v>
       </c>
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.2">
@@ -23986,7 +23998,7 @@
       </c>
       <c r="C24" s="94">
         <f ca="1">C21+C22-C23</f>
-        <v>25779.482581467815</v>
+        <v>25627.10221362915</v>
       </c>
     </row>
     <row r="25" spans="2:3" x14ac:dyDescent="0.2">
@@ -24004,7 +24016,7 @@
       </c>
       <c r="C26" s="234">
         <f ca="1">C24/C25</f>
-        <v>122.75944086413246</v>
+        <v>122.03382006490071</v>
       </c>
     </row>
   </sheetData>
@@ -24273,23 +24285,23 @@
       <c r="G9" s="140"/>
       <c r="H9" s="92">
         <f ca="1">DCF!H10</f>
-        <v>1866.8795000833261</v>
+        <v>1866.063695351347</v>
       </c>
       <c r="I9" s="92">
         <f ca="1">DCF!I10</f>
-        <v>1277.0258072947236</v>
+        <v>1275.909960162302</v>
       </c>
       <c r="J9" s="92">
         <f ca="1">DCF!J10</f>
-        <v>574.45301908650492</v>
+        <v>573.70026016954296</v>
       </c>
       <c r="K9" s="92">
         <f ca="1">DCF!K10</f>
-        <v>1435.2048747143547</v>
+        <v>1432.6978469563744</v>
       </c>
       <c r="L9" s="92">
         <f ca="1">DCF!L10</f>
-        <v>1501.4302093209835</v>
+        <v>1498.1525370723487</v>
       </c>
       <c r="N9" s="91"/>
     </row>
@@ -25075,7 +25087,7 @@
       </c>
       <c r="C41" s="137">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.10393629785186842</v>
+        <v>0.10441891613431764</v>
       </c>
     </row>
     <row r="42" spans="2:14" x14ac:dyDescent="0.2">
@@ -25101,7 +25113,7 @@
       </c>
       <c r="C44" s="24">
         <f ca="1">C43/(1+C41)^5</f>
-        <v>67892.685117749032</v>
+        <v>67744.473120605064</v>
       </c>
     </row>
     <row r="45" spans="2:14" x14ac:dyDescent="0.2">
@@ -25110,7 +25122,7 @@
       </c>
       <c r="C45" s="108">
         <f ca="1">SUM(H9:K9)+C44</f>
-        <v>73046.248318927945</v>
+        <v>72892.84488324463</v>
       </c>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.2">
@@ -25137,7 +25149,7 @@
       </c>
       <c r="C48" s="108">
         <f ca="1">C45+C46-C47</f>
-        <v>73925.248318927945</v>
+        <v>73771.84488324463</v>
       </c>
     </row>
     <row r="49" spans="2:3" x14ac:dyDescent="0.2">
@@ -25155,7 +25167,7 @@
       </c>
       <c r="C50" s="234">
         <f ca="1">C48/C49</f>
-        <v>352.02499199489495</v>
+        <v>351.29449944402205</v>
       </c>
     </row>
     <row r="52" spans="2:3" x14ac:dyDescent="0.2">
@@ -25179,7 +25191,7 @@
       </c>
       <c r="C54" s="137">
         <f ca="1">IF(Overview!C29&gt;0,Overview!C29,WACC!C19)</f>
-        <v>0.1076375</v>
+        <v>0.1082655</v>
       </c>
     </row>
     <row r="55" spans="2:3" x14ac:dyDescent="0.2">
@@ -25214,7 +25226,7 @@
       </c>
       <c r="C58" s="234">
         <f ca="1">C57/(1+C54)^5</f>
-        <v>191.84053365045287</v>
+        <v>191.29761592497329</v>
       </c>
     </row>
     <row r="60" spans="2:3" x14ac:dyDescent="0.2">
@@ -25238,7 +25250,7 @@
       </c>
       <c r="C62" s="137">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.10393629785186842</v>
+        <v>0.10441891613431764</v>
       </c>
     </row>
     <row r="63" spans="2:3" x14ac:dyDescent="0.2">
@@ -25264,7 +25276,7 @@
       </c>
       <c r="C65" s="24">
         <f ca="1">C64/(1+C62)^5</f>
-        <v>67564.359419444256</v>
+        <v>67416.864168255677</v>
       </c>
     </row>
     <row r="66" spans="2:3" x14ac:dyDescent="0.2">
@@ -25273,7 +25285,7 @@
       </c>
       <c r="C66" s="108">
         <f ca="1">SUM(H9:K9)+C65</f>
-        <v>72717.922620623169</v>
+        <v>72565.235930895244</v>
       </c>
     </row>
     <row r="67" spans="2:3" x14ac:dyDescent="0.2">
@@ -25300,7 +25312,7 @@
       </c>
       <c r="C69" s="108">
         <f ca="1">C66+C67-C68</f>
-        <v>73596.922620623169</v>
+        <v>73444.235930895244</v>
       </c>
     </row>
     <row r="70" spans="2:3" x14ac:dyDescent="0.2">
@@ -25318,7 +25330,7 @@
       </c>
       <c r="C71" s="234">
         <f ca="1">C69/C70</f>
-        <v>350.46153628868177</v>
+        <v>349.73445681378689</v>
       </c>
     </row>
     <row r="73" spans="2:3" x14ac:dyDescent="0.2">
@@ -25342,7 +25354,7 @@
       </c>
       <c r="C75" s="137">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.10393629785186842</v>
+        <v>0.10441891613431764</v>
       </c>
     </row>
     <row r="76" spans="2:3" x14ac:dyDescent="0.2">
@@ -25368,7 +25380,7 @@
       </c>
       <c r="C78" s="24">
         <f ca="1">C77/(1+C75)^5</f>
-        <v>40820.517747564343</v>
+        <v>40731.405195168976</v>
       </c>
     </row>
     <row r="79" spans="2:3" x14ac:dyDescent="0.2">
@@ -25377,7 +25389,7 @@
       </c>
       <c r="C79" s="108">
         <f ca="1">SUM(H9:K9)+C78</f>
-        <v>45974.080948743256</v>
+        <v>45879.776957808543</v>
       </c>
     </row>
     <row r="80" spans="2:3" x14ac:dyDescent="0.2">
@@ -25404,7 +25416,7 @@
       </c>
       <c r="C82" s="108">
         <f ca="1">C79+C80-C81</f>
-        <v>46853.080948743256</v>
+        <v>46758.776957808543</v>
       </c>
     </row>
     <row r="83" spans="2:3" x14ac:dyDescent="0.2">
@@ -25422,22 +25434,22 @@
       </c>
       <c r="C84" s="234">
         <f ca="1">C82/C83</f>
-        <v>223.10990927972978</v>
+        <v>222.66084265623115</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="B73:C73"/>
-    <mergeCell ref="C27:L27"/>
-    <mergeCell ref="B39:C39"/>
-    <mergeCell ref="B52:C52"/>
-    <mergeCell ref="B60:C60"/>
     <mergeCell ref="C22:L22"/>
     <mergeCell ref="C2:G2"/>
     <mergeCell ref="H2:L2"/>
     <mergeCell ref="C4:L4"/>
     <mergeCell ref="C11:L11"/>
     <mergeCell ref="C17:L17"/>
+    <mergeCell ref="B73:C73"/>
+    <mergeCell ref="C27:L27"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="B60:C60"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -25487,7 +25499,7 @@
       </c>
       <c r="C5" s="135">
         <f ca="1">DCF!C26</f>
-        <v>122.75944086413246</v>
+        <v>122.03382006490071</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.2">
@@ -25496,7 +25508,7 @@
       </c>
       <c r="C6" s="135">
         <f ca="1">Multiples!C50</f>
-        <v>352.02499199489495</v>
+        <v>351.29449944402205</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.2">
@@ -25505,7 +25517,7 @@
       </c>
       <c r="C7" s="135">
         <f ca="1">Multiples!C58</f>
-        <v>191.84053365045287</v>
+        <v>191.29761592497329</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.2">
@@ -25514,7 +25526,7 @@
       </c>
       <c r="C8" s="135">
         <f ca="1">Multiples!C71</f>
-        <v>350.46153628868177</v>
+        <v>349.73445681378689</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
@@ -25523,7 +25535,7 @@
       </c>
       <c r="C9" s="135">
         <f ca="1">Multiples!C84</f>
-        <v>223.10990927972978</v>
+        <v>222.66084265623115</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
@@ -25532,7 +25544,7 @@
       </c>
       <c r="C10" s="234">
         <f ca="1">AVERAGE(C5:C9)</f>
-        <v>248.03928241557833</v>
+        <v>247.40424698078283</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -25541,7 +25553,7 @@
       </c>
       <c r="C11" s="135">
         <f ca="1">Overview!C5</f>
-        <v>249.45</v>
+        <v>242.1</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.2">
@@ -25550,7 +25562,7 @@
       </c>
       <c r="C12" s="154">
         <f ca="1">(C10-C11)/C11</f>
-        <v>-5.6553120241397527E-3</v>
+        <v>2.1909322514592464E-2</v>
       </c>
     </row>
   </sheetData>
@@ -26059,7 +26071,7 @@
       </c>
       <c r="C24" s="137">
         <f ca="1">IF(Overview!C29&gt;0,Overview!C29,WACC!C19)</f>
-        <v>0.1076375</v>
+        <v>0.1082655</v>
       </c>
     </row>
     <row r="25" spans="2:14" x14ac:dyDescent="0.2">
@@ -26313,7 +26325,7 @@
       <c r="K8" s="139"/>
       <c r="L8" s="128">
         <f ca="1">L7*(1+C20)/(C21-C20)</f>
-        <v>69112.360296470622</v>
+        <v>68717.248748612983</v>
       </c>
       <c r="N8" s="91"/>
       <c r="O8" s="16"/>
@@ -26367,23 +26379,23 @@
       <c r="G10" s="140"/>
       <c r="H10" s="128">
         <f ca="1">H7/(1+$C$21)^H9</f>
-        <v>990.9541500710958</v>
+        <v>990.52111457803574</v>
       </c>
       <c r="I10" s="128">
         <f t="shared" ref="I10:L10" ca="1" si="1">I7/(1+$C$21)^I9</f>
-        <v>1355.4593408324915</v>
+        <v>1354.2749595851101</v>
       </c>
       <c r="J10" s="128">
         <f t="shared" ca="1" si="1"/>
-        <v>1854.0414049613069</v>
+        <v>1851.6118830445785</v>
       </c>
       <c r="K10" s="128">
         <f t="shared" ca="1" si="1"/>
-        <v>2536.0181805229827</v>
+        <v>2531.5882429681933</v>
       </c>
       <c r="L10" s="128">
         <f t="shared" ca="1" si="1"/>
-        <v>3468.8482116597183</v>
+        <v>3461.2756002606006</v>
       </c>
       <c r="N10" s="91"/>
     </row>
@@ -26402,15 +26414,15 @@
       <c r="K11" s="139"/>
       <c r="L11" s="128">
         <f ca="1">L8/(1+C21)^L9</f>
-        <v>42153.695915171367</v>
+        <v>41821.208728248617</v>
       </c>
     </row>
     <row r="13" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="14" spans="1:28" x14ac:dyDescent="0.2">
-      <c r="B14" s="257" t="s">
+      <c r="B14" s="258" t="s">
         <v>221</v>
       </c>
-      <c r="C14" s="258"/>
+      <c r="C14" s="259"/>
     </row>
     <row r="15" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B15" s="155" t="s">
@@ -26418,7 +26430,7 @@
       </c>
       <c r="C15" s="156">
         <f ca="1">Overview!C5</f>
-        <v>249.45</v>
+        <v>242.1</v>
       </c>
     </row>
     <row r="16" spans="1:28" x14ac:dyDescent="0.2">
@@ -26427,7 +26439,7 @@
       </c>
       <c r="C16" s="156">
         <f ca="1">C36</f>
-        <v>254.72735503932515</v>
+        <v>253.05971544825422</v>
       </c>
     </row>
     <row r="17" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -26437,20 +26449,20 @@
       <c r="C17" s="158">
         <v>0.51</v>
       </c>
-      <c r="E17" s="259" t="s">
+      <c r="E17" s="257" t="s">
         <v>224</v>
       </c>
-      <c r="F17" s="259"/>
-      <c r="G17" s="259"/>
-      <c r="H17" s="259"/>
-      <c r="I17" s="259"/>
+      <c r="F17" s="257"/>
+      <c r="G17" s="257"/>
+      <c r="H17" s="257"/>
+      <c r="I17" s="257"/>
     </row>
     <row r="18" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="19" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B19" s="257" t="s">
+      <c r="B19" s="258" t="s">
         <v>183</v>
       </c>
-      <c r="C19" s="258"/>
+      <c r="C19" s="259"/>
     </row>
     <row r="20" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B20" s="159" t="s">
@@ -26466,7 +26478,7 @@
       </c>
       <c r="C21" s="220">
         <f ca="1">IF(Overview!C28&gt;0,Overview!C28,WACC!C20)</f>
-        <v>0.10393629785186842</v>
+        <v>0.10441891613431764</v>
       </c>
     </row>
     <row r="22" spans="2:9" x14ac:dyDescent="0.2">
@@ -26484,7 +26496,7 @@
       </c>
       <c r="C23" s="161">
         <f ca="1">C15*C22</f>
-        <v>52135.049999999996</v>
+        <v>50598.9</v>
       </c>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.2">
@@ -26511,15 +26523,15 @@
       </c>
       <c r="C26" s="162">
         <f ca="1">C23+C25-C24</f>
-        <v>51256.049999999996</v>
+        <v>49719.9</v>
       </c>
     </row>
     <row r="27" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B28" s="257" t="s">
+      <c r="B28" s="258" t="s">
         <v>185</v>
       </c>
-      <c r="C28" s="258"/>
+      <c r="C28" s="259"/>
     </row>
     <row r="29" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B29" s="159" t="s">
@@ -26527,7 +26539,7 @@
       </c>
       <c r="C29" s="161">
         <f ca="1">SUM(H10:L10)</f>
-        <v>10205.321288047595</v>
+        <v>10189.271800436518</v>
       </c>
     </row>
     <row r="30" spans="2:9" x14ac:dyDescent="0.2">
@@ -26536,7 +26548,7 @@
       </c>
       <c r="C30" s="161">
         <f ca="1">L11</f>
-        <v>42153.695915171367</v>
+        <v>41821.208728248617</v>
       </c>
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.2">
@@ -26545,7 +26557,7 @@
       </c>
       <c r="C31" s="164">
         <f ca="1">C29+C30</f>
-        <v>52359.017203218958</v>
+        <v>52010.480528685133</v>
       </c>
     </row>
     <row r="32" spans="2:9" x14ac:dyDescent="0.2">
@@ -26572,7 +26584,7 @@
       </c>
       <c r="C34" s="164">
         <f ca="1">C31+C32-C33</f>
-        <v>53238.017203218958</v>
+        <v>52889.480528685133</v>
       </c>
     </row>
     <row r="35" spans="2:3" x14ac:dyDescent="0.2">
@@ -26590,21 +26602,21 @@
       </c>
       <c r="C36" s="167">
         <f ca="1">C34/C35</f>
-        <v>254.72735503932515</v>
+        <v>253.05971544825422</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="P3:W3"/>
+    <mergeCell ref="X3:Z3"/>
+    <mergeCell ref="C5:L5"/>
+    <mergeCell ref="P5:Z5"/>
+    <mergeCell ref="B14:C14"/>
     <mergeCell ref="E17:I17"/>
     <mergeCell ref="B19:C19"/>
     <mergeCell ref="B28:C28"/>
     <mergeCell ref="C3:G3"/>
     <mergeCell ref="H3:L3"/>
-    <mergeCell ref="P3:W3"/>
-    <mergeCell ref="X3:Z3"/>
-    <mergeCell ref="C5:L5"/>
-    <mergeCell ref="P5:Z5"/>
-    <mergeCell ref="B14:C14"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -33260,7 +33272,7 @@
       </c>
       <c r="AC117" s="63">
         <f ca="1">Overview!C5</f>
-        <v>249.45</v>
+        <v>242.1</v>
       </c>
     </row>
     <row r="118" spans="1:31" x14ac:dyDescent="0.2">
@@ -33331,7 +33343,7 @@
       </c>
       <c r="AC118" s="65">
         <f ca="1">AC117/AC86</f>
-        <v>249.45</v>
+        <v>242.1</v>
       </c>
     </row>
     <row r="120" spans="1:31" x14ac:dyDescent="0.2">
@@ -34637,7 +34649,7 @@
       <c r="AA151" s="49"/>
       <c r="AC151" s="72">
         <f ca="1">AC118/Statement!AC27</f>
-        <v>32.270375161707626</v>
+        <v>31.319534282018108</v>
       </c>
     </row>
     <row r="152" spans="2:29" x14ac:dyDescent="0.2">
@@ -34674,7 +34686,7 @@
       <c r="AA152" s="49"/>
       <c r="AC152" s="72">
         <f ca="1">AC118/(Statement!AC5/Statement!AC23)</f>
-        <v>6.8206482670089859</v>
+        <v>6.6196790757381265</v>
       </c>
     </row>
     <row r="153" spans="2:29" x14ac:dyDescent="0.2">
@@ -34735,7 +34747,7 @@
       </c>
       <c r="AC153" s="72">
         <f ca="1">AC118/(Statement!AC50/Statement!AC76)</f>
-        <v>15.410892698788055</v>
+        <v>14.956813479160507</v>
       </c>
     </row>
     <row r="154" spans="2:29" x14ac:dyDescent="0.2">
@@ -34796,7 +34808,7 @@
       </c>
       <c r="AC154" s="143">
         <f ca="1">Statement!AC118*Statement!AC79</f>
-        <v>52384.5</v>
+        <v>50841</v>
       </c>
     </row>
     <row r="155" spans="2:29" x14ac:dyDescent="0.2">
@@ -34857,7 +34869,7 @@
       </c>
       <c r="AC155" s="143">
         <f ca="1">AC154+AC109-AC108+AC49+AC46</f>
-        <v>51505.5</v>
+        <v>49962</v>
       </c>
     </row>
     <row r="156" spans="2:29" x14ac:dyDescent="0.2">
@@ -34894,7 +34906,7 @@
       <c r="AA156" s="49"/>
       <c r="AC156" s="181">
         <f ca="1">AC155/AC5</f>
-        <v>6.6117458279845955</v>
+        <v>6.413607188703466</v>
       </c>
     </row>
     <row r="157" spans="2:29" x14ac:dyDescent="0.2">
@@ -34931,7 +34943,7 @@
       <c r="AA157" s="49"/>
       <c r="AC157" s="181">
         <f ca="1">AC155/AC13</f>
-        <v>25.235423811856933</v>
+        <v>24.479176874081332</v>
       </c>
     </row>
     <row r="158" spans="2:29" x14ac:dyDescent="0.2">
@@ -35066,7 +35078,7 @@
       <c r="AA160" s="49"/>
       <c r="AC160" s="72">
         <f t="shared" ref="AC160:AC161" ca="1" si="155">AC154/AC158</f>
-        <v>24.968779790276454</v>
+        <v>24.23307912297426</v>
       </c>
     </row>
     <row r="161" spans="2:29" x14ac:dyDescent="0.2">
@@ -35103,7 +35115,7 @@
       <c r="AA161" s="49"/>
       <c r="AC161" s="72">
         <f t="shared" ca="1" si="155"/>
-        <v>42.353816173029422</v>
+        <v>41.084570844606809</v>
       </c>
     </row>
     <row r="162" spans="2:29" x14ac:dyDescent="0.2">
@@ -35140,7 +35152,7 @@
       <c r="AA162" s="49"/>
       <c r="AC162" s="74">
         <f t="shared" ref="AC162" ca="1" si="158">AC158/AC154</f>
-        <v>4.0050014794452554E-2</v>
+        <v>4.1265907436911158E-2</v>
       </c>
     </row>
     <row r="163" spans="2:29" x14ac:dyDescent="0.2">
@@ -35177,7 +35189,7 @@
       <c r="AA163" s="49"/>
       <c r="AC163" s="74">
         <f ca="1">AC27/AC118</f>
-        <v>3.0988173982762081E-2</v>
+        <v>3.1928954977282119E-2</v>
       </c>
     </row>
     <row r="164" spans="2:29" x14ac:dyDescent="0.2">
@@ -35251,7 +35263,7 @@
       <c r="AA165" s="49"/>
       <c r="AC165" s="154">
         <f ca="1">-AC64/AC154</f>
-        <v>3.0371579379396576E-2</v>
+        <v>3.1293640959068468E-2</v>
       </c>
     </row>
     <row r="166" spans="2:29" x14ac:dyDescent="0.2">
@@ -35288,7 +35300,7 @@
       <c r="AA166" s="49"/>
       <c r="AC166" s="154">
         <f ca="1">-(AC64+AC65)/AC154</f>
-        <v>3.0371579379396576E-2</v>
+        <v>3.1293640959068468E-2</v>
       </c>
     </row>
     <row r="167" spans="2:29" x14ac:dyDescent="0.2">
@@ -35791,7 +35803,7 @@
       <c r="AA177" s="49"/>
       <c r="AC177" s="154">
         <f ca="1">(AC108-AC109)/AC154</f>
-        <v>1.6779772642671019E-2</v>
+        <v>1.7289195727857438E-2</v>
       </c>
     </row>
     <row r="178" spans="1:31" x14ac:dyDescent="0.2">
@@ -37608,7 +37620,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9420C07F-23F5-F443-9A67-3073516055F8}">
-  <dimension ref="B1:G54"/>
+  <dimension ref="B1:G61"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="3.1640625" style="1" customWidth="1"/>
@@ -37641,7 +37653,7 @@
       </c>
       <c r="C5" s="170">
         <f ca="1">Overview!C5</f>
-        <v>249.45</v>
+        <v>242.1</v>
       </c>
       <c r="E5" s="12"/>
       <c r="F5" s="134" t="s">
@@ -37657,7 +37669,7 @@
       </c>
       <c r="C6" s="171">
         <f ca="1">Statement!AC154</f>
-        <v>52384.5</v>
+        <v>50841</v>
       </c>
       <c r="E6" s="20" t="s">
         <v>19</v>
@@ -37677,7 +37689,7 @@
       </c>
       <c r="C7" s="171">
         <f ca="1">Statement!AC155</f>
-        <v>51505.5</v>
+        <v>49962</v>
       </c>
       <c r="E7" s="20" t="s">
         <v>31</v>
@@ -37697,7 +37709,7 @@
       </c>
       <c r="C8" s="172">
         <f ca="1">Statement!AC151</f>
-        <v>32.270375161707626</v>
+        <v>31.319534282018108</v>
       </c>
       <c r="E8" s="20" t="s">
         <v>242</v>
@@ -37717,7 +37729,7 @@
       </c>
       <c r="C9" s="172">
         <f ca="1">Statement!AC152</f>
-        <v>6.8206482670089859</v>
+        <v>6.6196790757381265</v>
       </c>
       <c r="E9" s="20" t="s">
         <v>243</v>
@@ -37737,7 +37749,7 @@
       </c>
       <c r="C10" s="172">
         <f ca="1">Statement!AC153</f>
-        <v>15.410892698788055</v>
+        <v>14.956813479160507</v>
       </c>
       <c r="E10" s="20" t="s">
         <v>1</v>
@@ -37757,7 +37769,7 @@
       </c>
       <c r="C11" s="172">
         <f ca="1">Statement!AC156</f>
-        <v>6.6117458279845955</v>
+        <v>6.413607188703466</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.2">
@@ -37766,7 +37778,7 @@
       </c>
       <c r="C12" s="172">
         <f ca="1">Statement!AC157</f>
-        <v>25.235423811856933</v>
+        <v>24.479176874081332</v>
       </c>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.2">
@@ -38002,7 +38014,7 @@
       </c>
       <c r="C38" s="173">
         <f ca="1">Statement!AC163</f>
-        <v>3.0988173982762081E-2</v>
+        <v>3.1928954977282119E-2</v>
       </c>
       <c r="E38" s="20" t="s">
         <v>269</v>
@@ -38018,7 +38030,7 @@
       </c>
       <c r="C39" s="213">
         <f ca="1">Statement!AC162</f>
-        <v>4.0050014794452554E-2</v>
+        <v>4.1265907436911158E-2</v>
       </c>
       <c r="E39" s="20" t="s">
         <v>271</v>
@@ -38050,7 +38062,7 @@
       </c>
       <c r="C41" s="173">
         <f ca="1">Statement!AC165</f>
-        <v>3.0371579379396576E-2</v>
+        <v>3.1293640959068468E-2</v>
       </c>
     </row>
     <row r="42" spans="2:6" x14ac:dyDescent="0.2">
@@ -38059,7 +38071,7 @@
       </c>
       <c r="C42" s="173">
         <f ca="1">Statement!AC166</f>
-        <v>3.0371579379396576E-2</v>
+        <v>3.1293640959068468E-2</v>
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.2">
@@ -38103,7 +38115,7 @@
       </c>
       <c r="F48" s="173">
         <f ca="1">Statement!AC177</f>
-        <v>1.6779772642671019E-2</v>
+        <v>1.7289195727857438E-2</v>
       </c>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.2">
@@ -38157,8 +38169,51 @@
         <v>0.45771144278606968</v>
       </c>
     </row>
+    <row r="57" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B57" s="245" t="s">
+        <v>442</v>
+      </c>
+      <c r="C57" s="245"/>
+    </row>
+    <row r="58" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B58" s="20" t="s">
+        <v>262</v>
+      </c>
+      <c r="C58" s="172">
+        <f ca="1">Statement!AC160</f>
+        <v>24.23307912297426</v>
+      </c>
+    </row>
+    <row r="59" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B59" s="20" t="s">
+        <v>263</v>
+      </c>
+      <c r="C59" s="172">
+        <f ca="1">Statement!AC161</f>
+        <v>41.084570844606809</v>
+      </c>
+    </row>
+    <row r="60" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B60" s="20" t="s">
+        <v>443</v>
+      </c>
+      <c r="C60" s="173">
+        <f>Statement!AC167</f>
+        <v>0.15610744025930073</v>
+      </c>
+    </row>
+    <row r="61" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B61" s="20" t="s">
+        <v>444</v>
+      </c>
+      <c r="C61" s="173">
+        <f>Statement!AC168</f>
+        <v>0.26931964056482671</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="14">
+  <mergeCells count="15">
+    <mergeCell ref="B57:C57"/>
     <mergeCell ref="B51:C51"/>
     <mergeCell ref="B4:C4"/>
     <mergeCell ref="E4:G4"/>
@@ -38183,7 +38238,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{978EC990-97E1-EA42-B427-9F214546EBED}">
-  <dimension ref="B1:I93"/>
+  <dimension ref="B1:I99"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="3.33203125" style="1" customWidth="1"/>
@@ -38282,7 +38337,7 @@
       </c>
       <c r="I6" s="170">
         <f ca="1">Statement!AC117</f>
-        <v>249.45</v>
+        <v>242.1</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
@@ -38311,7 +38366,7 @@
       </c>
       <c r="I7" s="171">
         <f ca="1">Statement!AC154</f>
-        <v>52384.5</v>
+        <v>50841</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
@@ -38340,7 +38395,7 @@
       </c>
       <c r="I8" s="171">
         <f ca="1">Statement!AC155</f>
-        <v>51505.5</v>
+        <v>49962</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
@@ -38369,7 +38424,7 @@
       </c>
       <c r="I9" s="172">
         <f ca="1">Statement!AC151</f>
-        <v>32.270375161707626</v>
+        <v>31.319534282018108</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
@@ -38398,7 +38453,7 @@
       </c>
       <c r="I10" s="172">
         <f ca="1">Statement!AC152</f>
-        <v>6.8206482670089859</v>
+        <v>6.6196790757381265</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
@@ -38427,7 +38482,7 @@
       </c>
       <c r="I11" s="172">
         <f ca="1">Statement!AC153</f>
-        <v>15.410892698788055</v>
+        <v>14.956813479160507</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
@@ -38456,7 +38511,7 @@
       </c>
       <c r="I12" s="172">
         <f ca="1">Statement!AC156</f>
-        <v>6.6117458279845955</v>
+        <v>6.413607188703466</v>
       </c>
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.2">
@@ -38485,7 +38540,7 @@
       </c>
       <c r="I13" s="172">
         <f ca="1">Statement!AC157</f>
-        <v>25.235423811856933</v>
+        <v>24.479176874081332</v>
       </c>
     </row>
     <row r="15" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -39258,7 +39313,7 @@
       </c>
       <c r="I51" s="173">
         <f ca="1">Statement!AC163</f>
-        <v>3.0988173982762081E-2</v>
+        <v>3.1928954977282119E-2</v>
       </c>
     </row>
     <row r="52" spans="2:9" x14ac:dyDescent="0.2">
@@ -39287,7 +39342,7 @@
       </c>
       <c r="I52" s="173">
         <f ca="1">Statement!AC162</f>
-        <v>4.0050014794452554E-2</v>
+        <v>4.1265907436911158E-2</v>
       </c>
     </row>
     <row r="53" spans="2:9" x14ac:dyDescent="0.2">
@@ -39345,7 +39400,7 @@
       </c>
       <c r="I54" s="173">
         <f ca="1">Statement!AC165</f>
-        <v>3.0371579379396576E-2</v>
+        <v>3.1293640959068468E-2</v>
       </c>
     </row>
     <row r="55" spans="2:9" x14ac:dyDescent="0.2">
@@ -39374,7 +39429,7 @@
       </c>
       <c r="I55" s="173">
         <f ca="1">Statement!AC166</f>
-        <v>3.0371579379396576E-2</v>
+        <v>3.1293640959068468E-2</v>
       </c>
     </row>
     <row r="57" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -39610,7 +39665,7 @@
       </c>
       <c r="I68" s="194">
         <f ca="1">Statement!AC177</f>
-        <v>1.6779772642671019E-2</v>
+        <v>1.7289195727857438E-2</v>
       </c>
     </row>
     <row r="70" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -39947,107 +40002,234 @@
       </c>
       <c r="I85" s="195"/>
     </row>
-    <row r="88" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B88" s="14" t="s">
+    <row r="87" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B87" s="14" t="s">
+        <v>442</v>
+      </c>
+      <c r="C87" s="14"/>
+      <c r="D87" s="14"/>
+      <c r="E87" s="14"/>
+      <c r="F87" s="14"/>
+      <c r="G87" s="14"/>
+      <c r="I87" s="14"/>
+    </row>
+    <row r="88" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B88" s="20" t="s">
+        <v>262</v>
+      </c>
+      <c r="C88" s="172">
+        <f>Statement!M160</f>
+        <v>60.180429042904287</v>
+      </c>
+      <c r="D88" s="172">
+        <f>Statement!N160</f>
+        <v>34.287192982456141</v>
+      </c>
+      <c r="E88" s="172">
+        <f>Statement!O160</f>
+        <v>99.859672131147533</v>
+      </c>
+      <c r="F88" s="172">
+        <f>Statement!P160</f>
+        <v>82.156411192214108</v>
+      </c>
+      <c r="G88" s="172">
+        <f>Statement!Q160</f>
+        <v>34.236177581863984</v>
+      </c>
+      <c r="I88" s="172">
+        <f ca="1">Statement!AC160</f>
+        <v>24.23307912297426</v>
+      </c>
+    </row>
+    <row r="89" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B89" s="20" t="s">
+        <v>263</v>
+      </c>
+      <c r="C89" s="172">
+        <f>Statement!M161</f>
+        <v>65.558005724307904</v>
+      </c>
+      <c r="D89" s="172">
+        <f>Statement!N161</f>
+        <v>28.381805109629262</v>
+      </c>
+      <c r="E89" s="172">
+        <f>Statement!O161</f>
+        <v>103.73132281358649</v>
+      </c>
+      <c r="F89" s="172">
+        <f>Statement!P161</f>
+        <v>95.588298874789729</v>
+      </c>
+      <c r="G89" s="172">
+        <f>Statement!Q161</f>
+        <v>74.367499866531887</v>
+      </c>
+      <c r="I89" s="172">
+        <f ca="1">Statement!AC161</f>
+        <v>41.084570844606809</v>
+      </c>
+    </row>
+    <row r="90" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B90" s="20" t="s">
+        <v>443</v>
+      </c>
+      <c r="C90" s="173">
+        <f>Statement!M167</f>
+        <v>0.19188810737301709</v>
+      </c>
+      <c r="D90" s="173">
+        <f>Statement!N167</f>
+        <v>0.33095086731450368</v>
+      </c>
+      <c r="E90" s="173">
+        <f>Statement!O167</f>
+        <v>9.5801294944489593E-2</v>
+      </c>
+      <c r="F90" s="173">
+        <f>Statement!P167</f>
+        <v>0.11546174421093222</v>
+      </c>
+      <c r="G90" s="173">
+        <f>Statement!Q167</f>
+        <v>0.10053710353315122</v>
+      </c>
+      <c r="I90" s="173">
+        <f>Statement!AC167</f>
+        <v>0.15610744025930073</v>
+      </c>
+    </row>
+    <row r="91" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B91" s="20" t="s">
+        <v>444</v>
+      </c>
+      <c r="C91" s="173">
+        <f>Statement!M168</f>
+        <v>0.20725034199726403</v>
+      </c>
+      <c r="D91" s="173">
+        <f>Statement!N168</f>
+        <v>0.27332667332667332</v>
+      </c>
+      <c r="E91" s="173">
+        <f>Statement!O168</f>
+        <v>9.9872657813352736E-2</v>
+      </c>
+      <c r="F91" s="173">
+        <f>Statement!P168</f>
+        <v>0.13407274506605774</v>
+      </c>
+      <c r="G91" s="173">
+        <f>Statement!Q168</f>
+        <v>0.22037191229530947</v>
+      </c>
+      <c r="I91" s="173">
+        <f>Statement!AC168</f>
+        <v>0.26931964056482671</v>
+      </c>
+    </row>
+    <row r="93" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B93" s="14" t="s">
+        <v>445</v>
+      </c>
+      <c r="C93" s="14"/>
+      <c r="D93" s="14"/>
+      <c r="E93" s="14"/>
+      <c r="F93" s="14"/>
+      <c r="G93" s="14"/>
+      <c r="I93" s="14"/>
+    </row>
+    <row r="94" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B94" s="20" t="s">
+        <v>283</v>
+      </c>
+      <c r="C94" s="173">
+        <f>Statement!M214</f>
+        <v>0</v>
+      </c>
+      <c r="D94" s="173">
+        <f>Statement!N214</f>
+        <v>0</v>
+      </c>
+      <c r="E94" s="173">
+        <f>Statement!O214</f>
+        <v>0</v>
+      </c>
+      <c r="F94" s="173">
+        <f>Statement!P214</f>
+        <v>0</v>
+      </c>
+      <c r="G94" s="173">
+        <f>Statement!Q214</f>
+        <v>0</v>
+      </c>
+      <c r="I94" s="195"/>
+    </row>
+    <row r="97" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B97" s="14" t="s">
         <v>309</v>
       </c>
-      <c r="C88" s="14"/>
-      <c r="D88" s="14"/>
-      <c r="E88" s="14"/>
-      <c r="F88" s="14"/>
-      <c r="G88" s="14"/>
-      <c r="I88" s="14"/>
-    </row>
-    <row r="89" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B89" s="20" t="str">
+      <c r="C97" s="14"/>
+      <c r="D97" s="14"/>
+      <c r="E97" s="14"/>
+      <c r="F97" s="14"/>
+      <c r="G97" s="14"/>
+      <c r="I97" s="14"/>
+    </row>
+    <row r="98" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B98" s="20" t="str">
         <f>Statement!B188</f>
         <v>Subscription</v>
       </c>
-      <c r="C89" s="173">
+      <c r="C98" s="173">
         <f>Statement!M203</f>
         <v>1</v>
       </c>
-      <c r="D89" s="173">
+      <c r="D98" s="173">
         <f>Statement!N203</f>
         <v>0.14023210831721469</v>
       </c>
-      <c r="E89" s="173">
+      <c r="E98" s="173">
         <f>Statement!O203</f>
         <v>9.6268023748939779E-2</v>
       </c>
-      <c r="F89" s="173">
+      <c r="F98" s="173">
         <f>Statement!P203</f>
         <v>0.1137330754352031</v>
       </c>
-      <c r="G89" s="173">
+      <c r="G98" s="173">
         <f>Statement!Q203</f>
         <v>0.17679749913164294</v>
       </c>
-      <c r="I89" s="195"/>
-    </row>
-    <row r="90" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B90" s="20" t="str">
+      <c r="I98" s="195"/>
+    </row>
+    <row r="99" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B99" s="20" t="str">
         <f>Statement!B189</f>
         <v>Other</v>
       </c>
-      <c r="C90" s="173">
+      <c r="C99" s="173">
         <f>Statement!M204</f>
         <v>1</v>
       </c>
-      <c r="D90" s="173">
+      <c r="D99" s="173">
         <f>Statement!N204</f>
         <v>0.156</v>
       </c>
-      <c r="E90" s="173">
+      <c r="E99" s="173">
         <f>Statement!O204</f>
         <v>0.13148788927335639</v>
       </c>
-      <c r="F90" s="173">
+      <c r="F99" s="173">
         <f>Statement!P204</f>
         <v>0.14067278287461774</v>
       </c>
-      <c r="G90" s="173">
+      <c r="G99" s="173">
         <f>Statement!Q204</f>
         <v>0.15281501340482573</v>
       </c>
-      <c r="I90" s="195"/>
-    </row>
-    <row r="92" spans="2:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B92" s="14" t="s">
-        <v>311</v>
-      </c>
-      <c r="C92" s="14"/>
-      <c r="D92" s="14"/>
-      <c r="E92" s="14"/>
-      <c r="F92" s="14"/>
-      <c r="G92" s="14"/>
-      <c r="I92" s="14"/>
-    </row>
-    <row r="93" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B93" s="20" t="s">
-        <v>283</v>
-      </c>
-      <c r="C93" s="173">
-        <f>Statement!M214</f>
-        <v>0</v>
-      </c>
-      <c r="D93" s="173">
-        <f>Statement!N214</f>
-        <v>0</v>
-      </c>
-      <c r="E93" s="173">
-        <f>Statement!O214</f>
-        <v>0</v>
-      </c>
-      <c r="F93" s="173">
-        <f>Statement!P214</f>
-        <v>0</v>
-      </c>
-      <c r="G93" s="173">
-        <f>Statement!Q214</f>
-        <v>0</v>
-      </c>
-      <c r="I93" s="195"/>
+      <c r="I99" s="195"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -40763,30 +40945,6 @@
     </row>
   </sheetData>
   <mergeCells count="32">
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="F25:G25"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="F27:G27"/>
-    <mergeCell ref="C30:D30"/>
-    <mergeCell ref="F30:G30"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="F19:G19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="F21:G21"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="F9:G9"/>
     <mergeCell ref="C38:D38"/>
     <mergeCell ref="F38:G38"/>
     <mergeCell ref="C32:D32"/>
@@ -40795,6 +40953,30 @@
     <mergeCell ref="F34:G34"/>
     <mergeCell ref="C36:D36"/>
     <mergeCell ref="F36:G36"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="F25:G25"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="F27:G27"/>
+    <mergeCell ref="C30:D30"/>
+    <mergeCell ref="F30:G30"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
